--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471636</v>
+        <v>121471646</v>
       </c>
       <c r="B11" t="n">
-        <v>80239</v>
+        <v>94595</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427650</v>
+        <v>427692</v>
       </c>
       <c r="R11" t="n">
-        <v>6233855</v>
+        <v>6233796</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471650</v>
+        <v>121471624</v>
       </c>
       <c r="B12" t="n">
-        <v>80239</v>
+        <v>74560</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230185</v>
+        <v>1116</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427737</v>
+        <v>427594</v>
       </c>
       <c r="R12" t="n">
-        <v>6233784</v>
+        <v>6233828</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471593</v>
+        <v>121471964</v>
       </c>
       <c r="B13" t="n">
-        <v>80239</v>
+        <v>94595</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427699</v>
+        <v>427511</v>
       </c>
       <c r="R13" t="n">
-        <v>6233608</v>
+        <v>6233739</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,12 +2076,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471960</v>
+        <v>121471954</v>
       </c>
       <c r="B14" t="n">
-        <v>94584</v>
+        <v>80239</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427734</v>
+        <v>427742</v>
       </c>
       <c r="R14" t="n">
-        <v>6233532</v>
+        <v>6233542</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471957</v>
+        <v>121471976</v>
       </c>
       <c r="B15" t="n">
-        <v>94595</v>
+        <v>96721</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427731</v>
+        <v>427576</v>
       </c>
       <c r="R15" t="n">
-        <v>6233539</v>
+        <v>6233800</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121471720</v>
+        <v>121471978</v>
       </c>
       <c r="B16" t="n">
-        <v>80239</v>
+        <v>94595</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427595</v>
+        <v>427533</v>
       </c>
       <c r="R16" t="n">
-        <v>6233898</v>
+        <v>6233765</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121471609</v>
+        <v>121471971</v>
       </c>
       <c r="B17" t="n">
-        <v>80239</v>
+        <v>78860</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427543</v>
+        <v>427499</v>
       </c>
       <c r="R17" t="n">
-        <v>6233756</v>
+        <v>6233792</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121471577</v>
+        <v>121471975</v>
       </c>
       <c r="B18" t="n">
-        <v>94595</v>
+        <v>80239</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2532,21 +2532,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427749</v>
+        <v>427575</v>
       </c>
       <c r="R18" t="n">
-        <v>6233572</v>
+        <v>6233800</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121471631</v>
+        <v>121471951</v>
       </c>
       <c r="B19" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427601</v>
+        <v>427762</v>
       </c>
       <c r="R19" t="n">
-        <v>6233830</v>
+        <v>6233515</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121471563</v>
+        <v>121471955</v>
       </c>
       <c r="B20" t="n">
-        <v>96721</v>
+        <v>94597</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2606</v>
+        <v>2666</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428012</v>
+        <v>427741</v>
       </c>
       <c r="R20" t="n">
-        <v>6233689</v>
+        <v>6233529</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121471965</v>
+        <v>121471963</v>
       </c>
       <c r="B21" t="n">
-        <v>76945</v>
+        <v>94595</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>427509</v>
+        <v>427520</v>
       </c>
       <c r="R21" t="n">
-        <v>6233731</v>
+        <v>6233715</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121471590</v>
+        <v>121471618</v>
       </c>
       <c r="B22" t="n">
-        <v>80239</v>
+        <v>96721</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,21 +2940,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427753</v>
+        <v>427525</v>
       </c>
       <c r="R22" t="n">
-        <v>6233666</v>
+        <v>6233838</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471961</v>
+        <v>121471638</v>
       </c>
       <c r="B23" t="n">
-        <v>94595</v>
+        <v>80239</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427615</v>
+        <v>427638</v>
       </c>
       <c r="R23" t="n">
-        <v>6233649</v>
+        <v>6233822</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3096,12 +3096,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471600</v>
+        <v>121471631</v>
       </c>
       <c r="B24" t="n">
-        <v>94595</v>
+        <v>80239</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427698</v>
+        <v>427601</v>
       </c>
       <c r="R24" t="n">
-        <v>6233566</v>
+        <v>6233830</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471562</v>
+        <v>121471593</v>
       </c>
       <c r="B25" t="n">
-        <v>80575</v>
+        <v>80239</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3242,25 +3242,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1182</v>
+        <v>230185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428000</v>
+        <v>427699</v>
       </c>
       <c r="R25" t="n">
-        <v>6233692</v>
+        <v>6233608</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471983</v>
+        <v>121471965</v>
       </c>
       <c r="B26" t="n">
-        <v>74694</v>
+        <v>76945</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3344,25 +3344,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6439</v>
+        <v>1342</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427521</v>
+        <v>427509</v>
       </c>
       <c r="R26" t="n">
-        <v>6233737</v>
+        <v>6233731</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471985</v>
+        <v>121471952</v>
       </c>
       <c r="B27" t="n">
-        <v>80239</v>
+        <v>74694</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427558</v>
+        <v>427763</v>
       </c>
       <c r="R27" t="n">
-        <v>6233768</v>
+        <v>6233529</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471632</v>
+        <v>121472015</v>
       </c>
       <c r="B28" t="n">
-        <v>80239</v>
+        <v>74694</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,21 +3552,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427615</v>
+        <v>427903</v>
       </c>
       <c r="R28" t="n">
-        <v>6233825</v>
+        <v>6233639</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3606,12 +3606,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3638,10 +3638,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471574</v>
+        <v>121471643</v>
       </c>
       <c r="B29" t="n">
-        <v>80239</v>
+        <v>96721</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427838</v>
+        <v>427671</v>
       </c>
       <c r="R29" t="n">
-        <v>6233582</v>
+        <v>6233821</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471575</v>
+        <v>121471715</v>
       </c>
       <c r="B30" t="n">
-        <v>91108</v>
+        <v>80239</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2023</v>
+        <v>230185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427837</v>
+        <v>427445</v>
       </c>
       <c r="R30" t="n">
-        <v>6233582</v>
+        <v>6233860</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471601</v>
+        <v>121471619</v>
       </c>
       <c r="B31" t="n">
-        <v>80239</v>
+        <v>96721</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427688</v>
+        <v>427624</v>
       </c>
       <c r="R31" t="n">
-        <v>6233590</v>
+        <v>6233894</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471645</v>
+        <v>121471710</v>
       </c>
       <c r="B32" t="n">
-        <v>80239</v>
+        <v>94597</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427702</v>
+        <v>427448</v>
       </c>
       <c r="R32" t="n">
-        <v>6233806</v>
+        <v>6233789</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4046,10 +4046,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471556</v>
+        <v>121471601</v>
       </c>
       <c r="B33" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427948</v>
+        <v>427688</v>
       </c>
       <c r="R33" t="n">
-        <v>6233643</v>
+        <v>6233590</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121472003</v>
+        <v>121471707</v>
       </c>
       <c r="B34" t="n">
-        <v>79015</v>
+        <v>96721</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4160,23 +4160,27 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>132</v>
+        <v>2606</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liten lundlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bacidina phacodes/tarandina</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4184,10 +4188,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427911</v>
+        <v>427809</v>
       </c>
       <c r="R34" t="n">
-        <v>6233614</v>
+        <v>6233703</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4214,12 +4218,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4246,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471651</v>
+        <v>121471979</v>
       </c>
       <c r="B35" t="n">
-        <v>78860</v>
+        <v>76945</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4258,25 +4262,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4286,10 +4290,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427737</v>
+        <v>427533</v>
       </c>
       <c r="R35" t="n">
-        <v>6233789</v>
+        <v>6233765</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4316,12 +4320,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4348,10 +4352,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471976</v>
+        <v>121471962</v>
       </c>
       <c r="B36" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4364,21 +4368,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4388,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427576</v>
+        <v>427528</v>
       </c>
       <c r="R36" t="n">
-        <v>6233800</v>
+        <v>6233707</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,10 +4454,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471648</v>
+        <v>121471956</v>
       </c>
       <c r="B37" t="n">
-        <v>76945</v>
+        <v>94597</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4462,25 +4466,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1342</v>
+        <v>2666</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4490,10 +4494,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427721</v>
+        <v>427739</v>
       </c>
       <c r="R37" t="n">
-        <v>6233787</v>
+        <v>6233524</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4520,12 +4524,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4552,10 +4556,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471710</v>
+        <v>121471598</v>
       </c>
       <c r="B38" t="n">
-        <v>94597</v>
+        <v>94595</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4568,16 +4572,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4592,10 +4596,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427448</v>
+        <v>427690</v>
       </c>
       <c r="R38" t="n">
-        <v>6233789</v>
+        <v>6233595</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4654,10 +4658,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471705</v>
+        <v>121471578</v>
       </c>
       <c r="B39" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4666,25 +4670,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4694,10 +4698,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427753</v>
+        <v>427749</v>
       </c>
       <c r="R39" t="n">
-        <v>6233606</v>
+        <v>6233573</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4756,10 +4760,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471602</v>
+        <v>121471584</v>
       </c>
       <c r="B40" t="n">
-        <v>94595</v>
+        <v>96721</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4772,21 +4776,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4796,10 +4800,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427641</v>
+        <v>427817</v>
       </c>
       <c r="R40" t="n">
-        <v>6233630</v>
+        <v>6233621</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4858,10 +4862,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471612</v>
+        <v>121471576</v>
       </c>
       <c r="B41" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4870,25 +4874,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4898,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427466</v>
+        <v>427742</v>
       </c>
       <c r="R41" t="n">
-        <v>6233828</v>
+        <v>6233565</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4960,10 +4964,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121472014</v>
+        <v>121472010</v>
       </c>
       <c r="B42" t="n">
-        <v>80252</v>
+        <v>78984</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4972,25 +4976,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1144</v>
+        <v>6431</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5000,10 +5004,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427882</v>
+        <v>427877</v>
       </c>
       <c r="R42" t="n">
-        <v>6233622</v>
+        <v>6233615</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5062,10 +5066,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471995</v>
+        <v>121471967</v>
       </c>
       <c r="B43" t="n">
-        <v>78860</v>
+        <v>80252</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5074,25 +5078,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6459</v>
+        <v>1144</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5102,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427856</v>
+        <v>427508</v>
       </c>
       <c r="R43" t="n">
-        <v>6233613</v>
+        <v>6233737</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5164,10 +5168,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471572</v>
+        <v>121471957</v>
       </c>
       <c r="B44" t="n">
-        <v>96721</v>
+        <v>94595</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5180,21 +5184,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5204,10 +5208,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427982</v>
+        <v>427731</v>
       </c>
       <c r="R44" t="n">
-        <v>6233642</v>
+        <v>6233539</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5234,12 +5238,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5266,10 +5270,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471999</v>
+        <v>121471635</v>
       </c>
       <c r="B45" t="n">
-        <v>80252</v>
+        <v>78860</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5278,25 +5282,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1144</v>
+        <v>6459</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5306,10 +5310,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>427916</v>
+        <v>427637</v>
       </c>
       <c r="R45" t="n">
-        <v>6233634</v>
+        <v>6233845</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5336,12 +5340,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5368,10 +5372,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471703</v>
+        <v>121471706</v>
       </c>
       <c r="B46" t="n">
-        <v>74694</v>
+        <v>96721</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5384,21 +5388,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5408,10 +5412,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427770</v>
+        <v>427781</v>
       </c>
       <c r="R46" t="n">
-        <v>6233580</v>
+        <v>6233648</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5470,10 +5474,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471962</v>
+        <v>121471627</v>
       </c>
       <c r="B47" t="n">
-        <v>80239</v>
+        <v>74694</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5486,21 +5490,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5510,10 +5514,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427528</v>
+        <v>427613</v>
       </c>
       <c r="R47" t="n">
-        <v>6233707</v>
+        <v>6233840</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5540,12 +5544,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5572,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471557</v>
+        <v>121471589</v>
       </c>
       <c r="B48" t="n">
-        <v>94584</v>
+        <v>96721</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5588,21 +5592,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5612,10 +5616,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427948</v>
+        <v>427804</v>
       </c>
       <c r="R48" t="n">
-        <v>6233643</v>
+        <v>6233688</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5674,10 +5678,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471583</v>
+        <v>121472002</v>
       </c>
       <c r="B49" t="n">
-        <v>78860</v>
+        <v>94595</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5690,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6459</v>
+        <v>2667</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5714,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427813</v>
+        <v>427909</v>
       </c>
       <c r="R49" t="n">
-        <v>6233621</v>
+        <v>6233613</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5744,12 +5748,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5776,10 +5780,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471959</v>
+        <v>121472012</v>
       </c>
       <c r="B50" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5788,25 +5792,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5816,10 +5820,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427734</v>
+        <v>427855</v>
       </c>
       <c r="R50" t="n">
-        <v>6233532</v>
+        <v>6233612</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5878,10 +5882,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471993</v>
+        <v>121472014</v>
       </c>
       <c r="B51" t="n">
-        <v>91500</v>
+        <v>80252</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5890,41 +5894,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2014</v>
+        <v>1144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427859</v>
+        <v>427882</v>
       </c>
       <c r="R51" t="n">
-        <v>6233620</v>
+        <v>6233622</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5965,7 +5966,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5984,7 +5984,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471713</v>
+        <v>121471966</v>
       </c>
       <c r="B52" t="n">
         <v>76945</v>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427438</v>
+        <v>427505</v>
       </c>
       <c r="R52" t="n">
-        <v>6233852</v>
+        <v>6233740</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6054,12 +6054,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6086,10 +6086,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471592</v>
+        <v>121471557</v>
       </c>
       <c r="B53" t="n">
-        <v>80239</v>
+        <v>94584</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6102,21 +6102,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427703</v>
+        <v>427948</v>
       </c>
       <c r="R53" t="n">
-        <v>6233616</v>
+        <v>6233643</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6188,10 +6188,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471988</v>
+        <v>121471636</v>
       </c>
       <c r="B54" t="n">
-        <v>74522</v>
+        <v>80239</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6204,21 +6204,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6428</v>
+        <v>230185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427738</v>
+        <v>427650</v>
       </c>
       <c r="R54" t="n">
-        <v>6233780</v>
+        <v>6233855</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6290,10 +6290,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471643</v>
+        <v>121471718</v>
       </c>
       <c r="B55" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6302,25 +6302,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>427671</v>
+        <v>427584</v>
       </c>
       <c r="R55" t="n">
-        <v>6233821</v>
+        <v>6233863</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6392,10 +6392,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471998</v>
+        <v>121471564</v>
       </c>
       <c r="B56" t="n">
-        <v>76945</v>
+        <v>80252</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6404,25 +6404,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>427915</v>
+        <v>428014</v>
       </c>
       <c r="R56" t="n">
-        <v>6233632</v>
+        <v>6233692</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6462,12 +6462,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6494,10 +6494,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471952</v>
+        <v>121471620</v>
       </c>
       <c r="B57" t="n">
-        <v>74694</v>
+        <v>94584</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6439</v>
+        <v>2671</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427763</v>
+        <v>427625</v>
       </c>
       <c r="R57" t="n">
-        <v>6233529</v>
+        <v>6233894</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6564,12 +6564,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6596,10 +6596,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471628</v>
+        <v>121471988</v>
       </c>
       <c r="B58" t="n">
-        <v>96721</v>
+        <v>74522</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6612,21 +6612,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2606</v>
+        <v>6428</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427604</v>
+        <v>427738</v>
       </c>
       <c r="R58" t="n">
-        <v>6233834</v>
+        <v>6233780</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6698,10 +6698,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471604</v>
+        <v>121472009</v>
       </c>
       <c r="B59" t="n">
-        <v>80239</v>
+        <v>94595</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6714,21 +6714,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427595</v>
+        <v>427877</v>
       </c>
       <c r="R59" t="n">
-        <v>6233781</v>
+        <v>6233615</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6768,12 +6768,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6800,7 +6800,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471614</v>
+        <v>121471985</v>
       </c>
       <c r="B60" t="n">
         <v>80239</v>
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427475</v>
+        <v>427558</v>
       </c>
       <c r="R60" t="n">
-        <v>6233836</v>
+        <v>6233768</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6902,10 +6902,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471591</v>
+        <v>121471634</v>
       </c>
       <c r="B61" t="n">
-        <v>80239</v>
+        <v>96721</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6918,21 +6918,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427724</v>
+        <v>427636</v>
       </c>
       <c r="R61" t="n">
-        <v>6233617</v>
+        <v>6233848</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7004,10 +7004,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121472002</v>
+        <v>121471641</v>
       </c>
       <c r="B62" t="n">
-        <v>94595</v>
+        <v>78860</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7020,21 +7020,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2667</v>
+        <v>6459</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427909</v>
+        <v>427655</v>
       </c>
       <c r="R62" t="n">
-        <v>6233613</v>
+        <v>6233850</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7106,10 +7106,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121472010</v>
+        <v>121471629</v>
       </c>
       <c r="B63" t="n">
-        <v>78984</v>
+        <v>80252</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7118,25 +7118,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6431</v>
+        <v>1144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427877</v>
+        <v>427602</v>
       </c>
       <c r="R63" t="n">
-        <v>6233615</v>
+        <v>6233832</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7176,12 +7176,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7208,10 +7208,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471642</v>
+        <v>121471986</v>
       </c>
       <c r="B64" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7220,38 +7220,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427654</v>
+        <v>427558</v>
       </c>
       <c r="R64" t="n">
-        <v>6233848</v>
+        <v>6233769</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7278,12 +7281,17 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Med Refractohilum pluriseptatum</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7291,6 +7299,11 @@
       </c>
       <c r="AE64" t="b">
         <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG64" t="b">
         <v>0</v>
@@ -7310,10 +7323,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471608</v>
+        <v>121471982</v>
       </c>
       <c r="B65" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7322,25 +7335,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7350,10 +7363,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427566</v>
+        <v>427516</v>
       </c>
       <c r="R65" t="n">
-        <v>6233756</v>
+        <v>6233748</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7380,12 +7393,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7412,10 +7425,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471622</v>
+        <v>121471716</v>
       </c>
       <c r="B66" t="n">
-        <v>74694</v>
+        <v>80239</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7428,21 +7441,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7452,7 +7465,7 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427623</v>
+        <v>427547</v>
       </c>
       <c r="R66" t="n">
         <v>6233865</v>
@@ -7514,10 +7527,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471644</v>
+        <v>121471603</v>
       </c>
       <c r="B67" t="n">
-        <v>78860</v>
+        <v>80252</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7526,25 +7539,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6459</v>
+        <v>1144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7554,10 +7567,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427671</v>
+        <v>427596</v>
       </c>
       <c r="R67" t="n">
-        <v>6233821</v>
+        <v>6233681</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7616,10 +7629,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121472006</v>
+        <v>121471996</v>
       </c>
       <c r="B68" t="n">
-        <v>76945</v>
+        <v>80252</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7628,25 +7641,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7656,10 +7669,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427892</v>
+        <v>427855</v>
       </c>
       <c r="R68" t="n">
-        <v>6233623</v>
+        <v>6233614</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7718,10 +7731,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471565</v>
+        <v>121471645</v>
       </c>
       <c r="B69" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7730,25 +7743,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7758,10 +7771,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>428016</v>
+        <v>427702</v>
       </c>
       <c r="R69" t="n">
-        <v>6233689</v>
+        <v>6233806</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7820,10 +7833,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121472015</v>
+        <v>121471572</v>
       </c>
       <c r="B70" t="n">
-        <v>74694</v>
+        <v>96721</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7836,21 +7849,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7860,10 +7873,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>427903</v>
+        <v>427982</v>
       </c>
       <c r="R70" t="n">
-        <v>6233639</v>
+        <v>6233642</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7890,12 +7903,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7922,10 +7935,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471719</v>
+        <v>121471626</v>
       </c>
       <c r="B71" t="n">
-        <v>76945</v>
+        <v>74694</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7934,25 +7947,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1342</v>
+        <v>6439</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7962,10 +7975,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>427583</v>
+        <v>427597</v>
       </c>
       <c r="R71" t="n">
-        <v>6233861</v>
+        <v>6233825</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8024,10 +8037,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471992</v>
+        <v>121471617</v>
       </c>
       <c r="B72" t="n">
-        <v>94584</v>
+        <v>80239</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8040,21 +8053,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8064,10 +8077,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427861</v>
+        <v>427526</v>
       </c>
       <c r="R72" t="n">
-        <v>6233620</v>
+        <v>6233836</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8094,12 +8107,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8126,10 +8139,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471599</v>
+        <v>121471560</v>
       </c>
       <c r="B73" t="n">
-        <v>94597</v>
+        <v>80239</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8142,21 +8155,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8166,10 +8179,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427685</v>
+        <v>428008</v>
       </c>
       <c r="R73" t="n">
-        <v>6233593</v>
+        <v>6233671</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8228,7 +8241,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471984</v>
+        <v>121471604</v>
       </c>
       <c r="B74" t="n">
         <v>80239</v>
@@ -8268,10 +8281,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>427530</v>
+        <v>427595</v>
       </c>
       <c r="R74" t="n">
-        <v>6233736</v>
+        <v>6233781</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8298,12 +8311,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8330,10 +8343,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471587</v>
+        <v>121471998</v>
       </c>
       <c r="B75" t="n">
-        <v>80252</v>
+        <v>76945</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8342,25 +8355,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8370,10 +8383,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>427770</v>
+        <v>427915</v>
       </c>
       <c r="R75" t="n">
-        <v>6233624</v>
+        <v>6233632</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8400,12 +8413,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8432,10 +8445,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471624</v>
+        <v>121472013</v>
       </c>
       <c r="B76" t="n">
-        <v>74560</v>
+        <v>96721</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8444,25 +8457,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1116</v>
+        <v>2606</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8472,10 +8485,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427594</v>
+        <v>427882</v>
       </c>
       <c r="R76" t="n">
-        <v>6233828</v>
+        <v>6233622</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8502,12 +8515,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8534,10 +8547,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121472004</v>
+        <v>121472003</v>
       </c>
       <c r="B77" t="n">
-        <v>80239</v>
+        <v>79015</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8546,27 +8559,23 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>230185</v>
+        <v>132</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Liten lundlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Bacidina phacodes/tarandina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8574,10 +8583,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427892</v>
+        <v>427911</v>
       </c>
       <c r="R77" t="n">
-        <v>6233623</v>
+        <v>6233614</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8636,10 +8645,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471633</v>
+        <v>121471973</v>
       </c>
       <c r="B78" t="n">
-        <v>90504</v>
+        <v>76945</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8648,25 +8657,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1067</v>
+        <v>1342</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8676,10 +8685,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427629</v>
+        <v>427544</v>
       </c>
       <c r="R78" t="n">
-        <v>6233837</v>
+        <v>6233811</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8706,12 +8715,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8738,7 +8747,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471561</v>
+        <v>121471977</v>
       </c>
       <c r="B79" t="n">
         <v>96721</v>
@@ -8778,10 +8787,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427999</v>
+        <v>427533</v>
       </c>
       <c r="R79" t="n">
-        <v>6233695</v>
+        <v>6233765</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8808,12 +8817,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8840,10 +8849,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121472009</v>
+        <v>121471628</v>
       </c>
       <c r="B80" t="n">
-        <v>94595</v>
+        <v>96721</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8856,21 +8865,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8880,10 +8889,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427877</v>
+        <v>427604</v>
       </c>
       <c r="R80" t="n">
-        <v>6233615</v>
+        <v>6233834</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8910,12 +8919,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8942,7 +8951,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471709</v>
+        <v>121471581</v>
       </c>
       <c r="B81" t="n">
         <v>80239</v>
@@ -8982,10 +8991,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427452</v>
+        <v>427820</v>
       </c>
       <c r="R81" t="n">
-        <v>6233794</v>
+        <v>6233599</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9044,10 +9053,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471702</v>
+        <v>121471650</v>
       </c>
       <c r="B82" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9060,21 +9069,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9084,10 +9093,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427811</v>
+        <v>427737</v>
       </c>
       <c r="R82" t="n">
-        <v>6233480</v>
+        <v>6233784</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9146,10 +9155,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471641</v>
+        <v>121471704</v>
       </c>
       <c r="B83" t="n">
-        <v>78860</v>
+        <v>96721</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9162,21 +9171,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9186,10 +9195,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427655</v>
+        <v>427785</v>
       </c>
       <c r="R83" t="n">
-        <v>6233850</v>
+        <v>6233585</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9248,10 +9257,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471966</v>
+        <v>121471610</v>
       </c>
       <c r="B84" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9260,25 +9269,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9288,10 +9297,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427505</v>
+        <v>427487</v>
       </c>
       <c r="R84" t="n">
-        <v>6233740</v>
+        <v>6233816</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9318,12 +9327,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9350,7 +9359,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471607</v>
+        <v>121471720</v>
       </c>
       <c r="B85" t="n">
         <v>80239</v>
@@ -9390,10 +9399,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427582</v>
+        <v>427595</v>
       </c>
       <c r="R85" t="n">
-        <v>6233752</v>
+        <v>6233898</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9452,10 +9461,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471621</v>
+        <v>121471583</v>
       </c>
       <c r="B86" t="n">
-        <v>96721</v>
+        <v>78860</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9468,21 +9477,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9492,10 +9501,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427607</v>
+        <v>427813</v>
       </c>
       <c r="R86" t="n">
-        <v>6233875</v>
+        <v>6233621</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9554,10 +9563,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471630</v>
+        <v>121471596</v>
       </c>
       <c r="B87" t="n">
-        <v>76945</v>
+        <v>74696</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9566,25 +9575,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1342</v>
+        <v>306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9594,10 +9603,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427604</v>
+        <v>427686</v>
       </c>
       <c r="R87" t="n">
-        <v>6233829</v>
+        <v>6233621</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9656,7 +9665,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471584</v>
+        <v>121471637</v>
       </c>
       <c r="B88" t="n">
         <v>96721</v>
@@ -9696,10 +9705,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427817</v>
+        <v>427638</v>
       </c>
       <c r="R88" t="n">
-        <v>6233621</v>
+        <v>6233822</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9758,7 +9767,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471712</v>
+        <v>121471621</v>
       </c>
       <c r="B89" t="n">
         <v>96721</v>
@@ -9798,10 +9807,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427439</v>
+        <v>427607</v>
       </c>
       <c r="R89" t="n">
-        <v>6233838</v>
+        <v>6233875</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9860,10 +9869,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471978</v>
+        <v>121471702</v>
       </c>
       <c r="B90" t="n">
-        <v>94595</v>
+        <v>96721</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9876,21 +9885,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9900,10 +9909,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427533</v>
+        <v>427811</v>
       </c>
       <c r="R90" t="n">
-        <v>6233765</v>
+        <v>6233480</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9930,12 +9939,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9962,10 +9971,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471585</v>
+        <v>121471995</v>
       </c>
       <c r="B91" t="n">
-        <v>76945</v>
+        <v>78860</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9974,25 +9983,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1342</v>
+        <v>6459</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10002,10 +10011,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427748</v>
+        <v>427856</v>
       </c>
       <c r="R91" t="n">
-        <v>6233622</v>
+        <v>6233613</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10032,12 +10041,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10064,7 +10073,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471986</v>
+        <v>121472007</v>
       </c>
       <c r="B92" t="n">
         <v>80252</v>
@@ -10098,19 +10107,16 @@
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427558</v>
+        <v>427892</v>
       </c>
       <c r="R92" t="n">
-        <v>6233769</v>
+        <v>6233623</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10145,21 +10151,11 @@
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Med Refractohilum pluriseptatum</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
-      </c>
-      <c r="AF92" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG92" t="b">
         <v>0</v>
@@ -10179,10 +10175,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471955</v>
+        <v>121472000</v>
       </c>
       <c r="B93" t="n">
-        <v>94597</v>
+        <v>74694</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10195,21 +10191,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2666</v>
+        <v>6439</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10219,10 +10215,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427741</v>
+        <v>427926</v>
       </c>
       <c r="R93" t="n">
-        <v>6233529</v>
+        <v>6233617</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10281,10 +10277,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471578</v>
+        <v>121471562</v>
       </c>
       <c r="B94" t="n">
-        <v>76945</v>
+        <v>80575</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10297,21 +10293,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1342</v>
+        <v>1182</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10321,10 +10317,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427749</v>
+        <v>428000</v>
       </c>
       <c r="R94" t="n">
-        <v>6233573</v>
+        <v>6233692</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10383,10 +10379,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471708</v>
+        <v>121471559</v>
       </c>
       <c r="B95" t="n">
-        <v>96721</v>
+        <v>76945</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10395,25 +10391,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10423,10 +10419,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427785</v>
+        <v>427960</v>
       </c>
       <c r="R95" t="n">
-        <v>6233734</v>
+        <v>6233661</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10485,10 +10481,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121472001</v>
+        <v>121471591</v>
       </c>
       <c r="B96" t="n">
-        <v>94605</v>
+        <v>80239</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10501,21 +10497,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1080</v>
+        <v>230185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10525,7 +10521,7 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427908</v>
+        <v>427724</v>
       </c>
       <c r="R96" t="n">
         <v>6233617</v>
@@ -10555,12 +10551,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10587,10 +10583,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471646</v>
+        <v>121471607</v>
       </c>
       <c r="B97" t="n">
-        <v>94595</v>
+        <v>80239</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10603,21 +10599,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10627,10 +10623,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427692</v>
+        <v>427582</v>
       </c>
       <c r="R97" t="n">
-        <v>6233796</v>
+        <v>6233752</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10689,10 +10685,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471637</v>
+        <v>121471558</v>
       </c>
       <c r="B98" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10701,25 +10697,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10729,10 +10725,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427638</v>
+        <v>427960</v>
       </c>
       <c r="R98" t="n">
-        <v>6233822</v>
+        <v>6233661</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10791,7 +10787,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471707</v>
+        <v>121471640</v>
       </c>
       <c r="B99" t="n">
         <v>96721</v>
@@ -10831,10 +10827,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427809</v>
+        <v>427653</v>
       </c>
       <c r="R99" t="n">
-        <v>6233703</v>
+        <v>6233849</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10893,10 +10889,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471626</v>
+        <v>121471671</v>
       </c>
       <c r="B100" t="n">
-        <v>74694</v>
+        <v>105755</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10905,25 +10901,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6439</v>
+        <v>220785</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10933,10 +10929,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427597</v>
+        <v>427912</v>
       </c>
       <c r="R100" t="n">
-        <v>6233825</v>
+        <v>6233611</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10995,7 +10991,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471610</v>
+        <v>121471642</v>
       </c>
       <c r="B101" t="n">
         <v>80239</v>
@@ -11035,10 +11031,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>427487</v>
+        <v>427654</v>
       </c>
       <c r="R101" t="n">
-        <v>6233816</v>
+        <v>6233848</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11097,10 +11093,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471598</v>
+        <v>121471709</v>
       </c>
       <c r="B102" t="n">
-        <v>94595</v>
+        <v>80239</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11113,21 +11109,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11137,10 +11133,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427690</v>
+        <v>427452</v>
       </c>
       <c r="R102" t="n">
-        <v>6233595</v>
+        <v>6233794</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11199,10 +11195,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471971</v>
+        <v>121471622</v>
       </c>
       <c r="B103" t="n">
-        <v>78860</v>
+        <v>74694</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11215,21 +11211,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6459</v>
+        <v>6439</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11239,10 +11235,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427499</v>
+        <v>427623</v>
       </c>
       <c r="R103" t="n">
-        <v>6233792</v>
+        <v>6233865</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11269,12 +11265,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11301,10 +11297,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471617</v>
+        <v>121471651</v>
       </c>
       <c r="B104" t="n">
-        <v>80239</v>
+        <v>78860</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11317,21 +11313,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11341,10 +11337,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427526</v>
+        <v>427737</v>
       </c>
       <c r="R104" t="n">
-        <v>6233836</v>
+        <v>6233789</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11403,10 +11399,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471977</v>
+        <v>121472011</v>
       </c>
       <c r="B105" t="n">
-        <v>96721</v>
+        <v>76945</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11415,25 +11411,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11443,10 +11439,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427533</v>
+        <v>427874</v>
       </c>
       <c r="R105" t="n">
-        <v>6233765</v>
+        <v>6233615</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11505,10 +11501,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471973</v>
+        <v>121471632</v>
       </c>
       <c r="B106" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11517,25 +11513,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11545,10 +11541,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427544</v>
+        <v>427615</v>
       </c>
       <c r="R106" t="n">
-        <v>6233811</v>
+        <v>6233825</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11575,12 +11571,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11607,10 +11603,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471956</v>
+        <v>121471580</v>
       </c>
       <c r="B107" t="n">
-        <v>94597</v>
+        <v>80239</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11623,21 +11619,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11647,10 +11643,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427739</v>
+        <v>427804</v>
       </c>
       <c r="R107" t="n">
-        <v>6233524</v>
+        <v>6233576</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11677,12 +11673,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11811,10 +11807,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121472007</v>
+        <v>121471714</v>
       </c>
       <c r="B109" t="n">
-        <v>80252</v>
+        <v>78404</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11823,25 +11819,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1144</v>
+        <v>924</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11851,10 +11847,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>427892</v>
+        <v>427435</v>
       </c>
       <c r="R109" t="n">
-        <v>6233623</v>
+        <v>6233855</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11881,12 +11877,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11913,10 +11909,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471589</v>
+        <v>121471586</v>
       </c>
       <c r="B110" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11925,25 +11921,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11953,10 +11949,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427804</v>
+        <v>427748</v>
       </c>
       <c r="R110" t="n">
-        <v>6233688</v>
+        <v>6233622</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12015,10 +12011,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121472016</v>
+        <v>121471980</v>
       </c>
       <c r="B111" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12027,25 +12023,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12055,10 +12051,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427903</v>
+        <v>427532</v>
       </c>
       <c r="R111" t="n">
-        <v>6233640</v>
+        <v>6233767</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12117,10 +12113,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471963</v>
+        <v>121472016</v>
       </c>
       <c r="B112" t="n">
-        <v>94595</v>
+        <v>96721</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12133,21 +12129,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12157,10 +12153,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427520</v>
+        <v>427903</v>
       </c>
       <c r="R112" t="n">
-        <v>6233715</v>
+        <v>6233640</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12219,10 +12215,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471951</v>
+        <v>121471990</v>
       </c>
       <c r="B113" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12231,25 +12227,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12259,10 +12255,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427762</v>
+        <v>427765</v>
       </c>
       <c r="R113" t="n">
-        <v>6233515</v>
+        <v>6233765</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12321,10 +12317,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471620</v>
+        <v>121472001</v>
       </c>
       <c r="B114" t="n">
-        <v>94584</v>
+        <v>94605</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12337,21 +12333,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2671</v>
+        <v>1080</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12361,10 +12357,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427625</v>
+        <v>427908</v>
       </c>
       <c r="R114" t="n">
-        <v>6233894</v>
+        <v>6233617</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12391,12 +12387,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12423,10 +12419,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471718</v>
+        <v>121471993</v>
       </c>
       <c r="B115" t="n">
-        <v>80252</v>
+        <v>91500</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12435,38 +12431,41 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1144</v>
+        <v>2014</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427584</v>
+        <v>427859</v>
       </c>
       <c r="R115" t="n">
-        <v>6233863</v>
+        <v>6233620</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12493,12 +12492,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12507,6 +12506,7 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
+      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12525,10 +12525,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471996</v>
+        <v>121471984</v>
       </c>
       <c r="B116" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12537,25 +12537,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12565,10 +12565,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427855</v>
+        <v>427530</v>
       </c>
       <c r="R116" t="n">
-        <v>6233614</v>
+        <v>6233736</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12627,10 +12627,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121472000</v>
+        <v>121471999</v>
       </c>
       <c r="B117" t="n">
-        <v>74694</v>
+        <v>80252</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12639,25 +12639,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12667,10 +12667,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427926</v>
+        <v>427916</v>
       </c>
       <c r="R117" t="n">
-        <v>6233617</v>
+        <v>6233634</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12729,10 +12729,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471558</v>
+        <v>121471992</v>
       </c>
       <c r="B118" t="n">
-        <v>80252</v>
+        <v>94584</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12741,25 +12741,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12769,10 +12769,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427960</v>
+        <v>427861</v>
       </c>
       <c r="R118" t="n">
-        <v>6233661</v>
+        <v>6233620</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12799,12 +12799,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12831,10 +12831,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471979</v>
+        <v>121471592</v>
       </c>
       <c r="B119" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12843,25 +12843,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12871,10 +12871,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427533</v>
+        <v>427703</v>
       </c>
       <c r="R119" t="n">
-        <v>6233765</v>
+        <v>6233616</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12933,10 +12933,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471649</v>
+        <v>121471623</v>
       </c>
       <c r="B120" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12945,25 +12945,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12973,10 +12973,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427720</v>
+        <v>427579</v>
       </c>
       <c r="R120" t="n">
-        <v>6233787</v>
+        <v>6233850</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13035,10 +13035,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121472012</v>
+        <v>121471575</v>
       </c>
       <c r="B121" t="n">
-        <v>76945</v>
+        <v>91108</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13051,21 +13051,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1342</v>
+        <v>2023</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13075,10 +13075,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427855</v>
+        <v>427837</v>
       </c>
       <c r="R121" t="n">
-        <v>6233612</v>
+        <v>6233582</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13137,10 +13137,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471618</v>
+        <v>121471648</v>
       </c>
       <c r="B122" t="n">
-        <v>96721</v>
+        <v>76945</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13149,25 +13149,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13177,10 +13177,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427525</v>
+        <v>427721</v>
       </c>
       <c r="R122" t="n">
-        <v>6233838</v>
+        <v>6233787</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13239,10 +13239,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471714</v>
+        <v>121471644</v>
       </c>
       <c r="B123" t="n">
-        <v>78404</v>
+        <v>78860</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13251,25 +13251,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13279,10 +13279,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427435</v>
+        <v>427671</v>
       </c>
       <c r="R123" t="n">
-        <v>6233855</v>
+        <v>6233821</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13341,10 +13341,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471990</v>
+        <v>121471585</v>
       </c>
       <c r="B124" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13353,25 +13353,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13381,10 +13381,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427765</v>
+        <v>427748</v>
       </c>
       <c r="R124" t="n">
-        <v>6233765</v>
+        <v>6233622</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13411,12 +13411,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13443,10 +13443,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471964</v>
+        <v>121471608</v>
       </c>
       <c r="B125" t="n">
-        <v>94595</v>
+        <v>80239</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13459,21 +13459,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13483,10 +13483,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427511</v>
+        <v>427566</v>
       </c>
       <c r="R125" t="n">
-        <v>6233739</v>
+        <v>6233756</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13513,12 +13513,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13545,10 +13545,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471974</v>
+        <v>121471574</v>
       </c>
       <c r="B126" t="n">
-        <v>90504</v>
+        <v>80239</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13557,25 +13557,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13585,10 +13585,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427554</v>
+        <v>427838</v>
       </c>
       <c r="R126" t="n">
-        <v>6233803</v>
+        <v>6233582</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13615,12 +13615,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13647,7 +13647,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471638</v>
+        <v>121471590</v>
       </c>
       <c r="B127" t="n">
         <v>80239</v>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427638</v>
+        <v>427753</v>
       </c>
       <c r="R127" t="n">
-        <v>6233822</v>
+        <v>6233666</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13749,10 +13749,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471706</v>
+        <v>121471961</v>
       </c>
       <c r="B128" t="n">
-        <v>96721</v>
+        <v>94595</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13765,21 +13765,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13789,10 +13789,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427781</v>
+        <v>427615</v>
       </c>
       <c r="R128" t="n">
-        <v>6233648</v>
+        <v>6233649</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13819,12 +13819,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13851,10 +13851,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471982</v>
+        <v>121471974</v>
       </c>
       <c r="B129" t="n">
-        <v>76945</v>
+        <v>90504</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13863,25 +13863,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1342</v>
+        <v>1067</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13891,10 +13891,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>427516</v>
+        <v>427554</v>
       </c>
       <c r="R129" t="n">
-        <v>6233748</v>
+        <v>6233803</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13953,10 +13953,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471623</v>
+        <v>121471563</v>
       </c>
       <c r="B130" t="n">
-        <v>80239</v>
+        <v>96721</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13969,21 +13969,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13993,10 +13993,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>427579</v>
+        <v>428012</v>
       </c>
       <c r="R130" t="n">
-        <v>6233850</v>
+        <v>6233689</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14055,7 +14055,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471619</v>
+        <v>121471556</v>
       </c>
       <c r="B131" t="n">
         <v>96721</v>
@@ -14095,10 +14095,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427624</v>
+        <v>427948</v>
       </c>
       <c r="R131" t="n">
-        <v>6233894</v>
+        <v>6233643</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14157,10 +14157,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471581</v>
+        <v>121471633</v>
       </c>
       <c r="B132" t="n">
-        <v>80239</v>
+        <v>90504</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14169,25 +14169,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14197,10 +14197,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427820</v>
+        <v>427629</v>
       </c>
       <c r="R132" t="n">
-        <v>6233599</v>
+        <v>6233837</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14259,10 +14259,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471521</v>
+        <v>121471565</v>
       </c>
       <c r="B133" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14271,25 +14271,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14299,10 +14299,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427794</v>
+        <v>428016</v>
       </c>
       <c r="R133" t="n">
-        <v>6233483</v>
+        <v>6233689</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14361,10 +14361,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471560</v>
+        <v>121471719</v>
       </c>
       <c r="B134" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14373,25 +14373,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14401,10 +14401,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>428008</v>
+        <v>427583</v>
       </c>
       <c r="R134" t="n">
-        <v>6233671</v>
+        <v>6233861</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14463,10 +14463,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471603</v>
+        <v>121471614</v>
       </c>
       <c r="B135" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14475,25 +14475,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14503,10 +14503,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427596</v>
+        <v>427475</v>
       </c>
       <c r="R135" t="n">
-        <v>6233681</v>
+        <v>6233836</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14667,10 +14667,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471715</v>
+        <v>121471587</v>
       </c>
       <c r="B137" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14679,25 +14679,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14707,10 +14707,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427445</v>
+        <v>427770</v>
       </c>
       <c r="R137" t="n">
-        <v>6233860</v>
+        <v>6233624</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14769,10 +14769,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471627</v>
+        <v>121471602</v>
       </c>
       <c r="B138" t="n">
-        <v>74694</v>
+        <v>94595</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14785,21 +14785,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6439</v>
+        <v>2667</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14809,10 +14809,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427613</v>
+        <v>427641</v>
       </c>
       <c r="R138" t="n">
-        <v>6233840</v>
+        <v>6233630</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14871,7 +14871,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471640</v>
+        <v>121471647</v>
       </c>
       <c r="B139" t="n">
         <v>96721</v>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>427653</v>
+        <v>427720</v>
       </c>
       <c r="R139" t="n">
-        <v>6233849</v>
+        <v>6233787</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14973,10 +14973,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471635</v>
+        <v>121471599</v>
       </c>
       <c r="B140" t="n">
-        <v>78860</v>
+        <v>94597</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14989,21 +14989,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6459</v>
+        <v>2666</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15013,10 +15013,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>427637</v>
+        <v>427685</v>
       </c>
       <c r="R140" t="n">
-        <v>6233845</v>
+        <v>6233593</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15075,10 +15075,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121472013</v>
+        <v>121471521</v>
       </c>
       <c r="B141" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15091,21 +15091,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15115,10 +15115,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>427882</v>
+        <v>427794</v>
       </c>
       <c r="R141" t="n">
-        <v>6233622</v>
+        <v>6233483</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15145,12 +15145,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15177,10 +15177,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471586</v>
+        <v>121471609</v>
       </c>
       <c r="B142" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15189,25 +15189,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15217,10 +15217,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>427748</v>
+        <v>427543</v>
       </c>
       <c r="R142" t="n">
-        <v>6233622</v>
+        <v>6233756</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15279,10 +15279,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471596</v>
+        <v>121471600</v>
       </c>
       <c r="B143" t="n">
-        <v>74696</v>
+        <v>94595</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15295,21 +15295,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>306</v>
+        <v>2667</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15319,10 +15319,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>427686</v>
+        <v>427698</v>
       </c>
       <c r="R143" t="n">
-        <v>6233621</v>
+        <v>6233566</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15381,10 +15381,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471700</v>
+        <v>121471649</v>
       </c>
       <c r="B144" t="n">
-        <v>78984</v>
+        <v>80252</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15393,25 +15393,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6431</v>
+        <v>1144</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15421,10 +15421,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>427806</v>
+        <v>427720</v>
       </c>
       <c r="R144" t="n">
-        <v>6233482</v>
+        <v>6233787</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15483,10 +15483,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471980</v>
+        <v>121472006</v>
       </c>
       <c r="B145" t="n">
-        <v>80252</v>
+        <v>76945</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15495,25 +15495,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15523,10 +15523,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427532</v>
+        <v>427892</v>
       </c>
       <c r="R145" t="n">
-        <v>6233767</v>
+        <v>6233623</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15585,10 +15585,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121472011</v>
+        <v>121472004</v>
       </c>
       <c r="B146" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15597,25 +15597,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15625,10 +15625,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427874</v>
+        <v>427892</v>
       </c>
       <c r="R146" t="n">
-        <v>6233615</v>
+        <v>6233623</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15687,10 +15687,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471968</v>
+        <v>121471959</v>
       </c>
       <c r="B147" t="n">
-        <v>57367</v>
+        <v>80239</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15699,25 +15699,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>230185</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15727,10 +15727,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427512</v>
+        <v>427734</v>
       </c>
       <c r="R147" t="n">
-        <v>6233745</v>
+        <v>6233532</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15789,10 +15789,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471576</v>
+        <v>121471612</v>
       </c>
       <c r="B148" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15801,25 +15801,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15829,10 +15829,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427742</v>
+        <v>427466</v>
       </c>
       <c r="R148" t="n">
-        <v>6233565</v>
+        <v>6233828</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15891,10 +15891,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471716</v>
+        <v>121471712</v>
       </c>
       <c r="B149" t="n">
-        <v>80239</v>
+        <v>96721</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15907,21 +15907,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15931,10 +15931,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>427547</v>
+        <v>427439</v>
       </c>
       <c r="R149" t="n">
-        <v>6233865</v>
+        <v>6233838</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15993,10 +15993,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471975</v>
+        <v>121471708</v>
       </c>
       <c r="B150" t="n">
-        <v>80239</v>
+        <v>96721</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16009,21 +16009,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16033,10 +16033,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>427575</v>
+        <v>427785</v>
       </c>
       <c r="R150" t="n">
-        <v>6233800</v>
+        <v>6233734</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16063,12 +16063,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16095,10 +16095,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471564</v>
+        <v>121471705</v>
       </c>
       <c r="B151" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16107,25 +16107,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16135,10 +16135,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>428014</v>
+        <v>427753</v>
       </c>
       <c r="R151" t="n">
-        <v>6233692</v>
+        <v>6233606</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16197,10 +16197,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471954</v>
+        <v>121471630</v>
       </c>
       <c r="B152" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16209,25 +16209,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16237,10 +16237,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>427742</v>
+        <v>427604</v>
       </c>
       <c r="R152" t="n">
-        <v>6233542</v>
+        <v>6233829</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16267,12 +16267,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16299,10 +16299,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471967</v>
+        <v>121471713</v>
       </c>
       <c r="B153" t="n">
-        <v>80252</v>
+        <v>76945</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16311,25 +16311,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16339,10 +16339,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>427508</v>
+        <v>427438</v>
       </c>
       <c r="R153" t="n">
-        <v>6233737</v>
+        <v>6233852</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16369,12 +16369,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16401,10 +16401,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471704</v>
+        <v>121471577</v>
       </c>
       <c r="B154" t="n">
-        <v>96721</v>
+        <v>94595</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16417,21 +16417,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16441,10 +16441,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>427785</v>
+        <v>427749</v>
       </c>
       <c r="R154" t="n">
-        <v>6233585</v>
+        <v>6233572</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16503,10 +16503,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471629</v>
+        <v>121471700</v>
       </c>
       <c r="B155" t="n">
-        <v>80252</v>
+        <v>78984</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16515,25 +16515,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1144</v>
+        <v>6431</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16543,10 +16543,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>427602</v>
+        <v>427806</v>
       </c>
       <c r="R155" t="n">
-        <v>6233832</v>
+        <v>6233482</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16605,7 +16605,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471647</v>
+        <v>121471561</v>
       </c>
       <c r="B156" t="n">
         <v>96721</v>
@@ -16645,10 +16645,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>427720</v>
+        <v>427999</v>
       </c>
       <c r="R156" t="n">
-        <v>6233787</v>
+        <v>6233695</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16707,10 +16707,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471634</v>
+        <v>121471703</v>
       </c>
       <c r="B157" t="n">
-        <v>96721</v>
+        <v>74694</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16723,21 +16723,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2606</v>
+        <v>6439</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16747,10 +16747,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>427636</v>
+        <v>427770</v>
       </c>
       <c r="R157" t="n">
-        <v>6233848</v>
+        <v>6233580</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16809,10 +16809,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471580</v>
+        <v>121471968</v>
       </c>
       <c r="B158" t="n">
-        <v>80239</v>
+        <v>57367</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16821,25 +16821,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>230185</v>
+        <v>100049</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16849,10 +16849,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>427804</v>
+        <v>427512</v>
       </c>
       <c r="R158" t="n">
-        <v>6233576</v>
+        <v>6233745</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16879,12 +16879,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16911,10 +16911,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471953</v>
+        <v>121471960</v>
       </c>
       <c r="B159" t="n">
-        <v>96721</v>
+        <v>94584</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16927,21 +16927,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16951,10 +16951,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>427769</v>
+        <v>427734</v>
       </c>
       <c r="R159" t="n">
-        <v>6233529</v>
+        <v>6233532</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17013,10 +17013,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471671</v>
+        <v>121471983</v>
       </c>
       <c r="B160" t="n">
-        <v>105755</v>
+        <v>74694</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17025,25 +17025,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>220785</v>
+        <v>6439</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17053,10 +17053,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>427912</v>
+        <v>427521</v>
       </c>
       <c r="R160" t="n">
-        <v>6233611</v>
+        <v>6233737</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17083,12 +17083,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17115,10 +17115,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471559</v>
+        <v>121471953</v>
       </c>
       <c r="B161" t="n">
-        <v>76945</v>
+        <v>96721</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17127,25 +17127,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17155,10 +17155,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>427960</v>
+        <v>427769</v>
       </c>
       <c r="R161" t="n">
-        <v>6233661</v>
+        <v>6233529</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17185,12 +17185,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471646</v>
+        <v>121471598</v>
       </c>
       <c r="B11" t="n">
-        <v>94595</v>
+        <v>94596</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427692</v>
+        <v>427690</v>
       </c>
       <c r="R11" t="n">
-        <v>6233796</v>
+        <v>6233595</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471624</v>
+        <v>121471561</v>
       </c>
       <c r="B12" t="n">
-        <v>74560</v>
+        <v>96722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1116</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427594</v>
+        <v>427999</v>
       </c>
       <c r="R12" t="n">
-        <v>6233828</v>
+        <v>6233695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471964</v>
+        <v>121471577</v>
       </c>
       <c r="B13" t="n">
-        <v>94595</v>
+        <v>94596</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427511</v>
+        <v>427749</v>
       </c>
       <c r="R13" t="n">
-        <v>6233739</v>
+        <v>6233572</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,12 +2076,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471954</v>
+        <v>121471600</v>
       </c>
       <c r="B14" t="n">
-        <v>80239</v>
+        <v>94596</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427742</v>
+        <v>427698</v>
       </c>
       <c r="R14" t="n">
-        <v>6233542</v>
+        <v>6233566</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471976</v>
+        <v>121471641</v>
       </c>
       <c r="B15" t="n">
-        <v>96721</v>
+        <v>78860</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427576</v>
+        <v>427655</v>
       </c>
       <c r="R15" t="n">
-        <v>6233800</v>
+        <v>6233850</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121471978</v>
+        <v>121471967</v>
       </c>
       <c r="B16" t="n">
-        <v>94595</v>
+        <v>80252</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427533</v>
+        <v>427508</v>
       </c>
       <c r="R16" t="n">
-        <v>6233765</v>
+        <v>6233737</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121471971</v>
+        <v>121471636</v>
       </c>
       <c r="B17" t="n">
-        <v>78860</v>
+        <v>80239</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427499</v>
+        <v>427650</v>
       </c>
       <c r="R17" t="n">
-        <v>6233792</v>
+        <v>6233855</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,7 +2516,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121471975</v>
+        <v>121471716</v>
       </c>
       <c r="B18" t="n">
         <v>80239</v>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427575</v>
+        <v>427547</v>
       </c>
       <c r="R18" t="n">
-        <v>6233800</v>
+        <v>6233865</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121471951</v>
+        <v>121471993</v>
       </c>
       <c r="B19" t="n">
-        <v>76945</v>
+        <v>91501</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2634,34 +2634,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1342</v>
+        <v>2014</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427762</v>
+        <v>427859</v>
       </c>
       <c r="R19" t="n">
-        <v>6233515</v>
+        <v>6233620</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2702,6 +2705,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2720,10 +2724,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121471955</v>
+        <v>121471704</v>
       </c>
       <c r="B20" t="n">
-        <v>94597</v>
+        <v>96722</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,21 +2740,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2666</v>
+        <v>2606</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,10 +2764,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427741</v>
+        <v>427785</v>
       </c>
       <c r="R20" t="n">
-        <v>6233529</v>
+        <v>6233585</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,12 +2794,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,10 +2826,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121471963</v>
+        <v>121471602</v>
       </c>
       <c r="B21" t="n">
-        <v>94595</v>
+        <v>94596</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2862,10 +2866,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>427520</v>
+        <v>427641</v>
       </c>
       <c r="R21" t="n">
-        <v>6233715</v>
+        <v>6233630</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,12 +2896,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,10 +2928,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121471618</v>
+        <v>121471620</v>
       </c>
       <c r="B22" t="n">
-        <v>96721</v>
+        <v>94585</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,21 +2944,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2968,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427525</v>
+        <v>427625</v>
       </c>
       <c r="R22" t="n">
-        <v>6233838</v>
+        <v>6233894</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471638</v>
+        <v>121471956</v>
       </c>
       <c r="B23" t="n">
-        <v>80239</v>
+        <v>94598</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,21 +3046,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3070,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427638</v>
+        <v>427739</v>
       </c>
       <c r="R23" t="n">
-        <v>6233822</v>
+        <v>6233524</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3096,12 +3100,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,10 +3132,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471631</v>
+        <v>121471628</v>
       </c>
       <c r="B24" t="n">
-        <v>80239</v>
+        <v>96722</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3144,21 +3148,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +3172,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427601</v>
+        <v>427604</v>
       </c>
       <c r="R24" t="n">
-        <v>6233830</v>
+        <v>6233834</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,10 +3234,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471593</v>
+        <v>121471558</v>
       </c>
       <c r="B25" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3242,25 +3246,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3270,10 +3274,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427699</v>
+        <v>427960</v>
       </c>
       <c r="R25" t="n">
-        <v>6233608</v>
+        <v>6233661</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3332,10 +3336,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471965</v>
+        <v>121471521</v>
       </c>
       <c r="B26" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3344,25 +3348,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3372,10 +3376,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427509</v>
+        <v>427794</v>
       </c>
       <c r="R26" t="n">
-        <v>6233731</v>
+        <v>6233483</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3402,12 +3406,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3434,10 +3438,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471952</v>
+        <v>121471610</v>
       </c>
       <c r="B27" t="n">
-        <v>74694</v>
+        <v>80239</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3450,21 +3454,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3478,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427763</v>
+        <v>427487</v>
       </c>
       <c r="R27" t="n">
-        <v>6233529</v>
+        <v>6233816</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3504,12 +3508,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,10 +3540,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121472015</v>
+        <v>121471623</v>
       </c>
       <c r="B28" t="n">
-        <v>74694</v>
+        <v>80239</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,21 +3556,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3580,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427903</v>
+        <v>427579</v>
       </c>
       <c r="R28" t="n">
-        <v>6233639</v>
+        <v>6233850</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3606,12 +3610,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3638,10 +3642,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471643</v>
+        <v>121471990</v>
       </c>
       <c r="B29" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3654,21 +3658,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3678,10 +3682,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427671</v>
+        <v>427765</v>
       </c>
       <c r="R29" t="n">
-        <v>6233821</v>
+        <v>6233765</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3708,12 +3712,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3740,7 +3744,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471715</v>
+        <v>121471520</v>
       </c>
       <c r="B30" t="n">
         <v>80239</v>
@@ -3780,10 +3784,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427445</v>
+        <v>427789</v>
       </c>
       <c r="R30" t="n">
-        <v>6233860</v>
+        <v>6233516</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,10 +3846,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471619</v>
+        <v>121471984</v>
       </c>
       <c r="B31" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3858,21 +3862,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3882,10 +3886,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427624</v>
+        <v>427530</v>
       </c>
       <c r="R31" t="n">
-        <v>6233894</v>
+        <v>6233736</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,12 +3916,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3944,10 +3948,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471710</v>
+        <v>121471951</v>
       </c>
       <c r="B32" t="n">
-        <v>94597</v>
+        <v>76945</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,25 +3960,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2666</v>
+        <v>1342</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,10 +3988,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427448</v>
+        <v>427762</v>
       </c>
       <c r="R32" t="n">
-        <v>6233789</v>
+        <v>6233515</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4014,12 +4018,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4046,10 +4050,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471601</v>
+        <v>121471587</v>
       </c>
       <c r="B33" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4058,25 +4062,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4086,10 +4090,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427688</v>
+        <v>427770</v>
       </c>
       <c r="R33" t="n">
-        <v>6233590</v>
+        <v>6233624</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,10 +4152,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471707</v>
+        <v>121471634</v>
       </c>
       <c r="B34" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4188,10 +4192,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427809</v>
+        <v>427636</v>
       </c>
       <c r="R34" t="n">
-        <v>6233703</v>
+        <v>6233848</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4250,10 +4254,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471979</v>
+        <v>121471646</v>
       </c>
       <c r="B35" t="n">
-        <v>76945</v>
+        <v>94596</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4262,25 +4266,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4290,10 +4294,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427533</v>
+        <v>427692</v>
       </c>
       <c r="R35" t="n">
-        <v>6233765</v>
+        <v>6233796</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,12 +4324,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4352,10 +4356,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471962</v>
+        <v>121471707</v>
       </c>
       <c r="B36" t="n">
-        <v>80239</v>
+        <v>96722</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4368,21 +4372,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4392,10 +4396,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427528</v>
+        <v>427809</v>
       </c>
       <c r="R36" t="n">
-        <v>6233707</v>
+        <v>6233703</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4422,12 +4426,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4454,10 +4458,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471956</v>
+        <v>121471627</v>
       </c>
       <c r="B37" t="n">
-        <v>94597</v>
+        <v>74694</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4470,21 +4474,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2666</v>
+        <v>6439</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4494,10 +4498,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427739</v>
+        <v>427613</v>
       </c>
       <c r="R37" t="n">
-        <v>6233524</v>
+        <v>6233840</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4524,12 +4528,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4556,10 +4560,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471598</v>
+        <v>121471983</v>
       </c>
       <c r="B38" t="n">
-        <v>94595</v>
+        <v>74694</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4572,21 +4576,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2667</v>
+        <v>6439</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4596,10 +4600,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427690</v>
+        <v>427521</v>
       </c>
       <c r="R38" t="n">
-        <v>6233595</v>
+        <v>6233737</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4626,12 +4630,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4658,10 +4662,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471578</v>
+        <v>121471583</v>
       </c>
       <c r="B39" t="n">
-        <v>76945</v>
+        <v>78860</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4670,25 +4674,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1342</v>
+        <v>6459</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4698,10 +4702,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427749</v>
+        <v>427813</v>
       </c>
       <c r="R39" t="n">
-        <v>6233573</v>
+        <v>6233621</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4760,10 +4764,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471584</v>
+        <v>121471985</v>
       </c>
       <c r="B40" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4776,21 +4780,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4800,10 +4804,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427817</v>
+        <v>427558</v>
       </c>
       <c r="R40" t="n">
-        <v>6233621</v>
+        <v>6233768</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,12 +4834,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4862,10 +4866,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471576</v>
+        <v>121471710</v>
       </c>
       <c r="B41" t="n">
-        <v>80252</v>
+        <v>94598</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4874,25 +4878,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1144</v>
+        <v>2666</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4906,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427742</v>
+        <v>427448</v>
       </c>
       <c r="R41" t="n">
-        <v>6233565</v>
+        <v>6233789</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4964,10 +4968,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121472010</v>
+        <v>121471999</v>
       </c>
       <c r="B42" t="n">
-        <v>78984</v>
+        <v>80252</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4976,25 +4980,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6431</v>
+        <v>1144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5004,10 +5008,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427877</v>
+        <v>427916</v>
       </c>
       <c r="R42" t="n">
-        <v>6233615</v>
+        <v>6233634</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5066,10 +5070,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471967</v>
+        <v>121471968</v>
       </c>
       <c r="B43" t="n">
-        <v>80252</v>
+        <v>57367</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5078,25 +5082,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1144</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5106,10 +5110,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427508</v>
+        <v>427512</v>
       </c>
       <c r="R43" t="n">
-        <v>6233737</v>
+        <v>6233745</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5168,10 +5172,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471957</v>
+        <v>121471703</v>
       </c>
       <c r="B44" t="n">
-        <v>94595</v>
+        <v>74694</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5184,21 +5188,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2667</v>
+        <v>6439</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5208,10 +5212,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427731</v>
+        <v>427770</v>
       </c>
       <c r="R44" t="n">
-        <v>6233539</v>
+        <v>6233580</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5238,12 +5242,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5270,10 +5274,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471635</v>
+        <v>121472013</v>
       </c>
       <c r="B45" t="n">
-        <v>78860</v>
+        <v>96722</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5286,21 +5290,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5310,10 +5314,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>427637</v>
+        <v>427882</v>
       </c>
       <c r="R45" t="n">
-        <v>6233845</v>
+        <v>6233622</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5340,12 +5344,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5372,10 +5376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471706</v>
+        <v>121471640</v>
       </c>
       <c r="B46" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5412,10 +5416,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427781</v>
+        <v>427653</v>
       </c>
       <c r="R46" t="n">
-        <v>6233648</v>
+        <v>6233849</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5474,10 +5478,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471627</v>
+        <v>121471584</v>
       </c>
       <c r="B47" t="n">
-        <v>74694</v>
+        <v>96722</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5490,21 +5494,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5514,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427613</v>
+        <v>427817</v>
       </c>
       <c r="R47" t="n">
-        <v>6233840</v>
+        <v>6233621</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5576,10 +5580,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471589</v>
+        <v>121471603</v>
       </c>
       <c r="B48" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5588,25 +5592,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5616,10 +5620,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427804</v>
+        <v>427596</v>
       </c>
       <c r="R48" t="n">
-        <v>6233688</v>
+        <v>6233681</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5678,10 +5682,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121472002</v>
+        <v>121471564</v>
       </c>
       <c r="B49" t="n">
-        <v>94595</v>
+        <v>80252</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5690,25 +5694,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5722,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427909</v>
+        <v>428014</v>
       </c>
       <c r="R49" t="n">
-        <v>6233613</v>
+        <v>6233692</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5748,12 +5752,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5780,10 +5784,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121472012</v>
+        <v>121471995</v>
       </c>
       <c r="B50" t="n">
-        <v>76945</v>
+        <v>78860</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5792,25 +5796,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1342</v>
+        <v>6459</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5820,10 +5824,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427855</v>
+        <v>427856</v>
       </c>
       <c r="R50" t="n">
-        <v>6233612</v>
+        <v>6233613</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5882,10 +5886,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121472014</v>
+        <v>121471608</v>
       </c>
       <c r="B51" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5894,25 +5898,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5922,10 +5926,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427882</v>
+        <v>427566</v>
       </c>
       <c r="R51" t="n">
-        <v>6233622</v>
+        <v>6233756</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5952,12 +5956,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5984,10 +5988,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471966</v>
+        <v>121471650</v>
       </c>
       <c r="B52" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5996,25 +6000,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6024,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427505</v>
+        <v>427737</v>
       </c>
       <c r="R52" t="n">
-        <v>6233740</v>
+        <v>6233784</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6054,12 +6058,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6086,10 +6090,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471557</v>
+        <v>121471574</v>
       </c>
       <c r="B53" t="n">
-        <v>94584</v>
+        <v>80239</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6102,21 +6106,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6126,10 +6130,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427948</v>
+        <v>427838</v>
       </c>
       <c r="R53" t="n">
-        <v>6233643</v>
+        <v>6233582</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6188,10 +6192,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471636</v>
+        <v>121471575</v>
       </c>
       <c r="B54" t="n">
-        <v>80239</v>
+        <v>91109</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6200,25 +6204,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>230185</v>
+        <v>2023</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6228,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427650</v>
+        <v>427837</v>
       </c>
       <c r="R54" t="n">
-        <v>6233855</v>
+        <v>6233582</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6290,10 +6294,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471718</v>
+        <v>121471714</v>
       </c>
       <c r="B55" t="n">
-        <v>80252</v>
+        <v>78404</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6302,25 +6306,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1144</v>
+        <v>924</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6330,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>427584</v>
+        <v>427435</v>
       </c>
       <c r="R55" t="n">
-        <v>6233863</v>
+        <v>6233855</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6392,10 +6396,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471564</v>
+        <v>121471556</v>
       </c>
       <c r="B56" t="n">
-        <v>80252</v>
+        <v>96722</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6404,25 +6408,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6432,10 +6436,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428014</v>
+        <v>427948</v>
       </c>
       <c r="R56" t="n">
-        <v>6233692</v>
+        <v>6233643</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6494,10 +6498,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471620</v>
+        <v>121471557</v>
       </c>
       <c r="B57" t="n">
-        <v>94584</v>
+        <v>94585</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6534,10 +6538,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427625</v>
+        <v>427948</v>
       </c>
       <c r="R57" t="n">
-        <v>6233894</v>
+        <v>6233643</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6596,10 +6600,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471988</v>
+        <v>121471708</v>
       </c>
       <c r="B58" t="n">
-        <v>74522</v>
+        <v>96722</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6612,21 +6616,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6428</v>
+        <v>2606</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6636,10 +6640,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427738</v>
+        <v>427785</v>
       </c>
       <c r="R58" t="n">
-        <v>6233780</v>
+        <v>6233734</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6666,12 +6670,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6698,10 +6702,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121472009</v>
+        <v>121471700</v>
       </c>
       <c r="B59" t="n">
-        <v>94595</v>
+        <v>78984</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6714,21 +6718,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2667</v>
+        <v>6431</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6738,10 +6742,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427877</v>
+        <v>427806</v>
       </c>
       <c r="R59" t="n">
-        <v>6233615</v>
+        <v>6233482</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6768,12 +6772,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6800,10 +6804,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471985</v>
+        <v>121472010</v>
       </c>
       <c r="B60" t="n">
-        <v>80239</v>
+        <v>78984</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6816,21 +6820,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>230185</v>
+        <v>6431</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6840,10 +6844,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427558</v>
+        <v>427877</v>
       </c>
       <c r="R60" t="n">
-        <v>6233768</v>
+        <v>6233615</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6902,10 +6906,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471634</v>
+        <v>121471965</v>
       </c>
       <c r="B61" t="n">
-        <v>96721</v>
+        <v>76945</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6914,25 +6918,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6942,10 +6946,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427636</v>
+        <v>427509</v>
       </c>
       <c r="R61" t="n">
-        <v>6233848</v>
+        <v>6233731</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6972,12 +6976,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7004,10 +7008,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471641</v>
+        <v>121472011</v>
       </c>
       <c r="B62" t="n">
-        <v>78860</v>
+        <v>76945</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7016,25 +7020,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7044,10 +7048,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427655</v>
+        <v>427874</v>
       </c>
       <c r="R62" t="n">
-        <v>6233850</v>
+        <v>6233615</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7074,12 +7078,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7106,10 +7110,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471629</v>
+        <v>121471590</v>
       </c>
       <c r="B63" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7118,25 +7122,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7146,10 +7150,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427602</v>
+        <v>427753</v>
       </c>
       <c r="R63" t="n">
-        <v>6233832</v>
+        <v>6233666</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7208,10 +7212,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471986</v>
+        <v>121471962</v>
       </c>
       <c r="B64" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7220,41 +7224,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427558</v>
+        <v>427528</v>
       </c>
       <c r="R64" t="n">
-        <v>6233769</v>
+        <v>6233707</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7289,21 +7290,11 @@
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Med Refractohilum pluriseptatum</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG64" t="b">
         <v>0</v>
@@ -7323,10 +7314,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471982</v>
+        <v>121471589</v>
       </c>
       <c r="B65" t="n">
-        <v>76945</v>
+        <v>96722</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7335,25 +7326,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7363,10 +7354,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427516</v>
+        <v>427804</v>
       </c>
       <c r="R65" t="n">
-        <v>6233748</v>
+        <v>6233688</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7393,12 +7384,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7425,10 +7416,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471716</v>
+        <v>121471955</v>
       </c>
       <c r="B66" t="n">
-        <v>80239</v>
+        <v>94598</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7441,21 +7432,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7465,10 +7456,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427547</v>
+        <v>427741</v>
       </c>
       <c r="R66" t="n">
-        <v>6233865</v>
+        <v>6233529</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7495,12 +7486,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7527,10 +7518,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471603</v>
+        <v>121471963</v>
       </c>
       <c r="B67" t="n">
-        <v>80252</v>
+        <v>94596</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7539,25 +7530,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7567,10 +7558,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427596</v>
+        <v>427520</v>
       </c>
       <c r="R67" t="n">
-        <v>6233681</v>
+        <v>6233715</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7597,12 +7588,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7629,10 +7620,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471996</v>
+        <v>121471626</v>
       </c>
       <c r="B68" t="n">
-        <v>80252</v>
+        <v>74694</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7641,25 +7632,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1144</v>
+        <v>6439</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7669,10 +7660,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427855</v>
+        <v>427597</v>
       </c>
       <c r="R68" t="n">
-        <v>6233614</v>
+        <v>6233825</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7699,12 +7690,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7731,10 +7722,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471645</v>
+        <v>121471979</v>
       </c>
       <c r="B69" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7743,25 +7734,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7771,10 +7762,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427702</v>
+        <v>427533</v>
       </c>
       <c r="R69" t="n">
-        <v>6233806</v>
+        <v>6233765</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7801,12 +7792,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7833,10 +7824,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471572</v>
+        <v>121471565</v>
       </c>
       <c r="B70" t="n">
-        <v>96721</v>
+        <v>76945</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7845,25 +7836,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7873,10 +7864,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>427982</v>
+        <v>428016</v>
       </c>
       <c r="R70" t="n">
-        <v>6233642</v>
+        <v>6233689</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7935,10 +7926,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471626</v>
+        <v>121471712</v>
       </c>
       <c r="B71" t="n">
-        <v>74694</v>
+        <v>96722</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7951,21 +7942,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7975,10 +7966,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>427597</v>
+        <v>427439</v>
       </c>
       <c r="R71" t="n">
-        <v>6233825</v>
+        <v>6233838</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8037,7 +8028,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471617</v>
+        <v>121471709</v>
       </c>
       <c r="B72" t="n">
         <v>80239</v>
@@ -8077,10 +8068,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427526</v>
+        <v>427452</v>
       </c>
       <c r="R72" t="n">
-        <v>6233836</v>
+        <v>6233794</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8139,7 +8130,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471560</v>
+        <v>121471581</v>
       </c>
       <c r="B73" t="n">
         <v>80239</v>
@@ -8179,10 +8170,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>428008</v>
+        <v>427820</v>
       </c>
       <c r="R73" t="n">
-        <v>6233671</v>
+        <v>6233599</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8241,10 +8232,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471604</v>
+        <v>121471713</v>
       </c>
       <c r="B74" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8253,25 +8244,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8281,10 +8272,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>427595</v>
+        <v>427438</v>
       </c>
       <c r="R74" t="n">
-        <v>6233781</v>
+        <v>6233852</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8343,10 +8334,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471998</v>
+        <v>121471952</v>
       </c>
       <c r="B75" t="n">
-        <v>76945</v>
+        <v>74694</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8355,25 +8346,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1342</v>
+        <v>6439</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8383,10 +8374,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>427915</v>
+        <v>427763</v>
       </c>
       <c r="R75" t="n">
-        <v>6233632</v>
+        <v>6233529</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8445,10 +8436,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121472013</v>
+        <v>121471609</v>
       </c>
       <c r="B76" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8461,21 +8452,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8485,10 +8476,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427882</v>
+        <v>427543</v>
       </c>
       <c r="R76" t="n">
-        <v>6233622</v>
+        <v>6233756</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8515,12 +8506,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8547,10 +8538,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121472003</v>
+        <v>121471720</v>
       </c>
       <c r="B77" t="n">
-        <v>79015</v>
+        <v>80239</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8559,23 +8550,27 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>132</v>
+        <v>230185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liten lundlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bacidina phacodes/tarandina</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
@@ -8583,10 +8578,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427911</v>
+        <v>427595</v>
       </c>
       <c r="R77" t="n">
-        <v>6233614</v>
+        <v>6233898</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8613,12 +8608,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8645,10 +8640,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471973</v>
+        <v>121471964</v>
       </c>
       <c r="B78" t="n">
-        <v>76945</v>
+        <v>94596</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8657,25 +8652,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8685,10 +8680,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427544</v>
+        <v>427511</v>
       </c>
       <c r="R78" t="n">
-        <v>6233811</v>
+        <v>6233739</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8747,10 +8742,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471977</v>
+        <v>121471644</v>
       </c>
       <c r="B79" t="n">
-        <v>96721</v>
+        <v>78860</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8763,21 +8758,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8787,10 +8782,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427533</v>
+        <v>427671</v>
       </c>
       <c r="R79" t="n">
-        <v>6233765</v>
+        <v>6233821</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8817,12 +8812,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8849,10 +8844,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471628</v>
+        <v>121471578</v>
       </c>
       <c r="B80" t="n">
-        <v>96721</v>
+        <v>76945</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8861,25 +8856,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8889,10 +8884,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427604</v>
+        <v>427749</v>
       </c>
       <c r="R80" t="n">
-        <v>6233834</v>
+        <v>6233573</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8951,10 +8946,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471581</v>
+        <v>121471966</v>
       </c>
       <c r="B81" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8963,25 +8958,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8991,10 +8986,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427820</v>
+        <v>427505</v>
       </c>
       <c r="R81" t="n">
-        <v>6233599</v>
+        <v>6233740</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9021,12 +9016,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9053,10 +9048,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471650</v>
+        <v>121472009</v>
       </c>
       <c r="B82" t="n">
-        <v>80239</v>
+        <v>94596</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9069,21 +9064,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9093,10 +9088,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427737</v>
+        <v>427877</v>
       </c>
       <c r="R82" t="n">
-        <v>6233784</v>
+        <v>6233615</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9123,12 +9118,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9155,10 +9150,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471704</v>
+        <v>121471957</v>
       </c>
       <c r="B83" t="n">
-        <v>96721</v>
+        <v>94596</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9171,21 +9166,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9195,10 +9190,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427785</v>
+        <v>427731</v>
       </c>
       <c r="R83" t="n">
-        <v>6233585</v>
+        <v>6233539</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9225,12 +9220,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9257,10 +9252,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471610</v>
+        <v>121472003</v>
       </c>
       <c r="B84" t="n">
-        <v>80239</v>
+        <v>79015</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9269,27 +9264,23 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>230185</v>
+        <v>132</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Liten lundlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Bacidina phacodes/tarandina</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9297,10 +9288,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427487</v>
+        <v>427911</v>
       </c>
       <c r="R84" t="n">
-        <v>6233816</v>
+        <v>6233614</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9327,12 +9318,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9359,7 +9350,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471720</v>
+        <v>121471645</v>
       </c>
       <c r="B85" t="n">
         <v>80239</v>
@@ -9399,10 +9390,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427595</v>
+        <v>427702</v>
       </c>
       <c r="R85" t="n">
-        <v>6233898</v>
+        <v>6233806</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9461,10 +9452,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471583</v>
+        <v>121471617</v>
       </c>
       <c r="B86" t="n">
-        <v>78860</v>
+        <v>80239</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9477,21 +9468,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9501,10 +9492,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427813</v>
+        <v>427526</v>
       </c>
       <c r="R86" t="n">
-        <v>6233621</v>
+        <v>6233836</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9563,10 +9554,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471596</v>
+        <v>121471604</v>
       </c>
       <c r="B87" t="n">
-        <v>74696</v>
+        <v>80239</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9579,21 +9570,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>306</v>
+        <v>230185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9603,10 +9594,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427686</v>
+        <v>427595</v>
       </c>
       <c r="R87" t="n">
-        <v>6233621</v>
+        <v>6233781</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9665,10 +9656,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471637</v>
+        <v>121471647</v>
       </c>
       <c r="B88" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9705,10 +9696,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427638</v>
+        <v>427720</v>
       </c>
       <c r="R88" t="n">
-        <v>6233822</v>
+        <v>6233787</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9767,10 +9758,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471621</v>
+        <v>121471651</v>
       </c>
       <c r="B89" t="n">
-        <v>96721</v>
+        <v>78860</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9783,21 +9774,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9807,10 +9798,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427607</v>
+        <v>427737</v>
       </c>
       <c r="R89" t="n">
-        <v>6233875</v>
+        <v>6233789</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9869,10 +9860,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471702</v>
+        <v>121471592</v>
       </c>
       <c r="B90" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9885,21 +9876,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9909,10 +9900,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427811</v>
+        <v>427703</v>
       </c>
       <c r="R90" t="n">
-        <v>6233480</v>
+        <v>6233616</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9971,10 +9962,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471995</v>
+        <v>121471607</v>
       </c>
       <c r="B91" t="n">
-        <v>78860</v>
+        <v>80239</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9987,21 +9978,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10011,10 +10002,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427856</v>
+        <v>427582</v>
       </c>
       <c r="R91" t="n">
-        <v>6233613</v>
+        <v>6233752</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10041,12 +10032,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10073,10 +10064,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121472007</v>
+        <v>121471580</v>
       </c>
       <c r="B92" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10085,25 +10076,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10113,10 +10104,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427892</v>
+        <v>427804</v>
       </c>
       <c r="R92" t="n">
-        <v>6233623</v>
+        <v>6233576</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10143,12 +10134,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10175,10 +10166,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121472000</v>
+        <v>121471631</v>
       </c>
       <c r="B93" t="n">
-        <v>74694</v>
+        <v>80239</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10191,21 +10182,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10215,10 +10206,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427926</v>
+        <v>427601</v>
       </c>
       <c r="R93" t="n">
-        <v>6233617</v>
+        <v>6233830</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10245,12 +10236,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10277,10 +10268,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471562</v>
+        <v>121471614</v>
       </c>
       <c r="B94" t="n">
-        <v>80575</v>
+        <v>80239</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10289,25 +10280,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1182</v>
+        <v>230185</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10317,10 +10308,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>428000</v>
+        <v>427475</v>
       </c>
       <c r="R94" t="n">
-        <v>6233692</v>
+        <v>6233836</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10379,7 +10370,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471559</v>
+        <v>121471973</v>
       </c>
       <c r="B95" t="n">
         <v>76945</v>
@@ -10419,10 +10410,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427960</v>
+        <v>427544</v>
       </c>
       <c r="R95" t="n">
-        <v>6233661</v>
+        <v>6233811</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10449,12 +10440,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10481,10 +10472,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471591</v>
+        <v>121471599</v>
       </c>
       <c r="B96" t="n">
-        <v>80239</v>
+        <v>94598</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10497,21 +10488,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10521,10 +10512,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427724</v>
+        <v>427685</v>
       </c>
       <c r="R96" t="n">
-        <v>6233617</v>
+        <v>6233593</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10583,10 +10574,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471607</v>
+        <v>121471706</v>
       </c>
       <c r="B97" t="n">
-        <v>80239</v>
+        <v>96722</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10599,21 +10590,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10623,10 +10614,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427582</v>
+        <v>427781</v>
       </c>
       <c r="R97" t="n">
-        <v>6233752</v>
+        <v>6233648</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10685,10 +10676,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471558</v>
+        <v>121471619</v>
       </c>
       <c r="B98" t="n">
-        <v>80252</v>
+        <v>96722</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10697,25 +10688,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10725,10 +10716,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427960</v>
+        <v>427624</v>
       </c>
       <c r="R98" t="n">
-        <v>6233661</v>
+        <v>6233894</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10787,10 +10778,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471640</v>
+        <v>121472007</v>
       </c>
       <c r="B99" t="n">
-        <v>96721</v>
+        <v>80252</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10799,25 +10790,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10827,10 +10818,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427653</v>
+        <v>427892</v>
       </c>
       <c r="R99" t="n">
-        <v>6233849</v>
+        <v>6233623</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10857,12 +10848,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10889,10 +10880,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471671</v>
+        <v>121471586</v>
       </c>
       <c r="B100" t="n">
-        <v>105755</v>
+        <v>80252</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10901,25 +10892,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220785</v>
+        <v>1144</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10929,10 +10920,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427912</v>
+        <v>427748</v>
       </c>
       <c r="R100" t="n">
-        <v>6233611</v>
+        <v>6233622</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10991,10 +10982,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471642</v>
+        <v>121471585</v>
       </c>
       <c r="B101" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11003,25 +10994,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11031,10 +11022,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>427654</v>
+        <v>427748</v>
       </c>
       <c r="R101" t="n">
-        <v>6233848</v>
+        <v>6233622</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11093,7 +11084,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471709</v>
+        <v>121471954</v>
       </c>
       <c r="B102" t="n">
         <v>80239</v>
@@ -11133,10 +11124,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427452</v>
+        <v>427742</v>
       </c>
       <c r="R102" t="n">
-        <v>6233794</v>
+        <v>6233542</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11163,12 +11154,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11195,10 +11186,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471622</v>
+        <v>121471719</v>
       </c>
       <c r="B103" t="n">
-        <v>74694</v>
+        <v>76945</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11207,25 +11198,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6439</v>
+        <v>1342</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11235,10 +11226,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427623</v>
+        <v>427583</v>
       </c>
       <c r="R103" t="n">
-        <v>6233865</v>
+        <v>6233861</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11297,10 +11288,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471651</v>
+        <v>121472002</v>
       </c>
       <c r="B104" t="n">
-        <v>78860</v>
+        <v>94596</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11313,21 +11304,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6459</v>
+        <v>2667</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11337,10 +11328,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427737</v>
+        <v>427909</v>
       </c>
       <c r="R104" t="n">
-        <v>6233789</v>
+        <v>6233613</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11367,12 +11358,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11399,10 +11390,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121472011</v>
+        <v>121471563</v>
       </c>
       <c r="B105" t="n">
-        <v>76945</v>
+        <v>96722</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11411,25 +11402,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11439,10 +11430,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427874</v>
+        <v>428012</v>
       </c>
       <c r="R105" t="n">
-        <v>6233615</v>
+        <v>6233689</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11469,12 +11460,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11501,10 +11492,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471632</v>
+        <v>121471953</v>
       </c>
       <c r="B106" t="n">
-        <v>80239</v>
+        <v>96722</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11517,21 +11508,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11541,10 +11532,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427615</v>
+        <v>427769</v>
       </c>
       <c r="R106" t="n">
-        <v>6233825</v>
+        <v>6233529</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11571,12 +11562,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11603,10 +11594,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471580</v>
+        <v>121472001</v>
       </c>
       <c r="B107" t="n">
-        <v>80239</v>
+        <v>94606</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11619,21 +11610,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>230185</v>
+        <v>1080</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11643,10 +11634,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427804</v>
+        <v>427908</v>
       </c>
       <c r="R107" t="n">
-        <v>6233576</v>
+        <v>6233617</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11673,12 +11664,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11705,10 +11696,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471520</v>
+        <v>121471986</v>
       </c>
       <c r="B108" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11717,38 +11708,41 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>427789</v>
+        <v>427558</v>
       </c>
       <c r="R108" t="n">
-        <v>6233516</v>
+        <v>6233769</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11775,12 +11769,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>Med Refractohilum pluriseptatum</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11788,6 +11787,11 @@
       </c>
       <c r="AE108" t="b">
         <v>0</v>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG108" t="b">
         <v>0</v>
@@ -11807,10 +11811,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471714</v>
+        <v>121471974</v>
       </c>
       <c r="B109" t="n">
-        <v>78404</v>
+        <v>90505</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11819,25 +11823,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>924</v>
+        <v>1067</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11847,10 +11851,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>427435</v>
+        <v>427554</v>
       </c>
       <c r="R109" t="n">
-        <v>6233855</v>
+        <v>6233803</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11877,12 +11881,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11909,10 +11913,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471586</v>
+        <v>121471976</v>
       </c>
       <c r="B110" t="n">
-        <v>80252</v>
+        <v>96722</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11921,25 +11925,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11949,10 +11953,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427748</v>
+        <v>427576</v>
       </c>
       <c r="R110" t="n">
-        <v>6233622</v>
+        <v>6233800</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11979,12 +11983,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12011,10 +12015,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471980</v>
+        <v>121471562</v>
       </c>
       <c r="B111" t="n">
-        <v>80252</v>
+        <v>80575</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12023,25 +12027,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1144</v>
+        <v>1182</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12051,10 +12055,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427532</v>
+        <v>428000</v>
       </c>
       <c r="R111" t="n">
-        <v>6233767</v>
+        <v>6233692</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12081,12 +12085,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12113,10 +12117,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121472016</v>
+        <v>121471632</v>
       </c>
       <c r="B112" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12129,21 +12133,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12153,10 +12157,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427903</v>
+        <v>427615</v>
       </c>
       <c r="R112" t="n">
-        <v>6233640</v>
+        <v>6233825</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12183,12 +12187,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12215,10 +12219,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471990</v>
+        <v>121471998</v>
       </c>
       <c r="B113" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12227,25 +12231,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12255,10 +12259,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427765</v>
+        <v>427915</v>
       </c>
       <c r="R113" t="n">
-        <v>6233765</v>
+        <v>6233632</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12317,10 +12321,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121472001</v>
+        <v>121472012</v>
       </c>
       <c r="B114" t="n">
-        <v>94605</v>
+        <v>76945</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12329,25 +12333,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1080</v>
+        <v>1342</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12357,10 +12361,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427908</v>
+        <v>427855</v>
       </c>
       <c r="R114" t="n">
-        <v>6233617</v>
+        <v>6233612</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12419,10 +12423,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471993</v>
+        <v>121471633</v>
       </c>
       <c r="B115" t="n">
-        <v>91500</v>
+        <v>90505</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12431,41 +12435,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>2014</v>
+        <v>1067</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427859</v>
+        <v>427629</v>
       </c>
       <c r="R115" t="n">
-        <v>6233620</v>
+        <v>6233837</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12492,12 +12493,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12506,7 +12507,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12525,10 +12525,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471984</v>
+        <v>121471596</v>
       </c>
       <c r="B116" t="n">
-        <v>80239</v>
+        <v>74696</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12541,21 +12541,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12565,10 +12565,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427530</v>
+        <v>427686</v>
       </c>
       <c r="R116" t="n">
-        <v>6233736</v>
+        <v>6233621</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12595,12 +12595,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12627,7 +12627,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471999</v>
+        <v>121472014</v>
       </c>
       <c r="B117" t="n">
         <v>80252</v>
@@ -12667,10 +12667,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427916</v>
+        <v>427882</v>
       </c>
       <c r="R117" t="n">
-        <v>6233634</v>
+        <v>6233622</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12729,10 +12729,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471992</v>
+        <v>121472000</v>
       </c>
       <c r="B118" t="n">
-        <v>94584</v>
+        <v>74694</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12745,21 +12745,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2671</v>
+        <v>6439</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12769,10 +12769,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427861</v>
+        <v>427926</v>
       </c>
       <c r="R118" t="n">
-        <v>6233620</v>
+        <v>6233617</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12831,10 +12831,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471592</v>
+        <v>121472006</v>
       </c>
       <c r="B119" t="n">
-        <v>80239</v>
+        <v>76945</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12843,25 +12843,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12871,10 +12871,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427703</v>
+        <v>427892</v>
       </c>
       <c r="R119" t="n">
-        <v>6233616</v>
+        <v>6233623</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12933,10 +12933,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471623</v>
+        <v>121471977</v>
       </c>
       <c r="B120" t="n">
-        <v>80239</v>
+        <v>96722</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12949,21 +12949,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12973,10 +12973,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427579</v>
+        <v>427533</v>
       </c>
       <c r="R120" t="n">
-        <v>6233850</v>
+        <v>6233765</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13003,12 +13003,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13035,10 +13035,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471575</v>
+        <v>121471992</v>
       </c>
       <c r="B121" t="n">
-        <v>91108</v>
+        <v>94585</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13047,25 +13047,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2023</v>
+        <v>2671</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13075,10 +13075,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427837</v>
+        <v>427861</v>
       </c>
       <c r="R121" t="n">
-        <v>6233582</v>
+        <v>6233620</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13137,10 +13137,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471648</v>
+        <v>121471978</v>
       </c>
       <c r="B122" t="n">
-        <v>76945</v>
+        <v>94596</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13149,25 +13149,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13177,10 +13177,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427721</v>
+        <v>427533</v>
       </c>
       <c r="R122" t="n">
-        <v>6233787</v>
+        <v>6233765</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13207,12 +13207,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13239,10 +13239,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471644</v>
+        <v>121471629</v>
       </c>
       <c r="B123" t="n">
-        <v>78860</v>
+        <v>80252</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13251,25 +13251,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6459</v>
+        <v>1144</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13279,10 +13279,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427671</v>
+        <v>427602</v>
       </c>
       <c r="R123" t="n">
-        <v>6233821</v>
+        <v>6233832</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13341,10 +13341,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471585</v>
+        <v>121471622</v>
       </c>
       <c r="B124" t="n">
-        <v>76945</v>
+        <v>74694</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13353,25 +13353,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1342</v>
+        <v>6439</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13381,10 +13381,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427748</v>
+        <v>427623</v>
       </c>
       <c r="R124" t="n">
-        <v>6233622</v>
+        <v>6233865</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13443,7 +13443,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471608</v>
+        <v>121471642</v>
       </c>
       <c r="B125" t="n">
         <v>80239</v>
@@ -13483,10 +13483,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427566</v>
+        <v>427654</v>
       </c>
       <c r="R125" t="n">
-        <v>6233756</v>
+        <v>6233848</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13545,7 +13545,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471574</v>
+        <v>121471591</v>
       </c>
       <c r="B126" t="n">
         <v>80239</v>
@@ -13585,10 +13585,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427838</v>
+        <v>427724</v>
       </c>
       <c r="R126" t="n">
-        <v>6233582</v>
+        <v>6233617</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13647,7 +13647,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471590</v>
+        <v>121471959</v>
       </c>
       <c r="B127" t="n">
         <v>80239</v>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427753</v>
+        <v>427734</v>
       </c>
       <c r="R127" t="n">
-        <v>6233666</v>
+        <v>6233532</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13717,12 +13717,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13749,10 +13749,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471961</v>
+        <v>121471705</v>
       </c>
       <c r="B128" t="n">
-        <v>94595</v>
+        <v>80239</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13765,21 +13765,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13789,10 +13789,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427615</v>
+        <v>427753</v>
       </c>
       <c r="R128" t="n">
-        <v>6233649</v>
+        <v>6233606</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13819,12 +13819,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13851,10 +13851,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471974</v>
+        <v>121471560</v>
       </c>
       <c r="B129" t="n">
-        <v>90504</v>
+        <v>80239</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13863,25 +13863,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13891,10 +13891,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>427554</v>
+        <v>428008</v>
       </c>
       <c r="R129" t="n">
-        <v>6233803</v>
+        <v>6233671</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13921,12 +13921,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13953,10 +13953,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471563</v>
+        <v>121471601</v>
       </c>
       <c r="B130" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13969,21 +13969,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13993,10 +13993,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>428012</v>
+        <v>427688</v>
       </c>
       <c r="R130" t="n">
-        <v>6233689</v>
+        <v>6233590</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14055,10 +14055,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471556</v>
+        <v>121471635</v>
       </c>
       <c r="B131" t="n">
-        <v>96721</v>
+        <v>78860</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14071,21 +14071,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14095,10 +14095,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427948</v>
+        <v>427637</v>
       </c>
       <c r="R131" t="n">
-        <v>6233643</v>
+        <v>6233845</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14157,10 +14157,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471633</v>
+        <v>121471572</v>
       </c>
       <c r="B132" t="n">
-        <v>90504</v>
+        <v>96722</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14169,25 +14169,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1067</v>
+        <v>2606</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14197,10 +14197,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427629</v>
+        <v>427982</v>
       </c>
       <c r="R132" t="n">
-        <v>6233837</v>
+        <v>6233642</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14259,10 +14259,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471565</v>
+        <v>121471961</v>
       </c>
       <c r="B133" t="n">
-        <v>76945</v>
+        <v>94596</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14271,25 +14271,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14299,10 +14299,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>428016</v>
+        <v>427615</v>
       </c>
       <c r="R133" t="n">
-        <v>6233689</v>
+        <v>6233649</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14329,12 +14329,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14361,10 +14361,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471719</v>
+        <v>121471718</v>
       </c>
       <c r="B134" t="n">
-        <v>76945</v>
+        <v>80252</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14373,25 +14373,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14401,10 +14401,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427583</v>
+        <v>427584</v>
       </c>
       <c r="R134" t="n">
-        <v>6233861</v>
+        <v>6233863</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14463,10 +14463,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471614</v>
+        <v>121471988</v>
       </c>
       <c r="B135" t="n">
-        <v>80239</v>
+        <v>74522</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14479,21 +14479,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14503,10 +14503,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427475</v>
+        <v>427738</v>
       </c>
       <c r="R135" t="n">
-        <v>6233836</v>
+        <v>6233780</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14533,12 +14533,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14565,10 +14565,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471597</v>
+        <v>121472015</v>
       </c>
       <c r="B136" t="n">
-        <v>80239</v>
+        <v>74694</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14581,21 +14581,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14605,10 +14605,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427693</v>
+        <v>427903</v>
       </c>
       <c r="R136" t="n">
-        <v>6233604</v>
+        <v>6233639</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14635,12 +14635,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14667,10 +14667,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471587</v>
+        <v>121471648</v>
       </c>
       <c r="B137" t="n">
-        <v>80252</v>
+        <v>76945</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14679,25 +14679,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14707,10 +14707,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427770</v>
+        <v>427721</v>
       </c>
       <c r="R137" t="n">
-        <v>6233624</v>
+        <v>6233787</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14769,10 +14769,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471602</v>
+        <v>121471630</v>
       </c>
       <c r="B138" t="n">
-        <v>94595</v>
+        <v>76945</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14781,25 +14781,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14809,10 +14809,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427641</v>
+        <v>427604</v>
       </c>
       <c r="R138" t="n">
-        <v>6233630</v>
+        <v>6233829</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14871,10 +14871,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471647</v>
+        <v>121472016</v>
       </c>
       <c r="B139" t="n">
-        <v>96721</v>
+        <v>96722</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>427720</v>
+        <v>427903</v>
       </c>
       <c r="R139" t="n">
-        <v>6233787</v>
+        <v>6233640</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14941,12 +14941,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14973,10 +14973,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471599</v>
+        <v>121471618</v>
       </c>
       <c r="B140" t="n">
-        <v>94597</v>
+        <v>96722</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14989,21 +14989,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2666</v>
+        <v>2606</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15013,10 +15013,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>427685</v>
+        <v>427525</v>
       </c>
       <c r="R140" t="n">
-        <v>6233593</v>
+        <v>6233838</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15075,10 +15075,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471521</v>
+        <v>121471643</v>
       </c>
       <c r="B141" t="n">
-        <v>80239</v>
+        <v>96722</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15091,21 +15091,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15115,10 +15115,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>427794</v>
+        <v>427671</v>
       </c>
       <c r="R141" t="n">
-        <v>6233483</v>
+        <v>6233821</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15177,10 +15177,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471609</v>
+        <v>121471960</v>
       </c>
       <c r="B142" t="n">
-        <v>80239</v>
+        <v>94585</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15193,21 +15193,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15217,10 +15217,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>427543</v>
+        <v>427734</v>
       </c>
       <c r="R142" t="n">
-        <v>6233756</v>
+        <v>6233532</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15247,12 +15247,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15279,10 +15279,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471600</v>
+        <v>121472004</v>
       </c>
       <c r="B143" t="n">
-        <v>94595</v>
+        <v>80239</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15295,21 +15295,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15319,10 +15319,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>427698</v>
+        <v>427892</v>
       </c>
       <c r="R143" t="n">
-        <v>6233566</v>
+        <v>6233623</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15381,10 +15381,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471649</v>
+        <v>121471597</v>
       </c>
       <c r="B144" t="n">
-        <v>80252</v>
+        <v>80239</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15393,25 +15393,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15421,10 +15421,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>427720</v>
+        <v>427693</v>
       </c>
       <c r="R144" t="n">
-        <v>6233787</v>
+        <v>6233604</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15483,10 +15483,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121472006</v>
+        <v>121471593</v>
       </c>
       <c r="B145" t="n">
-        <v>76945</v>
+        <v>80239</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15495,25 +15495,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15523,10 +15523,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427892</v>
+        <v>427699</v>
       </c>
       <c r="R145" t="n">
-        <v>6233623</v>
+        <v>6233608</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15553,12 +15553,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15585,10 +15585,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121472004</v>
+        <v>121471980</v>
       </c>
       <c r="B146" t="n">
-        <v>80239</v>
+        <v>80252</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15597,25 +15597,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15625,10 +15625,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427892</v>
+        <v>427532</v>
       </c>
       <c r="R146" t="n">
-        <v>6233623</v>
+        <v>6233767</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15687,7 +15687,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471959</v>
+        <v>121471612</v>
       </c>
       <c r="B147" t="n">
         <v>80239</v>
@@ -15727,10 +15727,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427734</v>
+        <v>427466</v>
       </c>
       <c r="R147" t="n">
-        <v>6233532</v>
+        <v>6233828</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15757,12 +15757,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15789,7 +15789,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471612</v>
+        <v>121471975</v>
       </c>
       <c r="B148" t="n">
         <v>80239</v>
@@ -15829,10 +15829,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427466</v>
+        <v>427575</v>
       </c>
       <c r="R148" t="n">
-        <v>6233828</v>
+        <v>6233800</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15859,12 +15859,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15891,10 +15891,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471712</v>
+        <v>121471715</v>
       </c>
       <c r="B149" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15907,21 +15907,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15931,10 +15931,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>427439</v>
+        <v>427445</v>
       </c>
       <c r="R149" t="n">
-        <v>6233838</v>
+        <v>6233860</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15993,10 +15993,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471708</v>
+        <v>121471638</v>
       </c>
       <c r="B150" t="n">
-        <v>96721</v>
+        <v>80239</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16009,21 +16009,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16033,10 +16033,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>427785</v>
+        <v>427638</v>
       </c>
       <c r="R150" t="n">
-        <v>6233734</v>
+        <v>6233822</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16095,10 +16095,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471705</v>
+        <v>121471671</v>
       </c>
       <c r="B151" t="n">
-        <v>80239</v>
+        <v>105756</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16107,25 +16107,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>230185</v>
+        <v>220785</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16135,10 +16135,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>427753</v>
+        <v>427912</v>
       </c>
       <c r="R151" t="n">
-        <v>6233606</v>
+        <v>6233611</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16197,10 +16197,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471630</v>
+        <v>121471621</v>
       </c>
       <c r="B152" t="n">
-        <v>76945</v>
+        <v>96722</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16209,25 +16209,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16237,10 +16237,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>427604</v>
+        <v>427607</v>
       </c>
       <c r="R152" t="n">
-        <v>6233829</v>
+        <v>6233875</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16299,10 +16299,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471713</v>
+        <v>121471702</v>
       </c>
       <c r="B153" t="n">
-        <v>76945</v>
+        <v>96722</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16311,25 +16311,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16339,10 +16339,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>427438</v>
+        <v>427811</v>
       </c>
       <c r="R153" t="n">
-        <v>6233852</v>
+        <v>6233480</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16401,10 +16401,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471577</v>
+        <v>121471637</v>
       </c>
       <c r="B154" t="n">
-        <v>94595</v>
+        <v>96722</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16417,21 +16417,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16441,10 +16441,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>427749</v>
+        <v>427638</v>
       </c>
       <c r="R154" t="n">
-        <v>6233572</v>
+        <v>6233822</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16503,10 +16503,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471700</v>
+        <v>121471559</v>
       </c>
       <c r="B155" t="n">
-        <v>78984</v>
+        <v>76945</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16515,25 +16515,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6431</v>
+        <v>1342</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16543,10 +16543,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>427806</v>
+        <v>427960</v>
       </c>
       <c r="R155" t="n">
-        <v>6233482</v>
+        <v>6233661</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16605,10 +16605,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471561</v>
+        <v>121471982</v>
       </c>
       <c r="B156" t="n">
-        <v>96721</v>
+        <v>76945</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16617,25 +16617,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16645,10 +16645,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>427999</v>
+        <v>427516</v>
       </c>
       <c r="R156" t="n">
-        <v>6233695</v>
+        <v>6233748</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16675,12 +16675,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16707,10 +16707,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471703</v>
+        <v>121471996</v>
       </c>
       <c r="B157" t="n">
-        <v>74694</v>
+        <v>80252</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16719,25 +16719,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16747,10 +16747,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>427770</v>
+        <v>427855</v>
       </c>
       <c r="R157" t="n">
-        <v>6233580</v>
+        <v>6233614</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16777,12 +16777,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16809,10 +16809,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471968</v>
+        <v>121471649</v>
       </c>
       <c r="B158" t="n">
-        <v>57367</v>
+        <v>80252</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16821,25 +16821,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100049</v>
+        <v>1144</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16849,10 +16849,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>427512</v>
+        <v>427720</v>
       </c>
       <c r="R158" t="n">
-        <v>6233745</v>
+        <v>6233787</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16879,12 +16879,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16911,10 +16911,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471960</v>
+        <v>121471624</v>
       </c>
       <c r="B159" t="n">
-        <v>94584</v>
+        <v>74560</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16923,25 +16923,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2671</v>
+        <v>1116</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16951,10 +16951,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>427734</v>
+        <v>427594</v>
       </c>
       <c r="R159" t="n">
-        <v>6233532</v>
+        <v>6233828</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16981,12 +16981,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17013,10 +17013,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471983</v>
+        <v>121471576</v>
       </c>
       <c r="B160" t="n">
-        <v>74694</v>
+        <v>80252</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17025,25 +17025,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17053,10 +17053,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>427521</v>
+        <v>427742</v>
       </c>
       <c r="R160" t="n">
-        <v>6233737</v>
+        <v>6233565</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17083,12 +17083,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17115,10 +17115,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471953</v>
+        <v>121471971</v>
       </c>
       <c r="B161" t="n">
-        <v>96721</v>
+        <v>78860</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17131,21 +17131,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17155,10 +17155,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>427769</v>
+        <v>427499</v>
       </c>
       <c r="R161" t="n">
-        <v>6233529</v>
+        <v>6233792</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471598</v>
+        <v>121471635</v>
       </c>
       <c r="B11" t="n">
-        <v>94596</v>
+        <v>78863</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2667</v>
+        <v>6459</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427690</v>
+        <v>427637</v>
       </c>
       <c r="R11" t="n">
-        <v>6233595</v>
+        <v>6233845</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471561</v>
+        <v>121471645</v>
       </c>
       <c r="B12" t="n">
-        <v>96722</v>
+        <v>80242</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427999</v>
+        <v>427702</v>
       </c>
       <c r="R12" t="n">
-        <v>6233695</v>
+        <v>6233806</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471577</v>
+        <v>121471642</v>
       </c>
       <c r="B13" t="n">
-        <v>94596</v>
+        <v>80242</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427749</v>
+        <v>427654</v>
       </c>
       <c r="R13" t="n">
-        <v>6233572</v>
+        <v>6233848</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471600</v>
+        <v>121471574</v>
       </c>
       <c r="B14" t="n">
-        <v>94596</v>
+        <v>80242</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427698</v>
+        <v>427838</v>
       </c>
       <c r="R14" t="n">
-        <v>6233566</v>
+        <v>6233582</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471641</v>
+        <v>121471705</v>
       </c>
       <c r="B15" t="n">
-        <v>78860</v>
+        <v>80242</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427655</v>
+        <v>427753</v>
       </c>
       <c r="R15" t="n">
-        <v>6233850</v>
+        <v>6233606</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121471967</v>
+        <v>121471599</v>
       </c>
       <c r="B16" t="n">
-        <v>80252</v>
+        <v>94601</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2324,25 +2324,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1144</v>
+        <v>2666</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427508</v>
+        <v>427685</v>
       </c>
       <c r="R16" t="n">
-        <v>6233737</v>
+        <v>6233593</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121471636</v>
+        <v>121471961</v>
       </c>
       <c r="B17" t="n">
-        <v>80239</v>
+        <v>94599</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427650</v>
+        <v>427615</v>
       </c>
       <c r="R17" t="n">
-        <v>6233855</v>
+        <v>6233649</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121471716</v>
+        <v>121471965</v>
       </c>
       <c r="B18" t="n">
-        <v>80239</v>
+        <v>76948</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427547</v>
+        <v>427509</v>
       </c>
       <c r="R18" t="n">
-        <v>6233865</v>
+        <v>6233731</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121471993</v>
+        <v>121471955</v>
       </c>
       <c r="B19" t="n">
-        <v>91501</v>
+        <v>94601</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,41 +2630,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2014</v>
+        <v>2666</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427859</v>
+        <v>427741</v>
       </c>
       <c r="R19" t="n">
-        <v>6233620</v>
+        <v>6233529</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2702,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2724,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121471704</v>
+        <v>121471585</v>
       </c>
       <c r="B20" t="n">
-        <v>96722</v>
+        <v>76948</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,25 +2732,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2764,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427785</v>
+        <v>427748</v>
       </c>
       <c r="R20" t="n">
-        <v>6233585</v>
+        <v>6233622</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2826,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121471602</v>
+        <v>121471584</v>
       </c>
       <c r="B21" t="n">
-        <v>94596</v>
+        <v>96725</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2842,21 +2838,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2866,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>427641</v>
+        <v>427817</v>
       </c>
       <c r="R21" t="n">
-        <v>6233630</v>
+        <v>6233621</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2928,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121471620</v>
+        <v>121472011</v>
       </c>
       <c r="B22" t="n">
-        <v>94585</v>
+        <v>76948</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,25 +2936,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2968,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427625</v>
+        <v>427874</v>
       </c>
       <c r="R22" t="n">
-        <v>6233894</v>
+        <v>6233615</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2998,12 +2994,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3030,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471956</v>
+        <v>121471671</v>
       </c>
       <c r="B23" t="n">
-        <v>94598</v>
+        <v>105759</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,25 +3038,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2666</v>
+        <v>220785</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3070,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427739</v>
+        <v>427912</v>
       </c>
       <c r="R23" t="n">
-        <v>6233524</v>
+        <v>6233611</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,12 +3096,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3132,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471628</v>
+        <v>121471647</v>
       </c>
       <c r="B24" t="n">
-        <v>96722</v>
+        <v>96725</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3172,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427604</v>
+        <v>427720</v>
       </c>
       <c r="R24" t="n">
-        <v>6233834</v>
+        <v>6233787</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3234,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471558</v>
+        <v>121471637</v>
       </c>
       <c r="B25" t="n">
-        <v>80252</v>
+        <v>96725</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3246,25 +3242,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3274,10 +3270,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427960</v>
+        <v>427638</v>
       </c>
       <c r="R25" t="n">
-        <v>6233661</v>
+        <v>6233822</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3336,10 +3332,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471521</v>
+        <v>121471982</v>
       </c>
       <c r="B26" t="n">
-        <v>80239</v>
+        <v>76948</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3348,25 +3344,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3376,10 +3372,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427794</v>
+        <v>427516</v>
       </c>
       <c r="R26" t="n">
-        <v>6233483</v>
+        <v>6233748</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3406,12 +3402,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3438,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471610</v>
+        <v>121471626</v>
       </c>
       <c r="B27" t="n">
-        <v>80239</v>
+        <v>74697</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3454,21 +3450,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3478,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427487</v>
+        <v>427597</v>
       </c>
       <c r="R27" t="n">
-        <v>6233816</v>
+        <v>6233825</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3540,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471623</v>
+        <v>121471996</v>
       </c>
       <c r="B28" t="n">
-        <v>80239</v>
+        <v>80255</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,25 +3548,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3580,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427579</v>
+        <v>427855</v>
       </c>
       <c r="R28" t="n">
-        <v>6233850</v>
+        <v>6233614</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3610,12 +3606,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3642,10 +3638,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471990</v>
+        <v>121471624</v>
       </c>
       <c r="B29" t="n">
-        <v>80239</v>
+        <v>74563</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3654,25 +3650,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230185</v>
+        <v>1116</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3682,10 +3678,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427765</v>
+        <v>427594</v>
       </c>
       <c r="R29" t="n">
-        <v>6233765</v>
+        <v>6233828</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3712,12 +3708,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3744,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471520</v>
+        <v>121471979</v>
       </c>
       <c r="B30" t="n">
-        <v>80239</v>
+        <v>76948</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3756,25 +3752,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3784,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427789</v>
+        <v>427533</v>
       </c>
       <c r="R30" t="n">
-        <v>6233516</v>
+        <v>6233765</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3814,12 +3810,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3846,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471984</v>
+        <v>121471628</v>
       </c>
       <c r="B31" t="n">
-        <v>80239</v>
+        <v>96725</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3862,21 +3858,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3886,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427530</v>
+        <v>427604</v>
       </c>
       <c r="R31" t="n">
-        <v>6233736</v>
+        <v>6233834</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3916,12 +3912,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3948,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471951</v>
+        <v>121471583</v>
       </c>
       <c r="B32" t="n">
-        <v>76945</v>
+        <v>78863</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3960,25 +3956,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1342</v>
+        <v>6459</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3988,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427762</v>
+        <v>427813</v>
       </c>
       <c r="R32" t="n">
-        <v>6233515</v>
+        <v>6233621</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4018,12 +4014,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4050,10 +4046,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471587</v>
+        <v>121471586</v>
       </c>
       <c r="B33" t="n">
-        <v>80252</v>
+        <v>80255</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4090,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427770</v>
+        <v>427748</v>
       </c>
       <c r="R33" t="n">
-        <v>6233624</v>
+        <v>6233622</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4152,10 +4148,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471634</v>
+        <v>121471986</v>
       </c>
       <c r="B34" t="n">
-        <v>96722</v>
+        <v>80255</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4164,38 +4160,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427636</v>
+        <v>427558</v>
       </c>
       <c r="R34" t="n">
-        <v>6233848</v>
+        <v>6233769</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4222,12 +4221,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Med Refractohilum pluriseptatum</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4235,6 +4239,11 @@
       </c>
       <c r="AE34" t="b">
         <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4254,10 +4263,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471646</v>
+        <v>121471581</v>
       </c>
       <c r="B35" t="n">
-        <v>94596</v>
+        <v>80242</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4270,21 +4279,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4294,10 +4303,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427692</v>
+        <v>427820</v>
       </c>
       <c r="R35" t="n">
-        <v>6233796</v>
+        <v>6233599</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4356,10 +4365,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471707</v>
+        <v>121471962</v>
       </c>
       <c r="B36" t="n">
-        <v>96722</v>
+        <v>80242</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4372,21 +4381,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4396,10 +4405,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427809</v>
+        <v>427528</v>
       </c>
       <c r="R36" t="n">
-        <v>6233703</v>
+        <v>6233707</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4426,12 +4435,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4458,10 +4467,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471627</v>
+        <v>121471630</v>
       </c>
       <c r="B37" t="n">
-        <v>74694</v>
+        <v>76948</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4470,25 +4479,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6439</v>
+        <v>1342</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4498,10 +4507,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427613</v>
+        <v>427604</v>
       </c>
       <c r="R37" t="n">
-        <v>6233840</v>
+        <v>6233829</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4560,10 +4569,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471983</v>
+        <v>121471951</v>
       </c>
       <c r="B38" t="n">
-        <v>74694</v>
+        <v>76948</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4572,25 +4581,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6439</v>
+        <v>1342</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4600,10 +4609,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427521</v>
+        <v>427762</v>
       </c>
       <c r="R38" t="n">
-        <v>6233737</v>
+        <v>6233515</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4662,10 +4671,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471583</v>
+        <v>121471713</v>
       </c>
       <c r="B39" t="n">
-        <v>78860</v>
+        <v>76948</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4674,25 +4683,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4702,10 +4711,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427813</v>
+        <v>427438</v>
       </c>
       <c r="R39" t="n">
-        <v>6233621</v>
+        <v>6233852</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4764,10 +4773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471985</v>
+        <v>121472000</v>
       </c>
       <c r="B40" t="n">
-        <v>80239</v>
+        <v>74697</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4780,21 +4789,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4804,10 +4813,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427558</v>
+        <v>427926</v>
       </c>
       <c r="R40" t="n">
-        <v>6233768</v>
+        <v>6233617</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4866,10 +4875,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471710</v>
+        <v>121472010</v>
       </c>
       <c r="B41" t="n">
-        <v>94598</v>
+        <v>78987</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4882,21 +4891,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2666</v>
+        <v>6431</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4906,10 +4915,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427448</v>
+        <v>427877</v>
       </c>
       <c r="R41" t="n">
-        <v>6233789</v>
+        <v>6233615</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4936,12 +4945,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4968,10 +4977,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471999</v>
+        <v>121471609</v>
       </c>
       <c r="B42" t="n">
-        <v>80252</v>
+        <v>80242</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4980,25 +4989,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5008,10 +5017,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427916</v>
+        <v>427543</v>
       </c>
       <c r="R42" t="n">
-        <v>6233634</v>
+        <v>6233756</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5038,12 +5047,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5070,10 +5079,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471968</v>
+        <v>121471984</v>
       </c>
       <c r="B43" t="n">
-        <v>57367</v>
+        <v>80242</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5082,25 +5091,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>230185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5110,10 +5119,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427512</v>
+        <v>427530</v>
       </c>
       <c r="R43" t="n">
-        <v>6233745</v>
+        <v>6233736</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5172,10 +5181,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471703</v>
+        <v>121471557</v>
       </c>
       <c r="B44" t="n">
-        <v>74694</v>
+        <v>94588</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5188,21 +5197,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6439</v>
+        <v>2671</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5212,10 +5221,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427770</v>
+        <v>427948</v>
       </c>
       <c r="R44" t="n">
-        <v>6233580</v>
+        <v>6233643</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5274,10 +5283,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121472013</v>
+        <v>121471960</v>
       </c>
       <c r="B45" t="n">
-        <v>96722</v>
+        <v>94588</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5290,21 +5299,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5314,10 +5323,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>427882</v>
+        <v>427734</v>
       </c>
       <c r="R45" t="n">
-        <v>6233622</v>
+        <v>6233532</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,10 +5385,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471640</v>
+        <v>121471971</v>
       </c>
       <c r="B46" t="n">
-        <v>96722</v>
+        <v>78863</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5392,21 +5401,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5416,10 +5425,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427653</v>
+        <v>427499</v>
       </c>
       <c r="R46" t="n">
-        <v>6233849</v>
+        <v>6233792</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5446,12 +5455,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5478,10 +5487,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471584</v>
+        <v>121471985</v>
       </c>
       <c r="B47" t="n">
-        <v>96722</v>
+        <v>80242</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5494,21 +5503,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5518,10 +5527,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427817</v>
+        <v>427558</v>
       </c>
       <c r="R47" t="n">
-        <v>6233621</v>
+        <v>6233768</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5548,12 +5557,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5580,10 +5589,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471603</v>
+        <v>121471614</v>
       </c>
       <c r="B48" t="n">
-        <v>80252</v>
+        <v>80242</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5592,25 +5601,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5620,10 +5629,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427596</v>
+        <v>427475</v>
       </c>
       <c r="R48" t="n">
-        <v>6233681</v>
+        <v>6233836</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5682,10 +5691,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471564</v>
+        <v>121471964</v>
       </c>
       <c r="B49" t="n">
-        <v>80252</v>
+        <v>94599</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5694,25 +5703,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5722,10 +5731,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428014</v>
+        <v>427511</v>
       </c>
       <c r="R49" t="n">
-        <v>6233692</v>
+        <v>6233739</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5752,12 +5761,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5784,10 +5793,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471995</v>
+        <v>121471561</v>
       </c>
       <c r="B50" t="n">
-        <v>78860</v>
+        <v>96725</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5800,21 +5809,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5824,10 +5833,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427856</v>
+        <v>427999</v>
       </c>
       <c r="R50" t="n">
-        <v>6233613</v>
+        <v>6233695</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5854,12 +5863,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,10 +5895,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471608</v>
+        <v>121471589</v>
       </c>
       <c r="B51" t="n">
-        <v>80239</v>
+        <v>96725</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5902,21 +5911,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5926,10 +5935,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427566</v>
+        <v>427804</v>
       </c>
       <c r="R51" t="n">
-        <v>6233756</v>
+        <v>6233688</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5988,10 +5997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471650</v>
+        <v>121471603</v>
       </c>
       <c r="B52" t="n">
-        <v>80239</v>
+        <v>80255</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6000,25 +6009,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6028,10 +6037,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427737</v>
+        <v>427596</v>
       </c>
       <c r="R52" t="n">
-        <v>6233784</v>
+        <v>6233681</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6090,10 +6099,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471574</v>
+        <v>121471558</v>
       </c>
       <c r="B53" t="n">
-        <v>80239</v>
+        <v>80255</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6102,25 +6111,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6130,10 +6139,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427838</v>
+        <v>427960</v>
       </c>
       <c r="R53" t="n">
-        <v>6233582</v>
+        <v>6233661</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6192,10 +6201,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471575</v>
+        <v>121471988</v>
       </c>
       <c r="B54" t="n">
-        <v>91109</v>
+        <v>74525</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6204,25 +6213,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2023</v>
+        <v>6428</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6232,10 +6241,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427837</v>
+        <v>427738</v>
       </c>
       <c r="R54" t="n">
-        <v>6233582</v>
+        <v>6233780</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6262,12 +6271,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6294,10 +6303,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471714</v>
+        <v>121472015</v>
       </c>
       <c r="B55" t="n">
-        <v>78404</v>
+        <v>74697</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6306,25 +6315,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>924</v>
+        <v>6439</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6334,10 +6343,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>427435</v>
+        <v>427903</v>
       </c>
       <c r="R55" t="n">
-        <v>6233855</v>
+        <v>6233639</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6364,12 +6373,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6396,10 +6405,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471556</v>
+        <v>121472009</v>
       </c>
       <c r="B56" t="n">
-        <v>96722</v>
+        <v>94599</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6412,21 +6421,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6436,10 +6445,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>427948</v>
+        <v>427877</v>
       </c>
       <c r="R56" t="n">
-        <v>6233643</v>
+        <v>6233615</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6466,12 +6475,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6498,10 +6507,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471557</v>
+        <v>121471704</v>
       </c>
       <c r="B57" t="n">
-        <v>94585</v>
+        <v>96725</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6514,21 +6523,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6538,10 +6547,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427948</v>
+        <v>427785</v>
       </c>
       <c r="R57" t="n">
-        <v>6233643</v>
+        <v>6233585</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6600,10 +6609,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471708</v>
+        <v>121471963</v>
       </c>
       <c r="B58" t="n">
-        <v>96722</v>
+        <v>94599</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6616,21 +6625,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6640,10 +6649,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427785</v>
+        <v>427520</v>
       </c>
       <c r="R58" t="n">
-        <v>6233734</v>
+        <v>6233715</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6670,12 +6679,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6702,10 +6711,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471700</v>
+        <v>121471602</v>
       </c>
       <c r="B59" t="n">
-        <v>78984</v>
+        <v>94599</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6718,21 +6727,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6431</v>
+        <v>2667</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6742,10 +6751,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427806</v>
+        <v>427641</v>
       </c>
       <c r="R59" t="n">
-        <v>6233482</v>
+        <v>6233630</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6804,10 +6813,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121472010</v>
+        <v>121471954</v>
       </c>
       <c r="B60" t="n">
-        <v>78984</v>
+        <v>80242</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6820,21 +6829,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6431</v>
+        <v>230185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6844,10 +6853,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427877</v>
+        <v>427742</v>
       </c>
       <c r="R60" t="n">
-        <v>6233615</v>
+        <v>6233542</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6906,10 +6915,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471965</v>
+        <v>121471560</v>
       </c>
       <c r="B61" t="n">
-        <v>76945</v>
+        <v>80242</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6918,25 +6927,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6946,10 +6955,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427509</v>
+        <v>428008</v>
       </c>
       <c r="R61" t="n">
-        <v>6233731</v>
+        <v>6233671</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6976,12 +6985,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7008,10 +7017,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121472011</v>
+        <v>121471604</v>
       </c>
       <c r="B62" t="n">
-        <v>76945</v>
+        <v>80242</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7020,25 +7029,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7048,10 +7057,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427874</v>
+        <v>427595</v>
       </c>
       <c r="R62" t="n">
-        <v>6233615</v>
+        <v>6233781</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7078,12 +7087,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7110,10 +7119,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471590</v>
+        <v>121471577</v>
       </c>
       <c r="B63" t="n">
-        <v>80239</v>
+        <v>94599</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7126,21 +7135,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7150,10 +7159,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427753</v>
+        <v>427749</v>
       </c>
       <c r="R63" t="n">
-        <v>6233666</v>
+        <v>6233572</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7212,10 +7221,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471962</v>
+        <v>121471956</v>
       </c>
       <c r="B64" t="n">
-        <v>80239</v>
+        <v>94601</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7228,21 +7237,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7252,10 +7261,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427528</v>
+        <v>427739</v>
       </c>
       <c r="R64" t="n">
-        <v>6233707</v>
+        <v>6233524</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7314,10 +7323,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471589</v>
+        <v>121471702</v>
       </c>
       <c r="B65" t="n">
-        <v>96722</v>
+        <v>96725</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7354,10 +7363,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427804</v>
+        <v>427811</v>
       </c>
       <c r="R65" t="n">
-        <v>6233688</v>
+        <v>6233480</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7416,10 +7425,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471955</v>
+        <v>121471643</v>
       </c>
       <c r="B66" t="n">
-        <v>94598</v>
+        <v>96725</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7432,21 +7441,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2666</v>
+        <v>2606</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7456,10 +7465,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427741</v>
+        <v>427671</v>
       </c>
       <c r="R66" t="n">
-        <v>6233529</v>
+        <v>6233821</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7486,12 +7495,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,10 +7527,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471963</v>
+        <v>121471718</v>
       </c>
       <c r="B67" t="n">
-        <v>94596</v>
+        <v>80255</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7530,25 +7539,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7558,10 +7567,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427520</v>
+        <v>427584</v>
       </c>
       <c r="R67" t="n">
-        <v>6233715</v>
+        <v>6233863</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7588,12 +7597,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7620,10 +7629,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471626</v>
+        <v>121472014</v>
       </c>
       <c r="B68" t="n">
-        <v>74694</v>
+        <v>80255</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7632,25 +7641,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7660,10 +7669,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427597</v>
+        <v>427882</v>
       </c>
       <c r="R68" t="n">
-        <v>6233825</v>
+        <v>6233622</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7690,12 +7699,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7722,10 +7731,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471979</v>
+        <v>121471706</v>
       </c>
       <c r="B69" t="n">
-        <v>76945</v>
+        <v>96725</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7734,25 +7743,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7762,10 +7771,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427533</v>
+        <v>427781</v>
       </c>
       <c r="R69" t="n">
-        <v>6233765</v>
+        <v>6233648</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7792,12 +7801,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7824,10 +7833,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471565</v>
+        <v>121472006</v>
       </c>
       <c r="B70" t="n">
-        <v>76945</v>
+        <v>76948</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7864,10 +7873,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>428016</v>
+        <v>427892</v>
       </c>
       <c r="R70" t="n">
-        <v>6233689</v>
+        <v>6233623</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7894,12 +7903,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7926,10 +7935,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471712</v>
+        <v>121471575</v>
       </c>
       <c r="B71" t="n">
-        <v>96722</v>
+        <v>91112</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7938,25 +7947,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2606</v>
+        <v>2023</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7966,10 +7975,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>427439</v>
+        <v>427837</v>
       </c>
       <c r="R71" t="n">
-        <v>6233838</v>
+        <v>6233582</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8028,10 +8037,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471709</v>
+        <v>121471966</v>
       </c>
       <c r="B72" t="n">
-        <v>80239</v>
+        <v>76948</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8040,25 +8049,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8068,10 +8077,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427452</v>
+        <v>427505</v>
       </c>
       <c r="R72" t="n">
-        <v>6233794</v>
+        <v>6233740</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8098,12 +8107,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8130,10 +8139,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471581</v>
+        <v>121471596</v>
       </c>
       <c r="B73" t="n">
-        <v>80239</v>
+        <v>74699</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8146,21 +8155,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8170,10 +8179,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427820</v>
+        <v>427686</v>
       </c>
       <c r="R73" t="n">
-        <v>6233599</v>
+        <v>6233621</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8232,10 +8241,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471713</v>
+        <v>121471590</v>
       </c>
       <c r="B74" t="n">
-        <v>76945</v>
+        <v>80242</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8244,25 +8253,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8272,10 +8281,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>427438</v>
+        <v>427753</v>
       </c>
       <c r="R74" t="n">
-        <v>6233852</v>
+        <v>6233666</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8334,10 +8343,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471952</v>
+        <v>121471636</v>
       </c>
       <c r="B75" t="n">
-        <v>74694</v>
+        <v>80242</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8350,21 +8359,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8374,10 +8383,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>427763</v>
+        <v>427650</v>
       </c>
       <c r="R75" t="n">
-        <v>6233529</v>
+        <v>6233855</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8404,12 +8413,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8436,10 +8445,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471609</v>
+        <v>121471593</v>
       </c>
       <c r="B76" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8476,10 +8485,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427543</v>
+        <v>427699</v>
       </c>
       <c r="R76" t="n">
-        <v>6233756</v>
+        <v>6233608</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8538,10 +8547,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471720</v>
+        <v>121471967</v>
       </c>
       <c r="B77" t="n">
-        <v>80239</v>
+        <v>80255</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8550,25 +8559,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8578,10 +8587,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427595</v>
+        <v>427508</v>
       </c>
       <c r="R77" t="n">
-        <v>6233898</v>
+        <v>6233737</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8608,12 +8617,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8640,10 +8649,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471964</v>
+        <v>121471563</v>
       </c>
       <c r="B78" t="n">
-        <v>94596</v>
+        <v>96725</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8656,21 +8665,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8680,10 +8689,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427511</v>
+        <v>428012</v>
       </c>
       <c r="R78" t="n">
-        <v>6233739</v>
+        <v>6233689</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8710,12 +8719,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8742,10 +8751,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471644</v>
+        <v>121471712</v>
       </c>
       <c r="B79" t="n">
-        <v>78860</v>
+        <v>96725</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8758,21 +8767,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8782,10 +8791,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427671</v>
+        <v>427439</v>
       </c>
       <c r="R79" t="n">
-        <v>6233821</v>
+        <v>6233838</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8844,10 +8853,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471578</v>
+        <v>121471973</v>
       </c>
       <c r="B80" t="n">
-        <v>76945</v>
+        <v>76948</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8884,10 +8893,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427749</v>
+        <v>427544</v>
       </c>
       <c r="R80" t="n">
-        <v>6233573</v>
+        <v>6233811</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8914,12 +8923,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8946,10 +8955,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471966</v>
+        <v>121471953</v>
       </c>
       <c r="B81" t="n">
-        <v>76945</v>
+        <v>96725</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8958,25 +8967,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8986,10 +8995,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427505</v>
+        <v>427769</v>
       </c>
       <c r="R81" t="n">
-        <v>6233740</v>
+        <v>6233529</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9048,10 +9057,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121472009</v>
+        <v>121471714</v>
       </c>
       <c r="B82" t="n">
-        <v>94596</v>
+        <v>78407</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9060,25 +9069,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2667</v>
+        <v>924</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9088,10 +9097,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427877</v>
+        <v>427435</v>
       </c>
       <c r="R82" t="n">
-        <v>6233615</v>
+        <v>6233855</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9118,12 +9127,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9150,10 +9159,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471957</v>
+        <v>121471977</v>
       </c>
       <c r="B83" t="n">
-        <v>94596</v>
+        <v>96725</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9166,21 +9175,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9190,10 +9199,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427731</v>
+        <v>427533</v>
       </c>
       <c r="R83" t="n">
-        <v>6233539</v>
+        <v>6233765</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9252,10 +9261,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121472003</v>
+        <v>121471621</v>
       </c>
       <c r="B84" t="n">
-        <v>79015</v>
+        <v>96725</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9264,23 +9273,27 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>132</v>
+        <v>2606</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Liten lundlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Bacidina phacodes/tarandina</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9288,10 +9301,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427911</v>
+        <v>427607</v>
       </c>
       <c r="R84" t="n">
-        <v>6233614</v>
+        <v>6233875</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9318,12 +9331,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9350,10 +9363,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471645</v>
+        <v>121471622</v>
       </c>
       <c r="B85" t="n">
-        <v>80239</v>
+        <v>74697</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9366,21 +9379,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9390,10 +9403,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427702</v>
+        <v>427623</v>
       </c>
       <c r="R85" t="n">
-        <v>6233806</v>
+        <v>6233865</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9452,10 +9465,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471617</v>
+        <v>121471592</v>
       </c>
       <c r="B86" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9492,10 +9505,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427526</v>
+        <v>427703</v>
       </c>
       <c r="R86" t="n">
-        <v>6233836</v>
+        <v>6233616</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9554,10 +9567,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471604</v>
+        <v>121471591</v>
       </c>
       <c r="B87" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9594,10 +9607,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427595</v>
+        <v>427724</v>
       </c>
       <c r="R87" t="n">
-        <v>6233781</v>
+        <v>6233617</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9656,10 +9669,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471647</v>
+        <v>121471608</v>
       </c>
       <c r="B88" t="n">
-        <v>96722</v>
+        <v>80242</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9672,21 +9685,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9696,10 +9709,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427720</v>
+        <v>427566</v>
       </c>
       <c r="R88" t="n">
-        <v>6233787</v>
+        <v>6233756</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9758,10 +9771,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471651</v>
+        <v>121471720</v>
       </c>
       <c r="B89" t="n">
-        <v>78860</v>
+        <v>80242</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9774,21 +9787,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9798,10 +9811,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427737</v>
+        <v>427595</v>
       </c>
       <c r="R89" t="n">
-        <v>6233789</v>
+        <v>6233898</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9860,10 +9873,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471592</v>
+        <v>121471968</v>
       </c>
       <c r="B90" t="n">
-        <v>80239</v>
+        <v>57370</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9872,25 +9885,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>230185</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9900,10 +9913,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427703</v>
+        <v>427512</v>
       </c>
       <c r="R90" t="n">
-        <v>6233616</v>
+        <v>6233745</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9930,12 +9943,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9962,10 +9975,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471607</v>
+        <v>121471644</v>
       </c>
       <c r="B91" t="n">
-        <v>80239</v>
+        <v>78863</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9978,21 +9991,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10002,10 +10015,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427582</v>
+        <v>427671</v>
       </c>
       <c r="R91" t="n">
-        <v>6233752</v>
+        <v>6233821</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10064,10 +10077,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471580</v>
+        <v>121471565</v>
       </c>
       <c r="B92" t="n">
-        <v>80239</v>
+        <v>76948</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10076,25 +10089,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10104,10 +10117,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427804</v>
+        <v>428016</v>
       </c>
       <c r="R92" t="n">
-        <v>6233576</v>
+        <v>6233689</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10166,10 +10179,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471631</v>
+        <v>121471978</v>
       </c>
       <c r="B93" t="n">
-        <v>80239</v>
+        <v>94599</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10182,21 +10195,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10206,10 +10219,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427601</v>
+        <v>427533</v>
       </c>
       <c r="R93" t="n">
-        <v>6233830</v>
+        <v>6233765</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10236,12 +10249,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10268,10 +10281,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471614</v>
+        <v>121471719</v>
       </c>
       <c r="B94" t="n">
-        <v>80239</v>
+        <v>76948</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10280,25 +10293,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10308,10 +10321,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427475</v>
+        <v>427583</v>
       </c>
       <c r="R94" t="n">
-        <v>6233836</v>
+        <v>6233861</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10370,10 +10383,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471973</v>
+        <v>121472012</v>
       </c>
       <c r="B95" t="n">
-        <v>76945</v>
+        <v>76948</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10410,10 +10423,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427544</v>
+        <v>427855</v>
       </c>
       <c r="R95" t="n">
-        <v>6233811</v>
+        <v>6233612</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,10 +10485,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471599</v>
+        <v>121471648</v>
       </c>
       <c r="B96" t="n">
-        <v>94598</v>
+        <v>76948</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10484,25 +10497,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2666</v>
+        <v>1342</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10512,10 +10525,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427685</v>
+        <v>427721</v>
       </c>
       <c r="R96" t="n">
-        <v>6233593</v>
+        <v>6233787</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10574,10 +10587,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471706</v>
+        <v>121471709</v>
       </c>
       <c r="B97" t="n">
-        <v>96722</v>
+        <v>80242</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10590,21 +10603,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10614,10 +10627,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427781</v>
+        <v>427452</v>
       </c>
       <c r="R97" t="n">
-        <v>6233648</v>
+        <v>6233794</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10676,10 +10689,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471619</v>
+        <v>121471975</v>
       </c>
       <c r="B98" t="n">
-        <v>96722</v>
+        <v>80242</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10692,21 +10705,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10716,10 +10729,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427624</v>
+        <v>427575</v>
       </c>
       <c r="R98" t="n">
-        <v>6233894</v>
+        <v>6233800</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10746,12 +10759,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10778,10 +10791,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121472007</v>
+        <v>121471580</v>
       </c>
       <c r="B99" t="n">
-        <v>80252</v>
+        <v>80242</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10790,25 +10803,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10818,10 +10831,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427892</v>
+        <v>427804</v>
       </c>
       <c r="R99" t="n">
-        <v>6233623</v>
+        <v>6233576</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10848,12 +10861,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10880,10 +10893,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471586</v>
+        <v>121471634</v>
       </c>
       <c r="B100" t="n">
-        <v>80252</v>
+        <v>96725</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10892,25 +10905,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10920,10 +10933,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427748</v>
+        <v>427636</v>
       </c>
       <c r="R100" t="n">
-        <v>6233622</v>
+        <v>6233848</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10982,10 +10995,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471585</v>
+        <v>121471620</v>
       </c>
       <c r="B101" t="n">
-        <v>76945</v>
+        <v>94588</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10994,25 +11007,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11022,10 +11035,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>427748</v>
+        <v>427625</v>
       </c>
       <c r="R101" t="n">
-        <v>6233622</v>
+        <v>6233894</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11084,10 +11097,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471954</v>
+        <v>121471710</v>
       </c>
       <c r="B102" t="n">
-        <v>80239</v>
+        <v>94601</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11100,21 +11113,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11124,10 +11137,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427742</v>
+        <v>427448</v>
       </c>
       <c r="R102" t="n">
-        <v>6233542</v>
+        <v>6233789</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11154,12 +11167,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11186,10 +11199,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471719</v>
+        <v>121471707</v>
       </c>
       <c r="B103" t="n">
-        <v>76945</v>
+        <v>96725</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11198,25 +11211,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11226,10 +11239,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427583</v>
+        <v>427809</v>
       </c>
       <c r="R103" t="n">
-        <v>6233861</v>
+        <v>6233703</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11288,10 +11301,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121472002</v>
+        <v>121471612</v>
       </c>
       <c r="B104" t="n">
-        <v>94596</v>
+        <v>80242</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11304,21 +11317,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11328,10 +11341,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427909</v>
+        <v>427466</v>
       </c>
       <c r="R104" t="n">
-        <v>6233613</v>
+        <v>6233828</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11358,12 +11371,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11390,10 +11403,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471563</v>
+        <v>121471629</v>
       </c>
       <c r="B105" t="n">
-        <v>96722</v>
+        <v>80255</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11402,25 +11415,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11430,10 +11443,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>428012</v>
+        <v>427602</v>
       </c>
       <c r="R105" t="n">
-        <v>6233689</v>
+        <v>6233832</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11492,10 +11505,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471953</v>
+        <v>121471995</v>
       </c>
       <c r="B106" t="n">
-        <v>96722</v>
+        <v>78863</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11508,21 +11521,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11532,10 +11545,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427769</v>
+        <v>427856</v>
       </c>
       <c r="R106" t="n">
-        <v>6233529</v>
+        <v>6233613</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11594,10 +11607,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121472001</v>
+        <v>121471576</v>
       </c>
       <c r="B107" t="n">
-        <v>94606</v>
+        <v>80255</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11606,25 +11619,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1080</v>
+        <v>1144</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11634,10 +11647,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427908</v>
+        <v>427742</v>
       </c>
       <c r="R107" t="n">
-        <v>6233617</v>
+        <v>6233565</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11664,12 +11677,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11696,10 +11709,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471986</v>
+        <v>121471700</v>
       </c>
       <c r="B108" t="n">
-        <v>80252</v>
+        <v>78987</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11708,41 +11721,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1144</v>
+        <v>6431</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>427558</v>
+        <v>427806</v>
       </c>
       <c r="R108" t="n">
-        <v>6233769</v>
+        <v>6233482</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11769,17 +11779,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
-        </is>
-      </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>Med Refractohilum pluriseptatum</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11787,11 +11792,6 @@
       </c>
       <c r="AE108" t="b">
         <v>0</v>
-      </c>
-      <c r="AF108" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG108" t="b">
         <v>0</v>
@@ -11811,10 +11811,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471974</v>
+        <v>121471952</v>
       </c>
       <c r="B109" t="n">
-        <v>90505</v>
+        <v>74697</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11823,25 +11823,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1067</v>
+        <v>6439</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>427554</v>
+        <v>427763</v>
       </c>
       <c r="R109" t="n">
-        <v>6233803</v>
+        <v>6233529</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11913,10 +11913,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471976</v>
+        <v>121471598</v>
       </c>
       <c r="B110" t="n">
-        <v>96722</v>
+        <v>94599</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11929,21 +11929,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11953,10 +11953,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427576</v>
+        <v>427690</v>
       </c>
       <c r="R110" t="n">
-        <v>6233800</v>
+        <v>6233595</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11983,12 +11983,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12015,10 +12015,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471562</v>
+        <v>121471708</v>
       </c>
       <c r="B111" t="n">
-        <v>80575</v>
+        <v>96725</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12027,25 +12027,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1182</v>
+        <v>2606</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12055,10 +12055,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>428000</v>
+        <v>427785</v>
       </c>
       <c r="R111" t="n">
-        <v>6233692</v>
+        <v>6233734</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12120,7 +12120,7 @@
         <v>121471632</v>
       </c>
       <c r="B112" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12219,10 +12219,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471998</v>
+        <v>121471617</v>
       </c>
       <c r="B113" t="n">
-        <v>76945</v>
+        <v>80242</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12231,25 +12231,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12259,10 +12259,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427915</v>
+        <v>427526</v>
       </c>
       <c r="R113" t="n">
-        <v>6233632</v>
+        <v>6233836</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12289,12 +12289,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12321,10 +12321,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121472012</v>
+        <v>121471587</v>
       </c>
       <c r="B114" t="n">
-        <v>76945</v>
+        <v>80255</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12333,25 +12333,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12361,10 +12361,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427855</v>
+        <v>427770</v>
       </c>
       <c r="R114" t="n">
-        <v>6233612</v>
+        <v>6233624</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12391,12 +12391,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12423,10 +12423,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471633</v>
+        <v>121471990</v>
       </c>
       <c r="B115" t="n">
-        <v>90505</v>
+        <v>80242</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12435,25 +12435,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12463,10 +12463,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427629</v>
+        <v>427765</v>
       </c>
       <c r="R115" t="n">
-        <v>6233837</v>
+        <v>6233765</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12493,12 +12493,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12525,10 +12525,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471596</v>
+        <v>121471610</v>
       </c>
       <c r="B116" t="n">
-        <v>74696</v>
+        <v>80242</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12541,21 +12541,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>306</v>
+        <v>230185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12565,10 +12565,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427686</v>
+        <v>427487</v>
       </c>
       <c r="R116" t="n">
-        <v>6233621</v>
+        <v>6233816</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12627,10 +12627,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121472014</v>
+        <v>121471572</v>
       </c>
       <c r="B117" t="n">
-        <v>80252</v>
+        <v>96725</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12639,25 +12639,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12667,10 +12667,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427882</v>
+        <v>427982</v>
       </c>
       <c r="R117" t="n">
-        <v>6233622</v>
+        <v>6233642</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12697,12 +12697,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12729,10 +12729,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121472000</v>
+        <v>121471556</v>
       </c>
       <c r="B118" t="n">
-        <v>74694</v>
+        <v>96725</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12745,21 +12745,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12769,10 +12769,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427926</v>
+        <v>427948</v>
       </c>
       <c r="R118" t="n">
-        <v>6233617</v>
+        <v>6233643</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12799,12 +12799,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12831,10 +12831,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121472006</v>
+        <v>121471976</v>
       </c>
       <c r="B119" t="n">
-        <v>76945</v>
+        <v>96725</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12843,25 +12843,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12871,10 +12871,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427892</v>
+        <v>427576</v>
       </c>
       <c r="R119" t="n">
-        <v>6233623</v>
+        <v>6233800</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12933,10 +12933,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471977</v>
+        <v>121472016</v>
       </c>
       <c r="B120" t="n">
-        <v>96722</v>
+        <v>96725</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12973,10 +12973,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427533</v>
+        <v>427903</v>
       </c>
       <c r="R120" t="n">
-        <v>6233765</v>
+        <v>6233640</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13035,10 +13035,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471992</v>
+        <v>121472013</v>
       </c>
       <c r="B121" t="n">
-        <v>94585</v>
+        <v>96725</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13051,21 +13051,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13075,10 +13075,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427861</v>
+        <v>427882</v>
       </c>
       <c r="R121" t="n">
-        <v>6233620</v>
+        <v>6233622</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13137,10 +13137,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471978</v>
+        <v>121471600</v>
       </c>
       <c r="B122" t="n">
-        <v>94596</v>
+        <v>94599</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13177,10 +13177,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427533</v>
+        <v>427698</v>
       </c>
       <c r="R122" t="n">
-        <v>6233765</v>
+        <v>6233566</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13207,12 +13207,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13239,10 +13239,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471629</v>
+        <v>121471640</v>
       </c>
       <c r="B123" t="n">
-        <v>80252</v>
+        <v>96725</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13251,25 +13251,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13279,10 +13279,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427602</v>
+        <v>427653</v>
       </c>
       <c r="R123" t="n">
-        <v>6233832</v>
+        <v>6233849</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13341,10 +13341,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471622</v>
+        <v>121471993</v>
       </c>
       <c r="B124" t="n">
-        <v>74694</v>
+        <v>91504</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13353,38 +13353,41 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6439</v>
+        <v>2014</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427623</v>
+        <v>427859</v>
       </c>
       <c r="R124" t="n">
-        <v>6233865</v>
+        <v>6233620</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13411,12 +13414,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13425,6 +13428,7 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13443,10 +13447,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471642</v>
+        <v>121472001</v>
       </c>
       <c r="B125" t="n">
-        <v>80239</v>
+        <v>94609</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13459,21 +13463,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>230185</v>
+        <v>1080</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13483,10 +13487,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427654</v>
+        <v>427908</v>
       </c>
       <c r="R125" t="n">
-        <v>6233848</v>
+        <v>6233617</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13513,12 +13517,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13545,10 +13549,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471591</v>
+        <v>121471633</v>
       </c>
       <c r="B126" t="n">
-        <v>80239</v>
+        <v>90508</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13557,25 +13561,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13585,10 +13589,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427724</v>
+        <v>427629</v>
       </c>
       <c r="R126" t="n">
-        <v>6233617</v>
+        <v>6233837</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13647,10 +13651,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471959</v>
+        <v>121471623</v>
       </c>
       <c r="B127" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13687,10 +13691,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427734</v>
+        <v>427579</v>
       </c>
       <c r="R127" t="n">
-        <v>6233532</v>
+        <v>6233850</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13717,12 +13721,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13749,10 +13753,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471705</v>
+        <v>121471597</v>
       </c>
       <c r="B128" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13789,10 +13793,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427753</v>
+        <v>427693</v>
       </c>
       <c r="R128" t="n">
-        <v>6233606</v>
+        <v>6233604</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13851,10 +13855,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471560</v>
+        <v>121471618</v>
       </c>
       <c r="B129" t="n">
-        <v>80239</v>
+        <v>96725</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13867,21 +13871,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13891,10 +13895,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>428008</v>
+        <v>427525</v>
       </c>
       <c r="R129" t="n">
-        <v>6233671</v>
+        <v>6233838</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13953,10 +13957,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471601</v>
+        <v>121472003</v>
       </c>
       <c r="B130" t="n">
-        <v>80239</v>
+        <v>79018</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13965,27 +13969,23 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>230185</v>
+        <v>132</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Liten lundlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Bacidina phacodes/tarandina</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -13993,10 +13993,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>427688</v>
+        <v>427911</v>
       </c>
       <c r="R130" t="n">
-        <v>6233590</v>
+        <v>6233614</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14023,12 +14023,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14055,10 +14055,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471635</v>
+        <v>121471627</v>
       </c>
       <c r="B131" t="n">
-        <v>78860</v>
+        <v>74697</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14071,21 +14071,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6459</v>
+        <v>6439</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14095,10 +14095,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427637</v>
+        <v>427613</v>
       </c>
       <c r="R131" t="n">
-        <v>6233845</v>
+        <v>6233840</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14157,10 +14157,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471572</v>
+        <v>121471646</v>
       </c>
       <c r="B132" t="n">
-        <v>96722</v>
+        <v>94599</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14173,21 +14173,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14197,10 +14197,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427982</v>
+        <v>427692</v>
       </c>
       <c r="R132" t="n">
-        <v>6233642</v>
+        <v>6233796</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14259,10 +14259,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471961</v>
+        <v>121471650</v>
       </c>
       <c r="B133" t="n">
-        <v>94596</v>
+        <v>80242</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14275,21 +14275,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14299,10 +14299,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427615</v>
+        <v>427737</v>
       </c>
       <c r="R133" t="n">
-        <v>6233649</v>
+        <v>6233784</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14329,12 +14329,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14361,10 +14361,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471718</v>
+        <v>121471638</v>
       </c>
       <c r="B134" t="n">
-        <v>80252</v>
+        <v>80242</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14373,25 +14373,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14401,10 +14401,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427584</v>
+        <v>427638</v>
       </c>
       <c r="R134" t="n">
-        <v>6233863</v>
+        <v>6233822</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14463,10 +14463,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471988</v>
+        <v>121471631</v>
       </c>
       <c r="B135" t="n">
-        <v>74522</v>
+        <v>80242</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14479,21 +14479,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6428</v>
+        <v>230185</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14503,10 +14503,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427738</v>
+        <v>427601</v>
       </c>
       <c r="R135" t="n">
-        <v>6233780</v>
+        <v>6233830</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14533,12 +14533,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14565,10 +14565,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121472015</v>
+        <v>121471959</v>
       </c>
       <c r="B136" t="n">
-        <v>74694</v>
+        <v>80242</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14581,21 +14581,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14605,10 +14605,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427903</v>
+        <v>427734</v>
       </c>
       <c r="R136" t="n">
-        <v>6233639</v>
+        <v>6233532</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14667,10 +14667,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471648</v>
+        <v>121471957</v>
       </c>
       <c r="B137" t="n">
-        <v>76945</v>
+        <v>94599</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14679,25 +14679,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14707,10 +14707,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427721</v>
+        <v>427731</v>
       </c>
       <c r="R137" t="n">
-        <v>6233787</v>
+        <v>6233539</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14737,12 +14737,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14769,10 +14769,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471630</v>
+        <v>121471651</v>
       </c>
       <c r="B138" t="n">
-        <v>76945</v>
+        <v>78863</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14781,25 +14781,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1342</v>
+        <v>6459</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14809,10 +14809,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427604</v>
+        <v>427737</v>
       </c>
       <c r="R138" t="n">
-        <v>6233829</v>
+        <v>6233789</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14871,10 +14871,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121472016</v>
+        <v>121471703</v>
       </c>
       <c r="B139" t="n">
-        <v>96722</v>
+        <v>74697</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14887,21 +14887,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>2606</v>
+        <v>6439</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>427903</v>
+        <v>427770</v>
       </c>
       <c r="R139" t="n">
-        <v>6233640</v>
+        <v>6233580</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14941,12 +14941,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14973,10 +14973,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471618</v>
+        <v>121471649</v>
       </c>
       <c r="B140" t="n">
-        <v>96722</v>
+        <v>80255</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14985,25 +14985,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15013,10 +15013,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>427525</v>
+        <v>427720</v>
       </c>
       <c r="R140" t="n">
-        <v>6233838</v>
+        <v>6233787</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15075,10 +15075,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471643</v>
+        <v>121471578</v>
       </c>
       <c r="B141" t="n">
-        <v>96722</v>
+        <v>76948</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15087,25 +15087,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15115,10 +15115,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>427671</v>
+        <v>427749</v>
       </c>
       <c r="R141" t="n">
-        <v>6233821</v>
+        <v>6233573</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15177,10 +15177,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471960</v>
+        <v>121471999</v>
       </c>
       <c r="B142" t="n">
-        <v>94585</v>
+        <v>80255</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15189,25 +15189,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15217,10 +15217,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>427734</v>
+        <v>427916</v>
       </c>
       <c r="R142" t="n">
-        <v>6233532</v>
+        <v>6233634</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15279,10 +15279,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121472004</v>
+        <v>121471715</v>
       </c>
       <c r="B143" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15319,10 +15319,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>427892</v>
+        <v>427445</v>
       </c>
       <c r="R143" t="n">
-        <v>6233623</v>
+        <v>6233860</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15381,10 +15381,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471597</v>
+        <v>121471607</v>
       </c>
       <c r="B144" t="n">
-        <v>80239</v>
+        <v>80242</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15421,10 +15421,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>427693</v>
+        <v>427582</v>
       </c>
       <c r="R144" t="n">
-        <v>6233604</v>
+        <v>6233752</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15483,10 +15483,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471593</v>
+        <v>121471559</v>
       </c>
       <c r="B145" t="n">
-        <v>80239</v>
+        <v>76948</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15495,25 +15495,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15523,10 +15523,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427699</v>
+        <v>427960</v>
       </c>
       <c r="R145" t="n">
-        <v>6233608</v>
+        <v>6233661</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15585,10 +15585,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471980</v>
+        <v>121472002</v>
       </c>
       <c r="B146" t="n">
-        <v>80252</v>
+        <v>94599</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15597,25 +15597,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15625,10 +15625,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427532</v>
+        <v>427909</v>
       </c>
       <c r="R146" t="n">
-        <v>6233767</v>
+        <v>6233613</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15687,10 +15687,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471612</v>
+        <v>121471992</v>
       </c>
       <c r="B147" t="n">
-        <v>80239</v>
+        <v>94588</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15703,21 +15703,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15727,10 +15727,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427466</v>
+        <v>427861</v>
       </c>
       <c r="R147" t="n">
-        <v>6233828</v>
+        <v>6233620</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15757,12 +15757,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15789,10 +15789,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471975</v>
+        <v>121471983</v>
       </c>
       <c r="B148" t="n">
-        <v>80239</v>
+        <v>74697</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15805,21 +15805,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15829,10 +15829,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427575</v>
+        <v>427521</v>
       </c>
       <c r="R148" t="n">
-        <v>6233800</v>
+        <v>6233737</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15891,10 +15891,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471715</v>
+        <v>121471562</v>
       </c>
       <c r="B149" t="n">
-        <v>80239</v>
+        <v>80578</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15903,25 +15903,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>230185</v>
+        <v>1182</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15931,10 +15931,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>427445</v>
+        <v>428000</v>
       </c>
       <c r="R149" t="n">
-        <v>6233860</v>
+        <v>6233692</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15993,10 +15993,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471638</v>
+        <v>121471564</v>
       </c>
       <c r="B150" t="n">
-        <v>80239</v>
+        <v>80255</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16005,25 +16005,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16033,10 +16033,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>427638</v>
+        <v>428014</v>
       </c>
       <c r="R150" t="n">
-        <v>6233822</v>
+        <v>6233692</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16095,10 +16095,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471671</v>
+        <v>121471974</v>
       </c>
       <c r="B151" t="n">
-        <v>105756</v>
+        <v>90508</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16107,25 +16107,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220785</v>
+        <v>1067</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16135,10 +16135,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>427912</v>
+        <v>427554</v>
       </c>
       <c r="R151" t="n">
-        <v>6233611</v>
+        <v>6233803</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16165,12 +16165,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16197,10 +16197,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471621</v>
+        <v>121471716</v>
       </c>
       <c r="B152" t="n">
-        <v>96722</v>
+        <v>80242</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16213,21 +16213,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16237,10 +16237,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>427607</v>
+        <v>427547</v>
       </c>
       <c r="R152" t="n">
-        <v>6233875</v>
+        <v>6233865</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16299,10 +16299,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471702</v>
+        <v>121471521</v>
       </c>
       <c r="B153" t="n">
-        <v>96722</v>
+        <v>80242</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16315,21 +16315,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16339,10 +16339,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>427811</v>
+        <v>427794</v>
       </c>
       <c r="R153" t="n">
-        <v>6233480</v>
+        <v>6233483</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16401,10 +16401,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471637</v>
+        <v>121472004</v>
       </c>
       <c r="B154" t="n">
-        <v>96722</v>
+        <v>80242</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16417,21 +16417,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16441,10 +16441,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>427638</v>
+        <v>427892</v>
       </c>
       <c r="R154" t="n">
-        <v>6233822</v>
+        <v>6233623</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16471,12 +16471,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16503,10 +16503,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471559</v>
+        <v>121471641</v>
       </c>
       <c r="B155" t="n">
-        <v>76945</v>
+        <v>78863</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16515,25 +16515,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1342</v>
+        <v>6459</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16543,10 +16543,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>427960</v>
+        <v>427655</v>
       </c>
       <c r="R155" t="n">
-        <v>6233661</v>
+        <v>6233850</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16605,10 +16605,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471982</v>
+        <v>121471520</v>
       </c>
       <c r="B156" t="n">
-        <v>76945</v>
+        <v>80242</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16617,25 +16617,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16645,10 +16645,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>427516</v>
+        <v>427789</v>
       </c>
       <c r="R156" t="n">
-        <v>6233748</v>
+        <v>6233516</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16675,12 +16675,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16707,10 +16707,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471996</v>
+        <v>121471601</v>
       </c>
       <c r="B157" t="n">
-        <v>80252</v>
+        <v>80242</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16719,25 +16719,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16747,10 +16747,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>427855</v>
+        <v>427688</v>
       </c>
       <c r="R157" t="n">
-        <v>6233614</v>
+        <v>6233590</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16777,12 +16777,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16809,10 +16809,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471649</v>
+        <v>121471980</v>
       </c>
       <c r="B158" t="n">
-        <v>80252</v>
+        <v>80255</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16849,10 +16849,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>427720</v>
+        <v>427532</v>
       </c>
       <c r="R158" t="n">
-        <v>6233787</v>
+        <v>6233767</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16879,12 +16879,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16911,10 +16911,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471624</v>
+        <v>121472007</v>
       </c>
       <c r="B159" t="n">
-        <v>74560</v>
+        <v>80255</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16923,25 +16923,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1116</v>
+        <v>1144</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16951,10 +16951,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>427594</v>
+        <v>427892</v>
       </c>
       <c r="R159" t="n">
-        <v>6233828</v>
+        <v>6233623</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16981,12 +16981,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17013,10 +17013,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471576</v>
+        <v>121471998</v>
       </c>
       <c r="B160" t="n">
-        <v>80252</v>
+        <v>76948</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17025,25 +17025,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17053,10 +17053,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>427742</v>
+        <v>427915</v>
       </c>
       <c r="R160" t="n">
-        <v>6233565</v>
+        <v>6233632</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17083,12 +17083,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17115,10 +17115,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471971</v>
+        <v>121471619</v>
       </c>
       <c r="B161" t="n">
-        <v>78860</v>
+        <v>96725</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17131,21 +17131,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17155,10 +17155,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>427499</v>
+        <v>427624</v>
       </c>
       <c r="R161" t="n">
-        <v>6233792</v>
+        <v>6233894</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17185,12 +17185,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471635</v>
+        <v>121471646</v>
       </c>
       <c r="B11" t="n">
-        <v>78863</v>
+        <v>94599</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6459</v>
+        <v>2667</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427637</v>
+        <v>427692</v>
       </c>
       <c r="R11" t="n">
-        <v>6233845</v>
+        <v>6233796</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471645</v>
+        <v>121471956</v>
       </c>
       <c r="B12" t="n">
-        <v>80242</v>
+        <v>94601</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427702</v>
+        <v>427739</v>
       </c>
       <c r="R12" t="n">
-        <v>6233806</v>
+        <v>6233524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2006,7 +2006,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471642</v>
+        <v>121471623</v>
       </c>
       <c r="B13" t="n">
         <v>80242</v>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427654</v>
+        <v>427579</v>
       </c>
       <c r="R13" t="n">
-        <v>6233848</v>
+        <v>6233850</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2108,7 +2108,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471574</v>
+        <v>121471580</v>
       </c>
       <c r="B14" t="n">
         <v>80242</v>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427838</v>
+        <v>427804</v>
       </c>
       <c r="R14" t="n">
-        <v>6233582</v>
+        <v>6233576</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471705</v>
+        <v>121471572</v>
       </c>
       <c r="B15" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427753</v>
+        <v>427982</v>
       </c>
       <c r="R15" t="n">
-        <v>6233606</v>
+        <v>6233642</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121471599</v>
+        <v>121471608</v>
       </c>
       <c r="B16" t="n">
-        <v>94601</v>
+        <v>80242</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427685</v>
+        <v>427566</v>
       </c>
       <c r="R16" t="n">
-        <v>6233593</v>
+        <v>6233756</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121471961</v>
+        <v>121471560</v>
       </c>
       <c r="B17" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427615</v>
+        <v>428008</v>
       </c>
       <c r="R17" t="n">
-        <v>6233649</v>
+        <v>6233671</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121471965</v>
+        <v>121471604</v>
       </c>
       <c r="B18" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427509</v>
+        <v>427595</v>
       </c>
       <c r="R18" t="n">
-        <v>6233731</v>
+        <v>6233781</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121471955</v>
+        <v>121471633</v>
       </c>
       <c r="B19" t="n">
-        <v>94601</v>
+        <v>90508</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2666</v>
+        <v>1067</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427741</v>
+        <v>427629</v>
       </c>
       <c r="R19" t="n">
-        <v>6233529</v>
+        <v>6233837</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121471585</v>
+        <v>121472013</v>
       </c>
       <c r="B20" t="n">
-        <v>76948</v>
+        <v>96725</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,7 +2760,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427748</v>
+        <v>427882</v>
       </c>
       <c r="R20" t="n">
         <v>6233622</v>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,7 +2822,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121471584</v>
+        <v>121471712</v>
       </c>
       <c r="B21" t="n">
         <v>96725</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>427817</v>
+        <v>427439</v>
       </c>
       <c r="R21" t="n">
-        <v>6233621</v>
+        <v>6233838</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121472011</v>
+        <v>121471637</v>
       </c>
       <c r="B22" t="n">
-        <v>76948</v>
+        <v>96725</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427874</v>
+        <v>427638</v>
       </c>
       <c r="R22" t="n">
-        <v>6233615</v>
+        <v>6233822</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471671</v>
+        <v>121471622</v>
       </c>
       <c r="B23" t="n">
-        <v>105759</v>
+        <v>74697</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220785</v>
+        <v>6439</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427912</v>
+        <v>427623</v>
       </c>
       <c r="R23" t="n">
-        <v>6233611</v>
+        <v>6233865</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471647</v>
+        <v>121471626</v>
       </c>
       <c r="B24" t="n">
-        <v>96725</v>
+        <v>74697</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2606</v>
+        <v>6439</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427720</v>
+        <v>427597</v>
       </c>
       <c r="R24" t="n">
-        <v>6233787</v>
+        <v>6233825</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471637</v>
+        <v>121471714</v>
       </c>
       <c r="B25" t="n">
-        <v>96725</v>
+        <v>78407</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3242,25 +3242,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2606</v>
+        <v>924</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427638</v>
+        <v>427435</v>
       </c>
       <c r="R25" t="n">
-        <v>6233822</v>
+        <v>6233855</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471982</v>
+        <v>121471564</v>
       </c>
       <c r="B26" t="n">
-        <v>76948</v>
+        <v>80255</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3344,25 +3344,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427516</v>
+        <v>428014</v>
       </c>
       <c r="R26" t="n">
-        <v>6233748</v>
+        <v>6233692</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3402,12 +3402,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471626</v>
+        <v>121471999</v>
       </c>
       <c r="B27" t="n">
-        <v>74697</v>
+        <v>80255</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427597</v>
+        <v>427916</v>
       </c>
       <c r="R27" t="n">
-        <v>6233825</v>
+        <v>6233634</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471996</v>
+        <v>121471574</v>
       </c>
       <c r="B28" t="n">
-        <v>80255</v>
+        <v>80242</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3548,25 +3548,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427855</v>
+        <v>427838</v>
       </c>
       <c r="R28" t="n">
-        <v>6233614</v>
+        <v>6233582</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3606,12 +3606,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3638,10 +3638,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471624</v>
+        <v>121471609</v>
       </c>
       <c r="B29" t="n">
-        <v>74563</v>
+        <v>80242</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3650,25 +3650,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1116</v>
+        <v>230185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427594</v>
+        <v>427543</v>
       </c>
       <c r="R29" t="n">
-        <v>6233828</v>
+        <v>6233756</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471979</v>
+        <v>121471720</v>
       </c>
       <c r="B30" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427533</v>
+        <v>427595</v>
       </c>
       <c r="R30" t="n">
-        <v>6233765</v>
+        <v>6233898</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471628</v>
+        <v>121471601</v>
       </c>
       <c r="B31" t="n">
-        <v>96725</v>
+        <v>80242</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427604</v>
+        <v>427688</v>
       </c>
       <c r="R31" t="n">
-        <v>6233834</v>
+        <v>6233590</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471583</v>
+        <v>121471982</v>
       </c>
       <c r="B32" t="n">
-        <v>78863</v>
+        <v>76948</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,25 +3956,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427813</v>
+        <v>427516</v>
       </c>
       <c r="R32" t="n">
-        <v>6233621</v>
+        <v>6233748</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4046,10 +4046,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471586</v>
+        <v>121471713</v>
       </c>
       <c r="B33" t="n">
-        <v>80255</v>
+        <v>76948</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4058,25 +4058,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427748</v>
+        <v>427438</v>
       </c>
       <c r="R33" t="n">
-        <v>6233622</v>
+        <v>6233852</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471986</v>
+        <v>121471967</v>
       </c>
       <c r="B34" t="n">
         <v>80255</v>
@@ -4182,19 +4182,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427558</v>
+        <v>427508</v>
       </c>
       <c r="R34" t="n">
-        <v>6233769</v>
+        <v>6233737</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4229,21 +4226,11 @@
           <t>2024-11-18</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Med Refractohilum pluriseptatum</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4263,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471581</v>
+        <v>121471992</v>
       </c>
       <c r="B35" t="n">
-        <v>80242</v>
+        <v>94588</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4279,21 +4266,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4303,10 +4290,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427820</v>
+        <v>427861</v>
       </c>
       <c r="R35" t="n">
-        <v>6233599</v>
+        <v>6233620</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4333,12 +4320,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4365,7 +4352,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471962</v>
+        <v>121471642</v>
       </c>
       <c r="B36" t="n">
         <v>80242</v>
@@ -4405,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427528</v>
+        <v>427654</v>
       </c>
       <c r="R36" t="n">
-        <v>6233707</v>
+        <v>6233848</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4435,12 +4422,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4467,10 +4454,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471630</v>
+        <v>121471607</v>
       </c>
       <c r="B37" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4479,25 +4466,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4507,10 +4494,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427604</v>
+        <v>427582</v>
       </c>
       <c r="R37" t="n">
-        <v>6233829</v>
+        <v>6233752</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4569,10 +4556,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471951</v>
+        <v>121471520</v>
       </c>
       <c r="B38" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4581,25 +4568,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4609,10 +4596,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427762</v>
+        <v>427789</v>
       </c>
       <c r="R38" t="n">
-        <v>6233515</v>
+        <v>6233516</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4639,12 +4626,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4671,10 +4658,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471713</v>
+        <v>121471974</v>
       </c>
       <c r="B39" t="n">
-        <v>76948</v>
+        <v>90508</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4683,25 +4670,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1342</v>
+        <v>1067</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4711,10 +4698,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427438</v>
+        <v>427554</v>
       </c>
       <c r="R39" t="n">
-        <v>6233852</v>
+        <v>6233803</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4741,12 +4728,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4773,10 +4760,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121472000</v>
+        <v>121471521</v>
       </c>
       <c r="B40" t="n">
-        <v>74697</v>
+        <v>80242</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4789,21 +4776,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4813,10 +4800,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427926</v>
+        <v>427794</v>
       </c>
       <c r="R40" t="n">
-        <v>6233617</v>
+        <v>6233483</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4843,12 +4830,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4875,10 +4862,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121472010</v>
+        <v>121471649</v>
       </c>
       <c r="B41" t="n">
-        <v>78987</v>
+        <v>80255</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4887,25 +4874,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6431</v>
+        <v>1144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4915,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427877</v>
+        <v>427720</v>
       </c>
       <c r="R41" t="n">
-        <v>6233615</v>
+        <v>6233787</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4945,12 +4932,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4977,10 +4964,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471609</v>
+        <v>121471578</v>
       </c>
       <c r="B42" t="n">
-        <v>80242</v>
+        <v>76948</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4989,25 +4976,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5017,10 +5004,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427543</v>
+        <v>427749</v>
       </c>
       <c r="R42" t="n">
-        <v>6233756</v>
+        <v>6233573</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5079,10 +5066,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471984</v>
+        <v>121471648</v>
       </c>
       <c r="B43" t="n">
-        <v>80242</v>
+        <v>76948</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5091,25 +5078,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5119,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427530</v>
+        <v>427721</v>
       </c>
       <c r="R43" t="n">
-        <v>6233736</v>
+        <v>6233787</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5149,12 +5136,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5181,10 +5168,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471557</v>
+        <v>121471993</v>
       </c>
       <c r="B44" t="n">
-        <v>94588</v>
+        <v>91504</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5193,38 +5180,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2671</v>
+        <v>2014</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427948</v>
+        <v>427859</v>
       </c>
       <c r="R44" t="n">
-        <v>6233643</v>
+        <v>6233620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5251,12 +5241,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5265,6 +5255,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5283,10 +5274,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471960</v>
+        <v>121471598</v>
       </c>
       <c r="B45" t="n">
-        <v>94588</v>
+        <v>94599</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5299,21 +5290,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5323,10 +5314,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>427734</v>
+        <v>427690</v>
       </c>
       <c r="R45" t="n">
-        <v>6233532</v>
+        <v>6233595</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5353,12 +5344,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5385,10 +5376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471971</v>
+        <v>121471710</v>
       </c>
       <c r="B46" t="n">
-        <v>78863</v>
+        <v>94601</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5401,21 +5392,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6459</v>
+        <v>2666</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5425,10 +5416,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427499</v>
+        <v>427448</v>
       </c>
       <c r="R46" t="n">
-        <v>6233792</v>
+        <v>6233789</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5455,12 +5446,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5487,7 +5478,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471985</v>
+        <v>121472004</v>
       </c>
       <c r="B47" t="n">
         <v>80242</v>
@@ -5527,10 +5518,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427558</v>
+        <v>427892</v>
       </c>
       <c r="R47" t="n">
-        <v>6233768</v>
+        <v>6233623</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5589,10 +5580,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471614</v>
+        <v>121471979</v>
       </c>
       <c r="B48" t="n">
-        <v>80242</v>
+        <v>76948</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5601,25 +5592,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5629,10 +5620,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427475</v>
+        <v>427533</v>
       </c>
       <c r="R48" t="n">
-        <v>6233836</v>
+        <v>6233765</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5659,12 +5650,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5691,10 +5682,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471964</v>
+        <v>121471719</v>
       </c>
       <c r="B49" t="n">
-        <v>94599</v>
+        <v>76948</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5703,25 +5694,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5731,10 +5722,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427511</v>
+        <v>427583</v>
       </c>
       <c r="R49" t="n">
-        <v>6233739</v>
+        <v>6233861</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5761,12 +5752,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5793,10 +5784,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471561</v>
+        <v>121471978</v>
       </c>
       <c r="B50" t="n">
-        <v>96725</v>
+        <v>94599</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5809,21 +5800,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5833,10 +5824,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427999</v>
+        <v>427533</v>
       </c>
       <c r="R50" t="n">
-        <v>6233695</v>
+        <v>6233765</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5863,12 +5854,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5895,10 +5886,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471589</v>
+        <v>121471602</v>
       </c>
       <c r="B51" t="n">
-        <v>96725</v>
+        <v>94599</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5911,21 +5902,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5935,10 +5926,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427804</v>
+        <v>427641</v>
       </c>
       <c r="R51" t="n">
-        <v>6233688</v>
+        <v>6233630</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5997,10 +5988,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471603</v>
+        <v>121471644</v>
       </c>
       <c r="B52" t="n">
-        <v>80255</v>
+        <v>78863</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6009,25 +6000,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1144</v>
+        <v>6459</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6037,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427596</v>
+        <v>427671</v>
       </c>
       <c r="R52" t="n">
-        <v>6233681</v>
+        <v>6233821</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6099,10 +6090,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471558</v>
+        <v>121472010</v>
       </c>
       <c r="B53" t="n">
-        <v>80255</v>
+        <v>78987</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6111,25 +6102,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1144</v>
+        <v>6431</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6139,10 +6130,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427960</v>
+        <v>427877</v>
       </c>
       <c r="R53" t="n">
-        <v>6233661</v>
+        <v>6233615</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6169,12 +6160,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6201,10 +6192,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471988</v>
+        <v>121471628</v>
       </c>
       <c r="B54" t="n">
-        <v>74525</v>
+        <v>96725</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6217,21 +6208,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6428</v>
+        <v>2606</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6241,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427738</v>
+        <v>427604</v>
       </c>
       <c r="R54" t="n">
-        <v>6233780</v>
+        <v>6233834</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6271,12 +6262,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6303,10 +6294,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121472015</v>
+        <v>121471619</v>
       </c>
       <c r="B55" t="n">
-        <v>74697</v>
+        <v>96725</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6319,21 +6310,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6343,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>427903</v>
+        <v>427624</v>
       </c>
       <c r="R55" t="n">
-        <v>6233639</v>
+        <v>6233894</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6373,12 +6364,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6405,10 +6396,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121472009</v>
+        <v>121471996</v>
       </c>
       <c r="B56" t="n">
-        <v>94599</v>
+        <v>80255</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6417,25 +6408,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6445,10 +6436,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>427877</v>
+        <v>427855</v>
       </c>
       <c r="R56" t="n">
-        <v>6233615</v>
+        <v>6233614</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6507,10 +6498,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471704</v>
+        <v>121472012</v>
       </c>
       <c r="B57" t="n">
-        <v>96725</v>
+        <v>76948</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6519,25 +6510,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6547,10 +6538,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427785</v>
+        <v>427855</v>
       </c>
       <c r="R57" t="n">
-        <v>6233585</v>
+        <v>6233612</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6577,12 +6568,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6609,10 +6600,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471963</v>
+        <v>121471632</v>
       </c>
       <c r="B58" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6625,21 +6616,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6649,10 +6640,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427520</v>
+        <v>427615</v>
       </c>
       <c r="R58" t="n">
-        <v>6233715</v>
+        <v>6233825</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6679,12 +6670,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6711,10 +6702,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471602</v>
+        <v>121471612</v>
       </c>
       <c r="B59" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6727,21 +6718,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6751,10 +6742,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427641</v>
+        <v>427466</v>
       </c>
       <c r="R59" t="n">
-        <v>6233630</v>
+        <v>6233828</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6813,7 +6804,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471954</v>
+        <v>121471650</v>
       </c>
       <c r="B60" t="n">
         <v>80242</v>
@@ -6853,10 +6844,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427742</v>
+        <v>427737</v>
       </c>
       <c r="R60" t="n">
-        <v>6233542</v>
+        <v>6233784</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6883,12 +6874,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6915,7 +6906,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471560</v>
+        <v>121471590</v>
       </c>
       <c r="B61" t="n">
         <v>80242</v>
@@ -6955,10 +6946,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>428008</v>
+        <v>427753</v>
       </c>
       <c r="R61" t="n">
-        <v>6233671</v>
+        <v>6233666</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7017,7 +7008,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471604</v>
+        <v>121471962</v>
       </c>
       <c r="B62" t="n">
         <v>80242</v>
@@ -7057,10 +7048,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427595</v>
+        <v>427528</v>
       </c>
       <c r="R62" t="n">
-        <v>6233781</v>
+        <v>6233707</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7087,12 +7078,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7119,10 +7110,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471577</v>
+        <v>121471960</v>
       </c>
       <c r="B63" t="n">
-        <v>94599</v>
+        <v>94588</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7135,21 +7126,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7159,10 +7150,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427749</v>
+        <v>427734</v>
       </c>
       <c r="R63" t="n">
-        <v>6233572</v>
+        <v>6233532</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7189,12 +7180,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7221,10 +7212,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471956</v>
+        <v>121471603</v>
       </c>
       <c r="B64" t="n">
-        <v>94601</v>
+        <v>80255</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7233,25 +7224,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2666</v>
+        <v>1144</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7261,10 +7252,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427739</v>
+        <v>427596</v>
       </c>
       <c r="R64" t="n">
-        <v>6233524</v>
+        <v>6233681</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7291,12 +7282,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7323,10 +7314,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471702</v>
+        <v>121471559</v>
       </c>
       <c r="B65" t="n">
-        <v>96725</v>
+        <v>76948</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7335,25 +7326,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7363,10 +7354,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427811</v>
+        <v>427960</v>
       </c>
       <c r="R65" t="n">
-        <v>6233480</v>
+        <v>6233661</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7425,10 +7416,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471643</v>
+        <v>121471951</v>
       </c>
       <c r="B66" t="n">
-        <v>96725</v>
+        <v>76948</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7437,25 +7428,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7465,10 +7456,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427671</v>
+        <v>427762</v>
       </c>
       <c r="R66" t="n">
-        <v>6233821</v>
+        <v>6233515</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7495,12 +7486,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7527,10 +7518,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471718</v>
+        <v>121472016</v>
       </c>
       <c r="B67" t="n">
-        <v>80255</v>
+        <v>96725</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7539,25 +7530,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7567,10 +7558,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427584</v>
+        <v>427903</v>
       </c>
       <c r="R67" t="n">
-        <v>6233863</v>
+        <v>6233640</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7597,12 +7588,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7629,10 +7620,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121472014</v>
+        <v>121471618</v>
       </c>
       <c r="B68" t="n">
-        <v>80255</v>
+        <v>96725</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7641,25 +7632,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7669,10 +7660,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427882</v>
+        <v>427525</v>
       </c>
       <c r="R68" t="n">
-        <v>6233622</v>
+        <v>6233838</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7699,12 +7690,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7731,7 +7722,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471706</v>
+        <v>121471953</v>
       </c>
       <c r="B69" t="n">
         <v>96725</v>
@@ -7771,10 +7762,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427781</v>
+        <v>427769</v>
       </c>
       <c r="R69" t="n">
-        <v>6233648</v>
+        <v>6233529</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7801,12 +7792,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7833,10 +7824,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121472006</v>
+        <v>121471988</v>
       </c>
       <c r="B70" t="n">
-        <v>76948</v>
+        <v>74525</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7845,25 +7836,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1342</v>
+        <v>6428</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7873,10 +7864,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>427892</v>
+        <v>427738</v>
       </c>
       <c r="R70" t="n">
-        <v>6233623</v>
+        <v>6233780</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7935,10 +7926,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471575</v>
+        <v>121471975</v>
       </c>
       <c r="B71" t="n">
-        <v>91112</v>
+        <v>80242</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7947,25 +7938,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2023</v>
+        <v>230185</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7975,10 +7966,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>427837</v>
+        <v>427575</v>
       </c>
       <c r="R71" t="n">
-        <v>6233582</v>
+        <v>6233800</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8005,12 +7996,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8037,10 +8028,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471966</v>
+        <v>121471986</v>
       </c>
       <c r="B72" t="n">
-        <v>76948</v>
+        <v>80255</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8049,38 +8040,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427505</v>
+        <v>427558</v>
       </c>
       <c r="R72" t="n">
-        <v>6233740</v>
+        <v>6233769</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8115,11 +8109,21 @@
           <t>2024-11-18</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Med Refractohilum pluriseptatum</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
       <c r="AE72" t="b">
         <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG72" t="b">
         <v>0</v>
@@ -8139,10 +8143,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471596</v>
+        <v>121471586</v>
       </c>
       <c r="B73" t="n">
-        <v>74699</v>
+        <v>80255</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8151,25 +8155,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>306</v>
+        <v>1144</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8179,10 +8183,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427686</v>
+        <v>427748</v>
       </c>
       <c r="R73" t="n">
-        <v>6233621</v>
+        <v>6233622</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8241,10 +8245,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471590</v>
+        <v>121472006</v>
       </c>
       <c r="B74" t="n">
-        <v>80242</v>
+        <v>76948</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8253,25 +8257,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8281,10 +8285,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>427753</v>
+        <v>427892</v>
       </c>
       <c r="R74" t="n">
-        <v>6233666</v>
+        <v>6233623</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8311,12 +8315,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8343,10 +8347,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471636</v>
+        <v>121471585</v>
       </c>
       <c r="B75" t="n">
-        <v>80242</v>
+        <v>76948</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8355,25 +8359,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8383,10 +8387,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>427650</v>
+        <v>427748</v>
       </c>
       <c r="R75" t="n">
-        <v>6233855</v>
+        <v>6233622</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8445,10 +8449,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471593</v>
+        <v>121471557</v>
       </c>
       <c r="B76" t="n">
-        <v>80242</v>
+        <v>94588</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8461,21 +8465,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8485,10 +8489,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427699</v>
+        <v>427948</v>
       </c>
       <c r="R76" t="n">
-        <v>6233608</v>
+        <v>6233643</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8547,10 +8551,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471967</v>
+        <v>121471599</v>
       </c>
       <c r="B77" t="n">
-        <v>80255</v>
+        <v>94601</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8559,25 +8563,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1144</v>
+        <v>2666</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8587,10 +8591,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427508</v>
+        <v>427685</v>
       </c>
       <c r="R77" t="n">
-        <v>6233737</v>
+        <v>6233593</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8617,12 +8621,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8649,10 +8653,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471563</v>
+        <v>121471638</v>
       </c>
       <c r="B78" t="n">
-        <v>96725</v>
+        <v>80242</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8665,21 +8669,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8689,10 +8693,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>428012</v>
+        <v>427638</v>
       </c>
       <c r="R78" t="n">
-        <v>6233689</v>
+        <v>6233822</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8751,7 +8755,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471712</v>
+        <v>121471589</v>
       </c>
       <c r="B79" t="n">
         <v>96725</v>
@@ -8791,10 +8795,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427439</v>
+        <v>427804</v>
       </c>
       <c r="R79" t="n">
-        <v>6233838</v>
+        <v>6233688</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8853,10 +8857,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471973</v>
+        <v>121471584</v>
       </c>
       <c r="B80" t="n">
-        <v>76948</v>
+        <v>96725</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8865,25 +8869,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8893,10 +8897,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427544</v>
+        <v>427817</v>
       </c>
       <c r="R80" t="n">
-        <v>6233811</v>
+        <v>6233621</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8923,12 +8927,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8955,10 +8959,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471953</v>
+        <v>121471700</v>
       </c>
       <c r="B81" t="n">
-        <v>96725</v>
+        <v>78987</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8971,21 +8975,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2606</v>
+        <v>6431</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8995,10 +8999,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427769</v>
+        <v>427806</v>
       </c>
       <c r="R81" t="n">
-        <v>6233529</v>
+        <v>6233482</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9025,12 +9029,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9057,10 +9061,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471714</v>
+        <v>121471952</v>
       </c>
       <c r="B82" t="n">
-        <v>78407</v>
+        <v>74697</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9069,25 +9073,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>924</v>
+        <v>6439</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9097,10 +9101,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427435</v>
+        <v>427763</v>
       </c>
       <c r="R82" t="n">
-        <v>6233855</v>
+        <v>6233529</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9127,12 +9131,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9159,10 +9163,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471977</v>
+        <v>121471596</v>
       </c>
       <c r="B83" t="n">
-        <v>96725</v>
+        <v>74699</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9175,21 +9179,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2606</v>
+        <v>306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9199,10 +9203,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427533</v>
+        <v>427686</v>
       </c>
       <c r="R83" t="n">
-        <v>6233765</v>
+        <v>6233621</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9229,12 +9233,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9261,10 +9265,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471621</v>
+        <v>121471624</v>
       </c>
       <c r="B84" t="n">
-        <v>96725</v>
+        <v>74563</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9273,25 +9277,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2606</v>
+        <v>1116</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9301,10 +9305,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427607</v>
+        <v>427594</v>
       </c>
       <c r="R84" t="n">
-        <v>6233875</v>
+        <v>6233828</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9363,10 +9367,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471622</v>
+        <v>121472011</v>
       </c>
       <c r="B85" t="n">
-        <v>74697</v>
+        <v>76948</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9375,25 +9379,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6439</v>
+        <v>1342</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9403,10 +9407,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427623</v>
+        <v>427874</v>
       </c>
       <c r="R85" t="n">
-        <v>6233865</v>
+        <v>6233615</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9433,12 +9437,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9465,10 +9469,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471592</v>
+        <v>121471577</v>
       </c>
       <c r="B86" t="n">
-        <v>80242</v>
+        <v>94599</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9481,21 +9485,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9505,10 +9509,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427703</v>
+        <v>427749</v>
       </c>
       <c r="R86" t="n">
-        <v>6233616</v>
+        <v>6233572</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9567,10 +9571,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471591</v>
+        <v>121471702</v>
       </c>
       <c r="B87" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9583,21 +9587,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9607,10 +9611,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427724</v>
+        <v>427811</v>
       </c>
       <c r="R87" t="n">
-        <v>6233617</v>
+        <v>6233480</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9669,10 +9673,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471608</v>
+        <v>121471995</v>
       </c>
       <c r="B88" t="n">
-        <v>80242</v>
+        <v>78863</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9685,21 +9689,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9709,10 +9713,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427566</v>
+        <v>427856</v>
       </c>
       <c r="R88" t="n">
-        <v>6233756</v>
+        <v>6233613</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9739,12 +9743,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9771,10 +9775,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471720</v>
+        <v>121471703</v>
       </c>
       <c r="B89" t="n">
-        <v>80242</v>
+        <v>74697</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9787,21 +9791,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9811,10 +9815,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427595</v>
+        <v>427770</v>
       </c>
       <c r="R89" t="n">
-        <v>6233898</v>
+        <v>6233580</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9975,10 +9979,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471644</v>
+        <v>121471709</v>
       </c>
       <c r="B91" t="n">
-        <v>78863</v>
+        <v>80242</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9991,21 +9995,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10015,10 +10019,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427671</v>
+        <v>427452</v>
       </c>
       <c r="R91" t="n">
-        <v>6233821</v>
+        <v>6233794</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10077,10 +10081,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471565</v>
+        <v>121471954</v>
       </c>
       <c r="B92" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10089,25 +10093,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10117,10 +10121,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>428016</v>
+        <v>427742</v>
       </c>
       <c r="R92" t="n">
-        <v>6233689</v>
+        <v>6233542</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10147,12 +10151,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10179,10 +10183,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471978</v>
+        <v>121471705</v>
       </c>
       <c r="B93" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10195,21 +10199,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10219,10 +10223,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427533</v>
+        <v>427753</v>
       </c>
       <c r="R93" t="n">
-        <v>6233765</v>
+        <v>6233606</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10249,12 +10253,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10281,10 +10285,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471719</v>
+        <v>121471631</v>
       </c>
       <c r="B94" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10293,25 +10297,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10321,10 +10325,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427583</v>
+        <v>427601</v>
       </c>
       <c r="R94" t="n">
-        <v>6233861</v>
+        <v>6233830</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10383,7 +10387,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121472012</v>
+        <v>121471998</v>
       </c>
       <c r="B95" t="n">
         <v>76948</v>
@@ -10423,10 +10427,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427855</v>
+        <v>427915</v>
       </c>
       <c r="R95" t="n">
-        <v>6233612</v>
+        <v>6233632</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10485,10 +10489,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471648</v>
+        <v>121471957</v>
       </c>
       <c r="B96" t="n">
-        <v>76948</v>
+        <v>94599</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10497,25 +10501,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10525,10 +10529,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427721</v>
+        <v>427731</v>
       </c>
       <c r="R96" t="n">
-        <v>6233787</v>
+        <v>6233539</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10555,12 +10559,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10587,10 +10591,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471709</v>
+        <v>121472001</v>
       </c>
       <c r="B97" t="n">
-        <v>80242</v>
+        <v>94609</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10603,21 +10607,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>230185</v>
+        <v>1080</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10627,10 +10631,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427452</v>
+        <v>427908</v>
       </c>
       <c r="R97" t="n">
-        <v>6233794</v>
+        <v>6233617</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10657,12 +10661,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10689,10 +10693,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471975</v>
+        <v>121471640</v>
       </c>
       <c r="B98" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10705,21 +10709,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10729,10 +10733,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427575</v>
+        <v>427653</v>
       </c>
       <c r="R98" t="n">
-        <v>6233800</v>
+        <v>6233849</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10759,12 +10763,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10791,10 +10795,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471580</v>
+        <v>121471971</v>
       </c>
       <c r="B99" t="n">
-        <v>80242</v>
+        <v>78863</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10807,21 +10811,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10831,10 +10835,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427804</v>
+        <v>427499</v>
       </c>
       <c r="R99" t="n">
-        <v>6233576</v>
+        <v>6233792</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10861,12 +10865,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10893,10 +10897,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471634</v>
+        <v>121471583</v>
       </c>
       <c r="B100" t="n">
-        <v>96725</v>
+        <v>78863</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10909,21 +10913,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10933,10 +10937,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427636</v>
+        <v>427813</v>
       </c>
       <c r="R100" t="n">
-        <v>6233848</v>
+        <v>6233621</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10995,10 +10999,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471620</v>
+        <v>121471614</v>
       </c>
       <c r="B101" t="n">
-        <v>94588</v>
+        <v>80242</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11011,21 +11015,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11035,10 +11039,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>427625</v>
+        <v>427475</v>
       </c>
       <c r="R101" t="n">
-        <v>6233894</v>
+        <v>6233836</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11097,10 +11101,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471710</v>
+        <v>121471983</v>
       </c>
       <c r="B102" t="n">
-        <v>94601</v>
+        <v>74697</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11113,21 +11117,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2666</v>
+        <v>6439</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11137,10 +11141,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427448</v>
+        <v>427521</v>
       </c>
       <c r="R102" t="n">
-        <v>6233789</v>
+        <v>6233737</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11167,12 +11171,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11199,10 +11203,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471707</v>
+        <v>121471592</v>
       </c>
       <c r="B103" t="n">
-        <v>96725</v>
+        <v>80242</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11215,21 +11219,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11239,10 +11243,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427809</v>
+        <v>427703</v>
       </c>
       <c r="R103" t="n">
-        <v>6233703</v>
+        <v>6233616</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11301,7 +11305,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471612</v>
+        <v>121471715</v>
       </c>
       <c r="B104" t="n">
         <v>80242</v>
@@ -11341,10 +11345,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427466</v>
+        <v>427445</v>
       </c>
       <c r="R104" t="n">
-        <v>6233828</v>
+        <v>6233860</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11403,10 +11407,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471629</v>
+        <v>121471597</v>
       </c>
       <c r="B105" t="n">
-        <v>80255</v>
+        <v>80242</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11415,25 +11419,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11443,10 +11447,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427602</v>
+        <v>427693</v>
       </c>
       <c r="R105" t="n">
-        <v>6233832</v>
+        <v>6233604</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11505,10 +11509,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471995</v>
+        <v>121471961</v>
       </c>
       <c r="B106" t="n">
-        <v>78863</v>
+        <v>94599</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11521,21 +11525,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6459</v>
+        <v>2667</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11545,10 +11549,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427856</v>
+        <v>427615</v>
       </c>
       <c r="R106" t="n">
-        <v>6233613</v>
+        <v>6233649</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11607,10 +11611,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471576</v>
+        <v>121471955</v>
       </c>
       <c r="B107" t="n">
-        <v>80255</v>
+        <v>94601</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11619,25 +11623,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1144</v>
+        <v>2666</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11647,10 +11651,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427742</v>
+        <v>427741</v>
       </c>
       <c r="R107" t="n">
-        <v>6233565</v>
+        <v>6233529</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11677,12 +11681,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11709,10 +11713,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471700</v>
+        <v>121471558</v>
       </c>
       <c r="B108" t="n">
-        <v>78987</v>
+        <v>80255</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11721,25 +11725,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6431</v>
+        <v>1144</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11749,10 +11753,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>427806</v>
+        <v>427960</v>
       </c>
       <c r="R108" t="n">
-        <v>6233482</v>
+        <v>6233661</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11811,10 +11815,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471952</v>
+        <v>121472002</v>
       </c>
       <c r="B109" t="n">
-        <v>74697</v>
+        <v>94599</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11827,21 +11831,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6439</v>
+        <v>2667</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11851,10 +11855,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>427763</v>
+        <v>427909</v>
       </c>
       <c r="R109" t="n">
-        <v>6233529</v>
+        <v>6233613</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11913,10 +11917,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471598</v>
+        <v>121471704</v>
       </c>
       <c r="B110" t="n">
-        <v>94599</v>
+        <v>96725</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11929,21 +11933,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11953,10 +11957,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427690</v>
+        <v>427785</v>
       </c>
       <c r="R110" t="n">
-        <v>6233595</v>
+        <v>6233585</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12015,7 +12019,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471708</v>
+        <v>121471621</v>
       </c>
       <c r="B111" t="n">
         <v>96725</v>
@@ -12055,10 +12059,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427785</v>
+        <v>427607</v>
       </c>
       <c r="R111" t="n">
-        <v>6233734</v>
+        <v>6233875</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12117,10 +12121,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471632</v>
+        <v>121471643</v>
       </c>
       <c r="B112" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12133,21 +12137,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12157,10 +12161,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427615</v>
+        <v>427671</v>
       </c>
       <c r="R112" t="n">
-        <v>6233825</v>
+        <v>6233821</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12219,10 +12223,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471617</v>
+        <v>121471634</v>
       </c>
       <c r="B113" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12235,21 +12239,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12259,10 +12263,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427526</v>
+        <v>427636</v>
       </c>
       <c r="R113" t="n">
-        <v>6233836</v>
+        <v>6233848</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12321,7 +12325,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471587</v>
+        <v>121471980</v>
       </c>
       <c r="B114" t="n">
         <v>80255</v>
@@ -12361,10 +12365,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427770</v>
+        <v>427532</v>
       </c>
       <c r="R114" t="n">
-        <v>6233624</v>
+        <v>6233767</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12391,12 +12395,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12423,10 +12427,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471990</v>
+        <v>121472007</v>
       </c>
       <c r="B115" t="n">
-        <v>80242</v>
+        <v>80255</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12435,25 +12439,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12463,10 +12467,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427765</v>
+        <v>427892</v>
       </c>
       <c r="R115" t="n">
-        <v>6233765</v>
+        <v>6233623</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12525,10 +12529,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471610</v>
+        <v>121471973</v>
       </c>
       <c r="B116" t="n">
-        <v>80242</v>
+        <v>76948</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12537,25 +12541,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12565,10 +12569,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427487</v>
+        <v>427544</v>
       </c>
       <c r="R116" t="n">
-        <v>6233816</v>
+        <v>6233811</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12595,12 +12599,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12627,10 +12631,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471572</v>
+        <v>121471966</v>
       </c>
       <c r="B117" t="n">
-        <v>96725</v>
+        <v>76948</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12639,25 +12643,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12667,10 +12671,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427982</v>
+        <v>427505</v>
       </c>
       <c r="R117" t="n">
-        <v>6233642</v>
+        <v>6233740</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12697,12 +12701,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12729,10 +12733,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471556</v>
+        <v>121472009</v>
       </c>
       <c r="B118" t="n">
-        <v>96725</v>
+        <v>94599</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12745,21 +12749,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12769,10 +12773,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427948</v>
+        <v>427877</v>
       </c>
       <c r="R118" t="n">
-        <v>6233643</v>
+        <v>6233615</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12799,12 +12803,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12933,7 +12937,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121472016</v>
+        <v>121471708</v>
       </c>
       <c r="B120" t="n">
         <v>96725</v>
@@ -12973,10 +12977,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427903</v>
+        <v>427785</v>
       </c>
       <c r="R120" t="n">
-        <v>6233640</v>
+        <v>6233734</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13003,12 +13007,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13035,7 +13039,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121472013</v>
+        <v>121471706</v>
       </c>
       <c r="B121" t="n">
         <v>96725</v>
@@ -13075,10 +13079,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427882</v>
+        <v>427781</v>
       </c>
       <c r="R121" t="n">
-        <v>6233622</v>
+        <v>6233648</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13105,12 +13109,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13137,10 +13141,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471600</v>
+        <v>121471617</v>
       </c>
       <c r="B122" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13153,21 +13157,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13177,10 +13181,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427698</v>
+        <v>427526</v>
       </c>
       <c r="R122" t="n">
-        <v>6233566</v>
+        <v>6233836</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13239,10 +13243,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471640</v>
+        <v>121471581</v>
       </c>
       <c r="B123" t="n">
-        <v>96725</v>
+        <v>80242</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13255,21 +13259,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13279,10 +13283,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427653</v>
+        <v>427820</v>
       </c>
       <c r="R123" t="n">
-        <v>6233849</v>
+        <v>6233599</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13341,10 +13345,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471993</v>
+        <v>121471630</v>
       </c>
       <c r="B124" t="n">
-        <v>91504</v>
+        <v>76948</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13357,37 +13361,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2014</v>
+        <v>1342</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="J124" t="inlineStr"/>
-      <c r="K124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427859</v>
+        <v>427604</v>
       </c>
       <c r="R124" t="n">
-        <v>6233620</v>
+        <v>6233829</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13414,12 +13415,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13428,7 +13429,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -13447,10 +13447,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121472001</v>
+        <v>121471627</v>
       </c>
       <c r="B125" t="n">
-        <v>94609</v>
+        <v>74697</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13463,21 +13463,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1080</v>
+        <v>6439</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13487,10 +13487,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427908</v>
+        <v>427613</v>
       </c>
       <c r="R125" t="n">
-        <v>6233617</v>
+        <v>6233840</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13517,12 +13517,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13549,10 +13549,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471633</v>
+        <v>121472000</v>
       </c>
       <c r="B126" t="n">
-        <v>90508</v>
+        <v>74697</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13561,25 +13561,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1067</v>
+        <v>6439</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13589,10 +13589,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427629</v>
+        <v>427926</v>
       </c>
       <c r="R126" t="n">
-        <v>6233837</v>
+        <v>6233617</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13619,12 +13619,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13651,10 +13651,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471623</v>
+        <v>121471671</v>
       </c>
       <c r="B127" t="n">
-        <v>80242</v>
+        <v>105759</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13663,25 +13663,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>230185</v>
+        <v>220785</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13691,10 +13691,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427579</v>
+        <v>427912</v>
       </c>
       <c r="R127" t="n">
-        <v>6233850</v>
+        <v>6233611</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13753,10 +13753,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471597</v>
+        <v>121472014</v>
       </c>
       <c r="B128" t="n">
-        <v>80242</v>
+        <v>80255</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13765,25 +13765,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13793,10 +13793,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427693</v>
+        <v>427882</v>
       </c>
       <c r="R128" t="n">
-        <v>6233604</v>
+        <v>6233622</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13823,12 +13823,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13855,10 +13855,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471618</v>
+        <v>121471964</v>
       </c>
       <c r="B129" t="n">
-        <v>96725</v>
+        <v>94599</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13871,21 +13871,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13895,10 +13895,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>427525</v>
+        <v>427511</v>
       </c>
       <c r="R129" t="n">
-        <v>6233838</v>
+        <v>6233739</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13925,12 +13925,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13957,10 +13957,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121472003</v>
+        <v>121471600</v>
       </c>
       <c r="B130" t="n">
-        <v>79018</v>
+        <v>94599</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13969,23 +13969,27 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>132</v>
+        <v>2667</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Liten lundlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bacidina phacodes/tarandina</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
@@ -13993,10 +13997,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>427911</v>
+        <v>427698</v>
       </c>
       <c r="R130" t="n">
-        <v>6233614</v>
+        <v>6233566</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14023,12 +14027,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14055,10 +14059,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471627</v>
+        <v>121471561</v>
       </c>
       <c r="B131" t="n">
-        <v>74697</v>
+        <v>96725</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14071,21 +14075,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14095,10 +14099,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427613</v>
+        <v>427999</v>
       </c>
       <c r="R131" t="n">
-        <v>6233840</v>
+        <v>6233695</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14157,10 +14161,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471646</v>
+        <v>121471647</v>
       </c>
       <c r="B132" t="n">
-        <v>94599</v>
+        <v>96725</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14173,21 +14177,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14197,10 +14201,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427692</v>
+        <v>427720</v>
       </c>
       <c r="R132" t="n">
-        <v>6233796</v>
+        <v>6233787</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14259,7 +14263,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471650</v>
+        <v>121471985</v>
       </c>
       <c r="B133" t="n">
         <v>80242</v>
@@ -14299,10 +14303,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427737</v>
+        <v>427558</v>
       </c>
       <c r="R133" t="n">
-        <v>6233784</v>
+        <v>6233768</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14329,12 +14333,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14361,10 +14365,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471638</v>
+        <v>121471635</v>
       </c>
       <c r="B134" t="n">
-        <v>80242</v>
+        <v>78863</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14377,21 +14381,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14401,10 +14405,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427638</v>
+        <v>427637</v>
       </c>
       <c r="R134" t="n">
-        <v>6233822</v>
+        <v>6233845</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14463,10 +14467,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471631</v>
+        <v>121471651</v>
       </c>
       <c r="B135" t="n">
-        <v>80242</v>
+        <v>78863</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14479,21 +14483,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14503,10 +14507,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427601</v>
+        <v>427737</v>
       </c>
       <c r="R135" t="n">
-        <v>6233830</v>
+        <v>6233789</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14565,10 +14569,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471959</v>
+        <v>121471707</v>
       </c>
       <c r="B136" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14581,21 +14585,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14605,10 +14609,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427734</v>
+        <v>427809</v>
       </c>
       <c r="R136" t="n">
-        <v>6233532</v>
+        <v>6233703</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14635,12 +14639,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14667,10 +14671,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471957</v>
+        <v>121471587</v>
       </c>
       <c r="B137" t="n">
-        <v>94599</v>
+        <v>80255</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14679,25 +14683,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14707,10 +14711,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427731</v>
+        <v>427770</v>
       </c>
       <c r="R137" t="n">
-        <v>6233539</v>
+        <v>6233624</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14737,12 +14741,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14769,10 +14773,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471651</v>
+        <v>121471576</v>
       </c>
       <c r="B138" t="n">
-        <v>78863</v>
+        <v>80255</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14781,25 +14785,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6459</v>
+        <v>1144</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14809,10 +14813,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427737</v>
+        <v>427742</v>
       </c>
       <c r="R138" t="n">
-        <v>6233789</v>
+        <v>6233565</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14871,10 +14875,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471703</v>
+        <v>121471565</v>
       </c>
       <c r="B139" t="n">
-        <v>74697</v>
+        <v>76948</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14883,25 +14887,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6439</v>
+        <v>1342</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14911,10 +14915,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>427770</v>
+        <v>428016</v>
       </c>
       <c r="R139" t="n">
-        <v>6233580</v>
+        <v>6233689</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14973,10 +14977,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471649</v>
+        <v>121471965</v>
       </c>
       <c r="B140" t="n">
-        <v>80255</v>
+        <v>76948</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14985,25 +14989,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15013,10 +15017,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>427720</v>
+        <v>427509</v>
       </c>
       <c r="R140" t="n">
-        <v>6233787</v>
+        <v>6233731</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15043,12 +15047,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15075,10 +15079,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471578</v>
+        <v>121471645</v>
       </c>
       <c r="B141" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15087,25 +15091,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15115,10 +15119,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>427749</v>
+        <v>427702</v>
       </c>
       <c r="R141" t="n">
-        <v>6233573</v>
+        <v>6233806</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15177,10 +15181,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471999</v>
+        <v>121471716</v>
       </c>
       <c r="B142" t="n">
-        <v>80255</v>
+        <v>80242</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15189,25 +15193,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15217,10 +15221,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>427916</v>
+        <v>427547</v>
       </c>
       <c r="R142" t="n">
-        <v>6233634</v>
+        <v>6233865</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15247,12 +15251,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15279,7 +15283,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471715</v>
+        <v>121471990</v>
       </c>
       <c r="B143" t="n">
         <v>80242</v>
@@ -15319,10 +15323,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>427445</v>
+        <v>427765</v>
       </c>
       <c r="R143" t="n">
-        <v>6233860</v>
+        <v>6233765</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15349,12 +15353,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15381,7 +15385,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471607</v>
+        <v>121471984</v>
       </c>
       <c r="B144" t="n">
         <v>80242</v>
@@ -15421,10 +15425,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>427582</v>
+        <v>427530</v>
       </c>
       <c r="R144" t="n">
-        <v>6233752</v>
+        <v>6233736</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15451,12 +15455,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15483,10 +15487,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471559</v>
+        <v>121471610</v>
       </c>
       <c r="B145" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15495,25 +15499,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15523,10 +15527,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427960</v>
+        <v>427487</v>
       </c>
       <c r="R145" t="n">
-        <v>6233661</v>
+        <v>6233816</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15585,10 +15589,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121472002</v>
+        <v>121471977</v>
       </c>
       <c r="B146" t="n">
-        <v>94599</v>
+        <v>96725</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15601,21 +15605,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15625,10 +15629,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427909</v>
+        <v>427533</v>
       </c>
       <c r="R146" t="n">
-        <v>6233613</v>
+        <v>6233765</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15687,10 +15691,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471992</v>
+        <v>121471641</v>
       </c>
       <c r="B147" t="n">
-        <v>94588</v>
+        <v>78863</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15703,21 +15707,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2671</v>
+        <v>6459</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15727,10 +15731,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427861</v>
+        <v>427655</v>
       </c>
       <c r="R147" t="n">
-        <v>6233620</v>
+        <v>6233850</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15757,12 +15761,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15789,10 +15793,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471983</v>
+        <v>121471636</v>
       </c>
       <c r="B148" t="n">
-        <v>74697</v>
+        <v>80242</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15805,21 +15809,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15829,10 +15833,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427521</v>
+        <v>427650</v>
       </c>
       <c r="R148" t="n">
-        <v>6233737</v>
+        <v>6233855</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15859,12 +15863,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15891,10 +15895,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471562</v>
+        <v>121471591</v>
       </c>
       <c r="B149" t="n">
-        <v>80578</v>
+        <v>80242</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15903,25 +15907,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1182</v>
+        <v>230185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15931,10 +15935,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>428000</v>
+        <v>427724</v>
       </c>
       <c r="R149" t="n">
-        <v>6233692</v>
+        <v>6233617</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15993,10 +15997,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471564</v>
+        <v>121471593</v>
       </c>
       <c r="B150" t="n">
-        <v>80255</v>
+        <v>80242</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16005,25 +16009,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16033,10 +16037,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>428014</v>
+        <v>427699</v>
       </c>
       <c r="R150" t="n">
-        <v>6233692</v>
+        <v>6233608</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16095,10 +16099,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471974</v>
+        <v>121471959</v>
       </c>
       <c r="B151" t="n">
-        <v>90508</v>
+        <v>80242</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16107,25 +16111,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16135,10 +16139,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>427554</v>
+        <v>427734</v>
       </c>
       <c r="R151" t="n">
-        <v>6233803</v>
+        <v>6233532</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16197,10 +16201,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471716</v>
+        <v>121471562</v>
       </c>
       <c r="B152" t="n">
-        <v>80242</v>
+        <v>80578</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16209,25 +16213,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>230185</v>
+        <v>1182</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16237,10 +16241,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>427547</v>
+        <v>428000</v>
       </c>
       <c r="R152" t="n">
-        <v>6233865</v>
+        <v>6233692</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16299,10 +16303,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471521</v>
+        <v>121471629</v>
       </c>
       <c r="B153" t="n">
-        <v>80242</v>
+        <v>80255</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16311,25 +16315,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16339,10 +16343,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>427794</v>
+        <v>427602</v>
       </c>
       <c r="R153" t="n">
-        <v>6233483</v>
+        <v>6233832</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16401,10 +16405,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121472004</v>
+        <v>121471963</v>
       </c>
       <c r="B154" t="n">
-        <v>80242</v>
+        <v>94599</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16417,21 +16421,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16441,10 +16445,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>427892</v>
+        <v>427520</v>
       </c>
       <c r="R154" t="n">
-        <v>6233623</v>
+        <v>6233715</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16503,10 +16507,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471641</v>
+        <v>121471556</v>
       </c>
       <c r="B155" t="n">
-        <v>78863</v>
+        <v>96725</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16519,21 +16523,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16543,10 +16547,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>427655</v>
+        <v>427948</v>
       </c>
       <c r="R155" t="n">
-        <v>6233850</v>
+        <v>6233643</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16605,10 +16609,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471520</v>
+        <v>121472015</v>
       </c>
       <c r="B156" t="n">
-        <v>80242</v>
+        <v>74697</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16621,21 +16625,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16645,10 +16649,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>427789</v>
+        <v>427903</v>
       </c>
       <c r="R156" t="n">
-        <v>6233516</v>
+        <v>6233639</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16675,12 +16679,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16707,10 +16711,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471601</v>
+        <v>121471718</v>
       </c>
       <c r="B157" t="n">
-        <v>80242</v>
+        <v>80255</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16719,25 +16723,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16747,10 +16751,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>427688</v>
+        <v>427584</v>
       </c>
       <c r="R157" t="n">
-        <v>6233590</v>
+        <v>6233863</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16809,10 +16813,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471980</v>
+        <v>121471620</v>
       </c>
       <c r="B158" t="n">
-        <v>80255</v>
+        <v>94588</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16821,25 +16825,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1144</v>
+        <v>2671</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16849,10 +16853,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>427532</v>
+        <v>427625</v>
       </c>
       <c r="R158" t="n">
-        <v>6233767</v>
+        <v>6233894</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16879,12 +16883,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16911,10 +16915,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121472007</v>
+        <v>121471575</v>
       </c>
       <c r="B159" t="n">
-        <v>80255</v>
+        <v>91112</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16923,25 +16927,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1144</v>
+        <v>2023</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16951,10 +16955,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>427892</v>
+        <v>427837</v>
       </c>
       <c r="R159" t="n">
-        <v>6233623</v>
+        <v>6233582</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16981,12 +16985,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17013,10 +17017,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471998</v>
+        <v>121472003</v>
       </c>
       <c r="B160" t="n">
-        <v>76948</v>
+        <v>79018</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17029,23 +17033,19 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1342</v>
+        <v>132</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Liten lundlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>(Weigel) Ach.</t>
-        </is>
-      </c>
+          <t>Bacidina phacodes/tarandina</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -17053,10 +17053,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>427915</v>
+        <v>427911</v>
       </c>
       <c r="R160" t="n">
-        <v>6233632</v>
+        <v>6233614</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17115,7 +17115,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471619</v>
+        <v>121471563</v>
       </c>
       <c r="B161" t="n">
         <v>96725</v>
@@ -17155,10 +17155,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>427624</v>
+        <v>428012</v>
       </c>
       <c r="R161" t="n">
-        <v>6233894</v>
+        <v>6233689</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471572</v>
+        <v>121471633</v>
       </c>
       <c r="B15" t="n">
-        <v>96725</v>
+        <v>90508</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2606</v>
+        <v>1067</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427982</v>
+        <v>427629</v>
       </c>
       <c r="R15" t="n">
-        <v>6233642</v>
+        <v>6233837</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121471608</v>
+        <v>121471572</v>
       </c>
       <c r="B16" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427566</v>
+        <v>427982</v>
       </c>
       <c r="R16" t="n">
-        <v>6233756</v>
+        <v>6233642</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121471560</v>
+        <v>121471608</v>
       </c>
       <c r="B17" t="n">
         <v>80242</v>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428008</v>
+        <v>427566</v>
       </c>
       <c r="R17" t="n">
-        <v>6233671</v>
+        <v>6233756</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121471604</v>
+        <v>121471560</v>
       </c>
       <c r="B18" t="n">
         <v>80242</v>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427595</v>
+        <v>428008</v>
       </c>
       <c r="R18" t="n">
-        <v>6233781</v>
+        <v>6233671</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121471633</v>
+        <v>121471604</v>
       </c>
       <c r="B19" t="n">
-        <v>90508</v>
+        <v>80242</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427629</v>
+        <v>427595</v>
       </c>
       <c r="R19" t="n">
-        <v>6233837</v>
+        <v>6233781</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121472013</v>
+        <v>121471714</v>
       </c>
       <c r="B20" t="n">
-        <v>96725</v>
+        <v>78407</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2606</v>
+        <v>924</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427882</v>
+        <v>427435</v>
       </c>
       <c r="R20" t="n">
-        <v>6233622</v>
+        <v>6233855</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121471712</v>
+        <v>121471564</v>
       </c>
       <c r="B21" t="n">
-        <v>96725</v>
+        <v>80255</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>427439</v>
+        <v>428014</v>
       </c>
       <c r="R21" t="n">
-        <v>6233838</v>
+        <v>6233692</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121471637</v>
+        <v>121471999</v>
       </c>
       <c r="B22" t="n">
-        <v>96725</v>
+        <v>80255</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427638</v>
+        <v>427916</v>
       </c>
       <c r="R22" t="n">
-        <v>6233822</v>
+        <v>6233634</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3230,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471714</v>
+        <v>121472013</v>
       </c>
       <c r="B25" t="n">
-        <v>78407</v>
+        <v>96725</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3242,25 +3242,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>924</v>
+        <v>2606</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427435</v>
+        <v>427882</v>
       </c>
       <c r="R25" t="n">
-        <v>6233855</v>
+        <v>6233622</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3300,12 +3300,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,10 +3332,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471564</v>
+        <v>121471712</v>
       </c>
       <c r="B26" t="n">
-        <v>80255</v>
+        <v>96725</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3344,25 +3344,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428014</v>
+        <v>427439</v>
       </c>
       <c r="R26" t="n">
-        <v>6233692</v>
+        <v>6233838</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471999</v>
+        <v>121471637</v>
       </c>
       <c r="B27" t="n">
-        <v>80255</v>
+        <v>96725</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427916</v>
+        <v>427638</v>
       </c>
       <c r="R27" t="n">
-        <v>6233634</v>
+        <v>6233822</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471992</v>
+        <v>121471642</v>
       </c>
       <c r="B35" t="n">
-        <v>94588</v>
+        <v>80242</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4266,21 +4266,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427861</v>
+        <v>427654</v>
       </c>
       <c r="R35" t="n">
-        <v>6233620</v>
+        <v>6233848</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,12 +4320,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4352,7 +4352,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471642</v>
+        <v>121471607</v>
       </c>
       <c r="B36" t="n">
         <v>80242</v>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427654</v>
+        <v>427582</v>
       </c>
       <c r="R36" t="n">
-        <v>6233848</v>
+        <v>6233752</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471607</v>
+        <v>121471520</v>
       </c>
       <c r="B37" t="n">
         <v>80242</v>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427582</v>
+        <v>427789</v>
       </c>
       <c r="R37" t="n">
-        <v>6233752</v>
+        <v>6233516</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4556,10 +4556,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471520</v>
+        <v>121471992</v>
       </c>
       <c r="B38" t="n">
-        <v>80242</v>
+        <v>94588</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4572,21 +4572,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427789</v>
+        <v>427861</v>
       </c>
       <c r="R38" t="n">
-        <v>6233516</v>
+        <v>6233620</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4760,10 +4760,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471521</v>
+        <v>121471649</v>
       </c>
       <c r="B40" t="n">
-        <v>80242</v>
+        <v>80255</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4772,25 +4772,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427794</v>
+        <v>427720</v>
       </c>
       <c r="R40" t="n">
-        <v>6233483</v>
+        <v>6233787</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471649</v>
+        <v>121471578</v>
       </c>
       <c r="B41" t="n">
-        <v>80255</v>
+        <v>76948</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4874,25 +4874,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427720</v>
+        <v>427749</v>
       </c>
       <c r="R41" t="n">
-        <v>6233787</v>
+        <v>6233573</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4964,7 +4964,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471578</v>
+        <v>121471648</v>
       </c>
       <c r="B42" t="n">
         <v>76948</v>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427749</v>
+        <v>427721</v>
       </c>
       <c r="R42" t="n">
-        <v>6233573</v>
+        <v>6233787</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5066,10 +5066,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471648</v>
+        <v>121471521</v>
       </c>
       <c r="B43" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5078,25 +5078,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427721</v>
+        <v>427794</v>
       </c>
       <c r="R43" t="n">
-        <v>6233787</v>
+        <v>6233483</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5168,10 +5168,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471993</v>
+        <v>121471598</v>
       </c>
       <c r="B44" t="n">
-        <v>91504</v>
+        <v>94599</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5180,41 +5180,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2014</v>
+        <v>2667</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427859</v>
+        <v>427690</v>
       </c>
       <c r="R44" t="n">
-        <v>6233620</v>
+        <v>6233595</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5241,12 +5238,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5255,7 +5252,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5274,10 +5270,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471598</v>
+        <v>121471710</v>
       </c>
       <c r="B45" t="n">
-        <v>94599</v>
+        <v>94601</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5290,16 +5286,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5314,10 +5310,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>427690</v>
+        <v>427448</v>
       </c>
       <c r="R45" t="n">
-        <v>6233595</v>
+        <v>6233789</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,10 +5372,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471710</v>
+        <v>121472004</v>
       </c>
       <c r="B46" t="n">
-        <v>94601</v>
+        <v>80242</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5392,21 +5388,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5416,10 +5412,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427448</v>
+        <v>427892</v>
       </c>
       <c r="R46" t="n">
-        <v>6233789</v>
+        <v>6233623</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5446,12 +5442,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5478,10 +5474,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121472004</v>
+        <v>121471993</v>
       </c>
       <c r="B47" t="n">
-        <v>80242</v>
+        <v>91504</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5490,38 +5486,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230185</v>
+        <v>2014</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427892</v>
+        <v>427859</v>
       </c>
       <c r="R47" t="n">
-        <v>6233623</v>
+        <v>6233620</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5562,6 +5561,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -8245,10 +8245,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121472006</v>
+        <v>121471557</v>
       </c>
       <c r="B74" t="n">
-        <v>76948</v>
+        <v>94588</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8257,25 +8257,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>427892</v>
+        <v>427948</v>
       </c>
       <c r="R74" t="n">
-        <v>6233623</v>
+        <v>6233643</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8315,12 +8315,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8347,10 +8347,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471585</v>
+        <v>121471599</v>
       </c>
       <c r="B75" t="n">
-        <v>76948</v>
+        <v>94601</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8359,25 +8359,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1342</v>
+        <v>2666</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8387,10 +8387,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>427748</v>
+        <v>427685</v>
       </c>
       <c r="R75" t="n">
-        <v>6233622</v>
+        <v>6233593</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8449,10 +8449,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471557</v>
+        <v>121471589</v>
       </c>
       <c r="B76" t="n">
-        <v>94588</v>
+        <v>96725</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8465,21 +8465,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8489,10 +8489,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427948</v>
+        <v>427804</v>
       </c>
       <c r="R76" t="n">
-        <v>6233643</v>
+        <v>6233688</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8551,10 +8551,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471599</v>
+        <v>121471584</v>
       </c>
       <c r="B77" t="n">
-        <v>94601</v>
+        <v>96725</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8567,21 +8567,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2666</v>
+        <v>2606</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427685</v>
+        <v>427817</v>
       </c>
       <c r="R77" t="n">
-        <v>6233593</v>
+        <v>6233621</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8653,10 +8653,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471638</v>
+        <v>121471700</v>
       </c>
       <c r="B78" t="n">
-        <v>80242</v>
+        <v>78987</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8669,21 +8669,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>230185</v>
+        <v>6431</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8693,10 +8693,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427638</v>
+        <v>427806</v>
       </c>
       <c r="R78" t="n">
-        <v>6233822</v>
+        <v>6233482</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8755,10 +8755,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471589</v>
+        <v>121471952</v>
       </c>
       <c r="B79" t="n">
-        <v>96725</v>
+        <v>74697</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8771,21 +8771,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2606</v>
+        <v>6439</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427804</v>
+        <v>427763</v>
       </c>
       <c r="R79" t="n">
-        <v>6233688</v>
+        <v>6233529</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8825,12 +8825,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8857,10 +8857,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471584</v>
+        <v>121472006</v>
       </c>
       <c r="B80" t="n">
-        <v>96725</v>
+        <v>76948</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8869,25 +8869,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427817</v>
+        <v>427892</v>
       </c>
       <c r="R80" t="n">
-        <v>6233621</v>
+        <v>6233623</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8927,12 +8927,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8959,10 +8959,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471700</v>
+        <v>121471585</v>
       </c>
       <c r="B81" t="n">
-        <v>78987</v>
+        <v>76948</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8971,25 +8971,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6431</v>
+        <v>1342</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427806</v>
+        <v>427748</v>
       </c>
       <c r="R81" t="n">
-        <v>6233482</v>
+        <v>6233622</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9061,10 +9061,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471952</v>
+        <v>121471638</v>
       </c>
       <c r="B82" t="n">
-        <v>74697</v>
+        <v>80242</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9077,21 +9077,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9101,10 +9101,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427763</v>
+        <v>427638</v>
       </c>
       <c r="R82" t="n">
-        <v>6233529</v>
+        <v>6233822</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9131,12 +9131,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9163,10 +9163,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471596</v>
+        <v>121471968</v>
       </c>
       <c r="B83" t="n">
-        <v>74699</v>
+        <v>57370</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9175,25 +9175,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>306</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9203,10 +9203,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427686</v>
+        <v>427512</v>
       </c>
       <c r="R83" t="n">
-        <v>6233621</v>
+        <v>6233745</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9233,12 +9233,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9265,10 +9265,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471624</v>
+        <v>121471596</v>
       </c>
       <c r="B84" t="n">
-        <v>74563</v>
+        <v>74699</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9277,25 +9277,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1116</v>
+        <v>306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9305,10 +9305,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427594</v>
+        <v>427686</v>
       </c>
       <c r="R84" t="n">
-        <v>6233828</v>
+        <v>6233621</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9367,10 +9367,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121472011</v>
+        <v>121471709</v>
       </c>
       <c r="B85" t="n">
-        <v>76948</v>
+        <v>80242</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9379,25 +9379,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9407,10 +9407,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427874</v>
+        <v>427452</v>
       </c>
       <c r="R85" t="n">
-        <v>6233615</v>
+        <v>6233794</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9469,10 +9469,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471577</v>
+        <v>121471954</v>
       </c>
       <c r="B86" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9485,21 +9485,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427749</v>
+        <v>427742</v>
       </c>
       <c r="R86" t="n">
-        <v>6233572</v>
+        <v>6233542</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9539,12 +9539,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471702</v>
+        <v>121471705</v>
       </c>
       <c r="B87" t="n">
-        <v>96725</v>
+        <v>80242</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9587,21 +9587,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427811</v>
+        <v>427753</v>
       </c>
       <c r="R87" t="n">
-        <v>6233480</v>
+        <v>6233606</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9673,10 +9673,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471995</v>
+        <v>121471631</v>
       </c>
       <c r="B88" t="n">
-        <v>78863</v>
+        <v>80242</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9689,21 +9689,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427856</v>
+        <v>427601</v>
       </c>
       <c r="R88" t="n">
-        <v>6233613</v>
+        <v>6233830</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9743,12 +9743,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9775,10 +9775,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471703</v>
+        <v>121471624</v>
       </c>
       <c r="B89" t="n">
-        <v>74697</v>
+        <v>74563</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9787,25 +9787,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6439</v>
+        <v>1116</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9815,10 +9815,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427770</v>
+        <v>427594</v>
       </c>
       <c r="R89" t="n">
-        <v>6233580</v>
+        <v>6233828</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9877,10 +9877,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471968</v>
+        <v>121472011</v>
       </c>
       <c r="B90" t="n">
-        <v>57370</v>
+        <v>76948</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9893,21 +9893,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>1342</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427512</v>
+        <v>427874</v>
       </c>
       <c r="R90" t="n">
-        <v>6233745</v>
+        <v>6233615</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9979,10 +9979,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471709</v>
+        <v>121471577</v>
       </c>
       <c r="B91" t="n">
-        <v>80242</v>
+        <v>94599</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9995,21 +9995,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10019,10 +10019,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427452</v>
+        <v>427749</v>
       </c>
       <c r="R91" t="n">
-        <v>6233794</v>
+        <v>6233572</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10081,10 +10081,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471954</v>
+        <v>121471702</v>
       </c>
       <c r="B92" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10097,21 +10097,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427742</v>
+        <v>427811</v>
       </c>
       <c r="R92" t="n">
-        <v>6233542</v>
+        <v>6233480</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10151,12 +10151,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10183,10 +10183,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471705</v>
+        <v>121471995</v>
       </c>
       <c r="B93" t="n">
-        <v>80242</v>
+        <v>78863</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10199,21 +10199,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427753</v>
+        <v>427856</v>
       </c>
       <c r="R93" t="n">
-        <v>6233606</v>
+        <v>6233613</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10253,12 +10253,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10285,10 +10285,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471631</v>
+        <v>121471703</v>
       </c>
       <c r="B94" t="n">
-        <v>80242</v>
+        <v>74697</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10301,21 +10301,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427601</v>
+        <v>427770</v>
       </c>
       <c r="R94" t="n">
-        <v>6233830</v>
+        <v>6233580</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10387,10 +10387,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471998</v>
+        <v>121472001</v>
       </c>
       <c r="B95" t="n">
-        <v>76948</v>
+        <v>94609</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10399,25 +10399,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1342</v>
+        <v>1080</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10427,10 +10427,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427915</v>
+        <v>427908</v>
       </c>
       <c r="R95" t="n">
-        <v>6233632</v>
+        <v>6233617</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10489,10 +10489,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471957</v>
+        <v>121471998</v>
       </c>
       <c r="B96" t="n">
-        <v>94599</v>
+        <v>76948</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10501,25 +10501,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10529,10 +10529,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427731</v>
+        <v>427915</v>
       </c>
       <c r="R96" t="n">
-        <v>6233539</v>
+        <v>6233632</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10591,10 +10591,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121472001</v>
+        <v>121471640</v>
       </c>
       <c r="B97" t="n">
-        <v>94609</v>
+        <v>96725</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10607,21 +10607,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1080</v>
+        <v>2606</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10631,10 +10631,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427908</v>
+        <v>427653</v>
       </c>
       <c r="R97" t="n">
-        <v>6233617</v>
+        <v>6233849</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10661,12 +10661,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10693,10 +10693,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471640</v>
+        <v>121471971</v>
       </c>
       <c r="B98" t="n">
-        <v>96725</v>
+        <v>78863</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10709,21 +10709,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10733,10 +10733,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427653</v>
+        <v>427499</v>
       </c>
       <c r="R98" t="n">
-        <v>6233849</v>
+        <v>6233792</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10763,12 +10763,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10795,7 +10795,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471971</v>
+        <v>121471583</v>
       </c>
       <c r="B99" t="n">
         <v>78863</v>
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427499</v>
+        <v>427813</v>
       </c>
       <c r="R99" t="n">
-        <v>6233792</v>
+        <v>6233621</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10865,12 +10865,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10897,10 +10897,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471583</v>
+        <v>121471957</v>
       </c>
       <c r="B100" t="n">
-        <v>78863</v>
+        <v>94599</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10913,21 +10913,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6459</v>
+        <v>2667</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10937,10 +10937,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427813</v>
+        <v>427731</v>
       </c>
       <c r="R100" t="n">
-        <v>6233621</v>
+        <v>6233539</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11101,10 +11101,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471983</v>
+        <v>121471961</v>
       </c>
       <c r="B102" t="n">
-        <v>74697</v>
+        <v>94599</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11117,21 +11117,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6439</v>
+        <v>2667</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11141,10 +11141,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427521</v>
+        <v>427615</v>
       </c>
       <c r="R102" t="n">
-        <v>6233737</v>
+        <v>6233649</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11203,10 +11203,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471592</v>
+        <v>121471955</v>
       </c>
       <c r="B103" t="n">
-        <v>80242</v>
+        <v>94601</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11219,21 +11219,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11243,10 +11243,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427703</v>
+        <v>427741</v>
       </c>
       <c r="R103" t="n">
-        <v>6233616</v>
+        <v>6233529</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11273,12 +11273,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11305,10 +11305,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471715</v>
+        <v>121471983</v>
       </c>
       <c r="B104" t="n">
-        <v>80242</v>
+        <v>74697</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11321,21 +11321,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427445</v>
+        <v>427521</v>
       </c>
       <c r="R104" t="n">
-        <v>6233860</v>
+        <v>6233737</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11375,12 +11375,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11407,7 +11407,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471597</v>
+        <v>121471592</v>
       </c>
       <c r="B105" t="n">
         <v>80242</v>
@@ -11447,10 +11447,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427693</v>
+        <v>427703</v>
       </c>
       <c r="R105" t="n">
-        <v>6233604</v>
+        <v>6233616</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11509,10 +11509,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471961</v>
+        <v>121471715</v>
       </c>
       <c r="B106" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11525,21 +11525,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11549,10 +11549,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427615</v>
+        <v>427445</v>
       </c>
       <c r="R106" t="n">
-        <v>6233649</v>
+        <v>6233860</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11579,12 +11579,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11611,10 +11611,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471955</v>
+        <v>121471597</v>
       </c>
       <c r="B107" t="n">
-        <v>94601</v>
+        <v>80242</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11627,21 +11627,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11651,10 +11651,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427741</v>
+        <v>427693</v>
       </c>
       <c r="R107" t="n">
-        <v>6233529</v>
+        <v>6233604</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11681,12 +11681,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11713,10 +11713,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471558</v>
+        <v>121472002</v>
       </c>
       <c r="B108" t="n">
-        <v>80255</v>
+        <v>94599</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11725,25 +11725,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11753,10 +11753,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>427960</v>
+        <v>427909</v>
       </c>
       <c r="R108" t="n">
-        <v>6233661</v>
+        <v>6233613</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11783,12 +11783,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11815,10 +11815,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121472002</v>
+        <v>121471558</v>
       </c>
       <c r="B109" t="n">
-        <v>94599</v>
+        <v>80255</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11827,25 +11827,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11855,10 +11855,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>427909</v>
+        <v>427960</v>
       </c>
       <c r="R109" t="n">
-        <v>6233613</v>
+        <v>6233661</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12835,10 +12835,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471976</v>
+        <v>121471617</v>
       </c>
       <c r="B119" t="n">
-        <v>96725</v>
+        <v>80242</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12851,21 +12851,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12875,10 +12875,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427576</v>
+        <v>427526</v>
       </c>
       <c r="R119" t="n">
-        <v>6233800</v>
+        <v>6233836</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12905,12 +12905,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12937,10 +12937,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471708</v>
+        <v>121471581</v>
       </c>
       <c r="B120" t="n">
-        <v>96725</v>
+        <v>80242</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12953,21 +12953,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12977,10 +12977,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427785</v>
+        <v>427820</v>
       </c>
       <c r="R120" t="n">
-        <v>6233734</v>
+        <v>6233599</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13039,7 +13039,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471706</v>
+        <v>121471976</v>
       </c>
       <c r="B121" t="n">
         <v>96725</v>
@@ -13079,10 +13079,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427781</v>
+        <v>427576</v>
       </c>
       <c r="R121" t="n">
-        <v>6233648</v>
+        <v>6233800</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13109,12 +13109,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13141,10 +13141,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471617</v>
+        <v>121471708</v>
       </c>
       <c r="B122" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13157,21 +13157,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13181,10 +13181,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427526</v>
+        <v>427785</v>
       </c>
       <c r="R122" t="n">
-        <v>6233836</v>
+        <v>6233734</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13243,10 +13243,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471581</v>
+        <v>121471706</v>
       </c>
       <c r="B123" t="n">
-        <v>80242</v>
+        <v>96725</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13259,21 +13259,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13283,10 +13283,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427820</v>
+        <v>427781</v>
       </c>
       <c r="R123" t="n">
-        <v>6233599</v>
+        <v>6233648</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -15079,10 +15079,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471645</v>
+        <v>121471641</v>
       </c>
       <c r="B141" t="n">
-        <v>80242</v>
+        <v>78863</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15095,21 +15095,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15119,10 +15119,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>427702</v>
+        <v>427655</v>
       </c>
       <c r="R141" t="n">
-        <v>6233806</v>
+        <v>6233850</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15181,7 +15181,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471716</v>
+        <v>121471645</v>
       </c>
       <c r="B142" t="n">
         <v>80242</v>
@@ -15221,10 +15221,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>427547</v>
+        <v>427702</v>
       </c>
       <c r="R142" t="n">
-        <v>6233865</v>
+        <v>6233806</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15283,7 +15283,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471990</v>
+        <v>121471716</v>
       </c>
       <c r="B143" t="n">
         <v>80242</v>
@@ -15323,10 +15323,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>427765</v>
+        <v>427547</v>
       </c>
       <c r="R143" t="n">
-        <v>6233765</v>
+        <v>6233865</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15353,12 +15353,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15385,7 +15385,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471984</v>
+        <v>121471990</v>
       </c>
       <c r="B144" t="n">
         <v>80242</v>
@@ -15425,10 +15425,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>427530</v>
+        <v>427765</v>
       </c>
       <c r="R144" t="n">
-        <v>6233736</v>
+        <v>6233765</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15487,7 +15487,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471610</v>
+        <v>121471984</v>
       </c>
       <c r="B145" t="n">
         <v>80242</v>
@@ -15527,10 +15527,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427487</v>
+        <v>427530</v>
       </c>
       <c r="R145" t="n">
-        <v>6233816</v>
+        <v>6233736</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15557,12 +15557,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15589,10 +15589,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471977</v>
+        <v>121471610</v>
       </c>
       <c r="B146" t="n">
-        <v>96725</v>
+        <v>80242</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15605,21 +15605,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15629,10 +15629,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427533</v>
+        <v>427487</v>
       </c>
       <c r="R146" t="n">
-        <v>6233765</v>
+        <v>6233816</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15659,12 +15659,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15691,10 +15691,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471641</v>
+        <v>121471977</v>
       </c>
       <c r="B147" t="n">
-        <v>78863</v>
+        <v>96725</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15707,21 +15707,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15731,10 +15731,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427655</v>
+        <v>427533</v>
       </c>
       <c r="R147" t="n">
-        <v>6233850</v>
+        <v>6233765</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15761,12 +15761,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15793,10 +15793,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471636</v>
+        <v>121471963</v>
       </c>
       <c r="B148" t="n">
-        <v>80242</v>
+        <v>94599</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15809,21 +15809,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15833,10 +15833,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427650</v>
+        <v>427520</v>
       </c>
       <c r="R148" t="n">
-        <v>6233855</v>
+        <v>6233715</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15863,12 +15863,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15895,10 +15895,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471591</v>
+        <v>121471562</v>
       </c>
       <c r="B149" t="n">
-        <v>80242</v>
+        <v>80578</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15907,25 +15907,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>230185</v>
+        <v>1182</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15935,10 +15935,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>427724</v>
+        <v>428000</v>
       </c>
       <c r="R149" t="n">
-        <v>6233617</v>
+        <v>6233692</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15997,10 +15997,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471593</v>
+        <v>121471629</v>
       </c>
       <c r="B150" t="n">
-        <v>80242</v>
+        <v>80255</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16009,25 +16009,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16037,10 +16037,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>427699</v>
+        <v>427602</v>
       </c>
       <c r="R150" t="n">
-        <v>6233608</v>
+        <v>6233832</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16099,7 +16099,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471959</v>
+        <v>121471636</v>
       </c>
       <c r="B151" t="n">
         <v>80242</v>
@@ -16139,10 +16139,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>427734</v>
+        <v>427650</v>
       </c>
       <c r="R151" t="n">
-        <v>6233532</v>
+        <v>6233855</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16169,12 +16169,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16201,10 +16201,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471562</v>
+        <v>121471591</v>
       </c>
       <c r="B152" t="n">
-        <v>80578</v>
+        <v>80242</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16213,25 +16213,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1182</v>
+        <v>230185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16241,10 +16241,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>428000</v>
+        <v>427724</v>
       </c>
       <c r="R152" t="n">
-        <v>6233692</v>
+        <v>6233617</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16303,10 +16303,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471629</v>
+        <v>121471593</v>
       </c>
       <c r="B153" t="n">
-        <v>80255</v>
+        <v>80242</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16315,25 +16315,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16343,10 +16343,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>427602</v>
+        <v>427699</v>
       </c>
       <c r="R153" t="n">
-        <v>6233832</v>
+        <v>6233608</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16405,10 +16405,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471963</v>
+        <v>121471959</v>
       </c>
       <c r="B154" t="n">
-        <v>94599</v>
+        <v>80242</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16421,21 +16421,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16445,10 +16445,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>427520</v>
+        <v>427734</v>
       </c>
       <c r="R154" t="n">
-        <v>6233715</v>
+        <v>6233532</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -5168,10 +5168,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471598</v>
+        <v>121471993</v>
       </c>
       <c r="B44" t="n">
-        <v>94599</v>
+        <v>91504</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5180,38 +5180,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2667</v>
+        <v>2014</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427690</v>
+        <v>427859</v>
       </c>
       <c r="R44" t="n">
-        <v>6233595</v>
+        <v>6233620</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5238,12 +5241,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5252,6 +5255,7 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5270,10 +5274,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471710</v>
+        <v>121471598</v>
       </c>
       <c r="B45" t="n">
-        <v>94601</v>
+        <v>94599</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5286,16 +5290,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5310,10 +5314,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>427448</v>
+        <v>427690</v>
       </c>
       <c r="R45" t="n">
-        <v>6233789</v>
+        <v>6233595</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5372,10 +5376,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121472004</v>
+        <v>121471710</v>
       </c>
       <c r="B46" t="n">
-        <v>80242</v>
+        <v>94601</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5388,21 +5392,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5412,10 +5416,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427892</v>
+        <v>427448</v>
       </c>
       <c r="R46" t="n">
-        <v>6233623</v>
+        <v>6233789</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5442,12 +5446,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5474,10 +5478,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471993</v>
+        <v>121472004</v>
       </c>
       <c r="B47" t="n">
-        <v>91504</v>
+        <v>80242</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5486,41 +5490,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2014</v>
+        <v>230185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427859</v>
+        <v>427892</v>
       </c>
       <c r="R47" t="n">
-        <v>6233620</v>
+        <v>6233623</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5561,7 +5562,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5580,10 +5580,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471979</v>
+        <v>121471628</v>
       </c>
       <c r="B48" t="n">
-        <v>76948</v>
+        <v>96725</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5592,25 +5592,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427533</v>
+        <v>427604</v>
       </c>
       <c r="R48" t="n">
-        <v>6233765</v>
+        <v>6233834</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5650,12 +5650,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5682,10 +5682,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471719</v>
+        <v>121471619</v>
       </c>
       <c r="B49" t="n">
-        <v>76948</v>
+        <v>96725</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5694,25 +5694,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5722,10 +5722,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427583</v>
+        <v>427624</v>
       </c>
       <c r="R49" t="n">
-        <v>6233861</v>
+        <v>6233894</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5784,10 +5784,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471978</v>
+        <v>121471644</v>
       </c>
       <c r="B50" t="n">
-        <v>94599</v>
+        <v>78863</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5800,21 +5800,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2667</v>
+        <v>6459</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5824,10 +5824,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427533</v>
+        <v>427671</v>
       </c>
       <c r="R50" t="n">
-        <v>6233765</v>
+        <v>6233821</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5886,10 +5886,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471602</v>
+        <v>121472010</v>
       </c>
       <c r="B51" t="n">
-        <v>94599</v>
+        <v>78987</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5902,21 +5902,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2667</v>
+        <v>6431</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5926,10 +5926,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427641</v>
+        <v>427877</v>
       </c>
       <c r="R51" t="n">
-        <v>6233630</v>
+        <v>6233615</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5956,12 +5956,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5988,10 +5988,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471644</v>
+        <v>121471979</v>
       </c>
       <c r="B52" t="n">
-        <v>78863</v>
+        <v>76948</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6000,25 +6000,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6028,10 +6028,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427671</v>
+        <v>427533</v>
       </c>
       <c r="R52" t="n">
-        <v>6233821</v>
+        <v>6233765</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6058,12 +6058,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6090,10 +6090,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121472010</v>
+        <v>121471719</v>
       </c>
       <c r="B53" t="n">
-        <v>78987</v>
+        <v>76948</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6102,25 +6102,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6431</v>
+        <v>1342</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6130,10 +6130,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427877</v>
+        <v>427583</v>
       </c>
       <c r="R53" t="n">
-        <v>6233615</v>
+        <v>6233861</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6160,12 +6160,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6192,10 +6192,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471628</v>
+        <v>121471978</v>
       </c>
       <c r="B54" t="n">
-        <v>96725</v>
+        <v>94599</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6208,21 +6208,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427604</v>
+        <v>427533</v>
       </c>
       <c r="R54" t="n">
-        <v>6233834</v>
+        <v>6233765</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6262,12 +6262,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6294,10 +6294,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471619</v>
+        <v>121471602</v>
       </c>
       <c r="B55" t="n">
-        <v>96725</v>
+        <v>94599</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6310,21 +6310,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6334,10 +6334,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>427624</v>
+        <v>427641</v>
       </c>
       <c r="R55" t="n">
-        <v>6233894</v>
+        <v>6233630</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -14365,10 +14365,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471635</v>
+        <v>121471707</v>
       </c>
       <c r="B134" t="n">
-        <v>78863</v>
+        <v>96725</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14381,21 +14381,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14405,10 +14405,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427637</v>
+        <v>427809</v>
       </c>
       <c r="R134" t="n">
-        <v>6233845</v>
+        <v>6233703</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14467,7 +14467,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471651</v>
+        <v>121471635</v>
       </c>
       <c r="B135" t="n">
         <v>78863</v>
@@ -14507,10 +14507,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427737</v>
+        <v>427637</v>
       </c>
       <c r="R135" t="n">
-        <v>6233789</v>
+        <v>6233845</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14569,10 +14569,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471707</v>
+        <v>121471651</v>
       </c>
       <c r="B136" t="n">
-        <v>96725</v>
+        <v>78863</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14585,21 +14585,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14609,10 +14609,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427809</v>
+        <v>427737</v>
       </c>
       <c r="R136" t="n">
-        <v>6233703</v>
+        <v>6233789</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471646</v>
+        <v>121471719</v>
       </c>
       <c r="B11" t="n">
-        <v>94599</v>
+        <v>76949</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427692</v>
+        <v>427583</v>
       </c>
       <c r="R11" t="n">
-        <v>6233796</v>
+        <v>6233861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471956</v>
+        <v>121471634</v>
       </c>
       <c r="B12" t="n">
-        <v>94601</v>
+        <v>96731</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2666</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427739</v>
+        <v>427636</v>
       </c>
       <c r="R12" t="n">
-        <v>6233524</v>
+        <v>6233848</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2006,10 +2006,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471623</v>
+        <v>121471966</v>
       </c>
       <c r="B13" t="n">
-        <v>80242</v>
+        <v>76949</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427579</v>
+        <v>427505</v>
       </c>
       <c r="R13" t="n">
-        <v>6233850</v>
+        <v>6233740</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,12 +2076,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471580</v>
+        <v>121471604</v>
       </c>
       <c r="B14" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427804</v>
+        <v>427595</v>
       </c>
       <c r="R14" t="n">
-        <v>6233576</v>
+        <v>6233781</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471633</v>
+        <v>121471704</v>
       </c>
       <c r="B15" t="n">
-        <v>90508</v>
+        <v>96731</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2222,25 +2222,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1067</v>
+        <v>2606</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427629</v>
+        <v>427785</v>
       </c>
       <c r="R15" t="n">
-        <v>6233837</v>
+        <v>6233585</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121471572</v>
+        <v>121472002</v>
       </c>
       <c r="B16" t="n">
-        <v>96725</v>
+        <v>94605</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427982</v>
+        <v>427909</v>
       </c>
       <c r="R16" t="n">
-        <v>6233642</v>
+        <v>6233613</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121471608</v>
+        <v>121471712</v>
       </c>
       <c r="B17" t="n">
-        <v>80242</v>
+        <v>96731</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427566</v>
+        <v>427439</v>
       </c>
       <c r="R17" t="n">
-        <v>6233756</v>
+        <v>6233838</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121471560</v>
+        <v>121471974</v>
       </c>
       <c r="B18" t="n">
-        <v>80242</v>
+        <v>90514</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428008</v>
+        <v>427554</v>
       </c>
       <c r="R18" t="n">
-        <v>6233671</v>
+        <v>6233803</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121471604</v>
+        <v>121471995</v>
       </c>
       <c r="B19" t="n">
-        <v>80242</v>
+        <v>78864</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427595</v>
+        <v>427856</v>
       </c>
       <c r="R19" t="n">
-        <v>6233781</v>
+        <v>6233613</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121471714</v>
+        <v>121471641</v>
       </c>
       <c r="B20" t="n">
-        <v>78407</v>
+        <v>78864</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427435</v>
+        <v>427655</v>
       </c>
       <c r="R20" t="n">
-        <v>6233855</v>
+        <v>6233850</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121471564</v>
+        <v>121471983</v>
       </c>
       <c r="B21" t="n">
-        <v>80255</v>
+        <v>74698</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1144</v>
+        <v>6439</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428014</v>
+        <v>427521</v>
       </c>
       <c r="R21" t="n">
-        <v>6233692</v>
+        <v>6233737</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121471999</v>
+        <v>121471590</v>
       </c>
       <c r="B22" t="n">
-        <v>80255</v>
+        <v>80243</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427916</v>
+        <v>427753</v>
       </c>
       <c r="R22" t="n">
-        <v>6233634</v>
+        <v>6233666</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471622</v>
+        <v>121471962</v>
       </c>
       <c r="B23" t="n">
-        <v>74697</v>
+        <v>80243</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3042,21 +3042,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427623</v>
+        <v>427528</v>
       </c>
       <c r="R23" t="n">
-        <v>6233865</v>
+        <v>6233707</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3096,12 +3096,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471626</v>
+        <v>121471706</v>
       </c>
       <c r="B24" t="n">
-        <v>74697</v>
+        <v>96731</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427597</v>
+        <v>427781</v>
       </c>
       <c r="R24" t="n">
-        <v>6233825</v>
+        <v>6233648</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121472013</v>
+        <v>121471628</v>
       </c>
       <c r="B25" t="n">
-        <v>96725</v>
+        <v>96731</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427882</v>
+        <v>427604</v>
       </c>
       <c r="R25" t="n">
-        <v>6233622</v>
+        <v>6233834</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3300,12 +3300,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,10 +3332,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471712</v>
+        <v>121471630</v>
       </c>
       <c r="B26" t="n">
-        <v>96725</v>
+        <v>76949</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3344,25 +3344,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427439</v>
+        <v>427604</v>
       </c>
       <c r="R26" t="n">
-        <v>6233838</v>
+        <v>6233829</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471637</v>
+        <v>121471713</v>
       </c>
       <c r="B27" t="n">
-        <v>96725</v>
+        <v>76949</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427638</v>
+        <v>427438</v>
       </c>
       <c r="R27" t="n">
-        <v>6233822</v>
+        <v>6233852</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471574</v>
+        <v>121471964</v>
       </c>
       <c r="B28" t="n">
-        <v>80242</v>
+        <v>94605</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,21 +3552,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427838</v>
+        <v>427511</v>
       </c>
       <c r="R28" t="n">
-        <v>6233582</v>
+        <v>6233739</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3606,12 +3606,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3638,10 +3638,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471609</v>
+        <v>121471996</v>
       </c>
       <c r="B29" t="n">
-        <v>80242</v>
+        <v>80256</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3650,25 +3650,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427543</v>
+        <v>427855</v>
       </c>
       <c r="R29" t="n">
-        <v>6233756</v>
+        <v>6233614</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3740,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471720</v>
+        <v>121471610</v>
       </c>
       <c r="B30" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427595</v>
+        <v>427487</v>
       </c>
       <c r="R30" t="n">
-        <v>6233898</v>
+        <v>6233816</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471601</v>
+        <v>121471621</v>
       </c>
       <c r="B31" t="n">
-        <v>80242</v>
+        <v>96731</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427688</v>
+        <v>427607</v>
       </c>
       <c r="R31" t="n">
-        <v>6233590</v>
+        <v>6233875</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471982</v>
+        <v>121471714</v>
       </c>
       <c r="B32" t="n">
-        <v>76948</v>
+        <v>78408</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1342</v>
+        <v>924</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427516</v>
+        <v>427435</v>
       </c>
       <c r="R32" t="n">
-        <v>6233748</v>
+        <v>6233855</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4046,10 +4046,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471713</v>
+        <v>121471988</v>
       </c>
       <c r="B33" t="n">
-        <v>76948</v>
+        <v>74526</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4058,25 +4058,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1342</v>
+        <v>6428</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427438</v>
+        <v>427738</v>
       </c>
       <c r="R33" t="n">
-        <v>6233852</v>
+        <v>6233780</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4116,12 +4116,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4148,10 +4148,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471967</v>
+        <v>121471622</v>
       </c>
       <c r="B34" t="n">
-        <v>80255</v>
+        <v>74698</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4160,25 +4160,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1144</v>
+        <v>6439</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427508</v>
+        <v>427623</v>
       </c>
       <c r="R34" t="n">
-        <v>6233737</v>
+        <v>6233865</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4218,12 +4218,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471642</v>
+        <v>121471627</v>
       </c>
       <c r="B35" t="n">
-        <v>80242</v>
+        <v>74698</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4266,21 +4266,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427654</v>
+        <v>427613</v>
       </c>
       <c r="R35" t="n">
-        <v>6233848</v>
+        <v>6233840</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471607</v>
+        <v>121471651</v>
       </c>
       <c r="B36" t="n">
-        <v>80242</v>
+        <v>78864</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4368,21 +4368,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427582</v>
+        <v>427737</v>
       </c>
       <c r="R36" t="n">
-        <v>6233752</v>
+        <v>6233789</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4454,10 +4454,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471520</v>
+        <v>121471612</v>
       </c>
       <c r="B37" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427789</v>
+        <v>427466</v>
       </c>
       <c r="R37" t="n">
-        <v>6233516</v>
+        <v>6233828</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4556,10 +4556,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471992</v>
+        <v>121471715</v>
       </c>
       <c r="B38" t="n">
-        <v>94588</v>
+        <v>80243</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4572,21 +4572,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427861</v>
+        <v>427445</v>
       </c>
       <c r="R38" t="n">
-        <v>6233620</v>
+        <v>6233860</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4626,12 +4626,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4658,10 +4658,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471974</v>
+        <v>121471984</v>
       </c>
       <c r="B39" t="n">
-        <v>90508</v>
+        <v>80243</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4670,25 +4670,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427554</v>
+        <v>427530</v>
       </c>
       <c r="R39" t="n">
-        <v>6233803</v>
+        <v>6233736</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4760,10 +4760,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471649</v>
+        <v>121471601</v>
       </c>
       <c r="B40" t="n">
-        <v>80255</v>
+        <v>80243</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4772,25 +4772,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427720</v>
+        <v>427688</v>
       </c>
       <c r="R40" t="n">
-        <v>6233787</v>
+        <v>6233590</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471578</v>
+        <v>121471959</v>
       </c>
       <c r="B41" t="n">
-        <v>76948</v>
+        <v>80243</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4874,25 +4874,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427749</v>
+        <v>427734</v>
       </c>
       <c r="R41" t="n">
-        <v>6233573</v>
+        <v>6233532</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4932,12 +4932,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4964,10 +4964,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471648</v>
+        <v>121471619</v>
       </c>
       <c r="B42" t="n">
-        <v>76948</v>
+        <v>96731</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4976,25 +4976,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427721</v>
+        <v>427624</v>
       </c>
       <c r="R42" t="n">
-        <v>6233787</v>
+        <v>6233894</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5066,10 +5066,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471521</v>
+        <v>121471647</v>
       </c>
       <c r="B43" t="n">
-        <v>80242</v>
+        <v>96731</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5082,21 +5082,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427794</v>
+        <v>427720</v>
       </c>
       <c r="R43" t="n">
-        <v>6233483</v>
+        <v>6233787</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5168,10 +5168,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471993</v>
+        <v>121471952</v>
       </c>
       <c r="B44" t="n">
-        <v>91504</v>
+        <v>74698</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5180,41 +5180,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>2014</v>
+        <v>6439</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427859</v>
+        <v>427763</v>
       </c>
       <c r="R44" t="n">
-        <v>6233620</v>
+        <v>6233529</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5255,7 +5252,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5274,10 +5270,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471598</v>
+        <v>121471631</v>
       </c>
       <c r="B45" t="n">
-        <v>94599</v>
+        <v>80243</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5290,21 +5286,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5314,10 +5310,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>427690</v>
+        <v>427601</v>
       </c>
       <c r="R45" t="n">
-        <v>6233595</v>
+        <v>6233830</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5376,10 +5372,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471710</v>
+        <v>121471965</v>
       </c>
       <c r="B46" t="n">
-        <v>94601</v>
+        <v>76949</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5388,25 +5384,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2666</v>
+        <v>1342</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5416,10 +5412,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427448</v>
+        <v>427509</v>
       </c>
       <c r="R46" t="n">
-        <v>6233789</v>
+        <v>6233731</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5446,12 +5442,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5478,10 +5474,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121472004</v>
+        <v>121471973</v>
       </c>
       <c r="B47" t="n">
-        <v>80242</v>
+        <v>76949</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5490,25 +5486,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5518,10 +5514,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427892</v>
+        <v>427544</v>
       </c>
       <c r="R47" t="n">
-        <v>6233623</v>
+        <v>6233811</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5580,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471628</v>
+        <v>121471982</v>
       </c>
       <c r="B48" t="n">
-        <v>96725</v>
+        <v>76949</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5592,25 +5588,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5620,10 +5616,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427604</v>
+        <v>427516</v>
       </c>
       <c r="R48" t="n">
-        <v>6233834</v>
+        <v>6233748</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5650,12 +5646,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5682,10 +5678,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471619</v>
+        <v>121471646</v>
       </c>
       <c r="B49" t="n">
-        <v>96725</v>
+        <v>94605</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5698,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5722,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427624</v>
+        <v>427692</v>
       </c>
       <c r="R49" t="n">
-        <v>6233894</v>
+        <v>6233796</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5784,10 +5780,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471644</v>
+        <v>121471577</v>
       </c>
       <c r="B50" t="n">
-        <v>78863</v>
+        <v>94605</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5800,21 +5796,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6459</v>
+        <v>2667</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5824,10 +5820,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427671</v>
+        <v>427749</v>
       </c>
       <c r="R50" t="n">
-        <v>6233821</v>
+        <v>6233572</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5886,10 +5882,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121472010</v>
+        <v>121471986</v>
       </c>
       <c r="B51" t="n">
-        <v>78987</v>
+        <v>80256</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5898,38 +5894,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6431</v>
+        <v>1144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427877</v>
+        <v>427558</v>
       </c>
       <c r="R51" t="n">
-        <v>6233615</v>
+        <v>6233769</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5964,11 +5963,21 @@
           <t>2024-11-18</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Med Refractohilum pluriseptatum</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
       <c r="AE51" t="b">
         <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG51" t="b">
         <v>0</v>
@@ -5988,10 +5997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471979</v>
+        <v>121472007</v>
       </c>
       <c r="B52" t="n">
-        <v>76948</v>
+        <v>80256</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6000,25 +6009,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6028,10 +6037,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427533</v>
+        <v>427892</v>
       </c>
       <c r="R52" t="n">
-        <v>6233765</v>
+        <v>6233623</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6090,10 +6099,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471719</v>
+        <v>121471650</v>
       </c>
       <c r="B53" t="n">
-        <v>76948</v>
+        <v>80243</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6102,25 +6111,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6130,10 +6139,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427583</v>
+        <v>427737</v>
       </c>
       <c r="R53" t="n">
-        <v>6233861</v>
+        <v>6233784</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6192,10 +6201,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471978</v>
+        <v>121471990</v>
       </c>
       <c r="B54" t="n">
-        <v>94599</v>
+        <v>80243</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6208,21 +6217,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6232,7 +6241,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427533</v>
+        <v>427765</v>
       </c>
       <c r="R54" t="n">
         <v>6233765</v>
@@ -6294,10 +6303,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471602</v>
+        <v>121471520</v>
       </c>
       <c r="B55" t="n">
-        <v>94599</v>
+        <v>80243</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6310,21 +6319,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6334,10 +6343,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>427641</v>
+        <v>427789</v>
       </c>
       <c r="R55" t="n">
-        <v>6233630</v>
+        <v>6233516</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6396,10 +6405,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471996</v>
+        <v>121472004</v>
       </c>
       <c r="B56" t="n">
-        <v>80255</v>
+        <v>80243</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6408,25 +6417,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6436,10 +6445,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>427855</v>
+        <v>427892</v>
       </c>
       <c r="R56" t="n">
-        <v>6233614</v>
+        <v>6233623</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6498,10 +6507,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121472012</v>
+        <v>121471993</v>
       </c>
       <c r="B57" t="n">
-        <v>76948</v>
+        <v>91510</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6514,34 +6523,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1342</v>
+        <v>2014</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427855</v>
+        <v>427859</v>
       </c>
       <c r="R57" t="n">
-        <v>6233612</v>
+        <v>6233620</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6582,6 +6594,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6600,10 +6613,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471632</v>
+        <v>121471599</v>
       </c>
       <c r="B58" t="n">
-        <v>80242</v>
+        <v>94607</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6616,21 +6629,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6640,10 +6653,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427615</v>
+        <v>427685</v>
       </c>
       <c r="R58" t="n">
-        <v>6233825</v>
+        <v>6233593</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6702,10 +6715,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471612</v>
+        <v>121471632</v>
       </c>
       <c r="B59" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6742,10 +6755,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427466</v>
+        <v>427615</v>
       </c>
       <c r="R59" t="n">
-        <v>6233828</v>
+        <v>6233825</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6804,10 +6817,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471650</v>
+        <v>121472006</v>
       </c>
       <c r="B60" t="n">
-        <v>80242</v>
+        <v>76949</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6816,25 +6829,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6844,10 +6857,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427737</v>
+        <v>427892</v>
       </c>
       <c r="R60" t="n">
-        <v>6233784</v>
+        <v>6233623</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6874,12 +6887,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6906,10 +6919,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471590</v>
+        <v>121471585</v>
       </c>
       <c r="B61" t="n">
-        <v>80242</v>
+        <v>76949</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6918,25 +6931,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6946,10 +6959,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427753</v>
+        <v>427748</v>
       </c>
       <c r="R61" t="n">
-        <v>6233666</v>
+        <v>6233622</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7008,10 +7021,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471962</v>
+        <v>121471589</v>
       </c>
       <c r="B62" t="n">
-        <v>80242</v>
+        <v>96731</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7024,21 +7037,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7048,10 +7061,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427528</v>
+        <v>427804</v>
       </c>
       <c r="R62" t="n">
-        <v>6233707</v>
+        <v>6233688</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7078,12 +7091,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7110,10 +7123,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471960</v>
+        <v>121471703</v>
       </c>
       <c r="B63" t="n">
-        <v>94588</v>
+        <v>74698</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7126,21 +7139,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2671</v>
+        <v>6439</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7150,10 +7163,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427734</v>
+        <v>427770</v>
       </c>
       <c r="R63" t="n">
-        <v>6233532</v>
+        <v>6233580</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7180,12 +7193,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7212,10 +7225,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471603</v>
+        <v>121471602</v>
       </c>
       <c r="B64" t="n">
-        <v>80255</v>
+        <v>94605</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7224,25 +7237,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7252,10 +7265,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427596</v>
+        <v>427641</v>
       </c>
       <c r="R64" t="n">
-        <v>6233681</v>
+        <v>6233630</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7314,10 +7327,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471559</v>
+        <v>121472001</v>
       </c>
       <c r="B65" t="n">
-        <v>76948</v>
+        <v>94615</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7326,25 +7339,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1342</v>
+        <v>1080</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7354,10 +7367,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427960</v>
+        <v>427908</v>
       </c>
       <c r="R65" t="n">
-        <v>6233661</v>
+        <v>6233617</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7384,12 +7397,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7416,10 +7429,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471951</v>
+        <v>121471629</v>
       </c>
       <c r="B66" t="n">
-        <v>76948</v>
+        <v>80256</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7428,25 +7441,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7456,10 +7469,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427762</v>
+        <v>427602</v>
       </c>
       <c r="R66" t="n">
-        <v>6233515</v>
+        <v>6233832</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7486,12 +7499,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7518,10 +7531,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121472016</v>
+        <v>121471710</v>
       </c>
       <c r="B67" t="n">
-        <v>96725</v>
+        <v>94607</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7534,21 +7547,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2606</v>
+        <v>2666</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7558,10 +7571,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427903</v>
+        <v>427448</v>
       </c>
       <c r="R67" t="n">
-        <v>6233640</v>
+        <v>6233789</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7588,12 +7601,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7620,10 +7633,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471618</v>
+        <v>121471992</v>
       </c>
       <c r="B68" t="n">
-        <v>96725</v>
+        <v>94594</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7636,21 +7649,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7660,10 +7673,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427525</v>
+        <v>427861</v>
       </c>
       <c r="R68" t="n">
-        <v>6233838</v>
+        <v>6233620</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7690,12 +7703,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7722,10 +7735,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471953</v>
+        <v>121471700</v>
       </c>
       <c r="B69" t="n">
-        <v>96725</v>
+        <v>78988</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7738,21 +7751,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2606</v>
+        <v>6431</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7762,10 +7775,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427769</v>
+        <v>427806</v>
       </c>
       <c r="R69" t="n">
-        <v>6233529</v>
+        <v>6233482</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7792,12 +7805,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7824,10 +7837,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471988</v>
+        <v>121471608</v>
       </c>
       <c r="B70" t="n">
-        <v>74525</v>
+        <v>80243</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7840,21 +7853,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6428</v>
+        <v>230185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7864,10 +7877,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>427738</v>
+        <v>427566</v>
       </c>
       <c r="R70" t="n">
-        <v>6233780</v>
+        <v>6233756</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7894,12 +7907,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7926,10 +7939,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471975</v>
+        <v>121471954</v>
       </c>
       <c r="B71" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7966,10 +7979,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>427575</v>
+        <v>427742</v>
       </c>
       <c r="R71" t="n">
-        <v>6233800</v>
+        <v>6233542</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8028,10 +8041,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471986</v>
+        <v>121471581</v>
       </c>
       <c r="B72" t="n">
-        <v>80255</v>
+        <v>80243</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8040,41 +8053,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427558</v>
+        <v>427820</v>
       </c>
       <c r="R72" t="n">
-        <v>6233769</v>
+        <v>6233599</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8101,17 +8111,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Med Refractohilum pluriseptatum</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8119,11 +8124,6 @@
       </c>
       <c r="AE72" t="b">
         <v>0</v>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG72" t="b">
         <v>0</v>
@@ -8143,10 +8143,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471586</v>
+        <v>121471521</v>
       </c>
       <c r="B73" t="n">
-        <v>80255</v>
+        <v>80243</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8155,25 +8155,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8183,10 +8183,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427748</v>
+        <v>427794</v>
       </c>
       <c r="R73" t="n">
-        <v>6233622</v>
+        <v>6233483</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8245,10 +8245,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471557</v>
+        <v>121471638</v>
       </c>
       <c r="B74" t="n">
-        <v>94588</v>
+        <v>80243</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8261,21 +8261,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8285,10 +8285,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>427948</v>
+        <v>427638</v>
       </c>
       <c r="R74" t="n">
-        <v>6233643</v>
+        <v>6233822</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8347,10 +8347,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471599</v>
+        <v>121471614</v>
       </c>
       <c r="B75" t="n">
-        <v>94601</v>
+        <v>80243</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8363,21 +8363,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8387,10 +8387,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>427685</v>
+        <v>427475</v>
       </c>
       <c r="R75" t="n">
-        <v>6233593</v>
+        <v>6233836</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8449,10 +8449,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471589</v>
+        <v>121471572</v>
       </c>
       <c r="B76" t="n">
-        <v>96725</v>
+        <v>96731</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8489,10 +8489,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427804</v>
+        <v>427982</v>
       </c>
       <c r="R76" t="n">
-        <v>6233688</v>
+        <v>6233642</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8551,10 +8551,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471584</v>
+        <v>121471998</v>
       </c>
       <c r="B77" t="n">
-        <v>96725</v>
+        <v>76949</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8563,25 +8563,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427817</v>
+        <v>427915</v>
       </c>
       <c r="R77" t="n">
-        <v>6233621</v>
+        <v>6233632</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8621,12 +8621,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8653,10 +8653,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471700</v>
+        <v>121471977</v>
       </c>
       <c r="B78" t="n">
-        <v>78987</v>
+        <v>96731</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8669,21 +8669,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6431</v>
+        <v>2606</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8693,10 +8693,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427806</v>
+        <v>427533</v>
       </c>
       <c r="R78" t="n">
-        <v>6233482</v>
+        <v>6233765</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8755,10 +8755,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471952</v>
+        <v>121471637</v>
       </c>
       <c r="B79" t="n">
-        <v>74697</v>
+        <v>96731</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8771,21 +8771,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427763</v>
+        <v>427638</v>
       </c>
       <c r="R79" t="n">
-        <v>6233529</v>
+        <v>6233822</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8825,12 +8825,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8857,10 +8857,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121472006</v>
+        <v>121471955</v>
       </c>
       <c r="B80" t="n">
-        <v>76948</v>
+        <v>94607</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8869,25 +8869,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1342</v>
+        <v>2666</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427892</v>
+        <v>427741</v>
       </c>
       <c r="R80" t="n">
-        <v>6233623</v>
+        <v>6233529</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8959,10 +8959,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471585</v>
+        <v>121471956</v>
       </c>
       <c r="B81" t="n">
-        <v>76948</v>
+        <v>94607</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8971,25 +8971,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1342</v>
+        <v>2666</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427748</v>
+        <v>427739</v>
       </c>
       <c r="R81" t="n">
-        <v>6233622</v>
+        <v>6233524</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9029,12 +9029,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9061,10 +9061,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471638</v>
+        <v>121471718</v>
       </c>
       <c r="B82" t="n">
-        <v>80242</v>
+        <v>80256</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9073,25 +9073,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9101,10 +9101,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427638</v>
+        <v>427584</v>
       </c>
       <c r="R82" t="n">
-        <v>6233822</v>
+        <v>6233863</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9163,10 +9163,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471968</v>
+        <v>121471560</v>
       </c>
       <c r="B83" t="n">
-        <v>57370</v>
+        <v>80243</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9175,25 +9175,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>230185</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9203,10 +9203,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427512</v>
+        <v>428008</v>
       </c>
       <c r="R83" t="n">
-        <v>6233745</v>
+        <v>6233671</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9233,12 +9233,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9265,10 +9265,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471596</v>
+        <v>121471598</v>
       </c>
       <c r="B84" t="n">
-        <v>74699</v>
+        <v>94605</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9281,21 +9281,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>306</v>
+        <v>2667</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9305,10 +9305,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427686</v>
+        <v>427690</v>
       </c>
       <c r="R84" t="n">
-        <v>6233621</v>
+        <v>6233595</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9367,10 +9367,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471709</v>
+        <v>121471593</v>
       </c>
       <c r="B85" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9407,10 +9407,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427452</v>
+        <v>427699</v>
       </c>
       <c r="R85" t="n">
-        <v>6233794</v>
+        <v>6233608</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9469,10 +9469,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471954</v>
+        <v>121471671</v>
       </c>
       <c r="B86" t="n">
-        <v>80242</v>
+        <v>105765</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9481,25 +9481,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>230185</v>
+        <v>220785</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427742</v>
+        <v>427912</v>
       </c>
       <c r="R86" t="n">
-        <v>6233542</v>
+        <v>6233611</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9539,12 +9539,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9571,10 +9571,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471705</v>
+        <v>121471976</v>
       </c>
       <c r="B87" t="n">
-        <v>80242</v>
+        <v>96731</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9587,21 +9587,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9611,10 +9611,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427753</v>
+        <v>427576</v>
       </c>
       <c r="R87" t="n">
-        <v>6233606</v>
+        <v>6233800</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9641,12 +9641,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9673,10 +9673,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471631</v>
+        <v>121471618</v>
       </c>
       <c r="B88" t="n">
-        <v>80242</v>
+        <v>96731</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9689,21 +9689,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9713,10 +9713,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427601</v>
+        <v>427525</v>
       </c>
       <c r="R88" t="n">
-        <v>6233830</v>
+        <v>6233838</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9775,10 +9775,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471624</v>
+        <v>121472012</v>
       </c>
       <c r="B89" t="n">
-        <v>74563</v>
+        <v>76949</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9791,21 +9791,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1116</v>
+        <v>1342</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9815,10 +9815,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427594</v>
+        <v>427855</v>
       </c>
       <c r="R89" t="n">
-        <v>6233828</v>
+        <v>6233612</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9845,12 +9845,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9877,10 +9877,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121472011</v>
+        <v>121471575</v>
       </c>
       <c r="B90" t="n">
-        <v>76948</v>
+        <v>91118</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9893,21 +9893,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1342</v>
+        <v>2023</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9917,10 +9917,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427874</v>
+        <v>427837</v>
       </c>
       <c r="R90" t="n">
-        <v>6233615</v>
+        <v>6233582</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9947,12 +9947,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9979,10 +9979,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471577</v>
+        <v>121471709</v>
       </c>
       <c r="B91" t="n">
-        <v>94599</v>
+        <v>80243</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9995,21 +9995,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10019,10 +10019,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427749</v>
+        <v>427452</v>
       </c>
       <c r="R91" t="n">
-        <v>6233572</v>
+        <v>6233794</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10081,10 +10081,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471702</v>
+        <v>121471591</v>
       </c>
       <c r="B92" t="n">
-        <v>96725</v>
+        <v>80243</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10097,21 +10097,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10121,10 +10121,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427811</v>
+        <v>427724</v>
       </c>
       <c r="R92" t="n">
-        <v>6233480</v>
+        <v>6233617</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10183,10 +10183,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471995</v>
+        <v>121471708</v>
       </c>
       <c r="B93" t="n">
-        <v>78863</v>
+        <v>96731</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10199,21 +10199,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427856</v>
+        <v>427785</v>
       </c>
       <c r="R93" t="n">
-        <v>6233613</v>
+        <v>6233734</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10253,12 +10253,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10285,10 +10285,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471703</v>
+        <v>121471620</v>
       </c>
       <c r="B94" t="n">
-        <v>74697</v>
+        <v>94594</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10301,21 +10301,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6439</v>
+        <v>2671</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427770</v>
+        <v>427625</v>
       </c>
       <c r="R94" t="n">
-        <v>6233580</v>
+        <v>6233894</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10387,10 +10387,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121472001</v>
+        <v>121471957</v>
       </c>
       <c r="B95" t="n">
-        <v>94609</v>
+        <v>94605</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10403,21 +10403,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1080</v>
+        <v>2667</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10427,10 +10427,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427908</v>
+        <v>427731</v>
       </c>
       <c r="R95" t="n">
-        <v>6233617</v>
+        <v>6233539</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10489,10 +10489,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471998</v>
+        <v>121471961</v>
       </c>
       <c r="B96" t="n">
-        <v>76948</v>
+        <v>94605</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10501,25 +10501,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10529,10 +10529,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427915</v>
+        <v>427615</v>
       </c>
       <c r="R96" t="n">
-        <v>6233632</v>
+        <v>6233649</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10591,10 +10591,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471640</v>
+        <v>121471978</v>
       </c>
       <c r="B97" t="n">
-        <v>96725</v>
+        <v>94605</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10607,21 +10607,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10631,10 +10631,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427653</v>
+        <v>427533</v>
       </c>
       <c r="R97" t="n">
-        <v>6233849</v>
+        <v>6233765</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10661,12 +10661,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10693,10 +10693,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471971</v>
+        <v>121471558</v>
       </c>
       <c r="B98" t="n">
-        <v>78863</v>
+        <v>80256</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10705,25 +10705,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6459</v>
+        <v>1144</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10733,10 +10733,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427499</v>
+        <v>427960</v>
       </c>
       <c r="R98" t="n">
-        <v>6233792</v>
+        <v>6233661</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10763,12 +10763,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10795,10 +10795,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471583</v>
+        <v>121472015</v>
       </c>
       <c r="B99" t="n">
-        <v>78863</v>
+        <v>74698</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10811,21 +10811,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6459</v>
+        <v>6439</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427813</v>
+        <v>427903</v>
       </c>
       <c r="R99" t="n">
-        <v>6233621</v>
+        <v>6233639</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10865,12 +10865,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10897,10 +10897,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471957</v>
+        <v>121471565</v>
       </c>
       <c r="B100" t="n">
-        <v>94599</v>
+        <v>76949</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10909,25 +10909,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10937,10 +10937,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427731</v>
+        <v>428016</v>
       </c>
       <c r="R100" t="n">
-        <v>6233539</v>
+        <v>6233689</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10999,10 +10999,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471614</v>
+        <v>121471557</v>
       </c>
       <c r="B101" t="n">
-        <v>80242</v>
+        <v>94594</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11015,21 +11015,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11039,10 +11039,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>427475</v>
+        <v>427948</v>
       </c>
       <c r="R101" t="n">
-        <v>6233836</v>
+        <v>6233643</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11101,10 +11101,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471961</v>
+        <v>121472009</v>
       </c>
       <c r="B102" t="n">
-        <v>94599</v>
+        <v>94605</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11141,10 +11141,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427615</v>
+        <v>427877</v>
       </c>
       <c r="R102" t="n">
-        <v>6233649</v>
+        <v>6233615</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11203,10 +11203,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471955</v>
+        <v>121471603</v>
       </c>
       <c r="B103" t="n">
-        <v>94601</v>
+        <v>80256</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11215,25 +11215,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2666</v>
+        <v>1144</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11243,10 +11243,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427741</v>
+        <v>427596</v>
       </c>
       <c r="R103" t="n">
-        <v>6233529</v>
+        <v>6233681</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11273,12 +11273,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11305,10 +11305,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471983</v>
+        <v>121472003</v>
       </c>
       <c r="B104" t="n">
-        <v>74697</v>
+        <v>79019</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11317,27 +11317,23 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6439</v>
+        <v>132</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Liten lundlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
+          <t>Bacidina phacodes/tarandina</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -11345,10 +11341,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427521</v>
+        <v>427911</v>
       </c>
       <c r="R104" t="n">
-        <v>6233737</v>
+        <v>6233614</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11407,10 +11403,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471592</v>
+        <v>121471587</v>
       </c>
       <c r="B105" t="n">
-        <v>80242</v>
+        <v>80256</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11419,25 +11415,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11447,10 +11443,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427703</v>
+        <v>427770</v>
       </c>
       <c r="R105" t="n">
-        <v>6233616</v>
+        <v>6233624</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11509,10 +11505,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471715</v>
+        <v>121471576</v>
       </c>
       <c r="B106" t="n">
-        <v>80242</v>
+        <v>80256</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11521,25 +11517,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11549,10 +11545,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427445</v>
+        <v>427742</v>
       </c>
       <c r="R106" t="n">
-        <v>6233860</v>
+        <v>6233565</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11611,10 +11607,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471597</v>
+        <v>121471636</v>
       </c>
       <c r="B107" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11651,10 +11647,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427693</v>
+        <v>427650</v>
       </c>
       <c r="R107" t="n">
-        <v>6233604</v>
+        <v>6233855</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11713,10 +11709,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121472002</v>
+        <v>121471985</v>
       </c>
       <c r="B108" t="n">
-        <v>94599</v>
+        <v>80243</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11729,21 +11725,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11753,10 +11749,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>427909</v>
+        <v>427558</v>
       </c>
       <c r="R108" t="n">
-        <v>6233613</v>
+        <v>6233768</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11815,10 +11811,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471558</v>
+        <v>121471597</v>
       </c>
       <c r="B109" t="n">
-        <v>80255</v>
+        <v>80243</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11827,25 +11823,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11855,10 +11851,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>427960</v>
+        <v>427693</v>
       </c>
       <c r="R109" t="n">
-        <v>6233661</v>
+        <v>6233604</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11917,10 +11913,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471704</v>
+        <v>121472016</v>
       </c>
       <c r="B110" t="n">
-        <v>96725</v>
+        <v>96731</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11957,10 +11953,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427785</v>
+        <v>427903</v>
       </c>
       <c r="R110" t="n">
-        <v>6233585</v>
+        <v>6233640</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11987,12 +11983,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12019,10 +12015,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471621</v>
+        <v>121471596</v>
       </c>
       <c r="B111" t="n">
-        <v>96725</v>
+        <v>74700</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12035,21 +12031,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2606</v>
+        <v>306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12059,10 +12055,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427607</v>
+        <v>427686</v>
       </c>
       <c r="R111" t="n">
-        <v>6233875</v>
+        <v>6233621</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12121,10 +12117,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471643</v>
+        <v>121471562</v>
       </c>
       <c r="B112" t="n">
-        <v>96725</v>
+        <v>80579</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12133,25 +12129,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2606</v>
+        <v>1182</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12161,10 +12157,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427671</v>
+        <v>428000</v>
       </c>
       <c r="R112" t="n">
-        <v>6233821</v>
+        <v>6233692</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12223,10 +12219,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471634</v>
+        <v>121471559</v>
       </c>
       <c r="B113" t="n">
-        <v>96725</v>
+        <v>76949</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12235,25 +12231,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12263,10 +12259,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427636</v>
+        <v>427960</v>
       </c>
       <c r="R113" t="n">
-        <v>6233848</v>
+        <v>6233661</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12325,10 +12321,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471980</v>
+        <v>121471953</v>
       </c>
       <c r="B114" t="n">
-        <v>80255</v>
+        <v>96731</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12337,25 +12333,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12365,10 +12361,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427532</v>
+        <v>427769</v>
       </c>
       <c r="R114" t="n">
-        <v>6233767</v>
+        <v>6233529</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12427,10 +12423,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121472007</v>
+        <v>121471592</v>
       </c>
       <c r="B115" t="n">
-        <v>80255</v>
+        <v>80243</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12439,25 +12435,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12467,10 +12463,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427892</v>
+        <v>427703</v>
       </c>
       <c r="R115" t="n">
-        <v>6233623</v>
+        <v>6233616</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12497,12 +12493,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12529,10 +12525,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471973</v>
+        <v>121471617</v>
       </c>
       <c r="B116" t="n">
-        <v>76948</v>
+        <v>80243</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12541,25 +12537,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12569,10 +12565,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427544</v>
+        <v>427526</v>
       </c>
       <c r="R116" t="n">
-        <v>6233811</v>
+        <v>6233836</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12599,12 +12595,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12631,10 +12627,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471966</v>
+        <v>121471580</v>
       </c>
       <c r="B117" t="n">
-        <v>76948</v>
+        <v>80243</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12643,25 +12639,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12671,10 +12667,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427505</v>
+        <v>427804</v>
       </c>
       <c r="R117" t="n">
-        <v>6233740</v>
+        <v>6233576</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12701,12 +12697,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12733,10 +12729,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121472009</v>
+        <v>121472011</v>
       </c>
       <c r="B118" t="n">
-        <v>94599</v>
+        <v>76949</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12745,25 +12741,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12773,7 +12769,7 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427877</v>
+        <v>427874</v>
       </c>
       <c r="R118" t="n">
         <v>6233615</v>
@@ -12835,10 +12831,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471617</v>
+        <v>121471702</v>
       </c>
       <c r="B119" t="n">
-        <v>80242</v>
+        <v>96731</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12851,21 +12847,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12875,10 +12871,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427526</v>
+        <v>427811</v>
       </c>
       <c r="R119" t="n">
-        <v>6233836</v>
+        <v>6233480</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12937,10 +12933,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471581</v>
+        <v>121471643</v>
       </c>
       <c r="B120" t="n">
-        <v>80242</v>
+        <v>96731</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12953,21 +12949,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12977,10 +12973,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427820</v>
+        <v>427671</v>
       </c>
       <c r="R120" t="n">
-        <v>6233599</v>
+        <v>6233821</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13039,10 +13035,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471976</v>
+        <v>121471564</v>
       </c>
       <c r="B121" t="n">
-        <v>96725</v>
+        <v>80256</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13051,25 +13047,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13079,10 +13075,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427576</v>
+        <v>428014</v>
       </c>
       <c r="R121" t="n">
-        <v>6233800</v>
+        <v>6233692</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13109,12 +13105,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13141,10 +13137,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471708</v>
+        <v>121471624</v>
       </c>
       <c r="B122" t="n">
-        <v>96725</v>
+        <v>74564</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13153,25 +13149,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2606</v>
+        <v>1116</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13181,10 +13177,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427785</v>
+        <v>427594</v>
       </c>
       <c r="R122" t="n">
-        <v>6233734</v>
+        <v>6233828</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13243,10 +13239,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471706</v>
+        <v>121471607</v>
       </c>
       <c r="B123" t="n">
-        <v>96725</v>
+        <v>80243</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13259,21 +13255,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13283,10 +13279,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427781</v>
+        <v>427582</v>
       </c>
       <c r="R123" t="n">
-        <v>6233648</v>
+        <v>6233752</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13345,10 +13341,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471630</v>
+        <v>121471960</v>
       </c>
       <c r="B124" t="n">
-        <v>76948</v>
+        <v>94594</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13357,25 +13353,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13385,10 +13381,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427604</v>
+        <v>427734</v>
       </c>
       <c r="R124" t="n">
-        <v>6233829</v>
+        <v>6233532</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13415,12 +13411,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13447,10 +13443,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471627</v>
+        <v>121471633</v>
       </c>
       <c r="B125" t="n">
-        <v>74697</v>
+        <v>90514</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13459,25 +13455,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6439</v>
+        <v>1067</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13487,10 +13483,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427613</v>
+        <v>427629</v>
       </c>
       <c r="R125" t="n">
-        <v>6233840</v>
+        <v>6233837</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13549,10 +13545,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121472000</v>
+        <v>121471999</v>
       </c>
       <c r="B126" t="n">
-        <v>74697</v>
+        <v>80256</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13561,25 +13557,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13589,10 +13585,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427926</v>
+        <v>427916</v>
       </c>
       <c r="R126" t="n">
-        <v>6233617</v>
+        <v>6233634</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13651,10 +13647,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471671</v>
+        <v>121471716</v>
       </c>
       <c r="B127" t="n">
-        <v>105759</v>
+        <v>80243</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13663,25 +13659,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220785</v>
+        <v>230185</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13691,10 +13687,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427912</v>
+        <v>427547</v>
       </c>
       <c r="R127" t="n">
-        <v>6233611</v>
+        <v>6233865</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13753,10 +13749,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121472014</v>
+        <v>121472013</v>
       </c>
       <c r="B128" t="n">
-        <v>80255</v>
+        <v>96731</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13765,25 +13761,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13855,10 +13851,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471964</v>
+        <v>121471648</v>
       </c>
       <c r="B129" t="n">
-        <v>94599</v>
+        <v>76949</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13867,25 +13863,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13895,10 +13891,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>427511</v>
+        <v>427721</v>
       </c>
       <c r="R129" t="n">
-        <v>6233739</v>
+        <v>6233787</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13925,12 +13921,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13957,10 +13953,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471600</v>
+        <v>121471626</v>
       </c>
       <c r="B130" t="n">
-        <v>94599</v>
+        <v>74698</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13973,21 +13969,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2667</v>
+        <v>6439</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13997,10 +13993,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>427698</v>
+        <v>427597</v>
       </c>
       <c r="R130" t="n">
-        <v>6233566</v>
+        <v>6233825</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14059,10 +14055,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471561</v>
+        <v>121472010</v>
       </c>
       <c r="B131" t="n">
-        <v>96725</v>
+        <v>78988</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14075,21 +14071,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2606</v>
+        <v>6431</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14099,10 +14095,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427999</v>
+        <v>427877</v>
       </c>
       <c r="R131" t="n">
-        <v>6233695</v>
+        <v>6233615</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14129,12 +14125,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14161,10 +14157,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471647</v>
+        <v>121471556</v>
       </c>
       <c r="B132" t="n">
-        <v>96725</v>
+        <v>96731</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14201,10 +14197,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427720</v>
+        <v>427948</v>
       </c>
       <c r="R132" t="n">
-        <v>6233787</v>
+        <v>6233643</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14263,10 +14259,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471985</v>
+        <v>121471578</v>
       </c>
       <c r="B133" t="n">
-        <v>80242</v>
+        <v>76949</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14275,25 +14271,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14303,10 +14299,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427558</v>
+        <v>427749</v>
       </c>
       <c r="R133" t="n">
-        <v>6233768</v>
+        <v>6233573</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14333,12 +14329,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14365,10 +14361,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471707</v>
+        <v>121471963</v>
       </c>
       <c r="B134" t="n">
-        <v>96725</v>
+        <v>94605</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14381,21 +14377,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14405,10 +14401,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427809</v>
+        <v>427520</v>
       </c>
       <c r="R134" t="n">
-        <v>6233703</v>
+        <v>6233715</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14435,12 +14431,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14470,7 +14466,7 @@
         <v>121471635</v>
       </c>
       <c r="B135" t="n">
-        <v>78863</v>
+        <v>78864</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14569,10 +14565,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471651</v>
+        <v>121471980</v>
       </c>
       <c r="B136" t="n">
-        <v>78863</v>
+        <v>80256</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14581,25 +14577,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6459</v>
+        <v>1144</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14609,10 +14605,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427737</v>
+        <v>427532</v>
       </c>
       <c r="R136" t="n">
-        <v>6233789</v>
+        <v>6233767</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14639,12 +14635,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14671,10 +14667,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471587</v>
+        <v>121471649</v>
       </c>
       <c r="B137" t="n">
-        <v>80255</v>
+        <v>80256</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14711,10 +14707,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427770</v>
+        <v>427720</v>
       </c>
       <c r="R137" t="n">
-        <v>6233624</v>
+        <v>6233787</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14773,10 +14769,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471576</v>
+        <v>121471563</v>
       </c>
       <c r="B138" t="n">
-        <v>80255</v>
+        <v>96731</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14785,25 +14781,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14813,10 +14809,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427742</v>
+        <v>428012</v>
       </c>
       <c r="R138" t="n">
-        <v>6233565</v>
+        <v>6233689</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14875,10 +14871,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471565</v>
+        <v>121471979</v>
       </c>
       <c r="B139" t="n">
-        <v>76948</v>
+        <v>76949</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14915,10 +14911,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>428016</v>
+        <v>427533</v>
       </c>
       <c r="R139" t="n">
-        <v>6233689</v>
+        <v>6233765</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14945,12 +14941,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14977,10 +14973,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471965</v>
+        <v>121471951</v>
       </c>
       <c r="B140" t="n">
-        <v>76948</v>
+        <v>76949</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -15017,10 +15013,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>427509</v>
+        <v>427762</v>
       </c>
       <c r="R140" t="n">
-        <v>6233731</v>
+        <v>6233515</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15079,10 +15075,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471641</v>
+        <v>121471584</v>
       </c>
       <c r="B141" t="n">
-        <v>78863</v>
+        <v>96731</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15095,21 +15091,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15119,10 +15115,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>427655</v>
+        <v>427817</v>
       </c>
       <c r="R141" t="n">
-        <v>6233850</v>
+        <v>6233621</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15181,10 +15177,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471645</v>
+        <v>121471707</v>
       </c>
       <c r="B142" t="n">
-        <v>80242</v>
+        <v>96731</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15197,21 +15193,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15221,10 +15217,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>427702</v>
+        <v>427809</v>
       </c>
       <c r="R142" t="n">
-        <v>6233806</v>
+        <v>6233703</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15283,10 +15279,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471716</v>
+        <v>121471644</v>
       </c>
       <c r="B143" t="n">
-        <v>80242</v>
+        <v>78864</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15299,21 +15295,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15323,10 +15319,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>427547</v>
+        <v>427671</v>
       </c>
       <c r="R143" t="n">
-        <v>6233865</v>
+        <v>6233821</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15385,10 +15381,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471990</v>
+        <v>121471600</v>
       </c>
       <c r="B144" t="n">
-        <v>80242</v>
+        <v>94605</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15401,21 +15397,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15425,10 +15421,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>427765</v>
+        <v>427698</v>
       </c>
       <c r="R144" t="n">
-        <v>6233765</v>
+        <v>6233566</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15455,12 +15451,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15487,10 +15483,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471984</v>
+        <v>121471586</v>
       </c>
       <c r="B145" t="n">
-        <v>80242</v>
+        <v>80256</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15499,25 +15495,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15527,10 +15523,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427530</v>
+        <v>427748</v>
       </c>
       <c r="R145" t="n">
-        <v>6233736</v>
+        <v>6233622</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15557,12 +15553,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15589,10 +15585,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471610</v>
+        <v>121471645</v>
       </c>
       <c r="B146" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15629,10 +15625,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427487</v>
+        <v>427702</v>
       </c>
       <c r="R146" t="n">
-        <v>6233816</v>
+        <v>6233806</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15691,10 +15687,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471977</v>
+        <v>121471975</v>
       </c>
       <c r="B147" t="n">
-        <v>96725</v>
+        <v>80243</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15707,21 +15703,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15731,10 +15727,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427533</v>
+        <v>427575</v>
       </c>
       <c r="R147" t="n">
-        <v>6233765</v>
+        <v>6233800</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15793,10 +15789,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471963</v>
+        <v>121471705</v>
       </c>
       <c r="B148" t="n">
-        <v>94599</v>
+        <v>80243</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15809,21 +15805,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15833,10 +15829,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427520</v>
+        <v>427753</v>
       </c>
       <c r="R148" t="n">
-        <v>6233715</v>
+        <v>6233606</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15863,12 +15859,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15895,10 +15891,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471562</v>
+        <v>121471971</v>
       </c>
       <c r="B149" t="n">
-        <v>80578</v>
+        <v>78864</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15907,25 +15903,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1182</v>
+        <v>6459</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15935,10 +15931,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>428000</v>
+        <v>427499</v>
       </c>
       <c r="R149" t="n">
-        <v>6233692</v>
+        <v>6233792</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15965,12 +15961,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15997,10 +15993,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471629</v>
+        <v>121472000</v>
       </c>
       <c r="B150" t="n">
-        <v>80255</v>
+        <v>74698</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16009,25 +16005,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1144</v>
+        <v>6439</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16037,10 +16033,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>427602</v>
+        <v>427926</v>
       </c>
       <c r="R150" t="n">
-        <v>6233832</v>
+        <v>6233617</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16067,12 +16063,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16099,10 +16095,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471636</v>
+        <v>121471583</v>
       </c>
       <c r="B151" t="n">
-        <v>80242</v>
+        <v>78864</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16115,21 +16111,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16139,10 +16135,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>427650</v>
+        <v>427813</v>
       </c>
       <c r="R151" t="n">
-        <v>6233855</v>
+        <v>6233621</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16201,10 +16197,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471591</v>
+        <v>121471574</v>
       </c>
       <c r="B152" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16241,10 +16237,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>427724</v>
+        <v>427838</v>
       </c>
       <c r="R152" t="n">
-        <v>6233617</v>
+        <v>6233582</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16303,10 +16299,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471593</v>
+        <v>121471720</v>
       </c>
       <c r="B153" t="n">
-        <v>80242</v>
+        <v>80243</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16343,10 +16339,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>427699</v>
+        <v>427595</v>
       </c>
       <c r="R153" t="n">
-        <v>6233608</v>
+        <v>6233898</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16405,10 +16401,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471959</v>
+        <v>121471640</v>
       </c>
       <c r="B154" t="n">
-        <v>80242</v>
+        <v>96731</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16421,21 +16417,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16445,10 +16441,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>427734</v>
+        <v>427653</v>
       </c>
       <c r="R154" t="n">
-        <v>6233532</v>
+        <v>6233849</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16475,12 +16471,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16507,10 +16503,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471556</v>
+        <v>121471967</v>
       </c>
       <c r="B155" t="n">
-        <v>96725</v>
+        <v>80256</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16519,25 +16515,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16547,10 +16543,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>427948</v>
+        <v>427508</v>
       </c>
       <c r="R155" t="n">
-        <v>6233643</v>
+        <v>6233737</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16577,12 +16573,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16609,10 +16605,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121472015</v>
+        <v>121471561</v>
       </c>
       <c r="B156" t="n">
-        <v>74697</v>
+        <v>96731</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16625,21 +16621,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16649,10 +16645,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>427903</v>
+        <v>427999</v>
       </c>
       <c r="R156" t="n">
-        <v>6233639</v>
+        <v>6233695</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16679,12 +16675,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16711,10 +16707,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471718</v>
+        <v>121471968</v>
       </c>
       <c r="B157" t="n">
-        <v>80255</v>
+        <v>57371</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16723,25 +16719,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1144</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16751,10 +16747,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>427584</v>
+        <v>427512</v>
       </c>
       <c r="R157" t="n">
-        <v>6233863</v>
+        <v>6233745</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16781,12 +16777,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16813,10 +16809,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471620</v>
+        <v>121472014</v>
       </c>
       <c r="B158" t="n">
-        <v>94588</v>
+        <v>80256</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16825,25 +16821,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16853,10 +16849,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>427625</v>
+        <v>427882</v>
       </c>
       <c r="R158" t="n">
-        <v>6233894</v>
+        <v>6233622</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16883,12 +16879,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16915,10 +16911,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471575</v>
+        <v>121471642</v>
       </c>
       <c r="B159" t="n">
-        <v>91112</v>
+        <v>80243</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16927,25 +16923,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2023</v>
+        <v>230185</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16955,10 +16951,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>427837</v>
+        <v>427654</v>
       </c>
       <c r="R159" t="n">
-        <v>6233582</v>
+        <v>6233848</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17017,10 +17013,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121472003</v>
+        <v>121471623</v>
       </c>
       <c r="B160" t="n">
-        <v>79018</v>
+        <v>80243</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17029,23 +17025,27 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>132</v>
+        <v>230185</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Liten lundlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Bacidina phacodes/tarandina</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr"/>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
@@ -17053,10 +17053,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>427911</v>
+        <v>427579</v>
       </c>
       <c r="R160" t="n">
-        <v>6233614</v>
+        <v>6233850</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17083,12 +17083,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17115,10 +17115,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471563</v>
+        <v>121471609</v>
       </c>
       <c r="B161" t="n">
-        <v>96725</v>
+        <v>80243</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17131,21 +17131,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17155,10 +17155,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>428012</v>
+        <v>427543</v>
       </c>
       <c r="R161" t="n">
-        <v>6233689</v>
+        <v>6233756</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -3638,10 +3638,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471996</v>
+        <v>121471610</v>
       </c>
       <c r="B29" t="n">
-        <v>80256</v>
+        <v>80243</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3650,25 +3650,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427855</v>
+        <v>427487</v>
       </c>
       <c r="R29" t="n">
-        <v>6233614</v>
+        <v>6233816</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3740,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471610</v>
+        <v>121471996</v>
       </c>
       <c r="B30" t="n">
-        <v>80243</v>
+        <v>80256</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427487</v>
+        <v>427855</v>
       </c>
       <c r="R30" t="n">
-        <v>6233816</v>
+        <v>6233614</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -7531,10 +7531,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471710</v>
+        <v>121471572</v>
       </c>
       <c r="B67" t="n">
-        <v>94607</v>
+        <v>96731</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7547,21 +7547,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2666</v>
+        <v>2606</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7571,10 +7571,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427448</v>
+        <v>427982</v>
       </c>
       <c r="R67" t="n">
-        <v>6233789</v>
+        <v>6233642</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7633,10 +7633,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471992</v>
+        <v>121471998</v>
       </c>
       <c r="B68" t="n">
-        <v>94594</v>
+        <v>76949</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7645,25 +7645,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427861</v>
+        <v>427915</v>
       </c>
       <c r="R68" t="n">
-        <v>6233620</v>
+        <v>6233632</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7735,10 +7735,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471700</v>
+        <v>121471977</v>
       </c>
       <c r="B69" t="n">
-        <v>78988</v>
+        <v>96731</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7751,21 +7751,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6431</v>
+        <v>2606</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7775,10 +7775,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427806</v>
+        <v>427533</v>
       </c>
       <c r="R69" t="n">
-        <v>6233482</v>
+        <v>6233765</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7805,12 +7805,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8449,10 +8449,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471572</v>
+        <v>121471710</v>
       </c>
       <c r="B76" t="n">
-        <v>96731</v>
+        <v>94607</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8465,21 +8465,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2606</v>
+        <v>2666</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8489,10 +8489,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427982</v>
+        <v>427448</v>
       </c>
       <c r="R76" t="n">
-        <v>6233642</v>
+        <v>6233789</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8551,10 +8551,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471998</v>
+        <v>121471992</v>
       </c>
       <c r="B77" t="n">
-        <v>76949</v>
+        <v>94594</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8563,25 +8563,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8591,10 +8591,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427915</v>
+        <v>427861</v>
       </c>
       <c r="R77" t="n">
-        <v>6233632</v>
+        <v>6233620</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8653,10 +8653,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471977</v>
+        <v>121471700</v>
       </c>
       <c r="B78" t="n">
-        <v>96731</v>
+        <v>78988</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8669,21 +8669,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2606</v>
+        <v>6431</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8693,10 +8693,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427533</v>
+        <v>427806</v>
       </c>
       <c r="R78" t="n">
-        <v>6233765</v>
+        <v>6233482</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,12 +8723,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8755,10 +8755,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471637</v>
+        <v>121471955</v>
       </c>
       <c r="B79" t="n">
-        <v>96731</v>
+        <v>94607</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8771,21 +8771,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2606</v>
+        <v>2666</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427638</v>
+        <v>427741</v>
       </c>
       <c r="R79" t="n">
-        <v>6233822</v>
+        <v>6233529</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8825,12 +8825,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8857,7 +8857,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471955</v>
+        <v>121471956</v>
       </c>
       <c r="B80" t="n">
         <v>94607</v>
@@ -8897,10 +8897,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427741</v>
+        <v>427739</v>
       </c>
       <c r="R80" t="n">
-        <v>6233529</v>
+        <v>6233524</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8959,10 +8959,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471956</v>
+        <v>121471718</v>
       </c>
       <c r="B81" t="n">
-        <v>94607</v>
+        <v>80256</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8971,25 +8971,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2666</v>
+        <v>1144</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8999,10 +8999,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427739</v>
+        <v>427584</v>
       </c>
       <c r="R81" t="n">
-        <v>6233524</v>
+        <v>6233863</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9029,12 +9029,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9061,10 +9061,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471718</v>
+        <v>121471560</v>
       </c>
       <c r="B82" t="n">
-        <v>80256</v>
+        <v>80243</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9073,25 +9073,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9101,10 +9101,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427584</v>
+        <v>428008</v>
       </c>
       <c r="R82" t="n">
-        <v>6233863</v>
+        <v>6233671</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9163,10 +9163,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471560</v>
+        <v>121471637</v>
       </c>
       <c r="B83" t="n">
-        <v>80243</v>
+        <v>96731</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9179,21 +9179,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9203,10 +9203,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>428008</v>
+        <v>427638</v>
       </c>
       <c r="R83" t="n">
-        <v>6233671</v>
+        <v>6233822</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10999,10 +10999,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471557</v>
+        <v>121471636</v>
       </c>
       <c r="B101" t="n">
-        <v>94594</v>
+        <v>80243</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11015,21 +11015,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11039,10 +11039,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>427948</v>
+        <v>427650</v>
       </c>
       <c r="R101" t="n">
-        <v>6233643</v>
+        <v>6233855</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11101,10 +11101,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121472009</v>
+        <v>121471985</v>
       </c>
       <c r="B102" t="n">
-        <v>94605</v>
+        <v>80243</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11117,21 +11117,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11141,10 +11141,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427877</v>
+        <v>427558</v>
       </c>
       <c r="R102" t="n">
-        <v>6233615</v>
+        <v>6233768</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11203,10 +11203,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471603</v>
+        <v>121471597</v>
       </c>
       <c r="B103" t="n">
-        <v>80256</v>
+        <v>80243</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11215,25 +11215,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11243,10 +11243,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427596</v>
+        <v>427693</v>
       </c>
       <c r="R103" t="n">
-        <v>6233681</v>
+        <v>6233604</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11305,10 +11305,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121472003</v>
+        <v>121471557</v>
       </c>
       <c r="B104" t="n">
-        <v>79019</v>
+        <v>94594</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11317,23 +11317,27 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>132</v>
+        <v>2671</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Liten lundlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bacidina phacodes/tarandina</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -11341,10 +11345,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427911</v>
+        <v>427948</v>
       </c>
       <c r="R104" t="n">
-        <v>6233614</v>
+        <v>6233643</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11371,12 +11375,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11403,10 +11407,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471587</v>
+        <v>121472009</v>
       </c>
       <c r="B105" t="n">
-        <v>80256</v>
+        <v>94605</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11415,25 +11419,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11443,10 +11447,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427770</v>
+        <v>427877</v>
       </c>
       <c r="R105" t="n">
-        <v>6233624</v>
+        <v>6233615</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11473,12 +11477,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11505,7 +11509,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471576</v>
+        <v>121471603</v>
       </c>
       <c r="B106" t="n">
         <v>80256</v>
@@ -11545,10 +11549,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427742</v>
+        <v>427596</v>
       </c>
       <c r="R106" t="n">
-        <v>6233565</v>
+        <v>6233681</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11607,10 +11611,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471636</v>
+        <v>121472003</v>
       </c>
       <c r="B107" t="n">
-        <v>80243</v>
+        <v>79019</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11619,27 +11623,23 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>230185</v>
+        <v>132</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Liten lundlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Bacidina phacodes/tarandina</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11647,10 +11647,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427650</v>
+        <v>427911</v>
       </c>
       <c r="R107" t="n">
-        <v>6233855</v>
+        <v>6233614</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11677,12 +11677,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11709,10 +11709,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471985</v>
+        <v>121471587</v>
       </c>
       <c r="B108" t="n">
-        <v>80243</v>
+        <v>80256</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11721,25 +11721,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11749,10 +11749,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>427558</v>
+        <v>427770</v>
       </c>
       <c r="R108" t="n">
-        <v>6233768</v>
+        <v>6233624</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11779,12 +11779,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11811,10 +11811,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471597</v>
+        <v>121471576</v>
       </c>
       <c r="B109" t="n">
-        <v>80243</v>
+        <v>80256</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11823,25 +11823,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11851,10 +11851,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>427693</v>
+        <v>427742</v>
       </c>
       <c r="R109" t="n">
-        <v>6233604</v>
+        <v>6233565</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12933,10 +12933,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471643</v>
+        <v>121471564</v>
       </c>
       <c r="B120" t="n">
-        <v>96731</v>
+        <v>80256</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12945,25 +12945,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12973,10 +12973,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427671</v>
+        <v>428014</v>
       </c>
       <c r="R120" t="n">
-        <v>6233821</v>
+        <v>6233692</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13035,10 +13035,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471564</v>
+        <v>121471624</v>
       </c>
       <c r="B121" t="n">
-        <v>80256</v>
+        <v>74564</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13047,25 +13047,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1144</v>
+        <v>1116</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13075,10 +13075,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>428014</v>
+        <v>427594</v>
       </c>
       <c r="R121" t="n">
-        <v>6233692</v>
+        <v>6233828</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13137,10 +13137,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471624</v>
+        <v>121471643</v>
       </c>
       <c r="B122" t="n">
-        <v>74564</v>
+        <v>96731</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13149,25 +13149,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1116</v>
+        <v>2606</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13177,10 +13177,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427594</v>
+        <v>427671</v>
       </c>
       <c r="R122" t="n">
-        <v>6233828</v>
+        <v>6233821</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -15381,10 +15381,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471600</v>
+        <v>121471645</v>
       </c>
       <c r="B144" t="n">
-        <v>94605</v>
+        <v>80243</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15397,21 +15397,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15421,10 +15421,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>427698</v>
+        <v>427702</v>
       </c>
       <c r="R144" t="n">
-        <v>6233566</v>
+        <v>6233806</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15483,10 +15483,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471586</v>
+        <v>121471975</v>
       </c>
       <c r="B145" t="n">
-        <v>80256</v>
+        <v>80243</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15495,25 +15495,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15523,10 +15523,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427748</v>
+        <v>427575</v>
       </c>
       <c r="R145" t="n">
-        <v>6233622</v>
+        <v>6233800</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15553,12 +15553,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15585,7 +15585,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471645</v>
+        <v>121471705</v>
       </c>
       <c r="B146" t="n">
         <v>80243</v>
@@ -15625,10 +15625,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427702</v>
+        <v>427753</v>
       </c>
       <c r="R146" t="n">
-        <v>6233806</v>
+        <v>6233606</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15687,10 +15687,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471975</v>
+        <v>121471600</v>
       </c>
       <c r="B147" t="n">
-        <v>80243</v>
+        <v>94605</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15703,21 +15703,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15727,10 +15727,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427575</v>
+        <v>427698</v>
       </c>
       <c r="R147" t="n">
-        <v>6233800</v>
+        <v>6233566</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15757,12 +15757,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15789,10 +15789,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471705</v>
+        <v>121471586</v>
       </c>
       <c r="B148" t="n">
-        <v>80243</v>
+        <v>80256</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15801,25 +15801,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15829,10 +15829,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427753</v>
+        <v>427748</v>
       </c>
       <c r="R148" t="n">
-        <v>6233606</v>
+        <v>6233622</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16197,10 +16197,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471574</v>
+        <v>121471640</v>
       </c>
       <c r="B152" t="n">
-        <v>80243</v>
+        <v>96731</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16213,21 +16213,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16237,10 +16237,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>427838</v>
+        <v>427653</v>
       </c>
       <c r="R152" t="n">
-        <v>6233582</v>
+        <v>6233849</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16299,10 +16299,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471720</v>
+        <v>121471967</v>
       </c>
       <c r="B153" t="n">
-        <v>80243</v>
+        <v>80256</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16311,25 +16311,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16339,10 +16339,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>427595</v>
+        <v>427508</v>
       </c>
       <c r="R153" t="n">
-        <v>6233898</v>
+        <v>6233737</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16369,12 +16369,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16401,10 +16401,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471640</v>
+        <v>121471574</v>
       </c>
       <c r="B154" t="n">
-        <v>96731</v>
+        <v>80243</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16417,21 +16417,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16441,10 +16441,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>427653</v>
+        <v>427838</v>
       </c>
       <c r="R154" t="n">
-        <v>6233849</v>
+        <v>6233582</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16503,10 +16503,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471967</v>
+        <v>121471720</v>
       </c>
       <c r="B155" t="n">
-        <v>80256</v>
+        <v>80243</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16515,25 +16515,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16543,10 +16543,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>427508</v>
+        <v>427595</v>
       </c>
       <c r="R155" t="n">
-        <v>6233737</v>
+        <v>6233898</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16573,12 +16573,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD155" t="b">

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471719</v>
+        <v>121471977</v>
       </c>
       <c r="B11" t="n">
-        <v>76949</v>
+        <v>96732</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427583</v>
+        <v>427533</v>
       </c>
       <c r="R11" t="n">
-        <v>6233861</v>
+        <v>6233765</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,10 +1904,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471634</v>
+        <v>121471984</v>
       </c>
       <c r="B12" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427636</v>
+        <v>427530</v>
       </c>
       <c r="R12" t="n">
-        <v>6233848</v>
+        <v>6233736</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2006,10 +2006,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471966</v>
+        <v>121471719</v>
       </c>
       <c r="B13" t="n">
-        <v>76949</v>
+        <v>76950</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427505</v>
+        <v>427583</v>
       </c>
       <c r="R13" t="n">
-        <v>6233740</v>
+        <v>6233861</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,12 +2076,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471604</v>
+        <v>121471968</v>
       </c>
       <c r="B14" t="n">
-        <v>80243</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230185</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427595</v>
+        <v>427512</v>
       </c>
       <c r="R14" t="n">
-        <v>6233781</v>
+        <v>6233745</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471704</v>
+        <v>121471716</v>
       </c>
       <c r="B15" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427785</v>
+        <v>427547</v>
       </c>
       <c r="R15" t="n">
-        <v>6233585</v>
+        <v>6233865</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121472002</v>
+        <v>121471604</v>
       </c>
       <c r="B16" t="n">
-        <v>94605</v>
+        <v>80244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427909</v>
+        <v>427595</v>
       </c>
       <c r="R16" t="n">
-        <v>6233613</v>
+        <v>6233781</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121471712</v>
+        <v>121471584</v>
       </c>
       <c r="B17" t="n">
-        <v>96731</v>
+        <v>96732</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427439</v>
+        <v>427817</v>
       </c>
       <c r="R17" t="n">
-        <v>6233838</v>
+        <v>6233621</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121471974</v>
+        <v>121471706</v>
       </c>
       <c r="B18" t="n">
-        <v>90514</v>
+        <v>96732</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1067</v>
+        <v>2606</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427554</v>
+        <v>427781</v>
       </c>
       <c r="R18" t="n">
-        <v>6233803</v>
+        <v>6233648</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121471995</v>
+        <v>121471702</v>
       </c>
       <c r="B19" t="n">
-        <v>78864</v>
+        <v>96732</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427856</v>
+        <v>427811</v>
       </c>
       <c r="R19" t="n">
-        <v>6233613</v>
+        <v>6233480</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121471641</v>
+        <v>121471712</v>
       </c>
       <c r="B20" t="n">
-        <v>78864</v>
+        <v>96732</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427655</v>
+        <v>427439</v>
       </c>
       <c r="R20" t="n">
-        <v>6233850</v>
+        <v>6233838</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121471983</v>
+        <v>121471637</v>
       </c>
       <c r="B21" t="n">
-        <v>74698</v>
+        <v>96732</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>427521</v>
+        <v>427638</v>
       </c>
       <c r="R21" t="n">
-        <v>6233737</v>
+        <v>6233822</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121471590</v>
+        <v>121471718</v>
       </c>
       <c r="B22" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427753</v>
+        <v>427584</v>
       </c>
       <c r="R22" t="n">
-        <v>6233666</v>
+        <v>6233863</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471962</v>
+        <v>121471587</v>
       </c>
       <c r="B23" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427528</v>
+        <v>427770</v>
       </c>
       <c r="R23" t="n">
-        <v>6233707</v>
+        <v>6233624</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3096,12 +3096,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471706</v>
+        <v>121471651</v>
       </c>
       <c r="B24" t="n">
-        <v>96731</v>
+        <v>78865</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427781</v>
+        <v>427737</v>
       </c>
       <c r="R24" t="n">
-        <v>6233648</v>
+        <v>6233789</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471628</v>
+        <v>121471645</v>
       </c>
       <c r="B25" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427604</v>
+        <v>427702</v>
       </c>
       <c r="R25" t="n">
-        <v>6233834</v>
+        <v>6233806</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471630</v>
+        <v>121471557</v>
       </c>
       <c r="B26" t="n">
-        <v>76949</v>
+        <v>94595</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3344,25 +3344,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427604</v>
+        <v>427948</v>
       </c>
       <c r="R26" t="n">
-        <v>6233829</v>
+        <v>6233643</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471713</v>
+        <v>121471643</v>
       </c>
       <c r="B27" t="n">
-        <v>76949</v>
+        <v>96732</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427438</v>
+        <v>427671</v>
       </c>
       <c r="R27" t="n">
-        <v>6233852</v>
+        <v>6233821</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471964</v>
+        <v>121471960</v>
       </c>
       <c r="B28" t="n">
-        <v>94605</v>
+        <v>94595</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,21 +3552,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2667</v>
+        <v>2671</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427511</v>
+        <v>427734</v>
       </c>
       <c r="R28" t="n">
-        <v>6233739</v>
+        <v>6233532</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471610</v>
+        <v>121471565</v>
       </c>
       <c r="B29" t="n">
-        <v>80243</v>
+        <v>76950</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3650,25 +3650,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427487</v>
+        <v>428016</v>
       </c>
       <c r="R29" t="n">
-        <v>6233816</v>
+        <v>6233689</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471996</v>
+        <v>121472006</v>
       </c>
       <c r="B30" t="n">
-        <v>80256</v>
+        <v>76950</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427855</v>
+        <v>427892</v>
       </c>
       <c r="R30" t="n">
-        <v>6233614</v>
+        <v>6233623</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471621</v>
+        <v>121471558</v>
       </c>
       <c r="B31" t="n">
-        <v>96731</v>
+        <v>80257</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3854,25 +3854,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427607</v>
+        <v>427960</v>
       </c>
       <c r="R31" t="n">
-        <v>6233875</v>
+        <v>6233661</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471714</v>
+        <v>121471995</v>
       </c>
       <c r="B32" t="n">
-        <v>78408</v>
+        <v>78865</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,25 +3956,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427435</v>
+        <v>427856</v>
       </c>
       <c r="R32" t="n">
-        <v>6233855</v>
+        <v>6233613</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4046,10 +4046,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471988</v>
+        <v>121471952</v>
       </c>
       <c r="B33" t="n">
-        <v>74526</v>
+        <v>74699</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6428</v>
+        <v>6439</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427738</v>
+        <v>427763</v>
       </c>
       <c r="R33" t="n">
-        <v>6233780</v>
+        <v>6233529</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471622</v>
+        <v>121471986</v>
       </c>
       <c r="B34" t="n">
-        <v>74698</v>
+        <v>80257</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4160,38 +4160,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427623</v>
+        <v>427558</v>
       </c>
       <c r="R34" t="n">
-        <v>6233865</v>
+        <v>6233769</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4218,12 +4221,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Med Refractohilum pluriseptatum</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4231,6 +4239,11 @@
       </c>
       <c r="AE34" t="b">
         <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4250,10 +4263,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471627</v>
+        <v>121471561</v>
       </c>
       <c r="B35" t="n">
-        <v>74698</v>
+        <v>96732</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4266,21 +4279,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4290,10 +4303,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427613</v>
+        <v>427999</v>
       </c>
       <c r="R35" t="n">
-        <v>6233840</v>
+        <v>6233695</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4352,10 +4365,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471651</v>
+        <v>121471708</v>
       </c>
       <c r="B36" t="n">
-        <v>78864</v>
+        <v>96732</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4368,21 +4381,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4392,10 +4405,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427737</v>
+        <v>427785</v>
       </c>
       <c r="R36" t="n">
-        <v>6233789</v>
+        <v>6233734</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4454,10 +4467,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471612</v>
+        <v>121471578</v>
       </c>
       <c r="B37" t="n">
-        <v>80243</v>
+        <v>76950</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4466,25 +4479,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4494,10 +4507,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427466</v>
+        <v>427749</v>
       </c>
       <c r="R37" t="n">
-        <v>6233828</v>
+        <v>6233573</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4556,10 +4569,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471715</v>
+        <v>121471982</v>
       </c>
       <c r="B38" t="n">
-        <v>80243</v>
+        <v>76950</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4568,25 +4581,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4596,10 +4609,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427445</v>
+        <v>427516</v>
       </c>
       <c r="R38" t="n">
-        <v>6233860</v>
+        <v>6233748</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4626,12 +4639,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4658,10 +4671,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471984</v>
+        <v>121471966</v>
       </c>
       <c r="B39" t="n">
-        <v>80243</v>
+        <v>76950</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4670,25 +4683,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4698,10 +4711,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427530</v>
+        <v>427505</v>
       </c>
       <c r="R39" t="n">
-        <v>6233736</v>
+        <v>6233740</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4760,10 +4773,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471601</v>
+        <v>121472010</v>
       </c>
       <c r="B40" t="n">
-        <v>80243</v>
+        <v>78989</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4776,21 +4789,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>230185</v>
+        <v>6431</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4800,10 +4813,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427688</v>
+        <v>427877</v>
       </c>
       <c r="R40" t="n">
-        <v>6233590</v>
+        <v>6233615</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,12 +4843,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4862,10 +4875,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471959</v>
+        <v>121471602</v>
       </c>
       <c r="B41" t="n">
-        <v>80243</v>
+        <v>94606</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4878,21 +4891,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4915,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427734</v>
+        <v>427641</v>
       </c>
       <c r="R41" t="n">
-        <v>6233532</v>
+        <v>6233630</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4932,12 +4945,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4964,10 +4977,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471619</v>
+        <v>121471630</v>
       </c>
       <c r="B42" t="n">
-        <v>96731</v>
+        <v>76950</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4976,25 +4989,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5004,10 +5017,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427624</v>
+        <v>427604</v>
       </c>
       <c r="R42" t="n">
-        <v>6233894</v>
+        <v>6233829</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5066,10 +5079,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471647</v>
+        <v>121471642</v>
       </c>
       <c r="B43" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5082,21 +5095,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5106,10 +5119,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427720</v>
+        <v>427654</v>
       </c>
       <c r="R43" t="n">
-        <v>6233787</v>
+        <v>6233848</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5168,10 +5181,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471952</v>
+        <v>121471580</v>
       </c>
       <c r="B44" t="n">
-        <v>74698</v>
+        <v>80244</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5184,21 +5197,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5208,10 +5221,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427763</v>
+        <v>427804</v>
       </c>
       <c r="R44" t="n">
-        <v>6233529</v>
+        <v>6233576</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5238,12 +5251,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5270,10 +5283,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471631</v>
+        <v>121471597</v>
       </c>
       <c r="B45" t="n">
-        <v>80243</v>
+        <v>80244</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5310,10 +5323,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>427601</v>
+        <v>427693</v>
       </c>
       <c r="R45" t="n">
-        <v>6233830</v>
+        <v>6233604</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5372,10 +5385,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471965</v>
+        <v>121471976</v>
       </c>
       <c r="B46" t="n">
-        <v>76949</v>
+        <v>96732</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5384,25 +5397,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5412,10 +5425,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427509</v>
+        <v>427576</v>
       </c>
       <c r="R46" t="n">
-        <v>6233731</v>
+        <v>6233800</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5474,10 +5487,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471973</v>
+        <v>121471980</v>
       </c>
       <c r="B47" t="n">
-        <v>76949</v>
+        <v>80257</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5486,25 +5499,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5514,10 +5527,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427544</v>
+        <v>427532</v>
       </c>
       <c r="R47" t="n">
-        <v>6233811</v>
+        <v>6233767</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5576,10 +5589,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471982</v>
+        <v>121471951</v>
       </c>
       <c r="B48" t="n">
-        <v>76949</v>
+        <v>76950</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5616,10 +5629,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427516</v>
+        <v>427762</v>
       </c>
       <c r="R48" t="n">
-        <v>6233748</v>
+        <v>6233515</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5678,10 +5691,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471646</v>
+        <v>121471999</v>
       </c>
       <c r="B49" t="n">
-        <v>94605</v>
+        <v>80257</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5690,25 +5703,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5731,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427692</v>
+        <v>427916</v>
       </c>
       <c r="R49" t="n">
-        <v>6233796</v>
+        <v>6233634</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5748,12 +5761,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5780,10 +5793,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471577</v>
+        <v>121471520</v>
       </c>
       <c r="B50" t="n">
-        <v>94605</v>
+        <v>80244</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5796,21 +5809,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5820,10 +5833,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427749</v>
+        <v>427789</v>
       </c>
       <c r="R50" t="n">
-        <v>6233572</v>
+        <v>6233516</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5882,10 +5895,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471986</v>
+        <v>121471560</v>
       </c>
       <c r="B51" t="n">
-        <v>80256</v>
+        <v>80244</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5894,41 +5907,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427558</v>
+        <v>428008</v>
       </c>
       <c r="R51" t="n">
-        <v>6233769</v>
+        <v>6233671</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5955,17 +5965,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Med Refractohilum pluriseptatum</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5973,11 +5978,6 @@
       </c>
       <c r="AE51" t="b">
         <v>0</v>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG51" t="b">
         <v>0</v>
@@ -5997,10 +5997,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121472007</v>
+        <v>121471631</v>
       </c>
       <c r="B52" t="n">
-        <v>80256</v>
+        <v>80244</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6009,25 +6009,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6037,10 +6037,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427892</v>
+        <v>427601</v>
       </c>
       <c r="R52" t="n">
-        <v>6233623</v>
+        <v>6233830</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6067,12 +6067,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6099,10 +6099,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471650</v>
+        <v>121471583</v>
       </c>
       <c r="B53" t="n">
-        <v>80243</v>
+        <v>78865</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6115,21 +6115,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6139,10 +6139,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427737</v>
+        <v>427813</v>
       </c>
       <c r="R53" t="n">
-        <v>6233784</v>
+        <v>6233621</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6201,10 +6201,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471990</v>
+        <v>121471956</v>
       </c>
       <c r="B54" t="n">
-        <v>80243</v>
+        <v>94608</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6217,21 +6217,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6241,10 +6241,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427765</v>
+        <v>427739</v>
       </c>
       <c r="R54" t="n">
-        <v>6233765</v>
+        <v>6233524</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6303,10 +6303,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471520</v>
+        <v>121471563</v>
       </c>
       <c r="B55" t="n">
-        <v>80243</v>
+        <v>96732</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6319,21 +6319,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6343,10 +6343,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>427789</v>
+        <v>428012</v>
       </c>
       <c r="R55" t="n">
-        <v>6233516</v>
+        <v>6233689</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6405,10 +6405,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121472004</v>
+        <v>121471619</v>
       </c>
       <c r="B56" t="n">
-        <v>80243</v>
+        <v>96732</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6421,21 +6421,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>427892</v>
+        <v>427624</v>
       </c>
       <c r="R56" t="n">
-        <v>6233623</v>
+        <v>6233894</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6475,12 +6475,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6507,10 +6507,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471993</v>
+        <v>121471992</v>
       </c>
       <c r="B57" t="n">
-        <v>91510</v>
+        <v>94595</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6519,38 +6519,35 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2014</v>
+        <v>2671</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427859</v>
+        <v>427861</v>
       </c>
       <c r="R57" t="n">
         <v>6233620</v>
@@ -6594,7 +6591,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6613,10 +6609,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471599</v>
+        <v>121471973</v>
       </c>
       <c r="B58" t="n">
-        <v>94607</v>
+        <v>76950</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6625,25 +6621,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>2666</v>
+        <v>1342</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6653,10 +6649,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427685</v>
+        <v>427544</v>
       </c>
       <c r="R58" t="n">
-        <v>6233593</v>
+        <v>6233811</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6683,12 +6679,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6715,10 +6711,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471632</v>
+        <v>121471983</v>
       </c>
       <c r="B59" t="n">
-        <v>80243</v>
+        <v>74699</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6731,21 +6727,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6755,10 +6751,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427615</v>
+        <v>427521</v>
       </c>
       <c r="R59" t="n">
-        <v>6233825</v>
+        <v>6233737</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6785,12 +6781,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6817,10 +6813,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121472006</v>
+        <v>121471975</v>
       </c>
       <c r="B60" t="n">
-        <v>76949</v>
+        <v>80244</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6829,25 +6825,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6857,10 +6853,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427892</v>
+        <v>427575</v>
       </c>
       <c r="R60" t="n">
-        <v>6233623</v>
+        <v>6233800</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6919,10 +6915,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471585</v>
+        <v>121471601</v>
       </c>
       <c r="B61" t="n">
-        <v>76949</v>
+        <v>80244</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6931,25 +6927,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6959,10 +6955,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427748</v>
+        <v>427688</v>
       </c>
       <c r="R61" t="n">
-        <v>6233622</v>
+        <v>6233590</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7021,10 +7017,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471589</v>
+        <v>121471623</v>
       </c>
       <c r="B62" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7037,21 +7033,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7061,10 +7057,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427804</v>
+        <v>427579</v>
       </c>
       <c r="R62" t="n">
-        <v>6233688</v>
+        <v>6233850</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7123,10 +7119,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471703</v>
+        <v>121471581</v>
       </c>
       <c r="B63" t="n">
-        <v>74698</v>
+        <v>80244</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7139,21 +7135,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7163,10 +7159,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427770</v>
+        <v>427820</v>
       </c>
       <c r="R63" t="n">
-        <v>6233580</v>
+        <v>6233599</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7225,10 +7221,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471602</v>
+        <v>121471590</v>
       </c>
       <c r="B64" t="n">
-        <v>94605</v>
+        <v>80244</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7241,21 +7237,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7265,10 +7261,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427641</v>
+        <v>427753</v>
       </c>
       <c r="R64" t="n">
-        <v>6233630</v>
+        <v>6233666</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7327,10 +7323,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121472001</v>
+        <v>121472004</v>
       </c>
       <c r="B65" t="n">
-        <v>94615</v>
+        <v>80244</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7343,21 +7339,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1080</v>
+        <v>230185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7367,10 +7363,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427908</v>
+        <v>427892</v>
       </c>
       <c r="R65" t="n">
-        <v>6233617</v>
+        <v>6233623</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7429,10 +7425,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471629</v>
+        <v>121471962</v>
       </c>
       <c r="B66" t="n">
-        <v>80256</v>
+        <v>80244</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7441,25 +7437,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7469,10 +7465,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427602</v>
+        <v>427528</v>
       </c>
       <c r="R66" t="n">
-        <v>6233832</v>
+        <v>6233707</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7499,12 +7495,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7531,10 +7527,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471572</v>
+        <v>121471598</v>
       </c>
       <c r="B67" t="n">
-        <v>96731</v>
+        <v>94606</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7547,21 +7543,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7571,10 +7567,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427982</v>
+        <v>427690</v>
       </c>
       <c r="R67" t="n">
-        <v>6233642</v>
+        <v>6233595</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7633,10 +7629,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471998</v>
+        <v>121472016</v>
       </c>
       <c r="B68" t="n">
-        <v>76949</v>
+        <v>96732</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7645,25 +7641,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7673,10 +7669,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427915</v>
+        <v>427903</v>
       </c>
       <c r="R68" t="n">
-        <v>6233632</v>
+        <v>6233640</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7735,10 +7731,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471977</v>
+        <v>121471955</v>
       </c>
       <c r="B69" t="n">
-        <v>96731</v>
+        <v>94608</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7751,21 +7747,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2606</v>
+        <v>2666</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7775,10 +7771,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427533</v>
+        <v>427741</v>
       </c>
       <c r="R69" t="n">
-        <v>6233765</v>
+        <v>6233529</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7837,10 +7833,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471608</v>
+        <v>121471979</v>
       </c>
       <c r="B70" t="n">
-        <v>80243</v>
+        <v>76950</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7849,25 +7845,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7877,10 +7873,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>427566</v>
+        <v>427533</v>
       </c>
       <c r="R70" t="n">
-        <v>6233756</v>
+        <v>6233765</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7907,12 +7903,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7939,10 +7935,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471954</v>
+        <v>121471562</v>
       </c>
       <c r="B71" t="n">
-        <v>80243</v>
+        <v>80580</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7951,25 +7947,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>230185</v>
+        <v>1182</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7979,10 +7975,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>427742</v>
+        <v>428000</v>
       </c>
       <c r="R71" t="n">
-        <v>6233542</v>
+        <v>6233692</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8009,12 +8005,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8041,10 +8037,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471581</v>
+        <v>121471967</v>
       </c>
       <c r="B72" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8053,25 +8049,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8081,10 +8077,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427820</v>
+        <v>427508</v>
       </c>
       <c r="R72" t="n">
-        <v>6233599</v>
+        <v>6233737</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8111,12 +8107,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8143,10 +8139,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471521</v>
+        <v>121471586</v>
       </c>
       <c r="B73" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8155,25 +8151,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8183,10 +8179,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427794</v>
+        <v>427748</v>
       </c>
       <c r="R73" t="n">
-        <v>6233483</v>
+        <v>6233622</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8245,10 +8241,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471638</v>
+        <v>121471576</v>
       </c>
       <c r="B74" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8257,25 +8253,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8285,10 +8281,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>427638</v>
+        <v>427742</v>
       </c>
       <c r="R74" t="n">
-        <v>6233822</v>
+        <v>6233565</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8347,10 +8343,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471614</v>
+        <v>121471644</v>
       </c>
       <c r="B75" t="n">
-        <v>80243</v>
+        <v>78865</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8363,21 +8359,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8387,10 +8383,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>427475</v>
+        <v>427671</v>
       </c>
       <c r="R75" t="n">
-        <v>6233836</v>
+        <v>6233821</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8449,10 +8445,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471710</v>
+        <v>121471704</v>
       </c>
       <c r="B76" t="n">
-        <v>94607</v>
+        <v>96732</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8465,21 +8461,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2666</v>
+        <v>2606</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8489,10 +8485,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427448</v>
+        <v>427785</v>
       </c>
       <c r="R76" t="n">
-        <v>6233789</v>
+        <v>6233585</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8551,10 +8547,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471992</v>
+        <v>121471620</v>
       </c>
       <c r="B77" t="n">
-        <v>94594</v>
+        <v>94595</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8591,10 +8587,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427861</v>
+        <v>427625</v>
       </c>
       <c r="R77" t="n">
-        <v>6233620</v>
+        <v>6233894</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8621,12 +8617,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8653,10 +8649,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471700</v>
+        <v>121472009</v>
       </c>
       <c r="B78" t="n">
-        <v>78988</v>
+        <v>94606</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8669,21 +8665,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6431</v>
+        <v>2667</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8693,10 +8689,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427806</v>
+        <v>427877</v>
       </c>
       <c r="R78" t="n">
-        <v>6233482</v>
+        <v>6233615</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8723,12 +8719,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8755,10 +8751,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471955</v>
+        <v>121471964</v>
       </c>
       <c r="B79" t="n">
-        <v>94607</v>
+        <v>94606</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8771,16 +8767,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8795,10 +8791,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427741</v>
+        <v>427511</v>
       </c>
       <c r="R79" t="n">
-        <v>6233529</v>
+        <v>6233739</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8857,10 +8853,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471956</v>
+        <v>121471961</v>
       </c>
       <c r="B80" t="n">
-        <v>94607</v>
+        <v>94606</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8873,16 +8869,16 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -8897,10 +8893,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427739</v>
+        <v>427615</v>
       </c>
       <c r="R80" t="n">
-        <v>6233524</v>
+        <v>6233649</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8959,10 +8955,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471718</v>
+        <v>121471671</v>
       </c>
       <c r="B81" t="n">
-        <v>80256</v>
+        <v>105766</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8971,25 +8967,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1144</v>
+        <v>220785</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8999,10 +8995,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427584</v>
+        <v>427912</v>
       </c>
       <c r="R81" t="n">
-        <v>6233863</v>
+        <v>6233611</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9061,10 +9057,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471560</v>
+        <v>121471709</v>
       </c>
       <c r="B82" t="n">
-        <v>80243</v>
+        <v>80244</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9101,10 +9097,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>428008</v>
+        <v>427452</v>
       </c>
       <c r="R82" t="n">
-        <v>6233671</v>
+        <v>6233794</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9163,10 +9159,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121471637</v>
+        <v>121472001</v>
       </c>
       <c r="B83" t="n">
-        <v>96731</v>
+        <v>94616</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9179,21 +9175,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2606</v>
+        <v>1080</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9203,10 +9199,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427638</v>
+        <v>427908</v>
       </c>
       <c r="R83" t="n">
-        <v>6233822</v>
+        <v>6233617</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9233,12 +9229,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9265,10 +9261,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471598</v>
+        <v>121471603</v>
       </c>
       <c r="B84" t="n">
-        <v>94605</v>
+        <v>80257</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9277,25 +9273,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9305,10 +9301,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427690</v>
+        <v>427596</v>
       </c>
       <c r="R84" t="n">
-        <v>6233595</v>
+        <v>6233681</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9367,10 +9363,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471593</v>
+        <v>121471640</v>
       </c>
       <c r="B85" t="n">
-        <v>80243</v>
+        <v>96732</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9383,21 +9379,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9407,10 +9403,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427699</v>
+        <v>427653</v>
       </c>
       <c r="R85" t="n">
-        <v>6233608</v>
+        <v>6233849</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9469,10 +9465,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471671</v>
+        <v>121471572</v>
       </c>
       <c r="B86" t="n">
-        <v>105765</v>
+        <v>96732</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9481,25 +9477,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220785</v>
+        <v>2606</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9509,10 +9505,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427912</v>
+        <v>427982</v>
       </c>
       <c r="R86" t="n">
-        <v>6233611</v>
+        <v>6233642</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9571,10 +9567,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471976</v>
+        <v>121471650</v>
       </c>
       <c r="B87" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9587,21 +9583,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9611,10 +9607,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427576</v>
+        <v>427737</v>
       </c>
       <c r="R87" t="n">
-        <v>6233800</v>
+        <v>6233784</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9641,12 +9637,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9673,10 +9669,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471618</v>
+        <v>121471574</v>
       </c>
       <c r="B88" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9689,21 +9685,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9713,10 +9709,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427525</v>
+        <v>427838</v>
       </c>
       <c r="R88" t="n">
-        <v>6233838</v>
+        <v>6233582</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9775,10 +9771,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121472012</v>
+        <v>121471705</v>
       </c>
       <c r="B89" t="n">
-        <v>76949</v>
+        <v>80244</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9787,25 +9783,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9815,10 +9811,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427855</v>
+        <v>427753</v>
       </c>
       <c r="R89" t="n">
-        <v>6233612</v>
+        <v>6233606</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9845,12 +9841,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9877,10 +9873,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471575</v>
+        <v>121471633</v>
       </c>
       <c r="B90" t="n">
-        <v>91118</v>
+        <v>90515</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9889,25 +9885,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2023</v>
+        <v>1067</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9917,10 +9913,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427837</v>
+        <v>427629</v>
       </c>
       <c r="R90" t="n">
-        <v>6233582</v>
+        <v>6233837</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9979,10 +9975,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471709</v>
+        <v>121471608</v>
       </c>
       <c r="B91" t="n">
-        <v>80243</v>
+        <v>80244</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10019,10 +10015,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427452</v>
+        <v>427566</v>
       </c>
       <c r="R91" t="n">
-        <v>6233794</v>
+        <v>6233756</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10081,10 +10077,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471591</v>
+        <v>121472013</v>
       </c>
       <c r="B92" t="n">
-        <v>80243</v>
+        <v>96732</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10097,21 +10093,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10121,10 +10117,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427724</v>
+        <v>427882</v>
       </c>
       <c r="R92" t="n">
-        <v>6233617</v>
+        <v>6233622</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10151,12 +10147,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10183,10 +10179,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471708</v>
+        <v>121471993</v>
       </c>
       <c r="B93" t="n">
-        <v>96731</v>
+        <v>91511</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10195,38 +10191,41 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2606</v>
+        <v>2014</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427785</v>
+        <v>427859</v>
       </c>
       <c r="R93" t="n">
-        <v>6233734</v>
+        <v>6233620</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10253,12 +10252,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10267,6 +10266,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10285,10 +10285,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471620</v>
+        <v>121471577</v>
       </c>
       <c r="B94" t="n">
-        <v>94594</v>
+        <v>94606</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10301,21 +10301,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10325,10 +10325,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427625</v>
+        <v>427749</v>
       </c>
       <c r="R94" t="n">
-        <v>6233894</v>
+        <v>6233572</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10387,10 +10387,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471957</v>
+        <v>121471626</v>
       </c>
       <c r="B95" t="n">
-        <v>94605</v>
+        <v>74699</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10403,21 +10403,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>2667</v>
+        <v>6439</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10427,10 +10427,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427731</v>
+        <v>427597</v>
       </c>
       <c r="R95" t="n">
-        <v>6233539</v>
+        <v>6233825</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10457,12 +10457,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10489,10 +10489,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471961</v>
+        <v>121471521</v>
       </c>
       <c r="B96" t="n">
-        <v>94605</v>
+        <v>80244</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10505,21 +10505,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10529,10 +10529,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427615</v>
+        <v>427794</v>
       </c>
       <c r="R96" t="n">
-        <v>6233649</v>
+        <v>6233483</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10559,12 +10559,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10591,10 +10591,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471978</v>
+        <v>121471638</v>
       </c>
       <c r="B97" t="n">
-        <v>94605</v>
+        <v>80244</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10607,21 +10607,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10631,10 +10631,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427533</v>
+        <v>427638</v>
       </c>
       <c r="R97" t="n">
-        <v>6233765</v>
+        <v>6233822</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10661,12 +10661,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10693,10 +10693,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471558</v>
+        <v>121471974</v>
       </c>
       <c r="B98" t="n">
-        <v>80256</v>
+        <v>90515</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10709,21 +10709,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1144</v>
+        <v>1067</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10733,10 +10733,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427960</v>
+        <v>427554</v>
       </c>
       <c r="R98" t="n">
-        <v>6233661</v>
+        <v>6233803</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10763,12 +10763,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10795,10 +10795,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121472015</v>
+        <v>121471714</v>
       </c>
       <c r="B99" t="n">
-        <v>74698</v>
+        <v>78409</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10807,25 +10807,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6439</v>
+        <v>924</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10835,10 +10835,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427903</v>
+        <v>427435</v>
       </c>
       <c r="R99" t="n">
-        <v>6233639</v>
+        <v>6233855</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10865,12 +10865,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10897,10 +10897,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471565</v>
+        <v>121471589</v>
       </c>
       <c r="B100" t="n">
-        <v>76949</v>
+        <v>96732</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10909,25 +10909,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10937,10 +10937,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>428016</v>
+        <v>427804</v>
       </c>
       <c r="R100" t="n">
-        <v>6233689</v>
+        <v>6233688</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10999,10 +10999,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471636</v>
+        <v>121472002</v>
       </c>
       <c r="B101" t="n">
-        <v>80243</v>
+        <v>94606</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11015,21 +11015,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11039,10 +11039,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>427650</v>
+        <v>427909</v>
       </c>
       <c r="R101" t="n">
-        <v>6233855</v>
+        <v>6233613</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11069,12 +11069,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11101,10 +11101,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471985</v>
+        <v>121472000</v>
       </c>
       <c r="B102" t="n">
-        <v>80243</v>
+        <v>74699</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11117,21 +11117,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11141,10 +11141,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427558</v>
+        <v>427926</v>
       </c>
       <c r="R102" t="n">
-        <v>6233768</v>
+        <v>6233617</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11203,10 +11203,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471597</v>
+        <v>121471575</v>
       </c>
       <c r="B103" t="n">
-        <v>80243</v>
+        <v>91119</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11215,25 +11215,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>230185</v>
+        <v>2023</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11243,10 +11243,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427693</v>
+        <v>427837</v>
       </c>
       <c r="R103" t="n">
-        <v>6233604</v>
+        <v>6233582</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11305,10 +11305,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471557</v>
+        <v>121471978</v>
       </c>
       <c r="B104" t="n">
-        <v>94594</v>
+        <v>94606</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11321,21 +11321,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427948</v>
+        <v>427533</v>
       </c>
       <c r="R104" t="n">
-        <v>6233643</v>
+        <v>6233765</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11375,12 +11375,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11407,10 +11407,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121472009</v>
+        <v>121471600</v>
       </c>
       <c r="B105" t="n">
-        <v>94605</v>
+        <v>94606</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11447,10 +11447,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427877</v>
+        <v>427698</v>
       </c>
       <c r="R105" t="n">
-        <v>6233615</v>
+        <v>6233566</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11477,12 +11477,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11509,10 +11509,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471603</v>
+        <v>121471632</v>
       </c>
       <c r="B106" t="n">
-        <v>80256</v>
+        <v>80244</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11521,25 +11521,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11549,10 +11549,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427596</v>
+        <v>427615</v>
       </c>
       <c r="R106" t="n">
-        <v>6233681</v>
+        <v>6233825</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11611,10 +11611,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121472003</v>
+        <v>121471636</v>
       </c>
       <c r="B107" t="n">
-        <v>79019</v>
+        <v>80244</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11623,23 +11623,27 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>132</v>
+        <v>230185</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Liten lundlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bacidina phacodes/tarandina</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
@@ -11647,10 +11651,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427911</v>
+        <v>427650</v>
       </c>
       <c r="R107" t="n">
-        <v>6233614</v>
+        <v>6233855</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11677,12 +11681,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11709,10 +11713,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471587</v>
+        <v>121471592</v>
       </c>
       <c r="B108" t="n">
-        <v>80256</v>
+        <v>80244</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11721,25 +11725,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11749,10 +11753,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>427770</v>
+        <v>427703</v>
       </c>
       <c r="R108" t="n">
-        <v>6233624</v>
+        <v>6233616</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11811,10 +11815,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471576</v>
+        <v>121471990</v>
       </c>
       <c r="B109" t="n">
-        <v>80256</v>
+        <v>80244</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11823,25 +11827,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11851,10 +11855,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>427742</v>
+        <v>427765</v>
       </c>
       <c r="R109" t="n">
-        <v>6233565</v>
+        <v>6233765</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11881,12 +11885,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11913,10 +11917,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121472016</v>
+        <v>121471556</v>
       </c>
       <c r="B110" t="n">
-        <v>96731</v>
+        <v>96732</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11953,10 +11957,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427903</v>
+        <v>427948</v>
       </c>
       <c r="R110" t="n">
-        <v>6233640</v>
+        <v>6233643</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11983,12 +11987,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12015,10 +12019,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471596</v>
+        <v>121471647</v>
       </c>
       <c r="B111" t="n">
-        <v>74700</v>
+        <v>96732</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12031,21 +12035,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>306</v>
+        <v>2606</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12055,10 +12059,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427686</v>
+        <v>427720</v>
       </c>
       <c r="R111" t="n">
-        <v>6233621</v>
+        <v>6233787</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12117,10 +12121,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471562</v>
+        <v>121471628</v>
       </c>
       <c r="B112" t="n">
-        <v>80579</v>
+        <v>96732</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12129,25 +12133,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1182</v>
+        <v>2606</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12157,10 +12161,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>428000</v>
+        <v>427604</v>
       </c>
       <c r="R112" t="n">
-        <v>6233692</v>
+        <v>6233834</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12219,10 +12223,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471559</v>
+        <v>121471707</v>
       </c>
       <c r="B113" t="n">
-        <v>76949</v>
+        <v>96732</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12231,25 +12235,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12259,10 +12263,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427960</v>
+        <v>427809</v>
       </c>
       <c r="R113" t="n">
-        <v>6233661</v>
+        <v>6233703</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12321,10 +12325,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471953</v>
+        <v>121472011</v>
       </c>
       <c r="B114" t="n">
-        <v>96731</v>
+        <v>76950</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12333,25 +12337,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12361,10 +12365,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427769</v>
+        <v>427874</v>
       </c>
       <c r="R114" t="n">
-        <v>6233529</v>
+        <v>6233615</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12423,10 +12427,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471592</v>
+        <v>121471559</v>
       </c>
       <c r="B115" t="n">
-        <v>80243</v>
+        <v>76950</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12435,25 +12439,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12463,10 +12467,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427703</v>
+        <v>427960</v>
       </c>
       <c r="R115" t="n">
-        <v>6233616</v>
+        <v>6233661</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12525,10 +12529,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471617</v>
+        <v>121471713</v>
       </c>
       <c r="B116" t="n">
-        <v>80243</v>
+        <v>76950</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12537,25 +12541,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12565,10 +12569,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427526</v>
+        <v>427438</v>
       </c>
       <c r="R116" t="n">
-        <v>6233836</v>
+        <v>6233852</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12627,10 +12631,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471580</v>
+        <v>121471591</v>
       </c>
       <c r="B117" t="n">
-        <v>80243</v>
+        <v>80244</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12667,10 +12671,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427804</v>
+        <v>427724</v>
       </c>
       <c r="R117" t="n">
-        <v>6233576</v>
+        <v>6233617</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12729,10 +12733,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121472011</v>
+        <v>121471607</v>
       </c>
       <c r="B118" t="n">
-        <v>76949</v>
+        <v>80244</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12741,25 +12745,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12769,10 +12773,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427874</v>
+        <v>427582</v>
       </c>
       <c r="R118" t="n">
-        <v>6233615</v>
+        <v>6233752</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12799,12 +12803,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -12831,10 +12835,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471702</v>
+        <v>121471959</v>
       </c>
       <c r="B119" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12847,21 +12851,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12871,10 +12875,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427811</v>
+        <v>427734</v>
       </c>
       <c r="R119" t="n">
-        <v>6233480</v>
+        <v>6233532</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12901,12 +12905,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12933,10 +12937,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471564</v>
+        <v>121471710</v>
       </c>
       <c r="B120" t="n">
-        <v>80256</v>
+        <v>94608</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12945,25 +12949,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1144</v>
+        <v>2666</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12973,10 +12977,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>428014</v>
+        <v>427448</v>
       </c>
       <c r="R120" t="n">
-        <v>6233692</v>
+        <v>6233789</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13035,10 +13039,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471624</v>
+        <v>121472003</v>
       </c>
       <c r="B121" t="n">
-        <v>74564</v>
+        <v>79020</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13051,23 +13055,19 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1116</v>
+        <v>132</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Liten lundlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
-        </is>
-      </c>
+          <t>Bacidina phacodes/tarandina</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13075,10 +13075,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427594</v>
+        <v>427911</v>
       </c>
       <c r="R121" t="n">
-        <v>6233828</v>
+        <v>6233614</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13105,12 +13105,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13137,10 +13137,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471643</v>
+        <v>121471649</v>
       </c>
       <c r="B122" t="n">
-        <v>96731</v>
+        <v>80257</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13149,25 +13149,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13177,10 +13177,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427671</v>
+        <v>427720</v>
       </c>
       <c r="R122" t="n">
-        <v>6233821</v>
+        <v>6233787</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13239,10 +13239,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471607</v>
+        <v>121471635</v>
       </c>
       <c r="B123" t="n">
-        <v>80243</v>
+        <v>78865</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13255,21 +13255,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13279,10 +13279,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427582</v>
+        <v>427637</v>
       </c>
       <c r="R123" t="n">
-        <v>6233752</v>
+        <v>6233845</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13341,10 +13341,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471960</v>
+        <v>121471988</v>
       </c>
       <c r="B124" t="n">
-        <v>94594</v>
+        <v>74527</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13357,21 +13357,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2671</v>
+        <v>6428</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13381,10 +13381,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427734</v>
+        <v>427738</v>
       </c>
       <c r="R124" t="n">
-        <v>6233532</v>
+        <v>6233780</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13443,10 +13443,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471633</v>
+        <v>121472015</v>
       </c>
       <c r="B125" t="n">
-        <v>90514</v>
+        <v>74699</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13455,25 +13455,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1067</v>
+        <v>6439</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13483,10 +13483,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427629</v>
+        <v>427903</v>
       </c>
       <c r="R125" t="n">
-        <v>6233837</v>
+        <v>6233639</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13513,12 +13513,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13545,10 +13545,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471999</v>
+        <v>121471985</v>
       </c>
       <c r="B126" t="n">
-        <v>80256</v>
+        <v>80244</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13557,25 +13557,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13585,10 +13585,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427916</v>
+        <v>427558</v>
       </c>
       <c r="R126" t="n">
-        <v>6233634</v>
+        <v>6233768</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13647,10 +13647,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471716</v>
+        <v>121471610</v>
       </c>
       <c r="B127" t="n">
-        <v>80243</v>
+        <v>80244</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427547</v>
+        <v>427487</v>
       </c>
       <c r="R127" t="n">
-        <v>6233865</v>
+        <v>6233816</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13749,10 +13749,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121472013</v>
+        <v>121471996</v>
       </c>
       <c r="B128" t="n">
-        <v>96731</v>
+        <v>80257</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13761,25 +13761,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13789,10 +13789,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427882</v>
+        <v>427855</v>
       </c>
       <c r="R128" t="n">
-        <v>6233622</v>
+        <v>6233614</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13851,10 +13851,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471648</v>
+        <v>121471998</v>
       </c>
       <c r="B129" t="n">
-        <v>76949</v>
+        <v>76950</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13891,10 +13891,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>427721</v>
+        <v>427915</v>
       </c>
       <c r="R129" t="n">
-        <v>6233787</v>
+        <v>6233632</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13921,12 +13921,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13953,10 +13953,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471626</v>
+        <v>121472012</v>
       </c>
       <c r="B130" t="n">
-        <v>74698</v>
+        <v>76950</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13965,25 +13965,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6439</v>
+        <v>1342</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13993,10 +13993,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>427597</v>
+        <v>427855</v>
       </c>
       <c r="R130" t="n">
-        <v>6233825</v>
+        <v>6233612</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14023,12 +14023,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14055,10 +14055,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121472010</v>
+        <v>121471648</v>
       </c>
       <c r="B131" t="n">
-        <v>78988</v>
+        <v>76950</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14067,25 +14067,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6431</v>
+        <v>1342</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14095,10 +14095,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427877</v>
+        <v>427721</v>
       </c>
       <c r="R131" t="n">
-        <v>6233615</v>
+        <v>6233787</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14125,12 +14125,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14157,10 +14157,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471556</v>
+        <v>121472014</v>
       </c>
       <c r="B132" t="n">
-        <v>96731</v>
+        <v>80257</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14169,25 +14169,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14197,10 +14197,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427948</v>
+        <v>427882</v>
       </c>
       <c r="R132" t="n">
-        <v>6233643</v>
+        <v>6233622</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14227,12 +14227,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14259,10 +14259,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471578</v>
+        <v>121471622</v>
       </c>
       <c r="B133" t="n">
-        <v>76949</v>
+        <v>74699</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14271,25 +14271,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1342</v>
+        <v>6439</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14299,10 +14299,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427749</v>
+        <v>427623</v>
       </c>
       <c r="R133" t="n">
-        <v>6233573</v>
+        <v>6233865</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14361,10 +14361,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471963</v>
+        <v>121471627</v>
       </c>
       <c r="B134" t="n">
-        <v>94605</v>
+        <v>74699</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14377,21 +14377,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2667</v>
+        <v>6439</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14401,10 +14401,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427520</v>
+        <v>427613</v>
       </c>
       <c r="R134" t="n">
-        <v>6233715</v>
+        <v>6233840</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14431,12 +14431,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14463,10 +14463,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471635</v>
+        <v>121471596</v>
       </c>
       <c r="B135" t="n">
-        <v>78864</v>
+        <v>74701</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14479,21 +14479,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6459</v>
+        <v>306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14503,10 +14503,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427637</v>
+        <v>427686</v>
       </c>
       <c r="R135" t="n">
-        <v>6233845</v>
+        <v>6233621</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14565,10 +14565,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471980</v>
+        <v>121471965</v>
       </c>
       <c r="B136" t="n">
-        <v>80256</v>
+        <v>76950</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14577,25 +14577,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14605,10 +14605,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427532</v>
+        <v>427509</v>
       </c>
       <c r="R136" t="n">
-        <v>6233767</v>
+        <v>6233731</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14667,10 +14667,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471649</v>
+        <v>121471624</v>
       </c>
       <c r="B137" t="n">
-        <v>80256</v>
+        <v>74565</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14679,25 +14679,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1144</v>
+        <v>1116</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14707,10 +14707,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427720</v>
+        <v>427594</v>
       </c>
       <c r="R137" t="n">
-        <v>6233787</v>
+        <v>6233828</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14769,10 +14769,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471563</v>
+        <v>121471641</v>
       </c>
       <c r="B138" t="n">
-        <v>96731</v>
+        <v>78865</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14785,21 +14785,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14809,10 +14809,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>428012</v>
+        <v>427655</v>
       </c>
       <c r="R138" t="n">
-        <v>6233689</v>
+        <v>6233850</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14871,10 +14871,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471979</v>
+        <v>121471703</v>
       </c>
       <c r="B139" t="n">
-        <v>76949</v>
+        <v>74699</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14883,25 +14883,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1342</v>
+        <v>6439</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>427533</v>
+        <v>427770</v>
       </c>
       <c r="R139" t="n">
-        <v>6233765</v>
+        <v>6233580</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14941,12 +14941,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14973,10 +14973,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471951</v>
+        <v>121471954</v>
       </c>
       <c r="B140" t="n">
-        <v>76949</v>
+        <v>80244</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14985,25 +14985,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15013,10 +15013,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>427762</v>
+        <v>427742</v>
       </c>
       <c r="R140" t="n">
-        <v>6233515</v>
+        <v>6233542</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15075,10 +15075,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471584</v>
+        <v>121471720</v>
       </c>
       <c r="B141" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15091,21 +15091,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15115,10 +15115,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>427817</v>
+        <v>427595</v>
       </c>
       <c r="R141" t="n">
-        <v>6233621</v>
+        <v>6233898</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15177,10 +15177,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471707</v>
+        <v>121471585</v>
       </c>
       <c r="B142" t="n">
-        <v>96731</v>
+        <v>76950</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15189,25 +15189,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15217,10 +15217,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>427809</v>
+        <v>427748</v>
       </c>
       <c r="R142" t="n">
-        <v>6233703</v>
+        <v>6233622</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15279,10 +15279,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471644</v>
+        <v>121472007</v>
       </c>
       <c r="B143" t="n">
-        <v>78864</v>
+        <v>80257</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15291,25 +15291,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6459</v>
+        <v>1144</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15319,10 +15319,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>427671</v>
+        <v>427892</v>
       </c>
       <c r="R143" t="n">
-        <v>6233821</v>
+        <v>6233623</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15381,10 +15381,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471645</v>
+        <v>121471971</v>
       </c>
       <c r="B144" t="n">
-        <v>80243</v>
+        <v>78865</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15397,21 +15397,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15421,10 +15421,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>427702</v>
+        <v>427499</v>
       </c>
       <c r="R144" t="n">
-        <v>6233806</v>
+        <v>6233792</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15451,12 +15451,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15483,10 +15483,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471975</v>
+        <v>121471700</v>
       </c>
       <c r="B145" t="n">
-        <v>80243</v>
+        <v>78989</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15499,21 +15499,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>230185</v>
+        <v>6431</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15523,10 +15523,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427575</v>
+        <v>427806</v>
       </c>
       <c r="R145" t="n">
-        <v>6233800</v>
+        <v>6233482</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15553,12 +15553,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15585,10 +15585,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471705</v>
+        <v>121471617</v>
       </c>
       <c r="B146" t="n">
-        <v>80243</v>
+        <v>80244</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15625,10 +15625,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427753</v>
+        <v>427526</v>
       </c>
       <c r="R146" t="n">
-        <v>6233606</v>
+        <v>6233836</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15687,10 +15687,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471600</v>
+        <v>121471609</v>
       </c>
       <c r="B147" t="n">
-        <v>94605</v>
+        <v>80244</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15703,21 +15703,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15727,10 +15727,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427698</v>
+        <v>427543</v>
       </c>
       <c r="R147" t="n">
-        <v>6233566</v>
+        <v>6233756</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15789,10 +15789,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471586</v>
+        <v>121471599</v>
       </c>
       <c r="B148" t="n">
-        <v>80256</v>
+        <v>94608</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15801,25 +15801,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1144</v>
+        <v>2666</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15829,10 +15829,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427748</v>
+        <v>427685</v>
       </c>
       <c r="R148" t="n">
-        <v>6233622</v>
+        <v>6233593</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15891,10 +15891,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471971</v>
+        <v>121471963</v>
       </c>
       <c r="B149" t="n">
-        <v>78864</v>
+        <v>94606</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15907,21 +15907,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6459</v>
+        <v>2667</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15931,10 +15931,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>427499</v>
+        <v>427520</v>
       </c>
       <c r="R149" t="n">
-        <v>6233792</v>
+        <v>6233715</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15993,10 +15993,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121472000</v>
+        <v>121471621</v>
       </c>
       <c r="B150" t="n">
-        <v>74698</v>
+        <v>96732</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16009,21 +16009,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16033,10 +16033,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>427926</v>
+        <v>427607</v>
       </c>
       <c r="R150" t="n">
-        <v>6233617</v>
+        <v>6233875</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16063,12 +16063,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16095,10 +16095,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471583</v>
+        <v>121471612</v>
       </c>
       <c r="B151" t="n">
-        <v>78864</v>
+        <v>80244</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16111,21 +16111,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16135,10 +16135,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>427813</v>
+        <v>427466</v>
       </c>
       <c r="R151" t="n">
-        <v>6233621</v>
+        <v>6233828</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16197,10 +16197,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471640</v>
+        <v>121471715</v>
       </c>
       <c r="B152" t="n">
-        <v>96731</v>
+        <v>80244</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16213,21 +16213,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16237,10 +16237,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>427653</v>
+        <v>427445</v>
       </c>
       <c r="R152" t="n">
-        <v>6233849</v>
+        <v>6233860</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16299,10 +16299,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471967</v>
+        <v>121471634</v>
       </c>
       <c r="B153" t="n">
-        <v>80256</v>
+        <v>96732</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16311,25 +16311,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16339,10 +16339,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>427508</v>
+        <v>427636</v>
       </c>
       <c r="R153" t="n">
-        <v>6233737</v>
+        <v>6233848</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16369,12 +16369,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16401,10 +16401,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471574</v>
+        <v>121471953</v>
       </c>
       <c r="B154" t="n">
-        <v>80243</v>
+        <v>96732</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16417,21 +16417,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16441,10 +16441,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>427838</v>
+        <v>427769</v>
       </c>
       <c r="R154" t="n">
-        <v>6233582</v>
+        <v>6233529</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16471,12 +16471,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16503,10 +16503,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471720</v>
+        <v>121471564</v>
       </c>
       <c r="B155" t="n">
-        <v>80243</v>
+        <v>80257</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16515,25 +16515,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16543,10 +16543,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>427595</v>
+        <v>428014</v>
       </c>
       <c r="R155" t="n">
-        <v>6233898</v>
+        <v>6233692</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16605,10 +16605,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471561</v>
+        <v>121471629</v>
       </c>
       <c r="B156" t="n">
-        <v>96731</v>
+        <v>80257</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16617,25 +16617,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16645,10 +16645,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>427999</v>
+        <v>427602</v>
       </c>
       <c r="R156" t="n">
-        <v>6233695</v>
+        <v>6233832</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16707,10 +16707,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471968</v>
+        <v>121471614</v>
       </c>
       <c r="B157" t="n">
-        <v>57371</v>
+        <v>80244</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16719,25 +16719,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>230185</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16747,10 +16747,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>427512</v>
+        <v>427475</v>
       </c>
       <c r="R157" t="n">
-        <v>6233745</v>
+        <v>6233836</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16777,12 +16777,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16809,10 +16809,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121472014</v>
+        <v>121471593</v>
       </c>
       <c r="B158" t="n">
-        <v>80256</v>
+        <v>80244</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16821,25 +16821,25 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16849,10 +16849,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>427882</v>
+        <v>427699</v>
       </c>
       <c r="R158" t="n">
-        <v>6233622</v>
+        <v>6233608</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16879,12 +16879,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16911,10 +16911,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471642</v>
+        <v>121471618</v>
       </c>
       <c r="B159" t="n">
-        <v>80243</v>
+        <v>96732</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16927,21 +16927,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16951,10 +16951,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>427654</v>
+        <v>427525</v>
       </c>
       <c r="R159" t="n">
-        <v>6233848</v>
+        <v>6233838</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17013,10 +17013,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471623</v>
+        <v>121471646</v>
       </c>
       <c r="B160" t="n">
-        <v>80243</v>
+        <v>94606</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17029,21 +17029,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17053,10 +17053,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>427579</v>
+        <v>427692</v>
       </c>
       <c r="R160" t="n">
-        <v>6233850</v>
+        <v>6233796</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17115,10 +17115,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471609</v>
+        <v>121471957</v>
       </c>
       <c r="B161" t="n">
-        <v>80243</v>
+        <v>94606</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17131,21 +17131,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17155,10 +17155,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>427543</v>
+        <v>427731</v>
       </c>
       <c r="R161" t="n">
-        <v>6233756</v>
+        <v>6233539</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17185,12 +17185,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -1802,7 +1802,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471977</v>
+        <v>121471702</v>
       </c>
       <c r="B11" t="n">
         <v>96732</v>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427533</v>
+        <v>427811</v>
       </c>
       <c r="R11" t="n">
-        <v>6233765</v>
+        <v>6233480</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1904,10 +1904,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471984</v>
+        <v>121471953</v>
       </c>
       <c r="B12" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1920,21 +1920,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427530</v>
+        <v>427769</v>
       </c>
       <c r="R12" t="n">
-        <v>6233736</v>
+        <v>6233529</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471719</v>
+        <v>121471601</v>
       </c>
       <c r="B13" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2018,25 +2018,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427583</v>
+        <v>427688</v>
       </c>
       <c r="R13" t="n">
-        <v>6233861</v>
+        <v>6233590</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471968</v>
+        <v>121471564</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>80257</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>1144</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427512</v>
+        <v>428014</v>
       </c>
       <c r="R14" t="n">
-        <v>6233745</v>
+        <v>6233692</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471716</v>
+        <v>121471646</v>
       </c>
       <c r="B15" t="n">
-        <v>80244</v>
+        <v>94606</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427547</v>
+        <v>427692</v>
       </c>
       <c r="R15" t="n">
-        <v>6233865</v>
+        <v>6233796</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121471604</v>
+        <v>121471640</v>
       </c>
       <c r="B16" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427595</v>
+        <v>427653</v>
       </c>
       <c r="R16" t="n">
-        <v>6233781</v>
+        <v>6233849</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2414,7 +2414,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121471584</v>
+        <v>121471712</v>
       </c>
       <c r="B17" t="n">
         <v>96732</v>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427817</v>
+        <v>427439</v>
       </c>
       <c r="R17" t="n">
-        <v>6233621</v>
+        <v>6233838</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121471706</v>
+        <v>121471628</v>
       </c>
       <c r="B18" t="n">
         <v>96732</v>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427781</v>
+        <v>427604</v>
       </c>
       <c r="R18" t="n">
-        <v>6233648</v>
+        <v>6233834</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121471702</v>
+        <v>121472009</v>
       </c>
       <c r="B19" t="n">
-        <v>96732</v>
+        <v>94606</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427811</v>
+        <v>427877</v>
       </c>
       <c r="R19" t="n">
-        <v>6233480</v>
+        <v>6233615</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121471712</v>
+        <v>121471574</v>
       </c>
       <c r="B20" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427439</v>
+        <v>427838</v>
       </c>
       <c r="R20" t="n">
-        <v>6233838</v>
+        <v>6233582</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121471637</v>
+        <v>121471998</v>
       </c>
       <c r="B21" t="n">
-        <v>96732</v>
+        <v>76950</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>427638</v>
+        <v>427915</v>
       </c>
       <c r="R21" t="n">
-        <v>6233822</v>
+        <v>6233632</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121471718</v>
+        <v>121471650</v>
       </c>
       <c r="B22" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427584</v>
+        <v>427737</v>
       </c>
       <c r="R22" t="n">
-        <v>6233863</v>
+        <v>6233784</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471587</v>
+        <v>121471951</v>
       </c>
       <c r="B23" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427770</v>
+        <v>427762</v>
       </c>
       <c r="R23" t="n">
-        <v>6233624</v>
+        <v>6233515</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3096,12 +3096,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471651</v>
+        <v>121471614</v>
       </c>
       <c r="B24" t="n">
-        <v>78865</v>
+        <v>80244</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427737</v>
+        <v>427475</v>
       </c>
       <c r="R24" t="n">
-        <v>6233789</v>
+        <v>6233836</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471645</v>
+        <v>121471557</v>
       </c>
       <c r="B25" t="n">
-        <v>80244</v>
+        <v>94595</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427702</v>
+        <v>427948</v>
       </c>
       <c r="R25" t="n">
-        <v>6233806</v>
+        <v>6233643</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471557</v>
+        <v>121471627</v>
       </c>
       <c r="B26" t="n">
-        <v>94595</v>
+        <v>74699</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3348,21 +3348,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2671</v>
+        <v>6439</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427948</v>
+        <v>427613</v>
       </c>
       <c r="R26" t="n">
-        <v>6233643</v>
+        <v>6233840</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471643</v>
+        <v>121472001</v>
       </c>
       <c r="B27" t="n">
-        <v>96732</v>
+        <v>94616</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2606</v>
+        <v>1080</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427671</v>
+        <v>427908</v>
       </c>
       <c r="R27" t="n">
-        <v>6233821</v>
+        <v>6233617</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471960</v>
+        <v>121471556</v>
       </c>
       <c r="B28" t="n">
-        <v>94595</v>
+        <v>96732</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,21 +3552,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427734</v>
+        <v>427948</v>
       </c>
       <c r="R28" t="n">
-        <v>6233532</v>
+        <v>6233643</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3606,12 +3606,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3638,10 +3638,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471565</v>
+        <v>121471995</v>
       </c>
       <c r="B29" t="n">
-        <v>76950</v>
+        <v>78865</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3650,25 +3650,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1342</v>
+        <v>6459</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428016</v>
+        <v>427856</v>
       </c>
       <c r="R29" t="n">
-        <v>6233689</v>
+        <v>6233613</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3740,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121472006</v>
+        <v>121471980</v>
       </c>
       <c r="B30" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427892</v>
+        <v>427532</v>
       </c>
       <c r="R30" t="n">
-        <v>6233623</v>
+        <v>6233767</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471558</v>
+        <v>121471709</v>
       </c>
       <c r="B31" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3854,25 +3854,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427960</v>
+        <v>427452</v>
       </c>
       <c r="R31" t="n">
-        <v>6233661</v>
+        <v>6233794</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471995</v>
+        <v>121471577</v>
       </c>
       <c r="B32" t="n">
-        <v>78865</v>
+        <v>94606</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6459</v>
+        <v>2667</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427856</v>
+        <v>427749</v>
       </c>
       <c r="R32" t="n">
-        <v>6233613</v>
+        <v>6233572</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4046,10 +4046,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471952</v>
+        <v>121471624</v>
       </c>
       <c r="B33" t="n">
-        <v>74699</v>
+        <v>74565</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4058,25 +4058,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6439</v>
+        <v>1116</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427763</v>
+        <v>427594</v>
       </c>
       <c r="R33" t="n">
-        <v>6233529</v>
+        <v>6233828</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4116,12 +4116,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4148,10 +4148,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471986</v>
+        <v>121471583</v>
       </c>
       <c r="B34" t="n">
-        <v>80257</v>
+        <v>78865</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4160,41 +4160,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1144</v>
+        <v>6459</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427558</v>
+        <v>427813</v>
       </c>
       <c r="R34" t="n">
-        <v>6233769</v>
+        <v>6233621</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4221,17 +4218,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Med Refractohilum pluriseptatum</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4239,11 +4231,6 @@
       </c>
       <c r="AE34" t="b">
         <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG34" t="b">
         <v>0</v>
@@ -4263,7 +4250,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471561</v>
+        <v>121471589</v>
       </c>
       <c r="B35" t="n">
         <v>96732</v>
@@ -4303,10 +4290,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427999</v>
+        <v>427804</v>
       </c>
       <c r="R35" t="n">
-        <v>6233695</v>
+        <v>6233688</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4365,10 +4352,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471708</v>
+        <v>121471600</v>
       </c>
       <c r="B36" t="n">
-        <v>96732</v>
+        <v>94606</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4381,21 +4368,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4405,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427785</v>
+        <v>427698</v>
       </c>
       <c r="R36" t="n">
-        <v>6233734</v>
+        <v>6233566</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4467,10 +4454,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471578</v>
+        <v>121471960</v>
       </c>
       <c r="B37" t="n">
-        <v>76950</v>
+        <v>94595</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4479,25 +4466,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4507,10 +4494,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427749</v>
+        <v>427734</v>
       </c>
       <c r="R37" t="n">
-        <v>6233573</v>
+        <v>6233532</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4537,12 +4524,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4569,7 +4556,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471982</v>
+        <v>121471648</v>
       </c>
       <c r="B38" t="n">
         <v>76950</v>
@@ -4609,10 +4596,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427516</v>
+        <v>427721</v>
       </c>
       <c r="R38" t="n">
-        <v>6233748</v>
+        <v>6233787</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4639,12 +4626,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4671,10 +4658,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471966</v>
+        <v>121471562</v>
       </c>
       <c r="B39" t="n">
-        <v>76950</v>
+        <v>80580</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4687,21 +4674,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1342</v>
+        <v>1182</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4711,10 +4698,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427505</v>
+        <v>428000</v>
       </c>
       <c r="R39" t="n">
-        <v>6233740</v>
+        <v>6233692</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4741,12 +4728,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4773,10 +4760,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121472010</v>
+        <v>121471964</v>
       </c>
       <c r="B40" t="n">
-        <v>78989</v>
+        <v>94606</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4789,21 +4776,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6431</v>
+        <v>2667</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4813,10 +4800,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427877</v>
+        <v>427511</v>
       </c>
       <c r="R40" t="n">
-        <v>6233615</v>
+        <v>6233739</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4875,10 +4862,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471602</v>
+        <v>121471982</v>
       </c>
       <c r="B41" t="n">
-        <v>94606</v>
+        <v>76950</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4887,25 +4874,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4915,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427641</v>
+        <v>427516</v>
       </c>
       <c r="R41" t="n">
-        <v>6233630</v>
+        <v>6233748</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4945,12 +4932,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4977,10 +4964,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471630</v>
+        <v>121471705</v>
       </c>
       <c r="B42" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4989,25 +4976,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5017,10 +5004,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427604</v>
+        <v>427753</v>
       </c>
       <c r="R42" t="n">
-        <v>6233829</v>
+        <v>6233606</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5079,10 +5066,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471642</v>
+        <v>121471983</v>
       </c>
       <c r="B43" t="n">
-        <v>80244</v>
+        <v>74699</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5095,21 +5082,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5119,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427654</v>
+        <v>427521</v>
       </c>
       <c r="R43" t="n">
-        <v>6233848</v>
+        <v>6233737</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5149,12 +5136,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5181,7 +5168,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471580</v>
+        <v>121471962</v>
       </c>
       <c r="B44" t="n">
         <v>80244</v>
@@ -5221,10 +5208,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427804</v>
+        <v>427528</v>
       </c>
       <c r="R44" t="n">
-        <v>6233576</v>
+        <v>6233707</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5251,12 +5238,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5283,7 +5270,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471597</v>
+        <v>121471715</v>
       </c>
       <c r="B45" t="n">
         <v>80244</v>
@@ -5323,10 +5310,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>427693</v>
+        <v>427445</v>
       </c>
       <c r="R45" t="n">
-        <v>6233604</v>
+        <v>6233860</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5385,10 +5372,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471976</v>
+        <v>121471622</v>
       </c>
       <c r="B46" t="n">
-        <v>96732</v>
+        <v>74699</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5401,21 +5388,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2606</v>
+        <v>6439</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5425,10 +5412,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427576</v>
+        <v>427623</v>
       </c>
       <c r="R46" t="n">
-        <v>6233800</v>
+        <v>6233865</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5455,12 +5442,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5487,10 +5474,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471980</v>
+        <v>121471977</v>
       </c>
       <c r="B47" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5499,25 +5486,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5527,10 +5514,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427532</v>
+        <v>427533</v>
       </c>
       <c r="R47" t="n">
-        <v>6233767</v>
+        <v>6233765</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5589,7 +5576,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471951</v>
+        <v>121471973</v>
       </c>
       <c r="B48" t="n">
         <v>76950</v>
@@ -5629,10 +5616,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427762</v>
+        <v>427544</v>
       </c>
       <c r="R48" t="n">
-        <v>6233515</v>
+        <v>6233811</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5691,10 +5678,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471999</v>
+        <v>121471584</v>
       </c>
       <c r="B49" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5703,25 +5690,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5731,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427916</v>
+        <v>427817</v>
       </c>
       <c r="R49" t="n">
-        <v>6233634</v>
+        <v>6233621</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5761,12 +5748,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5793,7 +5780,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121471520</v>
+        <v>121472004</v>
       </c>
       <c r="B50" t="n">
         <v>80244</v>
@@ -5833,10 +5820,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427789</v>
+        <v>427892</v>
       </c>
       <c r="R50" t="n">
-        <v>6233516</v>
+        <v>6233623</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5863,12 +5850,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5895,10 +5882,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471560</v>
+        <v>121471641</v>
       </c>
       <c r="B51" t="n">
-        <v>80244</v>
+        <v>78865</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5911,21 +5898,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5935,10 +5922,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428008</v>
+        <v>427655</v>
       </c>
       <c r="R51" t="n">
-        <v>6233671</v>
+        <v>6233850</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5997,7 +5984,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471631</v>
+        <v>121471720</v>
       </c>
       <c r="B52" t="n">
         <v>80244</v>
@@ -6037,10 +6024,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427601</v>
+        <v>427595</v>
       </c>
       <c r="R52" t="n">
-        <v>6233830</v>
+        <v>6233898</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6099,10 +6086,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471583</v>
+        <v>121471979</v>
       </c>
       <c r="B53" t="n">
-        <v>78865</v>
+        <v>76950</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6111,25 +6098,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6139,10 +6126,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427813</v>
+        <v>427533</v>
       </c>
       <c r="R53" t="n">
-        <v>6233621</v>
+        <v>6233765</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6169,12 +6156,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6201,10 +6188,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471956</v>
+        <v>121471719</v>
       </c>
       <c r="B54" t="n">
-        <v>94608</v>
+        <v>76950</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6213,25 +6200,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>2666</v>
+        <v>1342</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6241,10 +6228,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427739</v>
+        <v>427583</v>
       </c>
       <c r="R54" t="n">
-        <v>6233524</v>
+        <v>6233861</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6271,12 +6258,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6303,10 +6290,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471563</v>
+        <v>121471642</v>
       </c>
       <c r="B55" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6319,21 +6306,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6343,10 +6330,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428012</v>
+        <v>427654</v>
       </c>
       <c r="R55" t="n">
-        <v>6233689</v>
+        <v>6233848</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6405,10 +6392,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471619</v>
+        <v>121471990</v>
       </c>
       <c r="B56" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6421,21 +6408,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6445,10 +6432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>427624</v>
+        <v>427765</v>
       </c>
       <c r="R56" t="n">
-        <v>6233894</v>
+        <v>6233765</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6475,12 +6462,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6507,10 +6494,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471992</v>
+        <v>121471618</v>
       </c>
       <c r="B57" t="n">
-        <v>94595</v>
+        <v>96732</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6523,21 +6510,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6547,10 +6534,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427861</v>
+        <v>427525</v>
       </c>
       <c r="R57" t="n">
-        <v>6233620</v>
+        <v>6233838</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6577,12 +6564,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6609,10 +6596,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471973</v>
+        <v>121471700</v>
       </c>
       <c r="B58" t="n">
-        <v>76950</v>
+        <v>78989</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6621,25 +6608,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1342</v>
+        <v>6431</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6649,10 +6636,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427544</v>
+        <v>427806</v>
       </c>
       <c r="R58" t="n">
-        <v>6233811</v>
+        <v>6233482</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6679,12 +6666,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6711,10 +6698,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471983</v>
+        <v>121471634</v>
       </c>
       <c r="B59" t="n">
-        <v>74699</v>
+        <v>96732</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6727,21 +6714,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6751,10 +6738,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427521</v>
+        <v>427636</v>
       </c>
       <c r="R59" t="n">
-        <v>6233737</v>
+        <v>6233848</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6781,12 +6768,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6813,7 +6800,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471975</v>
+        <v>121471984</v>
       </c>
       <c r="B60" t="n">
         <v>80244</v>
@@ -6853,10 +6840,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427575</v>
+        <v>427530</v>
       </c>
       <c r="R60" t="n">
-        <v>6233800</v>
+        <v>6233736</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6915,10 +6902,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471601</v>
+        <v>121471620</v>
       </c>
       <c r="B61" t="n">
-        <v>80244</v>
+        <v>94595</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6931,21 +6918,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6955,10 +6942,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427688</v>
+        <v>427625</v>
       </c>
       <c r="R61" t="n">
-        <v>6233590</v>
+        <v>6233894</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7017,10 +7004,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471623</v>
+        <v>121471644</v>
       </c>
       <c r="B62" t="n">
-        <v>80244</v>
+        <v>78865</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7033,21 +7020,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7057,10 +7044,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427579</v>
+        <v>427671</v>
       </c>
       <c r="R62" t="n">
-        <v>6233850</v>
+        <v>6233821</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7119,10 +7106,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471581</v>
+        <v>121471587</v>
       </c>
       <c r="B63" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7131,25 +7118,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7159,10 +7146,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427820</v>
+        <v>427770</v>
       </c>
       <c r="R63" t="n">
-        <v>6233599</v>
+        <v>6233624</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7221,10 +7208,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471590</v>
+        <v>121471713</v>
       </c>
       <c r="B64" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7233,25 +7220,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7261,10 +7248,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427753</v>
+        <v>427438</v>
       </c>
       <c r="R64" t="n">
-        <v>6233666</v>
+        <v>6233852</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7323,10 +7310,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121472004</v>
+        <v>121471578</v>
       </c>
       <c r="B65" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7335,25 +7322,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7363,10 +7350,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427892</v>
+        <v>427749</v>
       </c>
       <c r="R65" t="n">
-        <v>6233623</v>
+        <v>6233573</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7393,12 +7380,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7425,10 +7412,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471962</v>
+        <v>121471596</v>
       </c>
       <c r="B66" t="n">
-        <v>80244</v>
+        <v>74701</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7441,21 +7428,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7465,10 +7452,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427528</v>
+        <v>427686</v>
       </c>
       <c r="R66" t="n">
-        <v>6233707</v>
+        <v>6233621</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7495,12 +7482,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7527,10 +7514,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471598</v>
+        <v>121471576</v>
       </c>
       <c r="B67" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7539,25 +7526,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7567,10 +7554,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427690</v>
+        <v>427742</v>
       </c>
       <c r="R67" t="n">
-        <v>6233595</v>
+        <v>6233565</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7629,10 +7616,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121472016</v>
+        <v>121471996</v>
       </c>
       <c r="B68" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7641,25 +7628,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7669,10 +7656,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427903</v>
+        <v>427855</v>
       </c>
       <c r="R68" t="n">
-        <v>6233640</v>
+        <v>6233614</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7731,10 +7718,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471955</v>
+        <v>121471975</v>
       </c>
       <c r="B69" t="n">
-        <v>94608</v>
+        <v>80244</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7747,21 +7734,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7771,10 +7758,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427741</v>
+        <v>427575</v>
       </c>
       <c r="R69" t="n">
-        <v>6233529</v>
+        <v>6233800</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7833,7 +7820,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471979</v>
+        <v>121471965</v>
       </c>
       <c r="B70" t="n">
         <v>76950</v>
@@ -7873,10 +7860,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>427533</v>
+        <v>427509</v>
       </c>
       <c r="R70" t="n">
-        <v>6233765</v>
+        <v>6233731</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7935,10 +7922,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471562</v>
+        <v>121471643</v>
       </c>
       <c r="B71" t="n">
-        <v>80580</v>
+        <v>96732</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7947,25 +7934,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1182</v>
+        <v>2606</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7975,10 +7962,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>428000</v>
+        <v>427671</v>
       </c>
       <c r="R71" t="n">
-        <v>6233692</v>
+        <v>6233821</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8037,10 +8024,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471967</v>
+        <v>121471632</v>
       </c>
       <c r="B72" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8049,25 +8036,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8077,10 +8064,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427508</v>
+        <v>427615</v>
       </c>
       <c r="R72" t="n">
-        <v>6233737</v>
+        <v>6233825</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8107,12 +8094,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8139,10 +8126,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471586</v>
+        <v>121471955</v>
       </c>
       <c r="B73" t="n">
-        <v>80257</v>
+        <v>94608</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8151,25 +8138,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1144</v>
+        <v>2666</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8179,10 +8166,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427748</v>
+        <v>427741</v>
       </c>
       <c r="R73" t="n">
-        <v>6233622</v>
+        <v>6233529</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8209,12 +8196,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8241,10 +8228,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471576</v>
+        <v>121471645</v>
       </c>
       <c r="B74" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8253,25 +8240,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8281,10 +8268,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>427742</v>
+        <v>427702</v>
       </c>
       <c r="R74" t="n">
-        <v>6233565</v>
+        <v>6233806</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8343,10 +8330,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471644</v>
+        <v>121472006</v>
       </c>
       <c r="B75" t="n">
-        <v>78865</v>
+        <v>76950</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8355,25 +8342,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8383,10 +8370,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>427671</v>
+        <v>427892</v>
       </c>
       <c r="R75" t="n">
-        <v>6233821</v>
+        <v>6233623</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8413,12 +8400,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8445,10 +8432,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471704</v>
+        <v>121471558</v>
       </c>
       <c r="B76" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8457,25 +8444,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8485,10 +8472,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427785</v>
+        <v>427960</v>
       </c>
       <c r="R76" t="n">
-        <v>6233585</v>
+        <v>6233661</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8547,10 +8534,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471620</v>
+        <v>121471602</v>
       </c>
       <c r="B77" t="n">
-        <v>94595</v>
+        <v>94606</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8563,21 +8550,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8587,10 +8574,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427625</v>
+        <v>427641</v>
       </c>
       <c r="R77" t="n">
-        <v>6233894</v>
+        <v>6233630</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8649,10 +8636,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121472009</v>
+        <v>121471565</v>
       </c>
       <c r="B78" t="n">
-        <v>94606</v>
+        <v>76950</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8661,25 +8648,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8689,10 +8676,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427877</v>
+        <v>428016</v>
       </c>
       <c r="R78" t="n">
-        <v>6233615</v>
+        <v>6233689</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8719,12 +8706,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8751,10 +8738,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471964</v>
+        <v>121471629</v>
       </c>
       <c r="B79" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8763,25 +8750,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8791,10 +8778,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427511</v>
+        <v>427602</v>
       </c>
       <c r="R79" t="n">
-        <v>6233739</v>
+        <v>6233832</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8821,12 +8808,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8853,10 +8840,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471961</v>
+        <v>121472014</v>
       </c>
       <c r="B80" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8865,25 +8852,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8893,10 +8880,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427615</v>
+        <v>427882</v>
       </c>
       <c r="R80" t="n">
-        <v>6233649</v>
+        <v>6233622</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8955,10 +8942,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471671</v>
+        <v>121471593</v>
       </c>
       <c r="B81" t="n">
-        <v>105766</v>
+        <v>80244</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8967,25 +8954,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220785</v>
+        <v>230185</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8995,10 +8982,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427912</v>
+        <v>427699</v>
       </c>
       <c r="R81" t="n">
-        <v>6233611</v>
+        <v>6233608</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9057,10 +9044,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471709</v>
+        <v>121471992</v>
       </c>
       <c r="B82" t="n">
-        <v>80244</v>
+        <v>94595</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9073,21 +9060,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9097,10 +9084,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427452</v>
+        <v>427861</v>
       </c>
       <c r="R82" t="n">
-        <v>6233794</v>
+        <v>6233620</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9127,12 +9114,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9159,10 +9146,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121472001</v>
+        <v>121472003</v>
       </c>
       <c r="B83" t="n">
-        <v>94616</v>
+        <v>79020</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9171,27 +9158,23 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1080</v>
+        <v>132</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Liten lundlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
+          <t>Bacidina phacodes/tarandina</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9199,10 +9182,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427908</v>
+        <v>427911</v>
       </c>
       <c r="R83" t="n">
-        <v>6233617</v>
+        <v>6233614</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9261,10 +9244,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471603</v>
+        <v>121471957</v>
       </c>
       <c r="B84" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9273,25 +9256,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9301,10 +9284,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427596</v>
+        <v>427731</v>
       </c>
       <c r="R84" t="n">
-        <v>6233681</v>
+        <v>6233539</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9331,12 +9314,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9363,10 +9346,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471640</v>
+        <v>121471999</v>
       </c>
       <c r="B85" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9375,25 +9358,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9403,10 +9386,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427653</v>
+        <v>427916</v>
       </c>
       <c r="R85" t="n">
-        <v>6233849</v>
+        <v>6233634</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9433,12 +9416,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9465,10 +9448,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471572</v>
+        <v>121472000</v>
       </c>
       <c r="B86" t="n">
-        <v>96732</v>
+        <v>74699</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9481,21 +9464,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2606</v>
+        <v>6439</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9505,10 +9488,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427982</v>
+        <v>427926</v>
       </c>
       <c r="R86" t="n">
-        <v>6233642</v>
+        <v>6233617</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9535,12 +9518,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9567,7 +9550,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471650</v>
+        <v>121471610</v>
       </c>
       <c r="B87" t="n">
         <v>80244</v>
@@ -9607,10 +9590,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427737</v>
+        <v>427487</v>
       </c>
       <c r="R87" t="n">
-        <v>6233784</v>
+        <v>6233816</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9669,7 +9652,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471574</v>
+        <v>121471521</v>
       </c>
       <c r="B88" t="n">
         <v>80244</v>
@@ -9709,10 +9692,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427838</v>
+        <v>427794</v>
       </c>
       <c r="R88" t="n">
-        <v>6233582</v>
+        <v>6233483</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9771,7 +9754,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471705</v>
+        <v>121471580</v>
       </c>
       <c r="B89" t="n">
         <v>80244</v>
@@ -9811,10 +9794,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427753</v>
+        <v>427804</v>
       </c>
       <c r="R89" t="n">
-        <v>6233606</v>
+        <v>6233576</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9873,10 +9856,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471633</v>
+        <v>121471968</v>
       </c>
       <c r="B90" t="n">
-        <v>90515</v>
+        <v>57372</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9885,25 +9868,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1067</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9913,10 +9896,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427629</v>
+        <v>427512</v>
       </c>
       <c r="R90" t="n">
-        <v>6233837</v>
+        <v>6233745</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9943,12 +9926,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9975,7 +9958,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471608</v>
+        <v>121471597</v>
       </c>
       <c r="B91" t="n">
         <v>80244</v>
@@ -10015,10 +9998,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427566</v>
+        <v>427693</v>
       </c>
       <c r="R91" t="n">
-        <v>6233756</v>
+        <v>6233604</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10077,10 +10060,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121472013</v>
+        <v>121471560</v>
       </c>
       <c r="B92" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10093,21 +10076,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10117,10 +10100,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427882</v>
+        <v>428008</v>
       </c>
       <c r="R92" t="n">
-        <v>6233622</v>
+        <v>6233671</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10147,12 +10130,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10179,10 +10162,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471993</v>
+        <v>121471598</v>
       </c>
       <c r="B93" t="n">
-        <v>91511</v>
+        <v>94606</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10191,41 +10174,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2014</v>
+        <v>2667</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427859</v>
+        <v>427690</v>
       </c>
       <c r="R93" t="n">
-        <v>6233620</v>
+        <v>6233595</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10252,12 +10232,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10266,7 +10246,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10285,10 +10264,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471577</v>
+        <v>121471647</v>
       </c>
       <c r="B94" t="n">
-        <v>94606</v>
+        <v>96732</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10301,21 +10280,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10325,10 +10304,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427749</v>
+        <v>427720</v>
       </c>
       <c r="R94" t="n">
-        <v>6233572</v>
+        <v>6233787</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10387,10 +10366,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471626</v>
+        <v>121471617</v>
       </c>
       <c r="B95" t="n">
-        <v>74699</v>
+        <v>80244</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10403,21 +10382,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10427,10 +10406,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427597</v>
+        <v>427526</v>
       </c>
       <c r="R95" t="n">
-        <v>6233825</v>
+        <v>6233836</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10489,10 +10468,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471521</v>
+        <v>121471619</v>
       </c>
       <c r="B96" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10505,21 +10484,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10529,10 +10508,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427794</v>
+        <v>427624</v>
       </c>
       <c r="R96" t="n">
-        <v>6233483</v>
+        <v>6233894</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10591,10 +10570,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471638</v>
+        <v>121471575</v>
       </c>
       <c r="B97" t="n">
-        <v>80244</v>
+        <v>91119</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10603,25 +10582,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>230185</v>
+        <v>2023</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10631,10 +10610,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427638</v>
+        <v>427837</v>
       </c>
       <c r="R97" t="n">
-        <v>6233822</v>
+        <v>6233582</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10693,10 +10672,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471974</v>
+        <v>121471966</v>
       </c>
       <c r="B98" t="n">
-        <v>90515</v>
+        <v>76950</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10705,25 +10684,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1067</v>
+        <v>1342</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10733,10 +10712,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427554</v>
+        <v>427505</v>
       </c>
       <c r="R98" t="n">
-        <v>6233803</v>
+        <v>6233740</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10795,10 +10774,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471714</v>
+        <v>121471971</v>
       </c>
       <c r="B99" t="n">
-        <v>78409</v>
+        <v>78865</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10807,25 +10786,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>924</v>
+        <v>6459</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10835,10 +10814,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427435</v>
+        <v>427499</v>
       </c>
       <c r="R99" t="n">
-        <v>6233855</v>
+        <v>6233792</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10865,12 +10844,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10897,10 +10876,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471589</v>
+        <v>121471956</v>
       </c>
       <c r="B100" t="n">
-        <v>96732</v>
+        <v>94608</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10913,21 +10892,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2606</v>
+        <v>2666</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10937,10 +10916,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427804</v>
+        <v>427739</v>
       </c>
       <c r="R100" t="n">
-        <v>6233688</v>
+        <v>6233524</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10967,12 +10946,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10999,10 +10978,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121472002</v>
+        <v>121471592</v>
       </c>
       <c r="B101" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11015,21 +10994,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11039,10 +11018,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>427909</v>
+        <v>427703</v>
       </c>
       <c r="R101" t="n">
-        <v>6233613</v>
+        <v>6233616</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11069,12 +11048,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11101,10 +11080,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121472000</v>
+        <v>121471986</v>
       </c>
       <c r="B102" t="n">
-        <v>74699</v>
+        <v>80257</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11113,38 +11092,41 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427926</v>
+        <v>427558</v>
       </c>
       <c r="R102" t="n">
-        <v>6233617</v>
+        <v>6233769</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11179,11 +11161,21 @@
           <t>2024-11-18</t>
         </is>
       </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Med Refractohilum pluriseptatum</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG102" t="b">
         <v>0</v>
@@ -11203,10 +11195,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471575</v>
+        <v>121471581</v>
       </c>
       <c r="B103" t="n">
-        <v>91119</v>
+        <v>80244</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11215,25 +11207,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2023</v>
+        <v>230185</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11243,10 +11235,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427837</v>
+        <v>427820</v>
       </c>
       <c r="R103" t="n">
-        <v>6233582</v>
+        <v>6233599</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11305,7 +11297,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471978</v>
+        <v>121472002</v>
       </c>
       <c r="B104" t="n">
         <v>94606</v>
@@ -11345,10 +11337,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427533</v>
+        <v>427909</v>
       </c>
       <c r="R104" t="n">
-        <v>6233765</v>
+        <v>6233613</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11407,10 +11399,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471600</v>
+        <v>121471585</v>
       </c>
       <c r="B105" t="n">
-        <v>94606</v>
+        <v>76950</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11419,25 +11411,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11447,10 +11439,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427698</v>
+        <v>427748</v>
       </c>
       <c r="R105" t="n">
-        <v>6233566</v>
+        <v>6233622</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11509,7 +11501,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471632</v>
+        <v>121471520</v>
       </c>
       <c r="B106" t="n">
         <v>80244</v>
@@ -11549,10 +11541,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427615</v>
+        <v>427789</v>
       </c>
       <c r="R106" t="n">
-        <v>6233825</v>
+        <v>6233516</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11611,10 +11603,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471636</v>
+        <v>121471559</v>
       </c>
       <c r="B107" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11623,25 +11615,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11651,10 +11643,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427650</v>
+        <v>427960</v>
       </c>
       <c r="R107" t="n">
-        <v>6233855</v>
+        <v>6233661</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11713,10 +11705,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471592</v>
+        <v>121472010</v>
       </c>
       <c r="B108" t="n">
-        <v>80244</v>
+        <v>78989</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11729,21 +11721,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>230185</v>
+        <v>6431</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11753,10 +11745,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>427703</v>
+        <v>427877</v>
       </c>
       <c r="R108" t="n">
-        <v>6233616</v>
+        <v>6233615</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11783,12 +11775,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11815,10 +11807,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471990</v>
+        <v>121471974</v>
       </c>
       <c r="B109" t="n">
-        <v>80244</v>
+        <v>90515</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11827,25 +11819,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11855,10 +11847,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>427765</v>
+        <v>427554</v>
       </c>
       <c r="R109" t="n">
-        <v>6233765</v>
+        <v>6233803</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11917,10 +11909,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471556</v>
+        <v>121471671</v>
       </c>
       <c r="B110" t="n">
-        <v>96732</v>
+        <v>105766</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11929,25 +11921,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>2606</v>
+        <v>220785</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11957,10 +11949,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427948</v>
+        <v>427912</v>
       </c>
       <c r="R110" t="n">
-        <v>6233643</v>
+        <v>6233611</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12019,10 +12011,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471647</v>
+        <v>121471631</v>
       </c>
       <c r="B111" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12035,21 +12027,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12059,10 +12051,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427720</v>
+        <v>427601</v>
       </c>
       <c r="R111" t="n">
-        <v>6233787</v>
+        <v>6233830</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12121,10 +12113,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471628</v>
+        <v>121471967</v>
       </c>
       <c r="B112" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12133,25 +12125,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12161,10 +12153,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427604</v>
+        <v>427508</v>
       </c>
       <c r="R112" t="n">
-        <v>6233834</v>
+        <v>6233737</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12191,12 +12183,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12223,10 +12215,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471707</v>
+        <v>121471993</v>
       </c>
       <c r="B113" t="n">
-        <v>96732</v>
+        <v>91511</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12235,38 +12227,41 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2606</v>
+        <v>2014</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427809</v>
+        <v>427859</v>
       </c>
       <c r="R113" t="n">
-        <v>6233703</v>
+        <v>6233620</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12293,12 +12288,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12307,6 +12302,7 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12325,10 +12321,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121472011</v>
+        <v>121471704</v>
       </c>
       <c r="B114" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12337,25 +12333,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12365,10 +12361,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427874</v>
+        <v>427785</v>
       </c>
       <c r="R114" t="n">
-        <v>6233615</v>
+        <v>6233585</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12395,12 +12391,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12427,10 +12423,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471559</v>
+        <v>121471604</v>
       </c>
       <c r="B115" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12439,25 +12435,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12467,10 +12463,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427960</v>
+        <v>427595</v>
       </c>
       <c r="R115" t="n">
-        <v>6233661</v>
+        <v>6233781</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12529,10 +12525,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471713</v>
+        <v>121471985</v>
       </c>
       <c r="B116" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12541,25 +12537,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12569,10 +12565,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427438</v>
+        <v>427558</v>
       </c>
       <c r="R116" t="n">
-        <v>6233852</v>
+        <v>6233768</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12599,12 +12595,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12631,10 +12627,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471591</v>
+        <v>121471599</v>
       </c>
       <c r="B117" t="n">
-        <v>80244</v>
+        <v>94608</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12647,21 +12643,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12671,10 +12667,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427724</v>
+        <v>427685</v>
       </c>
       <c r="R117" t="n">
-        <v>6233617</v>
+        <v>6233593</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12733,10 +12729,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471607</v>
+        <v>121471710</v>
       </c>
       <c r="B118" t="n">
-        <v>80244</v>
+        <v>94608</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12749,21 +12745,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12773,10 +12769,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427582</v>
+        <v>427448</v>
       </c>
       <c r="R118" t="n">
-        <v>6233752</v>
+        <v>6233789</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12835,7 +12831,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471959</v>
+        <v>121471607</v>
       </c>
       <c r="B119" t="n">
         <v>80244</v>
@@ -12875,10 +12871,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427734</v>
+        <v>427582</v>
       </c>
       <c r="R119" t="n">
-        <v>6233532</v>
+        <v>6233752</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12905,12 +12901,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12937,10 +12933,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471710</v>
+        <v>121471703</v>
       </c>
       <c r="B120" t="n">
-        <v>94608</v>
+        <v>74699</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12953,21 +12949,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2666</v>
+        <v>6439</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12977,10 +12973,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427448</v>
+        <v>427770</v>
       </c>
       <c r="R120" t="n">
-        <v>6233789</v>
+        <v>6233580</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13039,10 +13035,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121472003</v>
+        <v>121472013</v>
       </c>
       <c r="B121" t="n">
-        <v>79020</v>
+        <v>96732</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13051,23 +13047,27 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>132</v>
+        <v>2606</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Liten lundlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Bacidina phacodes/tarandina</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Frullania tamarisci</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(L.) Dumort.</t>
+        </is>
+      </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
@@ -13075,10 +13075,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427911</v>
+        <v>427882</v>
       </c>
       <c r="R121" t="n">
-        <v>6233614</v>
+        <v>6233622</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13137,7 +13137,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471649</v>
+        <v>121471718</v>
       </c>
       <c r="B122" t="n">
         <v>80257</v>
@@ -13177,10 +13177,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427720</v>
+        <v>427584</v>
       </c>
       <c r="R122" t="n">
-        <v>6233787</v>
+        <v>6233863</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13341,10 +13341,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471988</v>
+        <v>121471626</v>
       </c>
       <c r="B124" t="n">
-        <v>74527</v>
+        <v>74699</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13357,21 +13357,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6428</v>
+        <v>6439</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13381,10 +13381,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427738</v>
+        <v>427597</v>
       </c>
       <c r="R124" t="n">
-        <v>6233780</v>
+        <v>6233825</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13411,12 +13411,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13443,10 +13443,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121472015</v>
+        <v>121471630</v>
       </c>
       <c r="B125" t="n">
-        <v>74699</v>
+        <v>76950</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13455,25 +13455,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6439</v>
+        <v>1342</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13483,10 +13483,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427903</v>
+        <v>427604</v>
       </c>
       <c r="R125" t="n">
-        <v>6233639</v>
+        <v>6233829</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13513,12 +13513,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13545,10 +13545,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471985</v>
+        <v>121471963</v>
       </c>
       <c r="B126" t="n">
-        <v>80244</v>
+        <v>94606</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13561,21 +13561,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13585,10 +13585,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427558</v>
+        <v>427520</v>
       </c>
       <c r="R126" t="n">
-        <v>6233768</v>
+        <v>6233715</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13647,10 +13647,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471610</v>
+        <v>121471649</v>
       </c>
       <c r="B127" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13659,25 +13659,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13687,10 +13687,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427487</v>
+        <v>427720</v>
       </c>
       <c r="R127" t="n">
-        <v>6233816</v>
+        <v>6233787</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13749,10 +13749,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471996</v>
+        <v>121471561</v>
       </c>
       <c r="B128" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13761,25 +13761,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13789,10 +13789,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427855</v>
+        <v>427999</v>
       </c>
       <c r="R128" t="n">
-        <v>6233614</v>
+        <v>6233695</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13819,12 +13819,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13851,10 +13851,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471998</v>
+        <v>121471708</v>
       </c>
       <c r="B129" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13863,25 +13863,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13891,10 +13891,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>427915</v>
+        <v>427785</v>
       </c>
       <c r="R129" t="n">
-        <v>6233632</v>
+        <v>6233734</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13921,12 +13921,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -13953,10 +13953,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121472012</v>
+        <v>121472016</v>
       </c>
       <c r="B130" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13965,25 +13965,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13993,10 +13993,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>427855</v>
+        <v>427903</v>
       </c>
       <c r="R130" t="n">
-        <v>6233612</v>
+        <v>6233640</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14055,10 +14055,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471648</v>
+        <v>121471591</v>
       </c>
       <c r="B131" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14067,25 +14067,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14095,10 +14095,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427721</v>
+        <v>427724</v>
       </c>
       <c r="R131" t="n">
-        <v>6233787</v>
+        <v>6233617</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14157,10 +14157,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121472014</v>
+        <v>121471976</v>
       </c>
       <c r="B132" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14169,25 +14169,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14197,10 +14197,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427882</v>
+        <v>427576</v>
       </c>
       <c r="R132" t="n">
-        <v>6233622</v>
+        <v>6233800</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14259,10 +14259,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471622</v>
+        <v>121471651</v>
       </c>
       <c r="B133" t="n">
-        <v>74699</v>
+        <v>78865</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14275,21 +14275,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6439</v>
+        <v>6459</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14299,10 +14299,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427623</v>
+        <v>427737</v>
       </c>
       <c r="R133" t="n">
-        <v>6233865</v>
+        <v>6233789</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14361,10 +14361,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471627</v>
+        <v>121471590</v>
       </c>
       <c r="B134" t="n">
-        <v>74699</v>
+        <v>80244</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14377,21 +14377,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14401,10 +14401,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427613</v>
+        <v>427753</v>
       </c>
       <c r="R134" t="n">
-        <v>6233840</v>
+        <v>6233666</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14463,10 +14463,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471596</v>
+        <v>121471637</v>
       </c>
       <c r="B135" t="n">
-        <v>74701</v>
+        <v>96732</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14479,21 +14479,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>306</v>
+        <v>2606</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14503,10 +14503,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427686</v>
+        <v>427638</v>
       </c>
       <c r="R135" t="n">
-        <v>6233621</v>
+        <v>6233822</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14565,10 +14565,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471965</v>
+        <v>121471572</v>
       </c>
       <c r="B136" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14577,25 +14577,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14605,10 +14605,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427509</v>
+        <v>427982</v>
       </c>
       <c r="R136" t="n">
-        <v>6233731</v>
+        <v>6233642</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14635,12 +14635,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14667,10 +14667,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471624</v>
+        <v>121471563</v>
       </c>
       <c r="B137" t="n">
-        <v>74565</v>
+        <v>96732</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14679,25 +14679,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1116</v>
+        <v>2606</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14707,10 +14707,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>427594</v>
+        <v>428012</v>
       </c>
       <c r="R137" t="n">
-        <v>6233828</v>
+        <v>6233689</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14769,10 +14769,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471641</v>
+        <v>121471633</v>
       </c>
       <c r="B138" t="n">
-        <v>78865</v>
+        <v>90515</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14781,25 +14781,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6459</v>
+        <v>1067</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14809,10 +14809,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427655</v>
+        <v>427629</v>
       </c>
       <c r="R138" t="n">
-        <v>6233850</v>
+        <v>6233837</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14871,10 +14871,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471703</v>
+        <v>121471623</v>
       </c>
       <c r="B139" t="n">
-        <v>74699</v>
+        <v>80244</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14887,21 +14887,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14911,10 +14911,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>427770</v>
+        <v>427579</v>
       </c>
       <c r="R139" t="n">
-        <v>6233580</v>
+        <v>6233850</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14973,10 +14973,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471954</v>
+        <v>121471707</v>
       </c>
       <c r="B140" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14989,21 +14989,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15013,10 +15013,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>427742</v>
+        <v>427809</v>
       </c>
       <c r="R140" t="n">
-        <v>6233542</v>
+        <v>6233703</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15043,12 +15043,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15075,7 +15075,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471720</v>
+        <v>121471954</v>
       </c>
       <c r="B141" t="n">
         <v>80244</v>
@@ -15115,10 +15115,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>427595</v>
+        <v>427742</v>
       </c>
       <c r="R141" t="n">
-        <v>6233898</v>
+        <v>6233542</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15145,12 +15145,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15177,10 +15177,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471585</v>
+        <v>121471621</v>
       </c>
       <c r="B142" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15189,25 +15189,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15217,10 +15217,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>427748</v>
+        <v>427607</v>
       </c>
       <c r="R142" t="n">
-        <v>6233622</v>
+        <v>6233875</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15279,10 +15279,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121472007</v>
+        <v>121471608</v>
       </c>
       <c r="B143" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15291,25 +15291,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15319,10 +15319,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>427892</v>
+        <v>427566</v>
       </c>
       <c r="R143" t="n">
-        <v>6233623</v>
+        <v>6233756</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15349,12 +15349,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15381,10 +15381,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471971</v>
+        <v>121471706</v>
       </c>
       <c r="B144" t="n">
-        <v>78865</v>
+        <v>96732</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15397,21 +15397,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15421,10 +15421,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>427499</v>
+        <v>427781</v>
       </c>
       <c r="R144" t="n">
-        <v>6233792</v>
+        <v>6233648</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15451,12 +15451,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -15483,10 +15483,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471700</v>
+        <v>121471603</v>
       </c>
       <c r="B145" t="n">
-        <v>78989</v>
+        <v>80257</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15495,25 +15495,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6431</v>
+        <v>1144</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15523,10 +15523,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427806</v>
+        <v>427596</v>
       </c>
       <c r="R145" t="n">
-        <v>6233482</v>
+        <v>6233681</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15585,10 +15585,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471617</v>
+        <v>121471714</v>
       </c>
       <c r="B146" t="n">
-        <v>80244</v>
+        <v>78409</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15597,25 +15597,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15625,10 +15625,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427526</v>
+        <v>427435</v>
       </c>
       <c r="R146" t="n">
-        <v>6233836</v>
+        <v>6233855</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15687,10 +15687,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471609</v>
+        <v>121471952</v>
       </c>
       <c r="B147" t="n">
-        <v>80244</v>
+        <v>74699</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15703,21 +15703,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15727,10 +15727,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427543</v>
+        <v>427763</v>
       </c>
       <c r="R147" t="n">
-        <v>6233756</v>
+        <v>6233529</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15757,12 +15757,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15789,10 +15789,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471599</v>
+        <v>121471959</v>
       </c>
       <c r="B148" t="n">
-        <v>94608</v>
+        <v>80244</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15805,21 +15805,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15829,10 +15829,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427685</v>
+        <v>427734</v>
       </c>
       <c r="R148" t="n">
-        <v>6233593</v>
+        <v>6233532</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15859,12 +15859,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15891,10 +15891,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471963</v>
+        <v>121471636</v>
       </c>
       <c r="B149" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15907,21 +15907,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15931,10 +15931,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>427520</v>
+        <v>427650</v>
       </c>
       <c r="R149" t="n">
-        <v>6233715</v>
+        <v>6233855</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15961,12 +15961,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15993,10 +15993,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471621</v>
+        <v>121471638</v>
       </c>
       <c r="B150" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16009,21 +16009,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16033,10 +16033,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>427607</v>
+        <v>427638</v>
       </c>
       <c r="R150" t="n">
-        <v>6233875</v>
+        <v>6233822</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16095,10 +16095,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471612</v>
+        <v>121472011</v>
       </c>
       <c r="B151" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16107,25 +16107,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16135,10 +16135,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>427466</v>
+        <v>427874</v>
       </c>
       <c r="R151" t="n">
-        <v>6233828</v>
+        <v>6233615</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16165,12 +16165,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16197,10 +16197,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471715</v>
+        <v>121472012</v>
       </c>
       <c r="B152" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16209,25 +16209,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16237,10 +16237,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>427445</v>
+        <v>427855</v>
       </c>
       <c r="R152" t="n">
-        <v>6233860</v>
+        <v>6233612</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16267,12 +16267,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16299,10 +16299,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471634</v>
+        <v>121472007</v>
       </c>
       <c r="B153" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16311,25 +16311,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16339,10 +16339,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>427636</v>
+        <v>427892</v>
       </c>
       <c r="R153" t="n">
-        <v>6233848</v>
+        <v>6233623</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16369,12 +16369,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16401,10 +16401,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471953</v>
+        <v>121472015</v>
       </c>
       <c r="B154" t="n">
-        <v>96732</v>
+        <v>74699</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16417,21 +16417,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2606</v>
+        <v>6439</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16441,10 +16441,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>427769</v>
+        <v>427903</v>
       </c>
       <c r="R154" t="n">
-        <v>6233529</v>
+        <v>6233639</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16503,10 +16503,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471564</v>
+        <v>121471961</v>
       </c>
       <c r="B155" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16515,25 +16515,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16543,10 +16543,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>428014</v>
+        <v>427615</v>
       </c>
       <c r="R155" t="n">
-        <v>6233692</v>
+        <v>6233649</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16573,12 +16573,12 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -16605,7 +16605,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471629</v>
+        <v>121471586</v>
       </c>
       <c r="B156" t="n">
         <v>80257</v>
@@ -16645,10 +16645,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>427602</v>
+        <v>427748</v>
       </c>
       <c r="R156" t="n">
-        <v>6233832</v>
+        <v>6233622</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16707,7 +16707,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471614</v>
+        <v>121471716</v>
       </c>
       <c r="B157" t="n">
         <v>80244</v>
@@ -16747,10 +16747,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>427475</v>
+        <v>427547</v>
       </c>
       <c r="R157" t="n">
-        <v>6233836</v>
+        <v>6233865</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16809,10 +16809,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471593</v>
+        <v>121471988</v>
       </c>
       <c r="B158" t="n">
-        <v>80244</v>
+        <v>74527</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16825,21 +16825,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16849,10 +16849,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>427699</v>
+        <v>427738</v>
       </c>
       <c r="R158" t="n">
-        <v>6233608</v>
+        <v>6233780</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16879,12 +16879,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16911,10 +16911,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471618</v>
+        <v>121471978</v>
       </c>
       <c r="B159" t="n">
-        <v>96732</v>
+        <v>94606</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16927,21 +16927,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16951,10 +16951,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>427525</v>
+        <v>427533</v>
       </c>
       <c r="R159" t="n">
-        <v>6233838</v>
+        <v>6233765</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16981,12 +16981,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17013,10 +17013,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471646</v>
+        <v>121471612</v>
       </c>
       <c r="B160" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17029,21 +17029,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17053,10 +17053,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>427692</v>
+        <v>427466</v>
       </c>
       <c r="R160" t="n">
-        <v>6233796</v>
+        <v>6233828</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17115,10 +17115,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471957</v>
+        <v>121471609</v>
       </c>
       <c r="B161" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17131,21 +17131,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17155,10 +17155,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>427731</v>
+        <v>427543</v>
       </c>
       <c r="R161" t="n">
-        <v>6233539</v>
+        <v>6233756</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17185,12 +17185,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD161" t="b">

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471702</v>
+        <v>121471599</v>
       </c>
       <c r="B11" t="n">
-        <v>96732</v>
+        <v>94608</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>2666</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427811</v>
+        <v>427685</v>
       </c>
       <c r="R11" t="n">
-        <v>6233480</v>
+        <v>6233593</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471953</v>
+        <v>121471561</v>
       </c>
       <c r="B12" t="n">
         <v>96732</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427769</v>
+        <v>427999</v>
       </c>
       <c r="R12" t="n">
-        <v>6233529</v>
+        <v>6233695</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2006,10 +2006,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471601</v>
+        <v>121471589</v>
       </c>
       <c r="B13" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427688</v>
+        <v>427804</v>
       </c>
       <c r="R13" t="n">
-        <v>6233590</v>
+        <v>6233688</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471564</v>
+        <v>121472011</v>
       </c>
       <c r="B14" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428014</v>
+        <v>427874</v>
       </c>
       <c r="R14" t="n">
-        <v>6233692</v>
+        <v>6233615</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471646</v>
+        <v>121471641</v>
       </c>
       <c r="B15" t="n">
-        <v>94606</v>
+        <v>78865</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2667</v>
+        <v>6459</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427692</v>
+        <v>427655</v>
       </c>
       <c r="R15" t="n">
-        <v>6233796</v>
+        <v>6233850</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121471640</v>
+        <v>121471716</v>
       </c>
       <c r="B16" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427653</v>
+        <v>427547</v>
       </c>
       <c r="R16" t="n">
-        <v>6233849</v>
+        <v>6233865</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121471712</v>
+        <v>121471705</v>
       </c>
       <c r="B17" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427439</v>
+        <v>427753</v>
       </c>
       <c r="R17" t="n">
-        <v>6233838</v>
+        <v>6233606</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121471628</v>
+        <v>121471996</v>
       </c>
       <c r="B18" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427604</v>
+        <v>427855</v>
       </c>
       <c r="R18" t="n">
-        <v>6233834</v>
+        <v>6233614</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121472009</v>
+        <v>121471719</v>
       </c>
       <c r="B19" t="n">
-        <v>94606</v>
+        <v>76950</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427877</v>
+        <v>427583</v>
       </c>
       <c r="R19" t="n">
-        <v>6233615</v>
+        <v>6233861</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2688,12 +2688,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121471574</v>
+        <v>121471951</v>
       </c>
       <c r="B20" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427838</v>
+        <v>427762</v>
       </c>
       <c r="R20" t="n">
-        <v>6233582</v>
+        <v>6233515</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121471998</v>
+        <v>121471624</v>
       </c>
       <c r="B21" t="n">
-        <v>76950</v>
+        <v>74565</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2838,21 +2838,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1342</v>
+        <v>1116</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>427915</v>
+        <v>427594</v>
       </c>
       <c r="R21" t="n">
-        <v>6233632</v>
+        <v>6233828</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,7 +2924,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121471650</v>
+        <v>121471636</v>
       </c>
       <c r="B22" t="n">
         <v>80244</v>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427737</v>
+        <v>427650</v>
       </c>
       <c r="R22" t="n">
-        <v>6233784</v>
+        <v>6233855</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471951</v>
+        <v>121471643</v>
       </c>
       <c r="B23" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427762</v>
+        <v>427671</v>
       </c>
       <c r="R23" t="n">
-        <v>6233515</v>
+        <v>6233821</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3096,12 +3096,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471614</v>
+        <v>121471647</v>
       </c>
       <c r="B24" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3144,21 +3144,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427475</v>
+        <v>427720</v>
       </c>
       <c r="R24" t="n">
-        <v>6233836</v>
+        <v>6233787</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471557</v>
+        <v>121471598</v>
       </c>
       <c r="B25" t="n">
-        <v>94595</v>
+        <v>94606</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3246,21 +3246,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427948</v>
+        <v>427690</v>
       </c>
       <c r="R25" t="n">
-        <v>6233643</v>
+        <v>6233595</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471627</v>
+        <v>121471637</v>
       </c>
       <c r="B26" t="n">
-        <v>74699</v>
+        <v>96732</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3348,21 +3348,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427613</v>
+        <v>427638</v>
       </c>
       <c r="R26" t="n">
-        <v>6233840</v>
+        <v>6233822</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121472001</v>
+        <v>121471640</v>
       </c>
       <c r="B27" t="n">
-        <v>94616</v>
+        <v>96732</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1080</v>
+        <v>2606</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427908</v>
+        <v>427653</v>
       </c>
       <c r="R27" t="n">
-        <v>6233617</v>
+        <v>6233849</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471556</v>
+        <v>121471700</v>
       </c>
       <c r="B28" t="n">
-        <v>96732</v>
+        <v>78989</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,21 +3552,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2606</v>
+        <v>6431</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427948</v>
+        <v>427806</v>
       </c>
       <c r="R28" t="n">
-        <v>6233643</v>
+        <v>6233482</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471995</v>
+        <v>121471642</v>
       </c>
       <c r="B29" t="n">
-        <v>78865</v>
+        <v>80244</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427856</v>
+        <v>427654</v>
       </c>
       <c r="R29" t="n">
-        <v>6233613</v>
+        <v>6233848</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3740,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471980</v>
+        <v>121471617</v>
       </c>
       <c r="B30" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427532</v>
+        <v>427526</v>
       </c>
       <c r="R30" t="n">
-        <v>6233767</v>
+        <v>6233836</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,7 +3842,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471709</v>
+        <v>121471990</v>
       </c>
       <c r="B31" t="n">
         <v>80244</v>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427452</v>
+        <v>427765</v>
       </c>
       <c r="R31" t="n">
-        <v>6233794</v>
+        <v>6233765</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471577</v>
+        <v>121471998</v>
       </c>
       <c r="B32" t="n">
-        <v>94606</v>
+        <v>76950</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,25 +3956,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427749</v>
+        <v>427915</v>
       </c>
       <c r="R32" t="n">
-        <v>6233572</v>
+        <v>6233632</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4046,10 +4046,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471624</v>
+        <v>121472006</v>
       </c>
       <c r="B33" t="n">
-        <v>74565</v>
+        <v>76950</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4062,21 +4062,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1116</v>
+        <v>1342</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427594</v>
+        <v>427892</v>
       </c>
       <c r="R33" t="n">
-        <v>6233828</v>
+        <v>6233623</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4116,12 +4116,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4148,10 +4148,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471583</v>
+        <v>121471585</v>
       </c>
       <c r="B34" t="n">
-        <v>78865</v>
+        <v>76950</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4160,25 +4160,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427813</v>
+        <v>427748</v>
       </c>
       <c r="R34" t="n">
-        <v>6233621</v>
+        <v>6233622</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471589</v>
+        <v>121471564</v>
       </c>
       <c r="B35" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4262,25 +4262,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>427804</v>
+        <v>428014</v>
       </c>
       <c r="R35" t="n">
-        <v>6233688</v>
+        <v>6233692</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4352,10 +4352,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471600</v>
+        <v>121471576</v>
       </c>
       <c r="B36" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4364,25 +4364,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427698</v>
+        <v>427742</v>
       </c>
       <c r="R36" t="n">
-        <v>6233566</v>
+        <v>6233565</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4454,10 +4454,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471960</v>
+        <v>121471712</v>
       </c>
       <c r="B37" t="n">
-        <v>94595</v>
+        <v>96732</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4470,21 +4470,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427734</v>
+        <v>427439</v>
       </c>
       <c r="R37" t="n">
-        <v>6233532</v>
+        <v>6233838</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4524,12 +4524,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4556,10 +4556,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471648</v>
+        <v>121471628</v>
       </c>
       <c r="B38" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4568,25 +4568,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427721</v>
+        <v>427604</v>
       </c>
       <c r="R38" t="n">
-        <v>6233787</v>
+        <v>6233834</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471562</v>
+        <v>121471961</v>
       </c>
       <c r="B39" t="n">
-        <v>80580</v>
+        <v>94606</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4670,25 +4670,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1182</v>
+        <v>2667</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428000</v>
+        <v>427615</v>
       </c>
       <c r="R39" t="n">
-        <v>6233692</v>
+        <v>6233649</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4760,10 +4760,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471964</v>
+        <v>121471955</v>
       </c>
       <c r="B40" t="n">
-        <v>94606</v>
+        <v>94608</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4776,16 +4776,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427511</v>
+        <v>427741</v>
       </c>
       <c r="R40" t="n">
-        <v>6233739</v>
+        <v>6233529</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4862,10 +4862,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471982</v>
+        <v>121471992</v>
       </c>
       <c r="B41" t="n">
-        <v>76950</v>
+        <v>94595</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4874,25 +4874,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427516</v>
+        <v>427861</v>
       </c>
       <c r="R41" t="n">
-        <v>6233748</v>
+        <v>6233620</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4964,10 +4964,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471705</v>
+        <v>121471586</v>
       </c>
       <c r="B42" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4976,25 +4976,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427753</v>
+        <v>427748</v>
       </c>
       <c r="R42" t="n">
-        <v>6233606</v>
+        <v>6233622</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5066,10 +5066,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471983</v>
+        <v>121471714</v>
       </c>
       <c r="B43" t="n">
-        <v>74699</v>
+        <v>78409</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5078,25 +5078,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6439</v>
+        <v>924</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427521</v>
+        <v>427435</v>
       </c>
       <c r="R43" t="n">
-        <v>6233737</v>
+        <v>6233855</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5168,10 +5168,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121471962</v>
+        <v>121472015</v>
       </c>
       <c r="B44" t="n">
-        <v>80244</v>
+        <v>74699</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5184,21 +5184,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427528</v>
+        <v>427903</v>
       </c>
       <c r="R44" t="n">
-        <v>6233707</v>
+        <v>6233639</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5270,10 +5270,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471715</v>
+        <v>121471626</v>
       </c>
       <c r="B45" t="n">
-        <v>80244</v>
+        <v>74699</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5286,21 +5286,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>427445</v>
+        <v>427597</v>
       </c>
       <c r="R45" t="n">
-        <v>6233860</v>
+        <v>6233825</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5372,10 +5372,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471622</v>
+        <v>121471995</v>
       </c>
       <c r="B46" t="n">
-        <v>74699</v>
+        <v>78865</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5388,21 +5388,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6439</v>
+        <v>6459</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427623</v>
+        <v>427856</v>
       </c>
       <c r="R46" t="n">
-        <v>6233865</v>
+        <v>6233613</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5442,12 +5442,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5474,10 +5474,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471977</v>
+        <v>121471608</v>
       </c>
       <c r="B47" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5490,21 +5490,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427533</v>
+        <v>427566</v>
       </c>
       <c r="R47" t="n">
-        <v>6233765</v>
+        <v>6233756</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5544,12 +5544,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5576,10 +5576,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471973</v>
+        <v>121471631</v>
       </c>
       <c r="B48" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5588,25 +5588,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427544</v>
+        <v>427601</v>
       </c>
       <c r="R48" t="n">
-        <v>6233811</v>
+        <v>6233830</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5646,12 +5646,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5678,7 +5678,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471584</v>
+        <v>121471634</v>
       </c>
       <c r="B49" t="n">
         <v>96732</v>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427817</v>
+        <v>427636</v>
       </c>
       <c r="R49" t="n">
-        <v>6233621</v>
+        <v>6233848</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121472004</v>
+        <v>121472001</v>
       </c>
       <c r="B50" t="n">
-        <v>80244</v>
+        <v>94616</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5796,21 +5796,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>230185</v>
+        <v>1080</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427892</v>
+        <v>427908</v>
       </c>
       <c r="R50" t="n">
-        <v>6233623</v>
+        <v>6233617</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471641</v>
+        <v>121471718</v>
       </c>
       <c r="B51" t="n">
-        <v>78865</v>
+        <v>80257</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5894,25 +5894,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6459</v>
+        <v>1144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427655</v>
+        <v>427584</v>
       </c>
       <c r="R51" t="n">
-        <v>6233850</v>
+        <v>6233863</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5984,10 +5984,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471720</v>
+        <v>121471973</v>
       </c>
       <c r="B52" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5996,25 +5996,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427595</v>
+        <v>427544</v>
       </c>
       <c r="R52" t="n">
-        <v>6233898</v>
+        <v>6233811</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6054,12 +6054,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6188,10 +6188,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471719</v>
+        <v>121471671</v>
       </c>
       <c r="B54" t="n">
-        <v>76950</v>
+        <v>105766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6200,25 +6200,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1342</v>
+        <v>220785</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427583</v>
+        <v>427912</v>
       </c>
       <c r="R54" t="n">
-        <v>6233861</v>
+        <v>6233611</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6290,10 +6290,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471642</v>
+        <v>121471622</v>
       </c>
       <c r="B55" t="n">
-        <v>80244</v>
+        <v>74699</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6306,21 +6306,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>427654</v>
+        <v>427623</v>
       </c>
       <c r="R55" t="n">
-        <v>6233848</v>
+        <v>6233865</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6392,7 +6392,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471990</v>
+        <v>121471715</v>
       </c>
       <c r="B56" t="n">
         <v>80244</v>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>427765</v>
+        <v>427445</v>
       </c>
       <c r="R56" t="n">
-        <v>6233765</v>
+        <v>6233860</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6462,12 +6462,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6494,10 +6494,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471618</v>
+        <v>121471960</v>
       </c>
       <c r="B57" t="n">
-        <v>96732</v>
+        <v>94595</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427525</v>
+        <v>427734</v>
       </c>
       <c r="R57" t="n">
-        <v>6233838</v>
+        <v>6233532</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6564,12 +6564,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6596,10 +6596,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471700</v>
+        <v>121471963</v>
       </c>
       <c r="B58" t="n">
-        <v>78989</v>
+        <v>94606</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6612,21 +6612,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6431</v>
+        <v>2667</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427806</v>
+        <v>427520</v>
       </c>
       <c r="R58" t="n">
-        <v>6233482</v>
+        <v>6233715</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6666,12 +6666,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6698,7 +6698,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471634</v>
+        <v>121471953</v>
       </c>
       <c r="B59" t="n">
         <v>96732</v>
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427636</v>
+        <v>427769</v>
       </c>
       <c r="R59" t="n">
-        <v>6233848</v>
+        <v>6233529</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6768,12 +6768,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6800,10 +6800,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471984</v>
+        <v>121471965</v>
       </c>
       <c r="B60" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6812,25 +6812,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427530</v>
+        <v>427509</v>
       </c>
       <c r="R60" t="n">
-        <v>6233736</v>
+        <v>6233731</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6902,10 +6902,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471620</v>
+        <v>121471967</v>
       </c>
       <c r="B61" t="n">
-        <v>94595</v>
+        <v>80257</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6914,25 +6914,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427625</v>
+        <v>427508</v>
       </c>
       <c r="R61" t="n">
-        <v>6233894</v>
+        <v>6233737</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6972,12 +6972,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7004,10 +7004,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471644</v>
+        <v>121471703</v>
       </c>
       <c r="B62" t="n">
-        <v>78865</v>
+        <v>74699</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7020,21 +7020,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6459</v>
+        <v>6439</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427671</v>
+        <v>427770</v>
       </c>
       <c r="R62" t="n">
-        <v>6233821</v>
+        <v>6233580</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7106,7 +7106,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471587</v>
+        <v>121471629</v>
       </c>
       <c r="B63" t="n">
         <v>80257</v>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427770</v>
+        <v>427602</v>
       </c>
       <c r="R63" t="n">
-        <v>6233624</v>
+        <v>6233832</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7208,10 +7208,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471713</v>
+        <v>121471557</v>
       </c>
       <c r="B64" t="n">
-        <v>76950</v>
+        <v>94595</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7220,25 +7220,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1342</v>
+        <v>2671</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7248,10 +7248,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427438</v>
+        <v>427948</v>
       </c>
       <c r="R64" t="n">
-        <v>6233852</v>
+        <v>6233643</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7310,10 +7310,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471578</v>
+        <v>121472010</v>
       </c>
       <c r="B65" t="n">
-        <v>76950</v>
+        <v>78989</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7322,25 +7322,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1342</v>
+        <v>6431</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427749</v>
+        <v>427877</v>
       </c>
       <c r="R65" t="n">
-        <v>6233573</v>
+        <v>6233615</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7412,10 +7412,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471596</v>
+        <v>121471521</v>
       </c>
       <c r="B66" t="n">
-        <v>74701</v>
+        <v>80244</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7428,21 +7428,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>306</v>
+        <v>230185</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7452,10 +7452,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427686</v>
+        <v>427794</v>
       </c>
       <c r="R66" t="n">
-        <v>6233621</v>
+        <v>6233483</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7514,10 +7514,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471576</v>
+        <v>121471609</v>
       </c>
       <c r="B67" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7526,25 +7526,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427742</v>
+        <v>427543</v>
       </c>
       <c r="R67" t="n">
-        <v>6233565</v>
+        <v>6233756</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7616,10 +7616,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471996</v>
+        <v>121471648</v>
       </c>
       <c r="B68" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7628,25 +7628,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7656,10 +7656,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427855</v>
+        <v>427721</v>
       </c>
       <c r="R68" t="n">
-        <v>6233614</v>
+        <v>6233787</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7686,12 +7686,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7718,10 +7718,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471975</v>
+        <v>121471620</v>
       </c>
       <c r="B69" t="n">
-        <v>80244</v>
+        <v>94595</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7734,21 +7734,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427575</v>
+        <v>427625</v>
       </c>
       <c r="R69" t="n">
-        <v>6233800</v>
+        <v>6233894</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7788,12 +7788,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7820,10 +7820,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471965</v>
+        <v>121471602</v>
       </c>
       <c r="B70" t="n">
-        <v>76950</v>
+        <v>94606</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7832,25 +7832,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7860,10 +7860,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>427509</v>
+        <v>427641</v>
       </c>
       <c r="R70" t="n">
-        <v>6233731</v>
+        <v>6233630</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7922,10 +7922,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471643</v>
+        <v>121471587</v>
       </c>
       <c r="B71" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7934,25 +7934,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7962,10 +7962,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>427671</v>
+        <v>427770</v>
       </c>
       <c r="R71" t="n">
-        <v>6233821</v>
+        <v>6233624</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8024,10 +8024,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471632</v>
+        <v>121471971</v>
       </c>
       <c r="B72" t="n">
-        <v>80244</v>
+        <v>78865</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8040,21 +8040,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8064,10 +8064,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427615</v>
+        <v>427499</v>
       </c>
       <c r="R72" t="n">
-        <v>6233825</v>
+        <v>6233792</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8094,12 +8094,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8126,10 +8126,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471955</v>
+        <v>121471591</v>
       </c>
       <c r="B73" t="n">
-        <v>94608</v>
+        <v>80244</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8142,21 +8142,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8166,10 +8166,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427741</v>
+        <v>427724</v>
       </c>
       <c r="R73" t="n">
-        <v>6233529</v>
+        <v>6233617</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8196,12 +8196,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8228,7 +8228,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471645</v>
+        <v>121471954</v>
       </c>
       <c r="B74" t="n">
         <v>80244</v>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>427702</v>
+        <v>427742</v>
       </c>
       <c r="R74" t="n">
-        <v>6233806</v>
+        <v>6233542</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8298,12 +8298,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8330,10 +8330,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121472006</v>
+        <v>121471520</v>
       </c>
       <c r="B75" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8342,25 +8342,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>427892</v>
+        <v>427789</v>
       </c>
       <c r="R75" t="n">
-        <v>6233623</v>
+        <v>6233516</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8400,12 +8400,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8432,10 +8432,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471558</v>
+        <v>121471720</v>
       </c>
       <c r="B76" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8444,25 +8444,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8472,10 +8472,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427960</v>
+        <v>427595</v>
       </c>
       <c r="R76" t="n">
-        <v>6233661</v>
+        <v>6233898</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8534,10 +8534,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471602</v>
+        <v>121471645</v>
       </c>
       <c r="B77" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8550,21 +8550,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8574,10 +8574,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427641</v>
+        <v>427702</v>
       </c>
       <c r="R77" t="n">
-        <v>6233630</v>
+        <v>6233806</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8636,10 +8636,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471565</v>
+        <v>121471592</v>
       </c>
       <c r="B78" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8648,25 +8648,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>428016</v>
+        <v>427703</v>
       </c>
       <c r="R78" t="n">
-        <v>6233689</v>
+        <v>6233616</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8738,10 +8738,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471629</v>
+        <v>121471581</v>
       </c>
       <c r="B79" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8750,25 +8750,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8778,10 +8778,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427602</v>
+        <v>427820</v>
       </c>
       <c r="R79" t="n">
-        <v>6233832</v>
+        <v>6233599</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8840,10 +8840,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121472014</v>
+        <v>121471959</v>
       </c>
       <c r="B80" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8852,25 +8852,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8880,10 +8880,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427882</v>
+        <v>427734</v>
       </c>
       <c r="R80" t="n">
-        <v>6233622</v>
+        <v>6233532</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8942,10 +8942,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471593</v>
+        <v>121471575</v>
       </c>
       <c r="B81" t="n">
-        <v>80244</v>
+        <v>91119</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8954,25 +8954,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>230185</v>
+        <v>2023</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8982,10 +8982,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427699</v>
+        <v>427837</v>
       </c>
       <c r="R81" t="n">
-        <v>6233608</v>
+        <v>6233582</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9044,10 +9044,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471992</v>
+        <v>121471706</v>
       </c>
       <c r="B82" t="n">
-        <v>94595</v>
+        <v>96732</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9060,21 +9060,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427861</v>
+        <v>427781</v>
       </c>
       <c r="R82" t="n">
-        <v>6233620</v>
+        <v>6233648</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9114,12 +9114,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9146,10 +9146,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121472003</v>
+        <v>121472009</v>
       </c>
       <c r="B83" t="n">
-        <v>79020</v>
+        <v>94606</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9158,23 +9158,27 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>132</v>
+        <v>2667</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Liten lundlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bacidina phacodes/tarandina</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9182,10 +9186,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427911</v>
+        <v>427877</v>
       </c>
       <c r="R83" t="n">
-        <v>6233614</v>
+        <v>6233615</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9244,10 +9248,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121471957</v>
+        <v>121472016</v>
       </c>
       <c r="B84" t="n">
-        <v>94606</v>
+        <v>96732</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9260,21 +9264,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9284,10 +9288,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427731</v>
+        <v>427903</v>
       </c>
       <c r="R84" t="n">
-        <v>6233539</v>
+        <v>6233640</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9346,10 +9350,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471999</v>
+        <v>121472013</v>
       </c>
       <c r="B85" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9358,25 +9362,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9386,10 +9390,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427916</v>
+        <v>427882</v>
       </c>
       <c r="R85" t="n">
-        <v>6233634</v>
+        <v>6233622</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9448,10 +9452,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121472000</v>
+        <v>121471708</v>
       </c>
       <c r="B86" t="n">
-        <v>74699</v>
+        <v>96732</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9464,21 +9468,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9488,10 +9492,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427926</v>
+        <v>427785</v>
       </c>
       <c r="R86" t="n">
-        <v>6233617</v>
+        <v>6233734</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9518,12 +9522,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9550,10 +9554,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471610</v>
+        <v>121471619</v>
       </c>
       <c r="B87" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9566,21 +9570,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9590,10 +9594,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427487</v>
+        <v>427624</v>
       </c>
       <c r="R87" t="n">
-        <v>6233816</v>
+        <v>6233894</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9652,10 +9656,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471521</v>
+        <v>121471980</v>
       </c>
       <c r="B88" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9664,25 +9668,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9692,10 +9696,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427794</v>
+        <v>427532</v>
       </c>
       <c r="R88" t="n">
-        <v>6233483</v>
+        <v>6233767</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9722,12 +9726,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9754,10 +9758,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471580</v>
+        <v>121472007</v>
       </c>
       <c r="B89" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9766,25 +9770,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9794,10 +9798,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427804</v>
+        <v>427892</v>
       </c>
       <c r="R89" t="n">
-        <v>6233576</v>
+        <v>6233623</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9824,12 +9828,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9856,10 +9860,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471968</v>
+        <v>121471633</v>
       </c>
       <c r="B90" t="n">
-        <v>57372</v>
+        <v>90515</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9868,25 +9872,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>1067</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9896,10 +9900,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427512</v>
+        <v>427629</v>
       </c>
       <c r="R90" t="n">
-        <v>6233745</v>
+        <v>6233837</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9926,12 +9930,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9958,10 +9962,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471597</v>
+        <v>121472002</v>
       </c>
       <c r="B91" t="n">
-        <v>80244</v>
+        <v>94606</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9974,21 +9978,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9998,10 +10002,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427693</v>
+        <v>427909</v>
       </c>
       <c r="R91" t="n">
-        <v>6233604</v>
+        <v>6233613</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10028,12 +10032,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10060,10 +10064,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471560</v>
+        <v>121471603</v>
       </c>
       <c r="B92" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10072,25 +10076,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10100,10 +10104,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>428008</v>
+        <v>427596</v>
       </c>
       <c r="R92" t="n">
-        <v>6233671</v>
+        <v>6233681</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10162,10 +10166,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471598</v>
+        <v>121471649</v>
       </c>
       <c r="B93" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10174,25 +10178,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10202,10 +10206,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427690</v>
+        <v>427720</v>
       </c>
       <c r="R93" t="n">
-        <v>6233595</v>
+        <v>6233787</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10264,10 +10268,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471647</v>
+        <v>121471999</v>
       </c>
       <c r="B94" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10276,25 +10280,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10304,10 +10308,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427720</v>
+        <v>427916</v>
       </c>
       <c r="R94" t="n">
-        <v>6233787</v>
+        <v>6233634</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10334,12 +10338,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10366,10 +10370,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471617</v>
+        <v>121471974</v>
       </c>
       <c r="B95" t="n">
-        <v>80244</v>
+        <v>90515</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10378,25 +10382,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10406,10 +10410,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427526</v>
+        <v>427554</v>
       </c>
       <c r="R95" t="n">
-        <v>6233836</v>
+        <v>6233803</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10436,12 +10440,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10468,10 +10472,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471619</v>
+        <v>121472000</v>
       </c>
       <c r="B96" t="n">
-        <v>96732</v>
+        <v>74699</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10484,21 +10488,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2606</v>
+        <v>6439</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10508,10 +10512,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427624</v>
+        <v>427926</v>
       </c>
       <c r="R96" t="n">
-        <v>6233894</v>
+        <v>6233617</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10538,12 +10542,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10570,10 +10574,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121471575</v>
+        <v>121472004</v>
       </c>
       <c r="B97" t="n">
-        <v>91119</v>
+        <v>80244</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10582,25 +10586,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>2023</v>
+        <v>230185</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10610,10 +10614,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427837</v>
+        <v>427892</v>
       </c>
       <c r="R97" t="n">
-        <v>6233582</v>
+        <v>6233623</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10640,12 +10644,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10672,7 +10676,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471966</v>
+        <v>121471578</v>
       </c>
       <c r="B98" t="n">
         <v>76950</v>
@@ -10712,10 +10716,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427505</v>
+        <v>427749</v>
       </c>
       <c r="R98" t="n">
-        <v>6233740</v>
+        <v>6233573</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10742,12 +10746,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10774,10 +10778,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471971</v>
+        <v>121471632</v>
       </c>
       <c r="B99" t="n">
-        <v>78865</v>
+        <v>80244</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10790,21 +10794,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10814,10 +10818,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427499</v>
+        <v>427615</v>
       </c>
       <c r="R99" t="n">
-        <v>6233792</v>
+        <v>6233825</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10844,12 +10848,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10876,10 +10880,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471956</v>
+        <v>121471985</v>
       </c>
       <c r="B100" t="n">
-        <v>94608</v>
+        <v>80244</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10892,21 +10896,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10916,10 +10920,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427739</v>
+        <v>427558</v>
       </c>
       <c r="R100" t="n">
-        <v>6233524</v>
+        <v>6233768</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10978,7 +10982,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471592</v>
+        <v>121471597</v>
       </c>
       <c r="B101" t="n">
         <v>80244</v>
@@ -11018,10 +11022,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>427703</v>
+        <v>427693</v>
       </c>
       <c r="R101" t="n">
-        <v>6233616</v>
+        <v>6233604</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11080,10 +11084,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471986</v>
+        <v>121471618</v>
       </c>
       <c r="B102" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11092,41 +11096,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427558</v>
+        <v>427525</v>
       </c>
       <c r="R102" t="n">
-        <v>6233769</v>
+        <v>6233838</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11153,17 +11154,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
-        </is>
-      </c>
-      <c r="AC102" t="inlineStr">
-        <is>
-          <t>Med Refractohilum pluriseptatum</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11171,11 +11167,6 @@
       </c>
       <c r="AE102" t="b">
         <v>0</v>
-      </c>
-      <c r="AF102" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG102" t="b">
         <v>0</v>
@@ -11195,7 +11186,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471581</v>
+        <v>121471614</v>
       </c>
       <c r="B103" t="n">
         <v>80244</v>
@@ -11235,10 +11226,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427820</v>
+        <v>427475</v>
       </c>
       <c r="R103" t="n">
-        <v>6233599</v>
+        <v>6233836</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11297,10 +11288,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121472002</v>
+        <v>121471644</v>
       </c>
       <c r="B104" t="n">
-        <v>94606</v>
+        <v>78865</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11313,21 +11304,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>2667</v>
+        <v>6459</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11337,10 +11328,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427909</v>
+        <v>427671</v>
       </c>
       <c r="R104" t="n">
-        <v>6233613</v>
+        <v>6233821</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11367,12 +11358,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11399,10 +11390,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471585</v>
+        <v>121471993</v>
       </c>
       <c r="B105" t="n">
-        <v>76950</v>
+        <v>91511</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11415,34 +11406,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1342</v>
+        <v>2014</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427748</v>
+        <v>427859</v>
       </c>
       <c r="R105" t="n">
-        <v>6233622</v>
+        <v>6233620</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11469,12 +11463,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11483,6 +11477,7 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
+      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11501,10 +11496,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471520</v>
+        <v>121471563</v>
       </c>
       <c r="B106" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11517,21 +11512,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11541,10 +11536,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427789</v>
+        <v>428012</v>
       </c>
       <c r="R106" t="n">
-        <v>6233516</v>
+        <v>6233689</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11603,10 +11598,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471559</v>
+        <v>121471704</v>
       </c>
       <c r="B107" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11615,25 +11610,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11643,10 +11638,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427960</v>
+        <v>427785</v>
       </c>
       <c r="R107" t="n">
-        <v>6233661</v>
+        <v>6233585</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11705,10 +11700,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121472010</v>
+        <v>121471577</v>
       </c>
       <c r="B108" t="n">
-        <v>78989</v>
+        <v>94606</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11721,21 +11716,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6431</v>
+        <v>2667</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11745,10 +11740,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>427877</v>
+        <v>427749</v>
       </c>
       <c r="R108" t="n">
-        <v>6233615</v>
+        <v>6233572</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11775,12 +11770,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11807,10 +11802,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471974</v>
+        <v>121471956</v>
       </c>
       <c r="B109" t="n">
-        <v>90515</v>
+        <v>94608</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11819,25 +11814,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1067</v>
+        <v>2666</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11847,10 +11842,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>427554</v>
+        <v>427739</v>
       </c>
       <c r="R109" t="n">
-        <v>6233803</v>
+        <v>6233524</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11909,10 +11904,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471671</v>
+        <v>121471562</v>
       </c>
       <c r="B110" t="n">
-        <v>105766</v>
+        <v>80580</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11921,25 +11916,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>220785</v>
+        <v>1182</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11949,10 +11944,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>427912</v>
+        <v>428000</v>
       </c>
       <c r="R110" t="n">
-        <v>6233611</v>
+        <v>6233692</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12011,10 +12006,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471631</v>
+        <v>121471702</v>
       </c>
       <c r="B111" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12027,21 +12022,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12051,10 +12046,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427601</v>
+        <v>427811</v>
       </c>
       <c r="R111" t="n">
-        <v>6233830</v>
+        <v>6233480</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12113,7 +12108,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471967</v>
+        <v>121471558</v>
       </c>
       <c r="B112" t="n">
         <v>80257</v>
@@ -12153,10 +12148,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427508</v>
+        <v>427960</v>
       </c>
       <c r="R112" t="n">
-        <v>6233737</v>
+        <v>6233661</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12183,12 +12178,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12215,10 +12210,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471993</v>
+        <v>121471604</v>
       </c>
       <c r="B113" t="n">
-        <v>91511</v>
+        <v>80244</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12227,41 +12222,38 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>2014</v>
+        <v>230185</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427859</v>
+        <v>427595</v>
       </c>
       <c r="R113" t="n">
-        <v>6233620</v>
+        <v>6233781</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12288,12 +12280,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12302,7 +12294,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12321,10 +12312,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471704</v>
+        <v>121471983</v>
       </c>
       <c r="B114" t="n">
-        <v>96732</v>
+        <v>74699</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12337,21 +12328,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2606</v>
+        <v>6439</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12361,10 +12352,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427785</v>
+        <v>427521</v>
       </c>
       <c r="R114" t="n">
-        <v>6233585</v>
+        <v>6233737</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12391,12 +12382,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12423,10 +12414,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471604</v>
+        <v>121471627</v>
       </c>
       <c r="B115" t="n">
-        <v>80244</v>
+        <v>74699</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12439,21 +12430,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12463,10 +12454,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427595</v>
+        <v>427613</v>
       </c>
       <c r="R115" t="n">
-        <v>6233781</v>
+        <v>6233840</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12525,10 +12516,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471985</v>
+        <v>121471968</v>
       </c>
       <c r="B116" t="n">
-        <v>80244</v>
+        <v>57372</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12537,25 +12528,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>230185</v>
+        <v>100049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12565,10 +12556,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427558</v>
+        <v>427512</v>
       </c>
       <c r="R116" t="n">
-        <v>6233768</v>
+        <v>6233745</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12627,10 +12618,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121471599</v>
+        <v>121472003</v>
       </c>
       <c r="B117" t="n">
-        <v>94608</v>
+        <v>79020</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12639,27 +12630,23 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2666</v>
+        <v>132</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Liten lundlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
-        </is>
-      </c>
+          <t>Bacidina phacodes/tarandina</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12667,10 +12654,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427685</v>
+        <v>427911</v>
       </c>
       <c r="R117" t="n">
-        <v>6233593</v>
+        <v>6233614</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12697,12 +12684,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12729,10 +12716,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471710</v>
+        <v>121471646</v>
       </c>
       <c r="B118" t="n">
-        <v>94608</v>
+        <v>94606</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12745,16 +12732,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -12769,10 +12756,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427448</v>
+        <v>427692</v>
       </c>
       <c r="R118" t="n">
-        <v>6233789</v>
+        <v>6233796</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12831,7 +12818,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471607</v>
+        <v>121471580</v>
       </c>
       <c r="B119" t="n">
         <v>80244</v>
@@ -12871,10 +12858,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427582</v>
+        <v>427804</v>
       </c>
       <c r="R119" t="n">
-        <v>6233752</v>
+        <v>6233576</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12933,10 +12920,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471703</v>
+        <v>121471650</v>
       </c>
       <c r="B120" t="n">
-        <v>74699</v>
+        <v>80244</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12949,21 +12936,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12973,10 +12960,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427770</v>
+        <v>427737</v>
       </c>
       <c r="R120" t="n">
-        <v>6233580</v>
+        <v>6233784</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13035,10 +13022,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121472013</v>
+        <v>121471574</v>
       </c>
       <c r="B121" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13051,21 +13038,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13075,10 +13062,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427882</v>
+        <v>427838</v>
       </c>
       <c r="R121" t="n">
-        <v>6233622</v>
+        <v>6233582</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13105,12 +13092,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13137,10 +13124,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471718</v>
+        <v>121471600</v>
       </c>
       <c r="B122" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13149,25 +13136,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13177,10 +13164,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427584</v>
+        <v>427698</v>
       </c>
       <c r="R122" t="n">
-        <v>6233863</v>
+        <v>6233566</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13239,10 +13226,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471635</v>
+        <v>121471621</v>
       </c>
       <c r="B123" t="n">
-        <v>78865</v>
+        <v>96732</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13255,21 +13242,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13279,10 +13266,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427637</v>
+        <v>427607</v>
       </c>
       <c r="R123" t="n">
-        <v>6233845</v>
+        <v>6233875</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13341,10 +13328,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471626</v>
+        <v>121471607</v>
       </c>
       <c r="B124" t="n">
-        <v>74699</v>
+        <v>80244</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13357,21 +13344,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13381,10 +13368,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427597</v>
+        <v>427582</v>
       </c>
       <c r="R124" t="n">
-        <v>6233825</v>
+        <v>6233752</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13443,10 +13430,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471630</v>
+        <v>121471638</v>
       </c>
       <c r="B125" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13455,25 +13442,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13483,10 +13470,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427604</v>
+        <v>427638</v>
       </c>
       <c r="R125" t="n">
-        <v>6233829</v>
+        <v>6233822</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13545,10 +13532,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471963</v>
+        <v>121471590</v>
       </c>
       <c r="B126" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13561,21 +13548,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13585,10 +13572,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427520</v>
+        <v>427753</v>
       </c>
       <c r="R126" t="n">
-        <v>6233715</v>
+        <v>6233666</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13615,12 +13602,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13647,10 +13634,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471649</v>
+        <v>121471593</v>
       </c>
       <c r="B127" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13659,25 +13646,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13687,10 +13674,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427720</v>
+        <v>427699</v>
       </c>
       <c r="R127" t="n">
-        <v>6233787</v>
+        <v>6233608</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13749,10 +13736,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471561</v>
+        <v>121471964</v>
       </c>
       <c r="B128" t="n">
-        <v>96732</v>
+        <v>94606</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13765,21 +13752,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13789,10 +13776,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427999</v>
+        <v>427511</v>
       </c>
       <c r="R128" t="n">
-        <v>6233695</v>
+        <v>6233739</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13819,12 +13806,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13851,10 +13838,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471708</v>
+        <v>121471710</v>
       </c>
       <c r="B129" t="n">
-        <v>96732</v>
+        <v>94608</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13867,21 +13854,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2606</v>
+        <v>2666</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13891,10 +13878,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>427785</v>
+        <v>427448</v>
       </c>
       <c r="R129" t="n">
-        <v>6233734</v>
+        <v>6233789</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13953,10 +13940,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121472016</v>
+        <v>121471630</v>
       </c>
       <c r="B130" t="n">
-        <v>96732</v>
+        <v>76950</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13965,25 +13952,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13993,10 +13980,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>427903</v>
+        <v>427604</v>
       </c>
       <c r="R130" t="n">
-        <v>6233640</v>
+        <v>6233829</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14023,12 +14010,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14055,10 +14042,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471591</v>
+        <v>121471713</v>
       </c>
       <c r="B131" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -14067,25 +14054,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14095,10 +14082,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427724</v>
+        <v>427438</v>
       </c>
       <c r="R131" t="n">
-        <v>6233617</v>
+        <v>6233852</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14157,7 +14144,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471976</v>
+        <v>121471572</v>
       </c>
       <c r="B132" t="n">
         <v>96732</v>
@@ -14197,10 +14184,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427576</v>
+        <v>427982</v>
       </c>
       <c r="R132" t="n">
-        <v>6233800</v>
+        <v>6233642</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14227,12 +14214,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14259,10 +14246,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471651</v>
+        <v>121471707</v>
       </c>
       <c r="B133" t="n">
-        <v>78865</v>
+        <v>96732</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14275,21 +14262,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6459</v>
+        <v>2606</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14299,10 +14286,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427737</v>
+        <v>427809</v>
       </c>
       <c r="R133" t="n">
-        <v>6233789</v>
+        <v>6233703</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14361,10 +14348,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471590</v>
+        <v>121471559</v>
       </c>
       <c r="B134" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14373,25 +14360,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14401,10 +14388,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427753</v>
+        <v>427960</v>
       </c>
       <c r="R134" t="n">
-        <v>6233666</v>
+        <v>6233661</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14463,10 +14450,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121471637</v>
+        <v>121472012</v>
       </c>
       <c r="B135" t="n">
-        <v>96732</v>
+        <v>76950</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14475,25 +14462,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14503,10 +14490,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427638</v>
+        <v>427855</v>
       </c>
       <c r="R135" t="n">
-        <v>6233822</v>
+        <v>6233612</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14533,12 +14520,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14565,10 +14552,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471572</v>
+        <v>121471583</v>
       </c>
       <c r="B136" t="n">
-        <v>96732</v>
+        <v>78865</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14581,21 +14568,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14605,10 +14592,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427982</v>
+        <v>427813</v>
       </c>
       <c r="R136" t="n">
-        <v>6233642</v>
+        <v>6233621</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14667,7 +14654,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471563</v>
+        <v>121471556</v>
       </c>
       <c r="B137" t="n">
         <v>96732</v>
@@ -14707,10 +14694,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>428012</v>
+        <v>427948</v>
       </c>
       <c r="R137" t="n">
-        <v>6233689</v>
+        <v>6233643</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14769,10 +14756,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471633</v>
+        <v>121471978</v>
       </c>
       <c r="B138" t="n">
-        <v>90515</v>
+        <v>94606</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14781,25 +14768,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>1067</v>
+        <v>2667</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14809,10 +14796,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427629</v>
+        <v>427533</v>
       </c>
       <c r="R138" t="n">
-        <v>6233837</v>
+        <v>6233765</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14839,12 +14826,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -14871,10 +14858,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471623</v>
+        <v>121471977</v>
       </c>
       <c r="B139" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14887,21 +14874,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14911,10 +14898,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>427579</v>
+        <v>427533</v>
       </c>
       <c r="R139" t="n">
-        <v>6233850</v>
+        <v>6233765</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14941,12 +14928,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -14973,10 +14960,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471707</v>
+        <v>121471957</v>
       </c>
       <c r="B140" t="n">
-        <v>96732</v>
+        <v>94606</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14989,21 +14976,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15013,10 +15000,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>427809</v>
+        <v>427731</v>
       </c>
       <c r="R140" t="n">
-        <v>6233703</v>
+        <v>6233539</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15043,12 +15030,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15075,10 +15062,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471954</v>
+        <v>121471635</v>
       </c>
       <c r="B141" t="n">
-        <v>80244</v>
+        <v>78865</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15091,21 +15078,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15115,10 +15102,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>427742</v>
+        <v>427637</v>
       </c>
       <c r="R141" t="n">
-        <v>6233542</v>
+        <v>6233845</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15145,12 +15132,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15177,10 +15164,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471621</v>
+        <v>121471975</v>
       </c>
       <c r="B142" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15193,21 +15180,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15217,10 +15204,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>427607</v>
+        <v>427575</v>
       </c>
       <c r="R142" t="n">
-        <v>6233875</v>
+        <v>6233800</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15247,12 +15234,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15279,7 +15266,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471608</v>
+        <v>121471984</v>
       </c>
       <c r="B143" t="n">
         <v>80244</v>
@@ -15319,10 +15306,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>427566</v>
+        <v>427530</v>
       </c>
       <c r="R143" t="n">
-        <v>6233756</v>
+        <v>6233736</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15349,12 +15336,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15381,10 +15368,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471706</v>
+        <v>121471601</v>
       </c>
       <c r="B144" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15397,21 +15384,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15421,10 +15408,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>427781</v>
+        <v>427688</v>
       </c>
       <c r="R144" t="n">
-        <v>6233648</v>
+        <v>6233590</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15483,10 +15470,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471603</v>
+        <v>121471610</v>
       </c>
       <c r="B145" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15495,25 +15482,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15523,10 +15510,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427596</v>
+        <v>427487</v>
       </c>
       <c r="R145" t="n">
-        <v>6233681</v>
+        <v>6233816</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15585,10 +15572,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471714</v>
+        <v>121471596</v>
       </c>
       <c r="B146" t="n">
-        <v>78409</v>
+        <v>74701</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15597,25 +15584,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>924</v>
+        <v>306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15625,10 +15612,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427435</v>
+        <v>427686</v>
       </c>
       <c r="R146" t="n">
-        <v>6233855</v>
+        <v>6233621</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15687,10 +15674,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471952</v>
+        <v>121471584</v>
       </c>
       <c r="B147" t="n">
-        <v>74699</v>
+        <v>96732</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15703,21 +15690,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15727,10 +15714,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427763</v>
+        <v>427817</v>
       </c>
       <c r="R147" t="n">
-        <v>6233529</v>
+        <v>6233621</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15757,12 +15744,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -15789,10 +15776,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471959</v>
+        <v>121471988</v>
       </c>
       <c r="B148" t="n">
-        <v>80244</v>
+        <v>74527</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15805,21 +15792,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>230185</v>
+        <v>6428</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15829,10 +15816,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427734</v>
+        <v>427738</v>
       </c>
       <c r="R148" t="n">
-        <v>6233532</v>
+        <v>6233780</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15891,10 +15878,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471636</v>
+        <v>121471952</v>
       </c>
       <c r="B149" t="n">
-        <v>80244</v>
+        <v>74699</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15907,21 +15894,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15931,10 +15918,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>427650</v>
+        <v>427763</v>
       </c>
       <c r="R149" t="n">
-        <v>6233855</v>
+        <v>6233529</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15961,12 +15948,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15993,10 +15980,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471638</v>
+        <v>121471651</v>
       </c>
       <c r="B150" t="n">
-        <v>80244</v>
+        <v>78865</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16009,21 +15996,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16033,10 +16020,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>427638</v>
+        <v>427737</v>
       </c>
       <c r="R150" t="n">
-        <v>6233822</v>
+        <v>6233789</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16095,10 +16082,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121472011</v>
+        <v>121471612</v>
       </c>
       <c r="B151" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16107,25 +16094,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16135,10 +16122,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>427874</v>
+        <v>427466</v>
       </c>
       <c r="R151" t="n">
-        <v>6233615</v>
+        <v>6233828</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16165,12 +16152,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16197,10 +16184,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121472012</v>
+        <v>121471560</v>
       </c>
       <c r="B152" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16209,25 +16196,25 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16237,10 +16224,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>427855</v>
+        <v>428008</v>
       </c>
       <c r="R152" t="n">
-        <v>6233612</v>
+        <v>6233671</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16267,12 +16254,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -16299,10 +16286,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121472007</v>
+        <v>121471565</v>
       </c>
       <c r="B153" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16311,25 +16298,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16339,10 +16326,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>427892</v>
+        <v>428016</v>
       </c>
       <c r="R153" t="n">
-        <v>6233623</v>
+        <v>6233689</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16369,12 +16356,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16401,10 +16388,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121472015</v>
+        <v>121471976</v>
       </c>
       <c r="B154" t="n">
-        <v>74699</v>
+        <v>96732</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16417,21 +16404,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16441,10 +16428,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>427903</v>
+        <v>427576</v>
       </c>
       <c r="R154" t="n">
-        <v>6233639</v>
+        <v>6233800</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16503,10 +16490,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471961</v>
+        <v>121471982</v>
       </c>
       <c r="B155" t="n">
-        <v>94606</v>
+        <v>76950</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16515,25 +16502,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2667</v>
+        <v>1342</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16543,10 +16530,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>427615</v>
+        <v>427516</v>
       </c>
       <c r="R155" t="n">
-        <v>6233649</v>
+        <v>6233748</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16605,7 +16592,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471586</v>
+        <v>121472014</v>
       </c>
       <c r="B156" t="n">
         <v>80257</v>
@@ -16645,7 +16632,7 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>427748</v>
+        <v>427882</v>
       </c>
       <c r="R156" t="n">
         <v>6233622</v>
@@ -16675,12 +16662,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16707,10 +16694,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471716</v>
+        <v>121471966</v>
       </c>
       <c r="B157" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16719,25 +16706,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16747,10 +16734,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>427547</v>
+        <v>427505</v>
       </c>
       <c r="R157" t="n">
-        <v>6233865</v>
+        <v>6233740</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16777,12 +16764,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16809,10 +16796,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471988</v>
+        <v>121471709</v>
       </c>
       <c r="B158" t="n">
-        <v>74527</v>
+        <v>80244</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16825,21 +16812,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6428</v>
+        <v>230185</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16849,10 +16836,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>427738</v>
+        <v>427452</v>
       </c>
       <c r="R158" t="n">
-        <v>6233780</v>
+        <v>6233794</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16879,12 +16866,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16911,10 +16898,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471978</v>
+        <v>121471623</v>
       </c>
       <c r="B159" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16927,21 +16914,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16951,10 +16938,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>427533</v>
+        <v>427579</v>
       </c>
       <c r="R159" t="n">
-        <v>6233765</v>
+        <v>6233850</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16981,12 +16968,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -17013,7 +17000,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471612</v>
+        <v>121471962</v>
       </c>
       <c r="B160" t="n">
         <v>80244</v>
@@ -17053,10 +17040,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>427466</v>
+        <v>427528</v>
       </c>
       <c r="R160" t="n">
-        <v>6233828</v>
+        <v>6233707</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17083,12 +17070,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17115,10 +17102,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471609</v>
+        <v>121471986</v>
       </c>
       <c r="B161" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17127,38 +17114,41 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>427543</v>
+        <v>427558</v>
       </c>
       <c r="R161" t="n">
-        <v>6233756</v>
+        <v>6233769</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17185,12 +17175,17 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Med Refractohilum pluriseptatum</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17198,6 +17193,11 @@
       </c>
       <c r="AE161" t="b">
         <v>0</v>
+      </c>
+      <c r="AF161" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG161" t="b">
         <v>0</v>

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471599</v>
+        <v>121471704</v>
       </c>
       <c r="B11" t="n">
-        <v>94608</v>
+        <v>96732</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1818,21 +1818,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2666</v>
+        <v>2606</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427685</v>
+        <v>427785</v>
       </c>
       <c r="R11" t="n">
-        <v>6233593</v>
+        <v>6233585</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471561</v>
+        <v>121471634</v>
       </c>
       <c r="B12" t="n">
         <v>96732</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427999</v>
+        <v>427636</v>
       </c>
       <c r="R12" t="n">
-        <v>6233695</v>
+        <v>6233848</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471589</v>
+        <v>121471620</v>
       </c>
       <c r="B13" t="n">
-        <v>96732</v>
+        <v>94595</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427804</v>
+        <v>427625</v>
       </c>
       <c r="R13" t="n">
-        <v>6233688</v>
+        <v>6233894</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121472011</v>
+        <v>121471702</v>
       </c>
       <c r="B14" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,25 +2120,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427874</v>
+        <v>427811</v>
       </c>
       <c r="R14" t="n">
-        <v>6233615</v>
+        <v>6233480</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2312,7 +2312,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121471716</v>
+        <v>121471580</v>
       </c>
       <c r="B16" t="n">
         <v>80244</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427547</v>
+        <v>427804</v>
       </c>
       <c r="R16" t="n">
-        <v>6233865</v>
+        <v>6233576</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121471705</v>
+        <v>121471630</v>
       </c>
       <c r="B17" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427753</v>
+        <v>427604</v>
       </c>
       <c r="R17" t="n">
-        <v>6233606</v>
+        <v>6233829</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2516,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121471996</v>
+        <v>121471651</v>
       </c>
       <c r="B18" t="n">
-        <v>80257</v>
+        <v>78865</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1144</v>
+        <v>6459</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427855</v>
+        <v>427737</v>
       </c>
       <c r="R18" t="n">
-        <v>6233614</v>
+        <v>6233789</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2586,12 +2586,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121471719</v>
+        <v>121471563</v>
       </c>
       <c r="B19" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427583</v>
+        <v>428012</v>
       </c>
       <c r="R19" t="n">
-        <v>6233861</v>
+        <v>6233689</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121471951</v>
+        <v>121471963</v>
       </c>
       <c r="B20" t="n">
-        <v>76950</v>
+        <v>94606</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427762</v>
+        <v>427520</v>
       </c>
       <c r="R20" t="n">
-        <v>6233515</v>
+        <v>6233715</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121471624</v>
+        <v>121471623</v>
       </c>
       <c r="B21" t="n">
-        <v>74565</v>
+        <v>80244</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1116</v>
+        <v>230185</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>427594</v>
+        <v>427579</v>
       </c>
       <c r="R21" t="n">
-        <v>6233828</v>
+        <v>6233850</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121471636</v>
+        <v>121471671</v>
       </c>
       <c r="B22" t="n">
-        <v>80244</v>
+        <v>105766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>230185</v>
+        <v>220785</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427650</v>
+        <v>427912</v>
       </c>
       <c r="R22" t="n">
-        <v>6233855</v>
+        <v>6233611</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471643</v>
+        <v>121471998</v>
       </c>
       <c r="B23" t="n">
-        <v>96732</v>
+        <v>76950</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427671</v>
+        <v>427915</v>
       </c>
       <c r="R23" t="n">
-        <v>6233821</v>
+        <v>6233632</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3096,12 +3096,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471647</v>
+        <v>121471719</v>
       </c>
       <c r="B24" t="n">
-        <v>96732</v>
+        <v>76950</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3140,25 +3140,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427720</v>
+        <v>427583</v>
       </c>
       <c r="R24" t="n">
-        <v>6233787</v>
+        <v>6233861</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471598</v>
+        <v>121471576</v>
       </c>
       <c r="B25" t="n">
-        <v>94606</v>
+        <v>80257</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3242,25 +3242,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>1144</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427690</v>
+        <v>427742</v>
       </c>
       <c r="R25" t="n">
-        <v>6233595</v>
+        <v>6233565</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3332,10 +3332,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471637</v>
+        <v>121471583</v>
       </c>
       <c r="B26" t="n">
-        <v>96732</v>
+        <v>78865</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3348,21 +3348,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2606</v>
+        <v>6459</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427638</v>
+        <v>427813</v>
       </c>
       <c r="R26" t="n">
-        <v>6233822</v>
+        <v>6233621</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471640</v>
+        <v>121471587</v>
       </c>
       <c r="B27" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427653</v>
+        <v>427770</v>
       </c>
       <c r="R27" t="n">
-        <v>6233849</v>
+        <v>6233624</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471700</v>
+        <v>121471647</v>
       </c>
       <c r="B28" t="n">
-        <v>78989</v>
+        <v>96732</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,21 +3552,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6431</v>
+        <v>2606</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427806</v>
+        <v>427720</v>
       </c>
       <c r="R28" t="n">
-        <v>6233482</v>
+        <v>6233787</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471642</v>
+        <v>121471618</v>
       </c>
       <c r="B29" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3654,21 +3654,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427654</v>
+        <v>427525</v>
       </c>
       <c r="R29" t="n">
-        <v>6233848</v>
+        <v>6233838</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471617</v>
+        <v>121471977</v>
       </c>
       <c r="B30" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427526</v>
+        <v>427533</v>
       </c>
       <c r="R30" t="n">
-        <v>6233836</v>
+        <v>6233765</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471990</v>
+        <v>121471992</v>
       </c>
       <c r="B31" t="n">
-        <v>80244</v>
+        <v>94595</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3858,21 +3858,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427765</v>
+        <v>427861</v>
       </c>
       <c r="R31" t="n">
-        <v>6233765</v>
+        <v>6233620</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471998</v>
+        <v>121471985</v>
       </c>
       <c r="B32" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3956,25 +3956,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427915</v>
+        <v>427558</v>
       </c>
       <c r="R32" t="n">
-        <v>6233632</v>
+        <v>6233768</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4046,10 +4046,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121472006</v>
+        <v>121471597</v>
       </c>
       <c r="B33" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4058,25 +4058,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427892</v>
+        <v>427693</v>
       </c>
       <c r="R33" t="n">
-        <v>6233623</v>
+        <v>6233604</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4116,12 +4116,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4148,10 +4148,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471585</v>
+        <v>121471712</v>
       </c>
       <c r="B34" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4160,25 +4160,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427748</v>
+        <v>427439</v>
       </c>
       <c r="R34" t="n">
-        <v>6233622</v>
+        <v>6233838</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4250,10 +4250,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121471564</v>
+        <v>121472000</v>
       </c>
       <c r="B35" t="n">
-        <v>80257</v>
+        <v>74699</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4262,25 +4262,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1144</v>
+        <v>6439</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4290,10 +4290,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428014</v>
+        <v>427926</v>
       </c>
       <c r="R35" t="n">
-        <v>6233692</v>
+        <v>6233617</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4320,12 +4320,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4352,10 +4352,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121471576</v>
+        <v>121471965</v>
       </c>
       <c r="B36" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4364,25 +4364,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4392,10 +4392,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>427742</v>
+        <v>427509</v>
       </c>
       <c r="R36" t="n">
-        <v>6233565</v>
+        <v>6233731</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4422,12 +4422,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4454,10 +4454,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121471712</v>
+        <v>121471638</v>
       </c>
       <c r="B37" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4470,21 +4470,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4494,10 +4494,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>427439</v>
+        <v>427638</v>
       </c>
       <c r="R37" t="n">
-        <v>6233838</v>
+        <v>6233822</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4556,10 +4556,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121471628</v>
+        <v>121471560</v>
       </c>
       <c r="B38" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4572,21 +4572,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4596,10 +4596,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>427604</v>
+        <v>428008</v>
       </c>
       <c r="R38" t="n">
-        <v>6233834</v>
+        <v>6233671</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4658,10 +4658,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121471961</v>
+        <v>121471644</v>
       </c>
       <c r="B39" t="n">
-        <v>94606</v>
+        <v>78865</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4674,21 +4674,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2667</v>
+        <v>6459</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4698,10 +4698,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>427615</v>
+        <v>427671</v>
       </c>
       <c r="R39" t="n">
-        <v>6233649</v>
+        <v>6233821</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4760,10 +4760,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121471955</v>
+        <v>121471584</v>
       </c>
       <c r="B40" t="n">
-        <v>94608</v>
+        <v>96732</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4776,21 +4776,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2666</v>
+        <v>2606</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>427741</v>
+        <v>427817</v>
       </c>
       <c r="R40" t="n">
-        <v>6233529</v>
+        <v>6233621</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4830,12 +4830,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4862,10 +4862,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121471992</v>
+        <v>121471559</v>
       </c>
       <c r="B41" t="n">
-        <v>94595</v>
+        <v>76950</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4874,25 +4874,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2671</v>
+        <v>1342</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4902,10 +4902,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>427861</v>
+        <v>427960</v>
       </c>
       <c r="R41" t="n">
-        <v>6233620</v>
+        <v>6233661</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4932,12 +4932,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4964,10 +4964,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121471586</v>
+        <v>121471713</v>
       </c>
       <c r="B42" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4976,25 +4976,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>427748</v>
+        <v>427438</v>
       </c>
       <c r="R42" t="n">
-        <v>6233622</v>
+        <v>6233852</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5066,10 +5066,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121471714</v>
+        <v>121471957</v>
       </c>
       <c r="B43" t="n">
-        <v>78409</v>
+        <v>94606</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5078,25 +5078,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>924</v>
+        <v>2667</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bokkantlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lecanora glabrata</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Malme</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5106,10 +5106,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>427435</v>
+        <v>427731</v>
       </c>
       <c r="R43" t="n">
-        <v>6233855</v>
+        <v>6233539</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5168,10 +5168,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121472015</v>
+        <v>121471577</v>
       </c>
       <c r="B44" t="n">
-        <v>74699</v>
+        <v>94606</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5184,21 +5184,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6439</v>
+        <v>2667</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5208,10 +5208,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>427903</v>
+        <v>427749</v>
       </c>
       <c r="R44" t="n">
-        <v>6233639</v>
+        <v>6233572</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5238,12 +5238,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5270,10 +5270,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121471626</v>
+        <v>121471988</v>
       </c>
       <c r="B45" t="n">
-        <v>74699</v>
+        <v>74527</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5286,21 +5286,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6439</v>
+        <v>6428</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5310,10 +5310,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>427597</v>
+        <v>427738</v>
       </c>
       <c r="R45" t="n">
-        <v>6233825</v>
+        <v>6233780</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5340,12 +5340,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5372,10 +5372,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121471995</v>
+        <v>121472010</v>
       </c>
       <c r="B46" t="n">
-        <v>78865</v>
+        <v>78989</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5388,21 +5388,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6459</v>
+        <v>6431</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5412,10 +5412,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>427856</v>
+        <v>427877</v>
       </c>
       <c r="R46" t="n">
-        <v>6233613</v>
+        <v>6233615</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5474,7 +5474,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121471608</v>
+        <v>121471709</v>
       </c>
       <c r="B47" t="n">
         <v>80244</v>
@@ -5514,10 +5514,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>427566</v>
+        <v>427452</v>
       </c>
       <c r="R47" t="n">
-        <v>6233756</v>
+        <v>6233794</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5576,7 +5576,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121471631</v>
+        <v>121471642</v>
       </c>
       <c r="B48" t="n">
         <v>80244</v>
@@ -5616,10 +5616,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>427601</v>
+        <v>427654</v>
       </c>
       <c r="R48" t="n">
-        <v>6233830</v>
+        <v>6233848</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5678,10 +5678,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121471634</v>
+        <v>121471607</v>
       </c>
       <c r="B49" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5694,21 +5694,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>427636</v>
+        <v>427582</v>
       </c>
       <c r="R49" t="n">
-        <v>6233848</v>
+        <v>6233752</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121472001</v>
+        <v>121471562</v>
       </c>
       <c r="B50" t="n">
-        <v>94616</v>
+        <v>80580</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5792,25 +5792,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1080</v>
+        <v>1182</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Violettgrå porlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Lepra multipuncta</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Turner) Hafellner</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>427908</v>
+        <v>428000</v>
       </c>
       <c r="R50" t="n">
-        <v>6233617</v>
+        <v>6233692</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5882,7 +5882,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121471718</v>
+        <v>121471603</v>
       </c>
       <c r="B51" t="n">
         <v>80257</v>
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>427584</v>
+        <v>427596</v>
       </c>
       <c r="R51" t="n">
-        <v>6233863</v>
+        <v>6233681</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5984,7 +5984,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121471973</v>
+        <v>121471648</v>
       </c>
       <c r="B52" t="n">
         <v>76950</v>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>427544</v>
+        <v>427721</v>
       </c>
       <c r="R52" t="n">
-        <v>6233811</v>
+        <v>6233787</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6054,12 +6054,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6086,7 +6086,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121471979</v>
+        <v>121472011</v>
       </c>
       <c r="B53" t="n">
         <v>76950</v>
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>427533</v>
+        <v>427874</v>
       </c>
       <c r="R53" t="n">
-        <v>6233765</v>
+        <v>6233615</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6188,10 +6188,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>121471671</v>
+        <v>121471706</v>
       </c>
       <c r="B54" t="n">
-        <v>105766</v>
+        <v>96732</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6200,25 +6200,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220785</v>
+        <v>2606</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>427912</v>
+        <v>427781</v>
       </c>
       <c r="R54" t="n">
-        <v>6233611</v>
+        <v>6233648</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6290,7 +6290,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>121471622</v>
+        <v>121472015</v>
       </c>
       <c r="B55" t="n">
         <v>74699</v>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>427623</v>
+        <v>427903</v>
       </c>
       <c r="R55" t="n">
-        <v>6233865</v>
+        <v>6233639</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6392,7 +6392,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>121471715</v>
+        <v>121471962</v>
       </c>
       <c r="B56" t="n">
         <v>80244</v>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>427445</v>
+        <v>427528</v>
       </c>
       <c r="R56" t="n">
-        <v>6233860</v>
+        <v>6233707</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6462,12 +6462,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6494,10 +6494,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>121471960</v>
+        <v>121471646</v>
       </c>
       <c r="B57" t="n">
-        <v>94595</v>
+        <v>94606</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>427734</v>
+        <v>427692</v>
       </c>
       <c r="R57" t="n">
-        <v>6233532</v>
+        <v>6233796</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6564,12 +6564,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6596,7 +6596,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>121471963</v>
+        <v>121471978</v>
       </c>
       <c r="B58" t="n">
         <v>94606</v>
@@ -6636,10 +6636,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>427520</v>
+        <v>427533</v>
       </c>
       <c r="R58" t="n">
-        <v>6233715</v>
+        <v>6233765</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6698,10 +6698,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121471953</v>
+        <v>121471960</v>
       </c>
       <c r="B59" t="n">
-        <v>96732</v>
+        <v>94595</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6714,21 +6714,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6738,10 +6738,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>427769</v>
+        <v>427734</v>
       </c>
       <c r="R59" t="n">
-        <v>6233529</v>
+        <v>6233532</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6800,10 +6800,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>121471965</v>
+        <v>121471964</v>
       </c>
       <c r="B60" t="n">
-        <v>76950</v>
+        <v>94606</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6812,25 +6812,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1342</v>
+        <v>2667</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6840,10 +6840,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>427509</v>
+        <v>427511</v>
       </c>
       <c r="R60" t="n">
-        <v>6233731</v>
+        <v>6233739</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6902,10 +6902,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>121471967</v>
+        <v>121471637</v>
       </c>
       <c r="B61" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6914,25 +6914,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6942,10 +6942,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>427508</v>
+        <v>427638</v>
       </c>
       <c r="R61" t="n">
-        <v>6233737</v>
+        <v>6233822</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6972,12 +6972,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7004,10 +7004,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>121471703</v>
+        <v>121471640</v>
       </c>
       <c r="B62" t="n">
-        <v>74699</v>
+        <v>96732</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7020,21 +7020,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6439</v>
+        <v>2606</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7044,10 +7044,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>427770</v>
+        <v>427653</v>
       </c>
       <c r="R62" t="n">
-        <v>6233580</v>
+        <v>6233849</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7106,10 +7106,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>121471629</v>
+        <v>121471983</v>
       </c>
       <c r="B63" t="n">
-        <v>80257</v>
+        <v>74699</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7118,25 +7118,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1144</v>
+        <v>6439</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7146,10 +7146,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>427602</v>
+        <v>427521</v>
       </c>
       <c r="R63" t="n">
-        <v>6233832</v>
+        <v>6233737</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7176,12 +7176,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7208,10 +7208,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471557</v>
+        <v>121471556</v>
       </c>
       <c r="B64" t="n">
-        <v>94595</v>
+        <v>96732</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7224,21 +7224,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7310,10 +7310,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121472010</v>
+        <v>121471628</v>
       </c>
       <c r="B65" t="n">
-        <v>78989</v>
+        <v>96732</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7326,21 +7326,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6431</v>
+        <v>2606</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427877</v>
+        <v>427604</v>
       </c>
       <c r="R65" t="n">
-        <v>6233615</v>
+        <v>6233834</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7380,12 +7380,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7412,10 +7412,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121471521</v>
+        <v>121472016</v>
       </c>
       <c r="B66" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7428,21 +7428,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7452,10 +7452,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427794</v>
+        <v>427903</v>
       </c>
       <c r="R66" t="n">
-        <v>6233483</v>
+        <v>6233640</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7482,12 +7482,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7514,10 +7514,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471609</v>
+        <v>121471578</v>
       </c>
       <c r="B67" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7526,25 +7526,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427543</v>
+        <v>427749</v>
       </c>
       <c r="R67" t="n">
-        <v>6233756</v>
+        <v>6233573</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7616,10 +7616,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471648</v>
+        <v>121471624</v>
       </c>
       <c r="B68" t="n">
-        <v>76950</v>
+        <v>74565</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7632,21 +7632,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1342</v>
+        <v>1116</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7656,10 +7656,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427721</v>
+        <v>427594</v>
       </c>
       <c r="R68" t="n">
-        <v>6233787</v>
+        <v>6233828</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7718,10 +7718,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471620</v>
+        <v>121471612</v>
       </c>
       <c r="B69" t="n">
-        <v>94595</v>
+        <v>80244</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7734,21 +7734,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2671</v>
+        <v>230185</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427625</v>
+        <v>427466</v>
       </c>
       <c r="R69" t="n">
-        <v>6233894</v>
+        <v>6233828</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7820,10 +7820,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471602</v>
+        <v>121471581</v>
       </c>
       <c r="B70" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7836,21 +7836,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7860,10 +7860,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>427641</v>
+        <v>427820</v>
       </c>
       <c r="R70" t="n">
-        <v>6233630</v>
+        <v>6233599</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7922,10 +7922,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>121471587</v>
+        <v>121471951</v>
       </c>
       <c r="B71" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7934,25 +7934,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7962,10 +7962,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>427770</v>
+        <v>427762</v>
       </c>
       <c r="R71" t="n">
-        <v>6233624</v>
+        <v>6233515</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7992,12 +7992,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8024,10 +8024,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121471971</v>
+        <v>121472009</v>
       </c>
       <c r="B72" t="n">
-        <v>78865</v>
+        <v>94606</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8040,21 +8040,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6459</v>
+        <v>2667</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8064,10 +8064,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>427499</v>
+        <v>427877</v>
       </c>
       <c r="R72" t="n">
-        <v>6233792</v>
+        <v>6233615</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8126,10 +8126,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>121471591</v>
+        <v>121471599</v>
       </c>
       <c r="B73" t="n">
-        <v>80244</v>
+        <v>94608</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8142,21 +8142,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8166,10 +8166,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>427724</v>
+        <v>427685</v>
       </c>
       <c r="R73" t="n">
-        <v>6233617</v>
+        <v>6233593</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8228,7 +8228,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>121471954</v>
+        <v>121471975</v>
       </c>
       <c r="B74" t="n">
         <v>80244</v>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>427742</v>
+        <v>427575</v>
       </c>
       <c r="R74" t="n">
-        <v>6233542</v>
+        <v>6233800</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8330,7 +8330,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>121471520</v>
+        <v>121471593</v>
       </c>
       <c r="B75" t="n">
         <v>80244</v>
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>427789</v>
+        <v>427699</v>
       </c>
       <c r="R75" t="n">
-        <v>6233516</v>
+        <v>6233608</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8432,7 +8432,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>121471720</v>
+        <v>121471601</v>
       </c>
       <c r="B76" t="n">
         <v>80244</v>
@@ -8472,10 +8472,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>427595</v>
+        <v>427688</v>
       </c>
       <c r="R76" t="n">
-        <v>6233898</v>
+        <v>6233590</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8534,10 +8534,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>121471645</v>
+        <v>121471980</v>
       </c>
       <c r="B77" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8546,25 +8546,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8574,10 +8574,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>427702</v>
+        <v>427532</v>
       </c>
       <c r="R77" t="n">
-        <v>6233806</v>
+        <v>6233767</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8604,12 +8604,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8636,10 +8636,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>121471592</v>
+        <v>121471982</v>
       </c>
       <c r="B78" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8648,25 +8648,25 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8676,10 +8676,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>427703</v>
+        <v>427516</v>
       </c>
       <c r="R78" t="n">
-        <v>6233616</v>
+        <v>6233748</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8706,12 +8706,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8738,10 +8738,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121471581</v>
+        <v>121471966</v>
       </c>
       <c r="B79" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8750,25 +8750,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8778,10 +8778,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>427820</v>
+        <v>427505</v>
       </c>
       <c r="R79" t="n">
-        <v>6233599</v>
+        <v>6233740</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8840,10 +8840,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121471959</v>
+        <v>121471643</v>
       </c>
       <c r="B80" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8856,21 +8856,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8880,10 +8880,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>427734</v>
+        <v>427671</v>
       </c>
       <c r="R80" t="n">
-        <v>6233532</v>
+        <v>6233821</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8910,12 +8910,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8942,10 +8942,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121471575</v>
+        <v>121471708</v>
       </c>
       <c r="B81" t="n">
-        <v>91119</v>
+        <v>96732</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -8954,25 +8954,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2023</v>
+        <v>2606</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8982,10 +8982,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>427837</v>
+        <v>427785</v>
       </c>
       <c r="R81" t="n">
-        <v>6233582</v>
+        <v>6233734</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9044,10 +9044,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>121471706</v>
+        <v>121471626</v>
       </c>
       <c r="B82" t="n">
-        <v>96732</v>
+        <v>74699</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9060,21 +9060,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2606</v>
+        <v>6439</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9084,10 +9084,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>427781</v>
+        <v>427597</v>
       </c>
       <c r="R82" t="n">
-        <v>6233648</v>
+        <v>6233825</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9146,10 +9146,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>121472009</v>
+        <v>121471703</v>
       </c>
       <c r="B83" t="n">
-        <v>94606</v>
+        <v>74699</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9162,21 +9162,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2667</v>
+        <v>6439</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9186,10 +9186,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>427877</v>
+        <v>427770</v>
       </c>
       <c r="R83" t="n">
-        <v>6233615</v>
+        <v>6233580</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9216,12 +9216,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9248,10 +9248,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>121472016</v>
+        <v>121471968</v>
       </c>
       <c r="B84" t="n">
-        <v>96732</v>
+        <v>57372</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9260,25 +9260,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2606</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9288,10 +9288,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>427903</v>
+        <v>427512</v>
       </c>
       <c r="R84" t="n">
-        <v>6233640</v>
+        <v>6233745</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9350,10 +9350,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121472013</v>
+        <v>121471956</v>
       </c>
       <c r="B85" t="n">
-        <v>96732</v>
+        <v>94608</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9366,21 +9366,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2606</v>
+        <v>2666</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427882</v>
+        <v>427739</v>
       </c>
       <c r="R85" t="n">
-        <v>6233622</v>
+        <v>6233524</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9452,10 +9452,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471708</v>
+        <v>121471952</v>
       </c>
       <c r="B86" t="n">
-        <v>96732</v>
+        <v>74699</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9468,21 +9468,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2606</v>
+        <v>6439</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427785</v>
+        <v>427763</v>
       </c>
       <c r="R86" t="n">
-        <v>6233734</v>
+        <v>6233529</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9554,10 +9554,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471619</v>
+        <v>121471715</v>
       </c>
       <c r="B87" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9570,21 +9570,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427624</v>
+        <v>427445</v>
       </c>
       <c r="R87" t="n">
-        <v>6233894</v>
+        <v>6233860</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9656,10 +9656,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471980</v>
+        <v>121471610</v>
       </c>
       <c r="B88" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9668,25 +9668,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427532</v>
+        <v>427487</v>
       </c>
       <c r="R88" t="n">
-        <v>6233767</v>
+        <v>6233816</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9726,12 +9726,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9758,10 +9758,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121472007</v>
+        <v>121471604</v>
       </c>
       <c r="B89" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9770,25 +9770,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427892</v>
+        <v>427595</v>
       </c>
       <c r="R89" t="n">
-        <v>6233623</v>
+        <v>6233781</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9828,12 +9828,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9860,10 +9860,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471633</v>
+        <v>121471959</v>
       </c>
       <c r="B90" t="n">
-        <v>90515</v>
+        <v>80244</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9872,25 +9872,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1067</v>
+        <v>230185</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9900,10 +9900,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427629</v>
+        <v>427734</v>
       </c>
       <c r="R90" t="n">
-        <v>6233837</v>
+        <v>6233532</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9930,12 +9930,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9962,10 +9962,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121472002</v>
+        <v>121471990</v>
       </c>
       <c r="B91" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9978,21 +9978,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10002,10 +10002,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427909</v>
+        <v>427765</v>
       </c>
       <c r="R91" t="n">
-        <v>6233613</v>
+        <v>6233765</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10064,10 +10064,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121471603</v>
+        <v>121472001</v>
       </c>
       <c r="B92" t="n">
-        <v>80257</v>
+        <v>94616</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10076,25 +10076,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1144</v>
+        <v>1080</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10104,10 +10104,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427596</v>
+        <v>427908</v>
       </c>
       <c r="R92" t="n">
-        <v>6233681</v>
+        <v>6233617</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10134,12 +10134,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10166,7 +10166,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471649</v>
+        <v>121471986</v>
       </c>
       <c r="B93" t="n">
         <v>80257</v>
@@ -10200,16 +10200,19 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427720</v>
+        <v>427558</v>
       </c>
       <c r="R93" t="n">
-        <v>6233787</v>
+        <v>6233769</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10236,12 +10239,17 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Med Refractohilum pluriseptatum</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10249,6 +10257,11 @@
       </c>
       <c r="AE93" t="b">
         <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG93" t="b">
         <v>0</v>
@@ -10268,10 +10281,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471999</v>
+        <v>121471585</v>
       </c>
       <c r="B94" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10280,25 +10293,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10308,10 +10321,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427916</v>
+        <v>427748</v>
       </c>
       <c r="R94" t="n">
-        <v>6233634</v>
+        <v>6233622</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10338,12 +10351,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10370,10 +10383,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471974</v>
+        <v>121471967</v>
       </c>
       <c r="B95" t="n">
-        <v>90515</v>
+        <v>80257</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10386,21 +10399,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1067</v>
+        <v>1144</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedlavklubba</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Multiclavula mucida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Pers.) R.H.Petersen</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10410,10 +10423,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427554</v>
+        <v>427508</v>
       </c>
       <c r="R95" t="n">
-        <v>6233803</v>
+        <v>6233737</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10472,10 +10485,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121472000</v>
+        <v>121471586</v>
       </c>
       <c r="B96" t="n">
-        <v>74699</v>
+        <v>80257</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10484,25 +10497,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6439</v>
+        <v>1144</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10512,10 +10525,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427926</v>
+        <v>427748</v>
       </c>
       <c r="R96" t="n">
-        <v>6233617</v>
+        <v>6233622</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10542,12 +10555,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10574,10 +10587,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>121472004</v>
+        <v>121471996</v>
       </c>
       <c r="B97" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10586,25 +10599,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10614,10 +10627,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>427892</v>
+        <v>427855</v>
       </c>
       <c r="R97" t="n">
-        <v>6233623</v>
+        <v>6233614</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10676,10 +10689,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121471578</v>
+        <v>121471718</v>
       </c>
       <c r="B98" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10688,25 +10701,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10716,10 +10729,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>427749</v>
+        <v>427584</v>
       </c>
       <c r="R98" t="n">
-        <v>6233573</v>
+        <v>6233863</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10778,10 +10791,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>121471632</v>
+        <v>121471564</v>
       </c>
       <c r="B99" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10790,25 +10803,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10818,10 +10831,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>427615</v>
+        <v>428014</v>
       </c>
       <c r="R99" t="n">
-        <v>6233825</v>
+        <v>6233692</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10880,10 +10893,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>121471985</v>
+        <v>121471714</v>
       </c>
       <c r="B100" t="n">
-        <v>80244</v>
+        <v>78409</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10892,25 +10905,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>230185</v>
+        <v>924</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokkantlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lecanora glabrata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Malme</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10920,10 +10933,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>427558</v>
+        <v>427435</v>
       </c>
       <c r="R100" t="n">
-        <v>6233768</v>
+        <v>6233855</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10950,12 +10963,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10982,10 +10995,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>121471597</v>
+        <v>121472002</v>
       </c>
       <c r="B101" t="n">
-        <v>80244</v>
+        <v>94606</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10998,21 +11011,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11022,10 +11035,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>427693</v>
+        <v>427909</v>
       </c>
       <c r="R101" t="n">
-        <v>6233604</v>
+        <v>6233613</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11052,12 +11065,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11084,10 +11097,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>121471618</v>
+        <v>121471598</v>
       </c>
       <c r="B102" t="n">
-        <v>96732</v>
+        <v>94606</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11100,21 +11113,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11124,10 +11137,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>427525</v>
+        <v>427690</v>
       </c>
       <c r="R102" t="n">
-        <v>6233838</v>
+        <v>6233595</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11186,10 +11199,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>121471614</v>
+        <v>121471619</v>
       </c>
       <c r="B103" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11202,21 +11215,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11226,10 +11239,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>427475</v>
+        <v>427624</v>
       </c>
       <c r="R103" t="n">
-        <v>6233836</v>
+        <v>6233894</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11288,10 +11301,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471644</v>
+        <v>121471700</v>
       </c>
       <c r="B104" t="n">
-        <v>78865</v>
+        <v>78989</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11304,21 +11317,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6459</v>
+        <v>6431</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11328,10 +11341,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427671</v>
+        <v>427806</v>
       </c>
       <c r="R104" t="n">
-        <v>6233821</v>
+        <v>6233482</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11390,10 +11403,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471993</v>
+        <v>121471558</v>
       </c>
       <c r="B105" t="n">
-        <v>91511</v>
+        <v>80257</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11402,41 +11415,38 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>2014</v>
+        <v>1144</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427859</v>
+        <v>427960</v>
       </c>
       <c r="R105" t="n">
-        <v>6233620</v>
+        <v>6233661</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11463,12 +11473,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11477,7 +11487,6 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
       </c>
@@ -11496,10 +11505,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471563</v>
+        <v>121471961</v>
       </c>
       <c r="B106" t="n">
-        <v>96732</v>
+        <v>94606</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11512,21 +11521,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2606</v>
+        <v>2667</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11536,10 +11545,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>428012</v>
+        <v>427615</v>
       </c>
       <c r="R106" t="n">
-        <v>6233689</v>
+        <v>6233649</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11566,12 +11575,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11598,7 +11607,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471704</v>
+        <v>121471707</v>
       </c>
       <c r="B107" t="n">
         <v>96732</v>
@@ -11638,10 +11647,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427785</v>
+        <v>427809</v>
       </c>
       <c r="R107" t="n">
-        <v>6233585</v>
+        <v>6233703</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11700,10 +11709,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>121471577</v>
+        <v>121471645</v>
       </c>
       <c r="B108" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11716,21 +11725,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11740,10 +11749,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>427749</v>
+        <v>427702</v>
       </c>
       <c r="R108" t="n">
-        <v>6233572</v>
+        <v>6233806</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11802,10 +11811,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121471956</v>
+        <v>121471521</v>
       </c>
       <c r="B109" t="n">
-        <v>94608</v>
+        <v>80244</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11818,21 +11827,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11842,10 +11851,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>427739</v>
+        <v>427794</v>
       </c>
       <c r="R109" t="n">
-        <v>6233524</v>
+        <v>6233483</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11872,12 +11881,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11904,10 +11913,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121471562</v>
+        <v>121472004</v>
       </c>
       <c r="B110" t="n">
-        <v>80580</v>
+        <v>80244</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11916,25 +11925,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1182</v>
+        <v>230185</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Violettgrå porlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lepra multipuncta</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Turner) Hafellner</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11944,10 +11953,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>428000</v>
+        <v>427892</v>
       </c>
       <c r="R110" t="n">
-        <v>6233692</v>
+        <v>6233623</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11974,12 +11983,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12006,10 +12015,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121471702</v>
+        <v>121471720</v>
       </c>
       <c r="B111" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12022,21 +12031,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12046,10 +12055,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>427811</v>
+        <v>427595</v>
       </c>
       <c r="R111" t="n">
-        <v>6233480</v>
+        <v>6233898</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12108,7 +12117,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>121471558</v>
+        <v>121471999</v>
       </c>
       <c r="B112" t="n">
         <v>80257</v>
@@ -12148,10 +12157,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>427960</v>
+        <v>427916</v>
       </c>
       <c r="R112" t="n">
-        <v>6233661</v>
+        <v>6233634</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12178,12 +12187,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12210,10 +12219,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>121471604</v>
+        <v>121471596</v>
       </c>
       <c r="B113" t="n">
-        <v>80244</v>
+        <v>74701</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12226,21 +12235,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>230185</v>
+        <v>306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12250,10 +12259,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>427595</v>
+        <v>427686</v>
       </c>
       <c r="R113" t="n">
-        <v>6233781</v>
+        <v>6233621</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12312,10 +12321,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121471983</v>
+        <v>121471608</v>
       </c>
       <c r="B114" t="n">
-        <v>74699</v>
+        <v>80244</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12328,21 +12337,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12352,10 +12361,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>427521</v>
+        <v>427566</v>
       </c>
       <c r="R114" t="n">
-        <v>6233737</v>
+        <v>6233756</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12382,12 +12391,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12414,10 +12423,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>121471627</v>
+        <v>121471954</v>
       </c>
       <c r="B115" t="n">
-        <v>74699</v>
+        <v>80244</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12430,21 +12439,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12454,10 +12463,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>427613</v>
+        <v>427742</v>
       </c>
       <c r="R115" t="n">
-        <v>6233840</v>
+        <v>6233542</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12484,12 +12493,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12516,10 +12525,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>121471968</v>
+        <v>121471574</v>
       </c>
       <c r="B116" t="n">
-        <v>57372</v>
+        <v>80244</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12528,25 +12537,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100049</v>
+        <v>230185</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12556,10 +12565,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>427512</v>
+        <v>427838</v>
       </c>
       <c r="R116" t="n">
-        <v>6233745</v>
+        <v>6233582</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12586,12 +12595,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12618,10 +12627,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>121472003</v>
+        <v>121471984</v>
       </c>
       <c r="B117" t="n">
-        <v>79020</v>
+        <v>80244</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12630,23 +12639,27 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>132</v>
+        <v>230185</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Liten lundlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bacidina phacodes/tarandina</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12654,10 +12667,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>427911</v>
+        <v>427530</v>
       </c>
       <c r="R117" t="n">
-        <v>6233614</v>
+        <v>6233736</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12716,10 +12729,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>121471646</v>
+        <v>121471590</v>
       </c>
       <c r="B118" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12732,21 +12745,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12756,10 +12769,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>427692</v>
+        <v>427753</v>
       </c>
       <c r="R118" t="n">
-        <v>6233796</v>
+        <v>6233666</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12818,10 +12831,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471580</v>
+        <v>121472012</v>
       </c>
       <c r="B119" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12830,25 +12843,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12858,10 +12871,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427804</v>
+        <v>427855</v>
       </c>
       <c r="R119" t="n">
-        <v>6233576</v>
+        <v>6233612</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12888,12 +12901,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12920,10 +12933,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471650</v>
+        <v>121471561</v>
       </c>
       <c r="B120" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12936,21 +12949,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12960,10 +12973,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427737</v>
+        <v>427999</v>
       </c>
       <c r="R120" t="n">
-        <v>6233784</v>
+        <v>6233695</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13022,10 +13035,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471574</v>
+        <v>121471993</v>
       </c>
       <c r="B121" t="n">
-        <v>80244</v>
+        <v>91511</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13034,38 +13047,41 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>230185</v>
+        <v>2014</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427838</v>
+        <v>427859</v>
       </c>
       <c r="R121" t="n">
-        <v>6233582</v>
+        <v>6233620</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13092,12 +13108,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13106,6 +13122,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13124,10 +13141,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471600</v>
+        <v>121471953</v>
       </c>
       <c r="B122" t="n">
-        <v>94606</v>
+        <v>96732</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13140,21 +13157,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13164,10 +13181,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427698</v>
+        <v>427769</v>
       </c>
       <c r="R122" t="n">
-        <v>6233566</v>
+        <v>6233529</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13194,12 +13211,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13226,10 +13243,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471621</v>
+        <v>121471591</v>
       </c>
       <c r="B123" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13242,21 +13259,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13266,10 +13283,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427607</v>
+        <v>427724</v>
       </c>
       <c r="R123" t="n">
-        <v>6233875</v>
+        <v>6233617</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13328,7 +13345,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471607</v>
+        <v>121471614</v>
       </c>
       <c r="B124" t="n">
         <v>80244</v>
@@ -13368,10 +13385,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427582</v>
+        <v>427475</v>
       </c>
       <c r="R124" t="n">
-        <v>6233752</v>
+        <v>6233836</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13430,10 +13447,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>121471638</v>
+        <v>121471971</v>
       </c>
       <c r="B125" t="n">
-        <v>80244</v>
+        <v>78865</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13446,21 +13463,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13470,10 +13487,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>427638</v>
+        <v>427499</v>
       </c>
       <c r="R125" t="n">
-        <v>6233822</v>
+        <v>6233792</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13500,12 +13517,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13532,7 +13549,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471590</v>
+        <v>121471716</v>
       </c>
       <c r="B126" t="n">
         <v>80244</v>
@@ -13572,10 +13589,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427753</v>
+        <v>427547</v>
       </c>
       <c r="R126" t="n">
-        <v>6233666</v>
+        <v>6233865</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13634,10 +13651,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>121471593</v>
+        <v>121471572</v>
       </c>
       <c r="B127" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13650,21 +13667,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13674,10 +13691,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>427699</v>
+        <v>427982</v>
       </c>
       <c r="R127" t="n">
-        <v>6233608</v>
+        <v>6233642</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13736,10 +13753,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>121471964</v>
+        <v>121471575</v>
       </c>
       <c r="B128" t="n">
-        <v>94606</v>
+        <v>91119</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13748,25 +13765,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>2667</v>
+        <v>2023</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13776,10 +13793,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>427511</v>
+        <v>427837</v>
       </c>
       <c r="R128" t="n">
-        <v>6233739</v>
+        <v>6233582</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13806,12 +13823,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13838,10 +13855,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>121471710</v>
+        <v>121471589</v>
       </c>
       <c r="B129" t="n">
-        <v>94608</v>
+        <v>96732</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -13854,21 +13871,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2666</v>
+        <v>2606</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -13878,10 +13895,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>427448</v>
+        <v>427804</v>
       </c>
       <c r="R129" t="n">
-        <v>6233789</v>
+        <v>6233688</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13940,10 +13957,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471630</v>
+        <v>121471650</v>
       </c>
       <c r="B130" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13952,25 +13969,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13980,10 +13997,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>427604</v>
+        <v>427737</v>
       </c>
       <c r="R130" t="n">
-        <v>6233829</v>
+        <v>6233784</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14042,7 +14059,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471713</v>
+        <v>121471979</v>
       </c>
       <c r="B131" t="n">
         <v>76950</v>
@@ -14082,10 +14099,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427438</v>
+        <v>427533</v>
       </c>
       <c r="R131" t="n">
-        <v>6233852</v>
+        <v>6233765</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14112,12 +14129,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14144,10 +14161,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471572</v>
+        <v>121472006</v>
       </c>
       <c r="B132" t="n">
-        <v>96732</v>
+        <v>76950</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -14156,25 +14173,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14184,10 +14201,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427982</v>
+        <v>427892</v>
       </c>
       <c r="R132" t="n">
-        <v>6233642</v>
+        <v>6233623</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14214,12 +14231,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14246,10 +14263,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471707</v>
+        <v>121471973</v>
       </c>
       <c r="B133" t="n">
-        <v>96732</v>
+        <v>76950</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14258,25 +14275,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14286,10 +14303,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427809</v>
+        <v>427544</v>
       </c>
       <c r="R133" t="n">
-        <v>6233703</v>
+        <v>6233811</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14316,12 +14333,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14348,10 +14365,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471559</v>
+        <v>121471622</v>
       </c>
       <c r="B134" t="n">
-        <v>76950</v>
+        <v>74699</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14360,25 +14377,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1342</v>
+        <v>6439</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14388,10 +14405,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427960</v>
+        <v>427623</v>
       </c>
       <c r="R134" t="n">
-        <v>6233661</v>
+        <v>6233865</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14450,7 +14467,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>121472012</v>
+        <v>121471565</v>
       </c>
       <c r="B135" t="n">
         <v>76950</v>
@@ -14490,10 +14507,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>427855</v>
+        <v>428016</v>
       </c>
       <c r="R135" t="n">
-        <v>6233612</v>
+        <v>6233689</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14520,12 +14537,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14552,10 +14569,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>121471583</v>
+        <v>121472014</v>
       </c>
       <c r="B136" t="n">
-        <v>78865</v>
+        <v>80257</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14564,25 +14581,25 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6459</v>
+        <v>1144</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14592,10 +14609,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>427813</v>
+        <v>427882</v>
       </c>
       <c r="R136" t="n">
-        <v>6233621</v>
+        <v>6233622</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14622,12 +14639,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14654,10 +14671,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>121471556</v>
+        <v>121471557</v>
       </c>
       <c r="B137" t="n">
-        <v>96732</v>
+        <v>94595</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14670,21 +14687,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14756,10 +14773,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121471978</v>
+        <v>121471955</v>
       </c>
       <c r="B138" t="n">
-        <v>94606</v>
+        <v>94608</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14772,16 +14789,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -14796,10 +14813,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>427533</v>
+        <v>427741</v>
       </c>
       <c r="R138" t="n">
-        <v>6233765</v>
+        <v>6233529</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14858,7 +14875,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>121471977</v>
+        <v>121472013</v>
       </c>
       <c r="B139" t="n">
         <v>96732</v>
@@ -14898,10 +14915,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>427533</v>
+        <v>427882</v>
       </c>
       <c r="R139" t="n">
-        <v>6233765</v>
+        <v>6233622</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14960,7 +14977,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>121471957</v>
+        <v>121471602</v>
       </c>
       <c r="B140" t="n">
         <v>94606</v>
@@ -15000,10 +15017,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>427731</v>
+        <v>427641</v>
       </c>
       <c r="R140" t="n">
-        <v>6233539</v>
+        <v>6233630</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15030,12 +15047,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15062,10 +15079,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471635</v>
+        <v>121471631</v>
       </c>
       <c r="B141" t="n">
-        <v>78865</v>
+        <v>80244</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -15078,21 +15095,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15102,10 +15119,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>427637</v>
+        <v>427601</v>
       </c>
       <c r="R141" t="n">
-        <v>6233845</v>
+        <v>6233830</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15164,7 +15181,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471975</v>
+        <v>121471592</v>
       </c>
       <c r="B142" t="n">
         <v>80244</v>
@@ -15204,10 +15221,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>427575</v>
+        <v>427703</v>
       </c>
       <c r="R142" t="n">
-        <v>6233800</v>
+        <v>6233616</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15234,12 +15251,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15266,10 +15283,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>121471984</v>
+        <v>121471633</v>
       </c>
       <c r="B143" t="n">
-        <v>80244</v>
+        <v>90515</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15278,25 +15295,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15306,10 +15323,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>427530</v>
+        <v>427629</v>
       </c>
       <c r="R143" t="n">
-        <v>6233736</v>
+        <v>6233837</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15336,12 +15353,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -15368,10 +15385,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>121471601</v>
+        <v>121471649</v>
       </c>
       <c r="B144" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15380,25 +15397,25 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15408,10 +15425,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>427688</v>
+        <v>427720</v>
       </c>
       <c r="R144" t="n">
-        <v>6233590</v>
+        <v>6233787</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15470,10 +15487,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>121471610</v>
+        <v>121471974</v>
       </c>
       <c r="B145" t="n">
-        <v>80244</v>
+        <v>90515</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15482,25 +15499,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>230185</v>
+        <v>1067</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15510,10 +15527,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>427487</v>
+        <v>427554</v>
       </c>
       <c r="R145" t="n">
-        <v>6233816</v>
+        <v>6233803</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15540,12 +15557,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15572,10 +15589,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>121471596</v>
+        <v>121471629</v>
       </c>
       <c r="B146" t="n">
-        <v>74701</v>
+        <v>80257</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15584,25 +15601,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>306</v>
+        <v>1144</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15612,10 +15629,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>427686</v>
+        <v>427602</v>
       </c>
       <c r="R146" t="n">
-        <v>6233621</v>
+        <v>6233832</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15674,10 +15691,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471584</v>
+        <v>121471627</v>
       </c>
       <c r="B147" t="n">
-        <v>96732</v>
+        <v>74699</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15690,21 +15707,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>2606</v>
+        <v>6439</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15714,10 +15731,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427817</v>
+        <v>427613</v>
       </c>
       <c r="R147" t="n">
-        <v>6233621</v>
+        <v>6233840</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15776,10 +15793,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121471988</v>
+        <v>121472003</v>
       </c>
       <c r="B148" t="n">
-        <v>74527</v>
+        <v>79020</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15788,27 +15805,23 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6428</v>
+        <v>132</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten lundlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>Leight.</t>
-        </is>
-      </c>
+          <t>Bacidina phacodes/tarandina</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
@@ -15816,10 +15829,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427738</v>
+        <v>427911</v>
       </c>
       <c r="R148" t="n">
-        <v>6233780</v>
+        <v>6233614</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15878,10 +15891,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471952</v>
+        <v>121471635</v>
       </c>
       <c r="B149" t="n">
-        <v>74699</v>
+        <v>78865</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15894,21 +15907,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6439</v>
+        <v>6459</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15918,10 +15931,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>427763</v>
+        <v>427637</v>
       </c>
       <c r="R149" t="n">
-        <v>6233529</v>
+        <v>6233845</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15948,12 +15961,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -15980,7 +15993,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471651</v>
+        <v>121471995</v>
       </c>
       <c r="B150" t="n">
         <v>78865</v>
@@ -16020,10 +16033,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>427737</v>
+        <v>427856</v>
       </c>
       <c r="R150" t="n">
-        <v>6233789</v>
+        <v>6233613</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16050,12 +16063,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16082,7 +16095,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471612</v>
+        <v>121471632</v>
       </c>
       <c r="B151" t="n">
         <v>80244</v>
@@ -16122,10 +16135,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>427466</v>
+        <v>427615</v>
       </c>
       <c r="R151" t="n">
-        <v>6233828</v>
+        <v>6233825</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16184,7 +16197,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471560</v>
+        <v>121471636</v>
       </c>
       <c r="B152" t="n">
         <v>80244</v>
@@ -16224,10 +16237,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>428008</v>
+        <v>427650</v>
       </c>
       <c r="R152" t="n">
-        <v>6233671</v>
+        <v>6233855</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16286,10 +16299,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471565</v>
+        <v>121471520</v>
       </c>
       <c r="B153" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16298,25 +16311,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16326,10 +16339,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>428016</v>
+        <v>427789</v>
       </c>
       <c r="R153" t="n">
-        <v>6233689</v>
+        <v>6233516</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16388,10 +16401,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121471976</v>
+        <v>121472007</v>
       </c>
       <c r="B154" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16400,25 +16413,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16428,10 +16441,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>427576</v>
+        <v>427892</v>
       </c>
       <c r="R154" t="n">
-        <v>6233800</v>
+        <v>6233623</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16490,10 +16503,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471982</v>
+        <v>121471976</v>
       </c>
       <c r="B155" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16502,25 +16515,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16530,10 +16543,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>427516</v>
+        <v>427576</v>
       </c>
       <c r="R155" t="n">
-        <v>6233748</v>
+        <v>6233800</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16592,10 +16605,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121472014</v>
+        <v>121471600</v>
       </c>
       <c r="B156" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16604,25 +16617,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16632,10 +16645,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>427882</v>
+        <v>427698</v>
       </c>
       <c r="R156" t="n">
-        <v>6233622</v>
+        <v>6233566</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16662,12 +16675,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -16694,10 +16707,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471966</v>
+        <v>121471710</v>
       </c>
       <c r="B157" t="n">
-        <v>76950</v>
+        <v>94608</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16706,25 +16719,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1342</v>
+        <v>2666</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16734,10 +16747,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>427505</v>
+        <v>427448</v>
       </c>
       <c r="R157" t="n">
-        <v>6233740</v>
+        <v>6233789</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16764,12 +16777,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -16796,10 +16809,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471709</v>
+        <v>121471621</v>
       </c>
       <c r="B158" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16812,21 +16825,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16836,10 +16849,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>427452</v>
+        <v>427607</v>
       </c>
       <c r="R158" t="n">
-        <v>6233794</v>
+        <v>6233875</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16898,7 +16911,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471623</v>
+        <v>121471617</v>
       </c>
       <c r="B159" t="n">
         <v>80244</v>
@@ -16938,10 +16951,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>427579</v>
+        <v>427526</v>
       </c>
       <c r="R159" t="n">
-        <v>6233850</v>
+        <v>6233836</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17000,7 +17013,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471962</v>
+        <v>121471705</v>
       </c>
       <c r="B160" t="n">
         <v>80244</v>
@@ -17040,10 +17053,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>427528</v>
+        <v>427753</v>
       </c>
       <c r="R160" t="n">
-        <v>6233707</v>
+        <v>6233606</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17070,12 +17083,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -17102,10 +17115,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471986</v>
+        <v>121471609</v>
       </c>
       <c r="B161" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17114,41 +17127,38 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>427558</v>
+        <v>427543</v>
       </c>
       <c r="R161" t="n">
-        <v>6233769</v>
+        <v>6233756</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17175,17 +17185,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Med Refractohilum pluriseptatum</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -17193,11 +17198,6 @@
       </c>
       <c r="AE161" t="b">
         <v>0</v>
-      </c>
-      <c r="AF161" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG161" t="b">
         <v>0</v>

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121471563</v>
+        <v>121471623</v>
       </c>
       <c r="B19" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2634,21 +2634,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428012</v>
+        <v>427579</v>
       </c>
       <c r="R19" t="n">
-        <v>6233689</v>
+        <v>6233850</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121471963</v>
+        <v>121471583</v>
       </c>
       <c r="B20" t="n">
-        <v>94606</v>
+        <v>78865</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2736,21 +2736,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2667</v>
+        <v>6459</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427520</v>
+        <v>427813</v>
       </c>
       <c r="R20" t="n">
-        <v>6233715</v>
+        <v>6233621</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121471623</v>
+        <v>121471998</v>
       </c>
       <c r="B21" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2834,25 +2834,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>427579</v>
+        <v>427915</v>
       </c>
       <c r="R21" t="n">
-        <v>6233850</v>
+        <v>6233632</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121471671</v>
+        <v>121471719</v>
       </c>
       <c r="B22" t="n">
-        <v>105766</v>
+        <v>76950</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2936,25 +2936,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220785</v>
+        <v>1342</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2964,10 +2964,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427912</v>
+        <v>427583</v>
       </c>
       <c r="R22" t="n">
-        <v>6233611</v>
+        <v>6233861</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,10 +3026,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471998</v>
+        <v>121471576</v>
       </c>
       <c r="B23" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3038,25 +3038,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427915</v>
+        <v>427742</v>
       </c>
       <c r="R23" t="n">
-        <v>6233632</v>
+        <v>6233565</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3096,12 +3096,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3128,10 +3128,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471719</v>
+        <v>121471563</v>
       </c>
       <c r="B24" t="n">
-        <v>76950</v>
+        <v>96732</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3140,25 +3140,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1342</v>
+        <v>2606</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +3168,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>427583</v>
+        <v>428012</v>
       </c>
       <c r="R24" t="n">
-        <v>6233861</v>
+        <v>6233689</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471576</v>
+        <v>121471963</v>
       </c>
       <c r="B25" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3242,25 +3242,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3270,10 +3270,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427742</v>
+        <v>427520</v>
       </c>
       <c r="R25" t="n">
-        <v>6233565</v>
+        <v>6233715</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3300,12 +3300,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,10 +3332,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471583</v>
+        <v>121471671</v>
       </c>
       <c r="B26" t="n">
-        <v>78865</v>
+        <v>105766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3344,25 +3344,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6459</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3372,10 +3372,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427813</v>
+        <v>427912</v>
       </c>
       <c r="R26" t="n">
-        <v>6233621</v>
+        <v>6233611</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471587</v>
+        <v>121471647</v>
       </c>
       <c r="B27" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,25 +3446,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427770</v>
+        <v>427720</v>
       </c>
       <c r="R27" t="n">
-        <v>6233624</v>
+        <v>6233787</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3536,7 +3536,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471647</v>
+        <v>121471618</v>
       </c>
       <c r="B28" t="n">
         <v>96732</v>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427720</v>
+        <v>427525</v>
       </c>
       <c r="R28" t="n">
-        <v>6233787</v>
+        <v>6233838</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471618</v>
+        <v>121471977</v>
       </c>
       <c r="B29" t="n">
         <v>96732</v>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427525</v>
+        <v>427533</v>
       </c>
       <c r="R29" t="n">
-        <v>6233838</v>
+        <v>6233765</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3740,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471977</v>
+        <v>121471992</v>
       </c>
       <c r="B30" t="n">
-        <v>96732</v>
+        <v>94595</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2606</v>
+        <v>2671</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427533</v>
+        <v>427861</v>
       </c>
       <c r="R30" t="n">
-        <v>6233765</v>
+        <v>6233620</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471992</v>
+        <v>121471587</v>
       </c>
       <c r="B31" t="n">
-        <v>94595</v>
+        <v>80257</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3854,25 +3854,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2671</v>
+        <v>1144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427861</v>
+        <v>427770</v>
       </c>
       <c r="R31" t="n">
-        <v>6233620</v>
+        <v>6233624</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -7208,10 +7208,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>121471556</v>
+        <v>121471612</v>
       </c>
       <c r="B64" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7224,21 +7224,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7248,10 +7248,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>427948</v>
+        <v>427466</v>
       </c>
       <c r="R64" t="n">
-        <v>6233643</v>
+        <v>6233828</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7310,10 +7310,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>121471628</v>
+        <v>121471581</v>
       </c>
       <c r="B65" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7326,21 +7326,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>427604</v>
+        <v>427820</v>
       </c>
       <c r="R65" t="n">
-        <v>6233834</v>
+        <v>6233599</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7412,10 +7412,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>121472016</v>
+        <v>121471578</v>
       </c>
       <c r="B66" t="n">
-        <v>96732</v>
+        <v>76950</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7424,25 +7424,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7452,10 +7452,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>427903</v>
+        <v>427749</v>
       </c>
       <c r="R66" t="n">
-        <v>6233640</v>
+        <v>6233573</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7482,12 +7482,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7514,10 +7514,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121471578</v>
+        <v>121471624</v>
       </c>
       <c r="B67" t="n">
-        <v>76950</v>
+        <v>74565</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7530,21 +7530,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1342</v>
+        <v>1116</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>427749</v>
+        <v>427594</v>
       </c>
       <c r="R67" t="n">
-        <v>6233573</v>
+        <v>6233828</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7616,10 +7616,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>121471624</v>
+        <v>121471556</v>
       </c>
       <c r="B68" t="n">
-        <v>74565</v>
+        <v>96732</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7628,25 +7628,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1116</v>
+        <v>2606</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Orangepudrad klotterlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alyxoria ochrocheila</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Ertz &amp; Tehler</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7656,10 +7656,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>427594</v>
+        <v>427948</v>
       </c>
       <c r="R68" t="n">
-        <v>6233828</v>
+        <v>6233643</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7718,10 +7718,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>121471612</v>
+        <v>121471628</v>
       </c>
       <c r="B69" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7734,21 +7734,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7758,10 +7758,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>427466</v>
+        <v>427604</v>
       </c>
       <c r="R69" t="n">
-        <v>6233828</v>
+        <v>6233834</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7820,10 +7820,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>121471581</v>
+        <v>121472016</v>
       </c>
       <c r="B70" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7836,21 +7836,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7860,10 +7860,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>427820</v>
+        <v>427903</v>
       </c>
       <c r="R70" t="n">
-        <v>6233599</v>
+        <v>6233640</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7890,12 +7890,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9350,10 +9350,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>121471956</v>
+        <v>121471715</v>
       </c>
       <c r="B85" t="n">
-        <v>94608</v>
+        <v>80244</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9366,21 +9366,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9390,10 +9390,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>427739</v>
+        <v>427445</v>
       </c>
       <c r="R85" t="n">
-        <v>6233524</v>
+        <v>6233860</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9420,12 +9420,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9452,10 +9452,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>121471952</v>
+        <v>121471610</v>
       </c>
       <c r="B86" t="n">
-        <v>74699</v>
+        <v>80244</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9468,21 +9468,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9492,10 +9492,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>427763</v>
+        <v>427487</v>
       </c>
       <c r="R86" t="n">
-        <v>6233529</v>
+        <v>6233816</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9522,12 +9522,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9554,7 +9554,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>121471715</v>
+        <v>121471604</v>
       </c>
       <c r="B87" t="n">
         <v>80244</v>
@@ -9594,10 +9594,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>427445</v>
+        <v>427595</v>
       </c>
       <c r="R87" t="n">
-        <v>6233860</v>
+        <v>6233781</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9656,7 +9656,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121471610</v>
+        <v>121471959</v>
       </c>
       <c r="B88" t="n">
         <v>80244</v>
@@ -9696,10 +9696,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>427487</v>
+        <v>427734</v>
       </c>
       <c r="R88" t="n">
-        <v>6233816</v>
+        <v>6233532</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9726,12 +9726,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9758,7 +9758,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>121471604</v>
+        <v>121471990</v>
       </c>
       <c r="B89" t="n">
         <v>80244</v>
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>427595</v>
+        <v>427765</v>
       </c>
       <c r="R89" t="n">
-        <v>6233781</v>
+        <v>6233765</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9828,12 +9828,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9860,10 +9860,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>121471959</v>
+        <v>121471956</v>
       </c>
       <c r="B90" t="n">
-        <v>80244</v>
+        <v>94608</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -9876,21 +9876,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9900,10 +9900,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>427734</v>
+        <v>427739</v>
       </c>
       <c r="R90" t="n">
-        <v>6233532</v>
+        <v>6233524</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9962,10 +9962,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>121471990</v>
+        <v>121472001</v>
       </c>
       <c r="B91" t="n">
-        <v>80244</v>
+        <v>94616</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9978,21 +9978,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>230185</v>
+        <v>1080</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokfjädermossa</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Neckera pumila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10002,10 +10002,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>427765</v>
+        <v>427908</v>
       </c>
       <c r="R91" t="n">
-        <v>6233765</v>
+        <v>6233617</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10064,10 +10064,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>121472001</v>
+        <v>121471986</v>
       </c>
       <c r="B92" t="n">
-        <v>94616</v>
+        <v>80257</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10076,38 +10076,41 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1080</v>
+        <v>1144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bokfjädermossa</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Neckera pumila</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>427908</v>
+        <v>427558</v>
       </c>
       <c r="R92" t="n">
-        <v>6233617</v>
+        <v>6233769</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10142,11 +10145,21 @@
           <t>2024-11-18</t>
         </is>
       </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Med Refractohilum pluriseptatum</t>
+        </is>
+      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
       <c r="AE92" t="b">
         <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
       </c>
       <c r="AG92" t="b">
         <v>0</v>
@@ -10166,10 +10179,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121471986</v>
+        <v>121471585</v>
       </c>
       <c r="B93" t="n">
-        <v>80257</v>
+        <v>76950</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10178,41 +10191,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>1144</v>
+        <v>1342</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>427558</v>
+        <v>427748</v>
       </c>
       <c r="R93" t="n">
-        <v>6233769</v>
+        <v>6233622</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10239,17 +10249,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Med Refractohilum pluriseptatum</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10257,11 +10262,6 @@
       </c>
       <c r="AE93" t="b">
         <v>0</v>
-      </c>
-      <c r="AF93" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
       </c>
       <c r="AG93" t="b">
         <v>0</v>
@@ -10281,10 +10281,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121471585</v>
+        <v>121471967</v>
       </c>
       <c r="B94" t="n">
-        <v>76950</v>
+        <v>80257</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10293,25 +10293,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1342</v>
+        <v>1144</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10321,10 +10321,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>427748</v>
+        <v>427508</v>
       </c>
       <c r="R94" t="n">
-        <v>6233622</v>
+        <v>6233737</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10351,12 +10351,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10383,7 +10383,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>121471967</v>
+        <v>121471586</v>
       </c>
       <c r="B95" t="n">
         <v>80257</v>
@@ -10423,10 +10423,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>427508</v>
+        <v>427748</v>
       </c>
       <c r="R95" t="n">
-        <v>6233737</v>
+        <v>6233622</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10453,12 +10453,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10485,10 +10485,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>121471586</v>
+        <v>121471952</v>
       </c>
       <c r="B96" t="n">
-        <v>80257</v>
+        <v>74699</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10497,25 +10497,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1144</v>
+        <v>6439</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10525,10 +10525,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>427748</v>
+        <v>427763</v>
       </c>
       <c r="R96" t="n">
-        <v>6233622</v>
+        <v>6233529</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10555,12 +10555,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11301,10 +11301,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>121471700</v>
+        <v>121471558</v>
       </c>
       <c r="B104" t="n">
-        <v>78989</v>
+        <v>80257</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11313,25 +11313,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6431</v>
+        <v>1144</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lönnlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bacidia rubella</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hoffm.) A.Massal.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11341,10 +11341,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>427806</v>
+        <v>427960</v>
       </c>
       <c r="R104" t="n">
-        <v>6233482</v>
+        <v>6233661</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11403,10 +11403,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>121471558</v>
+        <v>121471961</v>
       </c>
       <c r="B105" t="n">
-        <v>80257</v>
+        <v>94606</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11415,25 +11415,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1144</v>
+        <v>2667</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11443,10 +11443,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>427960</v>
+        <v>427615</v>
       </c>
       <c r="R105" t="n">
-        <v>6233661</v>
+        <v>6233649</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11473,12 +11473,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11505,10 +11505,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>121471961</v>
+        <v>121471707</v>
       </c>
       <c r="B106" t="n">
-        <v>94606</v>
+        <v>96732</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11521,21 +11521,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>2667</v>
+        <v>2606</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11545,10 +11545,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>427615</v>
+        <v>427809</v>
       </c>
       <c r="R106" t="n">
-        <v>6233649</v>
+        <v>6233703</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11575,12 +11575,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11607,10 +11607,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>121471707</v>
+        <v>121471700</v>
       </c>
       <c r="B107" t="n">
-        <v>96732</v>
+        <v>78989</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11623,21 +11623,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>2606</v>
+        <v>6431</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Lönnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Bacidia rubella</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11647,10 +11647,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>427809</v>
+        <v>427806</v>
       </c>
       <c r="R107" t="n">
-        <v>6233703</v>
+        <v>6233482</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12831,10 +12831,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121472012</v>
+        <v>121471591</v>
       </c>
       <c r="B119" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12843,25 +12843,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12871,10 +12871,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427855</v>
+        <v>427724</v>
       </c>
       <c r="R119" t="n">
-        <v>6233612</v>
+        <v>6233617</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12933,10 +12933,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471561</v>
+        <v>121471716</v>
       </c>
       <c r="B120" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12949,21 +12949,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12973,10 +12973,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427999</v>
+        <v>427547</v>
       </c>
       <c r="R120" t="n">
-        <v>6233695</v>
+        <v>6233865</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13035,10 +13035,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471993</v>
+        <v>121471614</v>
       </c>
       <c r="B121" t="n">
-        <v>91511</v>
+        <v>80244</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13047,41 +13047,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2014</v>
+        <v>230185</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427859</v>
+        <v>427475</v>
       </c>
       <c r="R121" t="n">
-        <v>6233620</v>
+        <v>6233836</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13108,12 +13105,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13122,7 +13119,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13141,7 +13137,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471953</v>
+        <v>121471561</v>
       </c>
       <c r="B122" t="n">
         <v>96732</v>
@@ -13181,10 +13177,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427769</v>
+        <v>427999</v>
       </c>
       <c r="R122" t="n">
-        <v>6233529</v>
+        <v>6233695</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13211,12 +13207,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13243,10 +13239,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471591</v>
+        <v>121471993</v>
       </c>
       <c r="B123" t="n">
-        <v>80244</v>
+        <v>91511</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13255,38 +13251,41 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>230185</v>
+        <v>2014</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427724</v>
+        <v>427859</v>
       </c>
       <c r="R123" t="n">
-        <v>6233617</v>
+        <v>6233620</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13313,12 +13312,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13327,6 +13326,7 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13345,10 +13345,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471614</v>
+        <v>121471953</v>
       </c>
       <c r="B124" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13361,21 +13361,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13385,10 +13385,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427475</v>
+        <v>427769</v>
       </c>
       <c r="R124" t="n">
-        <v>6233836</v>
+        <v>6233529</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13415,12 +13415,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13549,10 +13549,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121471716</v>
+        <v>121472012</v>
       </c>
       <c r="B126" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13561,25 +13561,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13589,10 +13589,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427547</v>
+        <v>427855</v>
       </c>
       <c r="R126" t="n">
-        <v>6233865</v>
+        <v>6233612</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13619,12 +13619,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13957,10 +13957,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471650</v>
+        <v>121471979</v>
       </c>
       <c r="B130" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13969,25 +13969,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13997,10 +13997,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>427737</v>
+        <v>427533</v>
       </c>
       <c r="R130" t="n">
-        <v>6233784</v>
+        <v>6233765</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14027,12 +14027,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14059,7 +14059,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121471979</v>
+        <v>121472006</v>
       </c>
       <c r="B131" t="n">
         <v>76950</v>
@@ -14099,10 +14099,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427533</v>
+        <v>427892</v>
       </c>
       <c r="R131" t="n">
-        <v>6233765</v>
+        <v>6233623</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14161,7 +14161,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121472006</v>
+        <v>121471973</v>
       </c>
       <c r="B132" t="n">
         <v>76950</v>
@@ -14201,10 +14201,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427892</v>
+        <v>427544</v>
       </c>
       <c r="R132" t="n">
-        <v>6233623</v>
+        <v>6233811</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14263,10 +14263,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471973</v>
+        <v>121471622</v>
       </c>
       <c r="B133" t="n">
-        <v>76950</v>
+        <v>74699</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14275,25 +14275,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1342</v>
+        <v>6439</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14303,10 +14303,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427544</v>
+        <v>427623</v>
       </c>
       <c r="R133" t="n">
-        <v>6233811</v>
+        <v>6233865</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14333,12 +14333,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14365,10 +14365,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471622</v>
+        <v>121471650</v>
       </c>
       <c r="B134" t="n">
-        <v>74699</v>
+        <v>80244</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14381,21 +14381,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14405,10 +14405,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427623</v>
+        <v>427737</v>
       </c>
       <c r="R134" t="n">
-        <v>6233865</v>
+        <v>6233784</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -3434,10 +3434,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471647</v>
+        <v>121471985</v>
       </c>
       <c r="B27" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3450,21 +3450,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427720</v>
+        <v>427558</v>
       </c>
       <c r="R27" t="n">
-        <v>6233787</v>
+        <v>6233768</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3504,12 +3504,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3536,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471618</v>
+        <v>121471597</v>
       </c>
       <c r="B28" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,21 +3552,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427525</v>
+        <v>427693</v>
       </c>
       <c r="R28" t="n">
-        <v>6233838</v>
+        <v>6233604</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3638,7 +3638,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471977</v>
+        <v>121471647</v>
       </c>
       <c r="B29" t="n">
         <v>96732</v>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427533</v>
+        <v>427720</v>
       </c>
       <c r="R29" t="n">
-        <v>6233765</v>
+        <v>6233787</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3708,12 +3708,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3740,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471992</v>
+        <v>121471618</v>
       </c>
       <c r="B30" t="n">
-        <v>94595</v>
+        <v>96732</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3756,21 +3756,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2671</v>
+        <v>2606</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427861</v>
+        <v>427525</v>
       </c>
       <c r="R30" t="n">
-        <v>6233620</v>
+        <v>6233838</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471587</v>
+        <v>121471977</v>
       </c>
       <c r="B31" t="n">
-        <v>80257</v>
+        <v>96732</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3854,25 +3854,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1144</v>
+        <v>2606</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427770</v>
+        <v>427533</v>
       </c>
       <c r="R31" t="n">
-        <v>6233624</v>
+        <v>6233765</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471985</v>
+        <v>121471992</v>
       </c>
       <c r="B32" t="n">
-        <v>80244</v>
+        <v>94595</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427558</v>
+        <v>427861</v>
       </c>
       <c r="R32" t="n">
-        <v>6233768</v>
+        <v>6233620</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4046,10 +4046,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471597</v>
+        <v>121471587</v>
       </c>
       <c r="B33" t="n">
-        <v>80244</v>
+        <v>80257</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4058,25 +4058,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>230185</v>
+        <v>1144</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427693</v>
+        <v>427770</v>
       </c>
       <c r="R33" t="n">
-        <v>6233604</v>
+        <v>6233624</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -12831,10 +12831,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>121471591</v>
+        <v>121472012</v>
       </c>
       <c r="B119" t="n">
-        <v>80244</v>
+        <v>76950</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12843,25 +12843,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12871,10 +12871,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>427724</v>
+        <v>427855</v>
       </c>
       <c r="R119" t="n">
-        <v>6233617</v>
+        <v>6233612</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -12933,10 +12933,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>121471716</v>
+        <v>121471561</v>
       </c>
       <c r="B120" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12949,21 +12949,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12973,10 +12973,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>427547</v>
+        <v>427999</v>
       </c>
       <c r="R120" t="n">
-        <v>6233865</v>
+        <v>6233695</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13035,10 +13035,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>121471614</v>
+        <v>121471993</v>
       </c>
       <c r="B121" t="n">
-        <v>80244</v>
+        <v>91511</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13047,38 +13047,41 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>230185</v>
+        <v>2014</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>427475</v>
+        <v>427859</v>
       </c>
       <c r="R121" t="n">
-        <v>6233836</v>
+        <v>6233620</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13105,12 +13108,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13119,6 +13122,7 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13137,7 +13141,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121471561</v>
+        <v>121471953</v>
       </c>
       <c r="B122" t="n">
         <v>96732</v>
@@ -13177,10 +13181,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>427999</v>
+        <v>427769</v>
       </c>
       <c r="R122" t="n">
-        <v>6233695</v>
+        <v>6233529</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13207,12 +13211,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13239,10 +13243,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>121471993</v>
+        <v>121471591</v>
       </c>
       <c r="B123" t="n">
-        <v>91511</v>
+        <v>80244</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13251,41 +13255,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2014</v>
+        <v>230185</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Koralltaggsvamp</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hericium coralloides</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Scop.) Pers.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="J123" t="inlineStr"/>
-      <c r="K123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>427859</v>
+        <v>427724</v>
       </c>
       <c r="R123" t="n">
-        <v>6233620</v>
+        <v>6233617</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13312,12 +13313,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13326,7 +13327,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -13345,10 +13345,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>121471953</v>
+        <v>121471614</v>
       </c>
       <c r="B124" t="n">
-        <v>96732</v>
+        <v>80244</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13361,21 +13361,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13385,10 +13385,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>427769</v>
+        <v>427475</v>
       </c>
       <c r="R124" t="n">
-        <v>6233529</v>
+        <v>6233836</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13415,12 +13415,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13549,10 +13549,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>121472012</v>
+        <v>121471716</v>
       </c>
       <c r="B126" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13561,25 +13561,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13589,10 +13589,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>427855</v>
+        <v>427547</v>
       </c>
       <c r="R126" t="n">
-        <v>6233612</v>
+        <v>6233865</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13619,12 +13619,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13957,10 +13957,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>121471979</v>
+        <v>121471650</v>
       </c>
       <c r="B130" t="n">
-        <v>76950</v>
+        <v>80244</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -13969,25 +13969,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -13997,10 +13997,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>427533</v>
+        <v>427737</v>
       </c>
       <c r="R130" t="n">
-        <v>6233765</v>
+        <v>6233784</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14027,12 +14027,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14059,7 +14059,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>121472006</v>
+        <v>121471979</v>
       </c>
       <c r="B131" t="n">
         <v>76950</v>
@@ -14099,10 +14099,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>427892</v>
+        <v>427533</v>
       </c>
       <c r="R131" t="n">
-        <v>6233623</v>
+        <v>6233765</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14161,7 +14161,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>121471973</v>
+        <v>121472006</v>
       </c>
       <c r="B132" t="n">
         <v>76950</v>
@@ -14201,10 +14201,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>427544</v>
+        <v>427892</v>
       </c>
       <c r="R132" t="n">
-        <v>6233811</v>
+        <v>6233623</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14263,10 +14263,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121471622</v>
+        <v>121471973</v>
       </c>
       <c r="B133" t="n">
-        <v>74699</v>
+        <v>76950</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14275,25 +14275,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6439</v>
+        <v>1342</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14303,10 +14303,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>427623</v>
+        <v>427544</v>
       </c>
       <c r="R133" t="n">
-        <v>6233865</v>
+        <v>6233811</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14333,12 +14333,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14365,10 +14365,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>121471650</v>
+        <v>121471622</v>
       </c>
       <c r="B134" t="n">
-        <v>80244</v>
+        <v>74699</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14381,21 +14381,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>230185</v>
+        <v>6439</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14405,10 +14405,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>427737</v>
+        <v>427623</v>
       </c>
       <c r="R134" t="n">
-        <v>6233784</v>
+        <v>6233865</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15079,7 +15079,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>121471631</v>
+        <v>121471592</v>
       </c>
       <c r="B141" t="n">
         <v>80244</v>
@@ -15119,10 +15119,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>427601</v>
+        <v>427703</v>
       </c>
       <c r="R141" t="n">
-        <v>6233830</v>
+        <v>6233616</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15181,7 +15181,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>121471592</v>
+        <v>121471631</v>
       </c>
       <c r="B142" t="n">
         <v>80244</v>
@@ -15221,10 +15221,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>427703</v>
+        <v>427601</v>
       </c>
       <c r="R142" t="n">
-        <v>6233616</v>
+        <v>6233830</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15691,10 +15691,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>121471627</v>
+        <v>121471632</v>
       </c>
       <c r="B147" t="n">
-        <v>74699</v>
+        <v>80244</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15707,21 +15707,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6439</v>
+        <v>230185</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15731,10 +15731,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>427613</v>
+        <v>427615</v>
       </c>
       <c r="R147" t="n">
-        <v>6233840</v>
+        <v>6233825</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15793,10 +15793,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>121472003</v>
+        <v>121471636</v>
       </c>
       <c r="B148" t="n">
-        <v>79020</v>
+        <v>80244</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15805,23 +15805,27 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>132</v>
+        <v>230185</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Liten lundlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Bacidina phacodes/tarandina</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr"/>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
@@ -15829,10 +15833,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>427911</v>
+        <v>427650</v>
       </c>
       <c r="R148" t="n">
-        <v>6233614</v>
+        <v>6233855</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15859,12 +15863,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -15891,10 +15895,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>121471635</v>
+        <v>121471520</v>
       </c>
       <c r="B149" t="n">
-        <v>78865</v>
+        <v>80244</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15907,21 +15911,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6459</v>
+        <v>230185</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15931,10 +15935,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>427637</v>
+        <v>427789</v>
       </c>
       <c r="R149" t="n">
-        <v>6233845</v>
+        <v>6233516</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15993,10 +15997,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>121471995</v>
+        <v>121471627</v>
       </c>
       <c r="B150" t="n">
-        <v>78865</v>
+        <v>74699</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -16009,21 +16013,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6459</v>
+        <v>6439</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16033,10 +16037,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>427856</v>
+        <v>427613</v>
       </c>
       <c r="R150" t="n">
-        <v>6233613</v>
+        <v>6233840</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16063,12 +16067,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16095,10 +16099,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>121471632</v>
+        <v>121472003</v>
       </c>
       <c r="B151" t="n">
-        <v>80244</v>
+        <v>79020</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16107,27 +16111,23 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>230185</v>
+        <v>132</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Liten lundlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Bacidina phacodes/tarandina</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
@@ -16135,10 +16135,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>427615</v>
+        <v>427911</v>
       </c>
       <c r="R151" t="n">
-        <v>6233825</v>
+        <v>6233614</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16165,12 +16165,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16197,10 +16197,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>121471636</v>
+        <v>121471635</v>
       </c>
       <c r="B152" t="n">
-        <v>80244</v>
+        <v>78865</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16213,21 +16213,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16237,10 +16237,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>427650</v>
+        <v>427637</v>
       </c>
       <c r="R152" t="n">
-        <v>6233855</v>
+        <v>6233845</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16299,10 +16299,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>121471520</v>
+        <v>121471995</v>
       </c>
       <c r="B153" t="n">
-        <v>80244</v>
+        <v>78865</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16315,21 +16315,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16339,10 +16339,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>427789</v>
+        <v>427856</v>
       </c>
       <c r="R153" t="n">
-        <v>6233516</v>
+        <v>6233613</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16369,12 +16369,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -16401,10 +16401,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>121472007</v>
+        <v>121471609</v>
       </c>
       <c r="B154" t="n">
-        <v>80257</v>
+        <v>80244</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16413,25 +16413,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16441,10 +16441,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>427892</v>
+        <v>427543</v>
       </c>
       <c r="R154" t="n">
-        <v>6233623</v>
+        <v>6233756</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16471,12 +16471,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -16503,10 +16503,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>121471976</v>
+        <v>121472007</v>
       </c>
       <c r="B155" t="n">
-        <v>96732</v>
+        <v>80257</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16515,25 +16515,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16543,10 +16543,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>427576</v>
+        <v>427892</v>
       </c>
       <c r="R155" t="n">
-        <v>6233800</v>
+        <v>6233623</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16605,10 +16605,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>121471600</v>
+        <v>121471617</v>
       </c>
       <c r="B156" t="n">
-        <v>94606</v>
+        <v>80244</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16621,21 +16621,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16645,10 +16645,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>427698</v>
+        <v>427526</v>
       </c>
       <c r="R156" t="n">
-        <v>6233566</v>
+        <v>6233836</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16707,10 +16707,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>121471710</v>
+        <v>121471705</v>
       </c>
       <c r="B157" t="n">
-        <v>94608</v>
+        <v>80244</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16723,21 +16723,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2666</v>
+        <v>230185</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Grov fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Exsertotheca crispa</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16747,10 +16747,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>427448</v>
+        <v>427753</v>
       </c>
       <c r="R157" t="n">
-        <v>6233789</v>
+        <v>6233606</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16809,7 +16809,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>121471621</v>
+        <v>121471976</v>
       </c>
       <c r="B158" t="n">
         <v>96732</v>
@@ -16849,10 +16849,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>427607</v>
+        <v>427576</v>
       </c>
       <c r="R158" t="n">
-        <v>6233875</v>
+        <v>6233800</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16879,12 +16879,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -16911,10 +16911,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>121471617</v>
+        <v>121471600</v>
       </c>
       <c r="B159" t="n">
-        <v>80244</v>
+        <v>94606</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16927,21 +16927,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>230185</v>
+        <v>2667</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16951,10 +16951,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>427526</v>
+        <v>427698</v>
       </c>
       <c r="R159" t="n">
-        <v>6233836</v>
+        <v>6233566</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17013,10 +17013,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>121471705</v>
+        <v>121471710</v>
       </c>
       <c r="B160" t="n">
-        <v>80244</v>
+        <v>94608</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -17029,21 +17029,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>230185</v>
+        <v>2666</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17053,10 +17053,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>427753</v>
+        <v>427448</v>
       </c>
       <c r="R160" t="n">
-        <v>6233606</v>
+        <v>6233789</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17115,10 +17115,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>121471609</v>
+        <v>121471621</v>
       </c>
       <c r="B161" t="n">
-        <v>80244</v>
+        <v>96732</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17131,21 +17131,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>230185</v>
+        <v>2606</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17155,10 +17155,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>427543</v>
+        <v>427607</v>
       </c>
       <c r="R161" t="n">
-        <v>6233756</v>
+        <v>6233875</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>

--- a/artfynd/A 18987-2024 artfynd.xlsx
+++ b/artfynd/A 18987-2024 artfynd.xlsx
@@ -1802,10 +1802,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121471704</v>
+        <v>121471719</v>
       </c>
       <c r="B11" t="n">
-        <v>96732</v>
+        <v>76957</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>427785</v>
+        <v>427583</v>
       </c>
       <c r="R11" t="n">
-        <v>6233585</v>
+        <v>6233861</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121471634</v>
+        <v>121471718</v>
       </c>
       <c r="B12" t="n">
-        <v>96732</v>
+        <v>80264</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1916,25 +1916,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>427636</v>
+        <v>427584</v>
       </c>
       <c r="R12" t="n">
-        <v>6233848</v>
+        <v>6233863</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2006,10 +2006,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121471620</v>
+        <v>121472009</v>
       </c>
       <c r="B13" t="n">
-        <v>94595</v>
+        <v>94614</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2022,21 +2022,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>427625</v>
+        <v>427877</v>
       </c>
       <c r="R13" t="n">
-        <v>6233894</v>
+        <v>6233615</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,12 +2076,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121471702</v>
+        <v>121472016</v>
       </c>
       <c r="B14" t="n">
-        <v>96732</v>
+        <v>96740</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>427811</v>
+        <v>427903</v>
       </c>
       <c r="R14" t="n">
-        <v>6233480</v>
+        <v>6233640</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121471641</v>
+        <v>121471620</v>
       </c>
       <c r="B15" t="n">
-        <v>78865</v>
+        <v>94603</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6459</v>
+        <v>2671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>427655</v>
+        <v>427625</v>
       </c>
       <c r="R15" t="n">
-        <v>6233850</v>
+        <v>6233894</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2312,10 +2312,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121471580</v>
+        <v>121471992</v>
       </c>
       <c r="B16" t="n">
-        <v>80244</v>
+        <v>94603</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2328,21 +2328,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>230185</v>
+        <v>2671</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>427804</v>
+        <v>427861</v>
       </c>
       <c r="R16" t="n">
-        <v>6233576</v>
+        <v>6233620</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121471630</v>
+        <v>121471984</v>
       </c>
       <c r="B17" t="n">
-        <v>76950</v>
+        <v>80251</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2426,25 +2426,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1342</v>
+        <v>230185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>427604</v>
+        <v>427530</v>
       </c>
       <c r="R17" t="n">
-        <v>6233829</v>
+        <v>6233736</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,10 +2516,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121471651</v>
+        <v>121471648</v>
       </c>
       <c r="B18" t="n">
-        <v>78865</v>
+        <v>76957</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2528,25 +2528,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2556,10 +2556,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>427737</v>
+        <v>427721</v>
       </c>
       <c r="R18" t="n">
-        <v>6233789</v>
+        <v>6233787</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2618,10 +2618,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121471623</v>
+        <v>121471630</v>
       </c>
       <c r="B19" t="n">
-        <v>80244</v>
+        <v>76957</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2630,25 +2630,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>230185</v>
+        <v>1342</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2658,10 +2658,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>427579</v>
+        <v>427604</v>
       </c>
       <c r="R19" t="n">
-        <v>6233850</v>
+        <v>6233829</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2720,10 +2720,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121471583</v>
+        <v>121471713</v>
       </c>
       <c r="B20" t="n">
-        <v>78865</v>
+        <v>76957</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,25 +2732,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6459</v>
+        <v>1342</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2760,10 +2760,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>427813</v>
+        <v>427438</v>
       </c>
       <c r="R20" t="n">
-        <v>6233621</v>
+        <v>6233852</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2822,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121471998</v>
+        <v>121471979</v>
       </c>
       <c r="B21" t="n">
-        <v>76950</v>
+        <v>76957</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>427915</v>
+        <v>427533</v>
       </c>
       <c r="R21" t="n">
-        <v>6233632</v>
+        <v>6233765</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121471719</v>
+        <v>121471993</v>
       </c>
       <c r="B22" t="n">
-        <v>76950</v>
+        <v>91519</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2940,34 +2940,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1342</v>
+        <v>2014</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bokvårtlav</t>
+          <t>Koralltaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrenula nitida</t>
+          <t>Hericium coralloides</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Weigel) Ach.</t>
+          <t>(Scop.) Pers.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Ballingslöv, Sk</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>427583</v>
+        <v>427859</v>
       </c>
       <c r="R22" t="n">
-        <v>6233861</v>
+        <v>6233620</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2994,12 +2997,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3008,6 +3011,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3026,10 +3030,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121471576</v>
+        <v>121471636</v>
       </c>
       <c r="B23" t="n">
-        <v>80257</v>
+        <v>80251</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3038,25 +3042,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3066,10 +3070,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>427742</v>
+        <v>427650</v>
       </c>
       <c r="R23" t="n">
-        <v>6233565</v>
+        <v>6233855</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3128,10 +3132,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121471563</v>
+        <v>121471954</v>
       </c>
       <c r="B24" t="n">
-        <v>96732</v>
+        <v>80251</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3144,21 +3148,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2606</v>
+        <v>230185</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3168,10 +3172,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428012</v>
+        <v>427742</v>
       </c>
       <c r="R24" t="n">
-        <v>6233689</v>
+        <v>6233542</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3198,12 +3202,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3230,10 +3234,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121471963</v>
+        <v>121471593</v>
       </c>
       <c r="B25" t="n">
-        <v>94606</v>
+        <v>80251</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3246,21 +3250,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2667</v>
+        <v>230185</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3270,10 +3274,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>427520</v>
+        <v>427699</v>
       </c>
       <c r="R25" t="n">
-        <v>6233715</v>
+        <v>6233608</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3300,12 +3304,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3332,10 +3336,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121471671</v>
+        <v>121471589</v>
       </c>
       <c r="B26" t="n">
-        <v>105766</v>
+        <v>96740</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3344,25 +3348,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>2606</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3372,10 +3376,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>427912</v>
+        <v>427804</v>
       </c>
       <c r="R26" t="n">
-        <v>6233611</v>
+        <v>6233688</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,10 +3438,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121471985</v>
+        <v>121472003</v>
       </c>
       <c r="B27" t="n">
-        <v>80244</v>
+        <v>79027</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3446,27 +3450,23 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>230185</v>
+        <v>132</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Liten lundlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Bacidina phacodes/tarandina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>427558</v>
+        <v>427911</v>
       </c>
       <c r="R27" t="n">
-        <v>6233768</v>
+        <v>6233614</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3536,10 +3536,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121471597</v>
+        <v>121471644</v>
       </c>
       <c r="B28" t="n">
-        <v>80244</v>
+        <v>78872</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3552,21 +3552,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>230185</v>
+        <v>6459</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Havstulpanlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Thelotrema lepadinum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>427693</v>
+        <v>427671</v>
       </c>
       <c r="R28" t="n">
-        <v>6233604</v>
+        <v>6233821</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121471647</v>
+        <v>121471559</v>
       </c>
       <c r="B29" t="n">
-        <v>96732</v>
+        <v>76957</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3650,25 +3650,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2606</v>
+        <v>1342</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Bokvårtlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Pyrenula nitida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Weigel) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3678,10 +3678,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>427720</v>
+        <v>427960</v>
       </c>
       <c r="R29" t="n">
-        <v>6233787</v>
+        <v>6233661</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3740,10 +3740,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121471618</v>
+        <v>121471564</v>
       </c>
       <c r="B30" t="n">
-        <v>96732</v>
+        <v>80264</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3780,10 +3780,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>427525</v>
+        <v>428014</v>
       </c>
       <c r="R30" t="n">
-        <v>6233838</v>
+        <v>6233692</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3842,10 +3842,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121471977</v>
+        <v>121471624</v>
       </c>
       <c r="B31" t="n">
-        <v>96732</v>
+        <v>74572</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3854,25 +3854,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2606</v>
+        <v>1116</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Orangepudrad klotterlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Alyxoria ochrocheila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Nyl.) Ertz &amp; Tehler</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3882,10 +3882,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>427533</v>
+        <v>427594</v>
       </c>
       <c r="R31" t="n">
-        <v>6233765</v>
+        <v>6233828</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3944,10 +3944,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121471992</v>
+        <v>121471635</v>
       </c>
       <c r="B32" t="n">
-        <v>94595</v>
+        <v>78872</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3960,21 +3960,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2671</v>
+        <v>6459</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3984,10 +3984,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>427861</v>
+        <v>427637</v>
       </c>
       <c r="R32" t="n">
-        <v>6233620</v>
+        <v>6233845</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4014,12 +4014,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-18</t>
+          <t>2024-11-29</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4046,10 +4046,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121471587</v>
+        <v>121471574</v>
       </c>
       <c r="B33" t="n">
-        <v>80257</v>
+        <v>80251</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4058,25 +4058,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1144</v>
+        <v>230185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ädelkronlav</t>
+          <t>Havstulpanlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Gyalecta carneola</t>
+          <t>Thelotrema lepadinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Hellb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4086,10 +4086,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>427770</v>
+        <v>427838</v>
       </c>
       <c r="R33" t="n">
-        <v>6233624</v>
+        <v>6233582</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,10 +4148,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121471712</v>
+        <v>121472014</v>
       </c>
       <c r="B34" t="n">
-        <v>96732</v>
+        <v>80264</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4160,25 +4160,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2606</v>
+        <v>1144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Klippfrullania</t>
+          <t>Ädelkronlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Frullania tamarisci</t>
+          <t>Gyalecta carneola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Dumort.</t>
+          <t>(Ach.) Hellb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4188,10 +4188,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>427439</v>
+        <v>427882</v>
       </c>
       <c r="R34" t="n">
-        <v>6233838</v>
+        <v>6233622</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4218,12 +4218,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-11-29</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="AD34" t="b">